--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10B1366-133F-40A1-A4D7-F3A22709858F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938C750A-8841-4A28-AE20-2C94C039A68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1140" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="783">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2357,6 +2357,30 @@
   </si>
   <si>
     <t>TRADE NOTICE-30 /2025-26</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE-32/2025-2026</t>
+  </si>
+  <si>
+    <t>Guidelines-Support for Emerging Export Opportunities under Export Promotion Mission (EPM) – NIRYAT PROTSAHAN</t>
+  </si>
+  <si>
+    <t>Trade Notice</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE-31/2025-2026</t>
+  </si>
+  <si>
+    <t>Guidelines for Credit Assistance for E-Commerce Exporters under Export Promotion Mission (EPM) – NIRYAT PROTSAHAN</t>
+  </si>
+  <si>
+    <t>Extension in the Export Obligation period of specified Advance &amp; EPCG Authorisations till 31.08.2026</t>
+  </si>
+  <si>
+    <t>Notices</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE-51/2025-26</t>
   </si>
 </sst>
 </file>
@@ -2392,7 +2416,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2402,6 +2426,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2427,7 +2457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2513,6 +2543,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2794,7 +2836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O366"/>
+  <dimension ref="A1:O367"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
@@ -2830,1197 +2872,1203 @@
       <c r="D4" s="5"/>
       <c r="E4" s="24"/>
     </row>
-    <row r="5" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="27">
+    <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="40" t="s">
+        <v>782</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>780</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>781</v>
+      </c>
+      <c r="F5" s="39">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f t="shared" ref="A6:A69" si="0">ROW()-4</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>754</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="C6" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>755</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="27">
-        <v>2</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>757</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>758</v>
       </c>
       <c r="E6" s="34" t="s">
         <v>756</v>
       </c>
-      <c r="O6" s="27" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="7" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="27">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E7" s="34" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <f>ROW()-4</f>
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="O7" s="27" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>760</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
         <v>386</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C9" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E9" s="2">
         <v>46328</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <f t="shared" ref="A9:A72" si="0">ROW()-4</f>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>388</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
-        <v>387</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="E9" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>388</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="E11" s="2">
         <v>46045</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <f t="shared" si="0"/>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
-        <v>389</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="E12" s="2">
         <v>46038</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
         <v>390</v>
-      </c>
-      <c r="C12" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="2">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>391</v>
       </c>
       <c r="C13" s="10">
         <v>2026</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2">
         <v>46031</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" t="s">
+        <v>391</v>
+      </c>
+      <c r="C14" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
         <v>392</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C15" s="10">
         <v>2025</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E15" s="2">
         <v>46022</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>393</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E16" s="2">
         <v>46010</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
         <v>394</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="2">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>395</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>19</v>
       </c>
       <c r="E17" s="2">
         <v>46008</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" t="s">
+        <v>395</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="2">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
         <v>396</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
         <v>374</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E19" s="2">
         <v>46002</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
         <v>397</v>
-      </c>
-      <c r="C19" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="2">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>398</v>
       </c>
       <c r="C20" s="10">
         <v>2025</v>
       </c>
       <c r="D20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2">
         <v>46001</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" t="s">
+        <v>398</v>
+      </c>
+      <c r="C21" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E21" s="2">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
         <v>399</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
         <v>23</v>
-      </c>
-      <c r="E21" s="2">
-        <v>45992</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>400</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
       </c>
       <c r="E22" s="2">
         <v>45992</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" t="s">
+        <v>400</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
         <v>401</v>
       </c>
-      <c r="C23" s="10">
+      <c r="C24" s="10">
         <v>2025</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>373</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E24" s="2">
         <v>45981</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
         <v>402</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E25" s="2">
         <v>45959</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
         <v>403</v>
-      </c>
-      <c r="C25" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D25" t="s">
-        <v>28</v>
-      </c>
-      <c r="E25" s="2">
-        <v>45958</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B26" t="s">
-        <v>404</v>
       </c>
       <c r="C26" s="10">
         <v>2025</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" s="2">
         <v>45958</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" t="s">
+        <v>404</v>
+      </c>
+      <c r="C27" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
         <v>405</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C28" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E28" s="2">
         <v>45953</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B28" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
         <v>406</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="C29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E29" s="2">
         <v>45952</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
         <v>407</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E30" s="2">
         <v>45945</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
         <v>39</v>
-      </c>
-      <c r="E30" s="2">
-        <v>45940</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>408</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>42</v>
       </c>
       <c r="E31" s="2">
         <v>45940</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B32" t="s">
+        <v>408</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45940</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
         <v>409</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E33" s="2">
         <v>45933</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
         <v>410</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E34" s="2">
         <v>45931</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
         <v>411</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E35" s="2">
         <v>45909</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
         <v>412</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E36" s="2">
         <v>45903</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
         <v>413</v>
       </c>
-      <c r="C36" s="10">
+      <c r="C37" s="10">
         <v>2025</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E37" s="2">
         <v>45895</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
         <v>414</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E38" s="2">
         <v>45891</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
         <v>415</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
         <v>65</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E39" s="2">
         <v>45870</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
         <v>416</v>
       </c>
-      <c r="C39" s="10">
+      <c r="C40" s="10">
         <v>2025</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>66</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E40" s="2">
         <v>45868</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
         <v>417</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E41" s="2">
         <v>45867</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
         <v>418</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E42" s="2">
         <v>45860</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
         <v>419</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E43" s="2">
         <v>45846</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B44" t="s">
         <v>420</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C44" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
         <v>77</v>
-      </c>
-      <c r="E43" s="2">
-        <v>45833</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B44" t="s">
-        <v>421</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
-        <v>78</v>
       </c>
       <c r="E44" s="2">
         <v>45833</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B45" t="s">
+        <v>421</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="2">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
         <v>422</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
         <v>82</v>
-      </c>
-      <c r="E45" s="2">
-        <v>45820</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B46" t="s">
-        <v>423</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
-        <v>83</v>
       </c>
       <c r="E46" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47">
+      <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B47" t="s">
+        <v>423</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="2">
+        <v>45820</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
         <v>424</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C48" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
         <v>84</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E48" s="2">
         <v>45818</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B48" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B49" t="s">
         <v>425</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C49" s="10">
         <v>2025</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E49" s="2">
         <v>45807</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B49" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B50" t="s">
         <v>426</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C50" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
         <v>96</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E50" s="2">
         <v>45793</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B50" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
         <v>427</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C51" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
         <v>97</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E51" s="2">
         <v>45784</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B51" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B52" t="s">
         <v>428</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C52" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
         <v>98</v>
-      </c>
-      <c r="E51" s="2">
-        <v>45783</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B52" t="s">
-        <v>429</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" t="s">
-        <v>99</v>
       </c>
       <c r="E52" s="2">
         <v>45783</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B53" t="s">
+        <v>429</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>99</v>
+      </c>
+      <c r="E53" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B54" t="s">
         <v>430</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C54" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
         <v>101</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E54" s="2">
         <v>45771</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B54" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
         <v>431</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C55" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
         <v>104</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E55" s="2">
         <v>45762</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
         <v>432</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C56" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
         <v>105</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E56" s="2">
         <v>45750</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B57" t="s">
         <v>433</v>
       </c>
-      <c r="C56" s="10">
+      <c r="C57" s="10">
         <v>2025</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>109</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E57" s="2">
         <v>45744</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="B57" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B58" t="s">
         <v>110</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C58" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
         <v>111</v>
-      </c>
-      <c r="E57" s="2">
-        <v>45743</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="B58" t="s">
-        <v>434</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" t="s">
-        <v>113</v>
       </c>
       <c r="E58" s="2">
         <v>45743</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B59" t="s">
+        <v>434</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D59" t="s">
+        <v>113</v>
+      </c>
+      <c r="E59" s="2">
+        <v>45743</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B60" t="s">
         <v>435</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C60" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" t="s">
         <v>116</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E60" s="2">
         <v>45735</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="B60" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B61" t="s">
         <v>436</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D60" t="s">
-        <v>121</v>
-      </c>
-      <c r="E60" s="2">
-        <v>45726</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="B61" t="s">
-        <v>437</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D61" t="s">
+        <v>121</v>
+      </c>
+      <c r="E61" s="2">
+        <v>45726</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B62" t="s">
+        <v>437</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D62" t="s">
         <v>124</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E62" s="2">
         <v>45719</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="B62" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B63" t="s">
         <v>438</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="C63" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" t="s">
         <v>125</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E63" s="2">
         <v>45700</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="B63" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B64" t="s">
         <v>439</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="C64" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" t="s">
         <v>128</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E64" s="2">
         <v>45695</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="B64" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
         <v>440</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="C65" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" t="s">
         <v>130</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E65" s="2">
         <v>45694</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="B65" t="s">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B66" t="s">
         <v>441</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="C66" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" t="s">
         <v>132</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E66" s="2">
         <v>45692</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="B66" t="s">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B67" t="s">
         <v>442</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="C67" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" t="s">
         <v>133</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E67" s="2">
         <v>45688</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="B67" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
         <v>443</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="C68" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" t="s">
         <v>135</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E68" s="2">
         <v>45684</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B68" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B69" t="s">
         <v>444</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="C69" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D69" t="s">
         <v>138</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E69" s="2">
         <v>45678</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="B69" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <f t="shared" ref="A70:A133" si="1">ROW()-4</f>
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
         <v>445</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C70" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" t="s">
         <v>141</v>
-      </c>
-      <c r="E69" s="2">
-        <v>45672</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="B70" t="s">
-        <v>446</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" t="s">
-        <v>142</v>
       </c>
       <c r="E70" s="2">
         <v>45672</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <f t="shared" si="0"/>
+      <c r="A71" s="1">
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B71" t="s">
@@ -4037,1123 +4085,1138 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <f t="shared" si="0"/>
+      <c r="A72" s="1">
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B72" t="s">
+        <v>446</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" t="s">
+        <v>142</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
         <v>447</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C73" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" t="s">
         <v>144</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E73" s="2">
         <v>45662</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <f t="shared" ref="A73:A133" si="1">ROW()-4</f>
-        <v>69</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
         <v>448</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="C74" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" t="s">
         <v>147</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E74" s="2">
         <v>45660</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="B74" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B75" t="s">
         <v>449</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C75" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" t="s">
         <v>149</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E75" s="2">
         <v>45659</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-      <c r="B75" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B76" t="s">
         <v>450</v>
-      </c>
-      <c r="C75" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D75" t="s">
-        <v>152</v>
-      </c>
-      <c r="E75" s="2">
-        <v>45653</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-      <c r="B76" t="s">
-        <v>451</v>
       </c>
       <c r="C76" s="10">
         <v>2024</v>
       </c>
       <c r="D76" t="s">
+        <v>152</v>
+      </c>
+      <c r="E76" s="2">
+        <v>45653</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B77" t="s">
+        <v>451</v>
+      </c>
+      <c r="C77" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D77" t="s">
         <v>154</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E77" s="2">
         <v>45650</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-      <c r="B77" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B78" t="s">
         <v>452</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="C78" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" t="s">
         <v>155</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E78" s="2">
         <v>45643</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-      <c r="B78" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B79" t="s">
         <v>284</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C79" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D79" t="s">
         <v>156</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E79" s="2">
         <v>45639</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="B79" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B80" t="s">
         <v>453</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C80" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" t="s">
         <v>160</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E80" s="2">
         <v>45610</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <f t="shared" si="1"/>
-        <v>76</v>
-      </c>
-      <c r="B80" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B81" t="s">
         <v>454</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C81" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" t="s">
         <v>161</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E81" s="2">
         <v>45609</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <f t="shared" si="1"/>
-        <v>77</v>
-      </c>
-      <c r="B81" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B82" t="s">
         <v>455</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C82" s="10">
         <v>2024</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D82" t="s">
         <v>162</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E82" s="2">
         <v>45601</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-      <c r="B82" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B83" t="s">
         <v>456</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="C83" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" t="s">
         <v>163</v>
-      </c>
-      <c r="E82" s="2">
-        <v>45597</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <f t="shared" si="1"/>
-        <v>79</v>
-      </c>
-      <c r="B83" t="s">
-        <v>457</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D83" t="s">
-        <v>164</v>
       </c>
       <c r="E83" s="2">
         <v>45597</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84">
+      <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B84" t="s">
+        <v>457</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" t="s">
+        <v>164</v>
+      </c>
+      <c r="E84" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B85" t="s">
         <v>458</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="C85" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" t="s">
         <v>166</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E85" s="2">
         <v>45593</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="B85" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
         <v>459</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C86" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D86" t="s">
         <v>169</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E86" s="2">
         <v>45588</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <f t="shared" si="1"/>
-        <v>82</v>
-      </c>
-      <c r="B86" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B87" t="s">
         <v>460</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="C87" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D87" t="s">
         <v>171</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E87" s="2">
         <v>45572</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <f t="shared" si="1"/>
-        <v>83</v>
-      </c>
-      <c r="B87" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B88" t="s">
         <v>461</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="C88" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" t="s">
         <v>176</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E88" s="2">
         <v>45562</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-      <c r="B88" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B89" t="s">
         <v>462</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="C89" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" t="s">
         <v>177</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E89" s="2">
         <v>45555</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="B89" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B90" t="s">
         <v>463</v>
       </c>
-      <c r="C89" s="10">
+      <c r="C90" s="10">
         <v>2024</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D90" t="s">
         <v>180</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E90" s="2">
         <v>45547</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-      <c r="B90" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B91" t="s">
         <v>464</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C91" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" t="s">
         <v>183</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E91" s="2">
         <v>45538</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="B91" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B92" t="s">
         <v>465</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C92" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" t="s">
         <v>185</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E92" s="2">
         <v>45534</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <f t="shared" si="1"/>
-        <v>88</v>
-      </c>
-      <c r="B92" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B93" t="s">
         <v>466</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D92" t="s">
-        <v>186</v>
-      </c>
-      <c r="E92" s="2">
-        <v>45533</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B93" t="s">
-        <v>467</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D93" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E93" s="2">
         <v>45533</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94">
+      <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B94" t="s">
+        <v>467</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D94" t="s">
+        <v>187</v>
+      </c>
+      <c r="E94" s="2">
+        <v>45533</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B95" t="s">
         <v>468</v>
-      </c>
-      <c r="C94" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D94" t="s">
-        <v>188</v>
-      </c>
-      <c r="E94" s="2">
-        <v>45526</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="B95" t="s">
-        <v>469</v>
       </c>
       <c r="C95" s="10">
         <v>2024</v>
       </c>
       <c r="D95" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95" s="2">
+        <v>45526</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B96" t="s">
+        <v>469</v>
+      </c>
+      <c r="C96" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D96" t="s">
         <v>191</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E96" s="2">
         <v>45518</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <f t="shared" si="1"/>
-        <v>92</v>
-      </c>
-      <c r="B96" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B97" t="s">
         <v>470</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="C97" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" t="s">
         <v>194</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E97" s="2">
         <v>45502</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-      <c r="B97" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B98" t="s">
         <v>471</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C98" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D98" t="s">
         <v>195</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E98" s="2">
         <v>45498</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <f t="shared" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="B98" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B99" t="s">
         <v>472</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="C99" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D99" t="s">
         <v>196</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E99" s="2">
         <v>45489</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="B99" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B100" t="s">
         <v>473</v>
       </c>
-      <c r="C99" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="C100" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D100" t="s">
         <v>199</v>
-      </c>
-      <c r="E99" s="2">
-        <v>45469</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="B100" t="s">
-        <v>474</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D100" t="s">
-        <v>200</v>
       </c>
       <c r="E100" s="2">
         <v>45469</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101">
+      <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B101" t="s">
+        <v>474</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D101" t="s">
+        <v>200</v>
+      </c>
+      <c r="E101" s="2">
+        <v>45469</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B102" t="s">
         <v>202</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C102" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D102" t="s">
         <v>203</v>
-      </c>
-      <c r="E101" s="2">
-        <v>45455</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <f t="shared" si="1"/>
-        <v>98</v>
-      </c>
-      <c r="B102" t="s">
-        <v>475</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" t="s">
-        <v>206</v>
       </c>
       <c r="E102" s="2">
         <v>45455</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103">
+      <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B103" t="s">
+        <v>475</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D103" t="s">
+        <v>206</v>
+      </c>
+      <c r="E103" s="2">
+        <v>45455</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B104" t="s">
         <v>476</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="C104" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D104" t="s">
         <v>162</v>
-      </c>
-      <c r="E103" s="2">
-        <v>45449</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="B104" t="s">
-        <v>477</v>
-      </c>
-      <c r="C104" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D104" t="s">
-        <v>209</v>
       </c>
       <c r="E104" s="2">
         <v>45449</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105">
+      <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B105" t="s">
+        <v>477</v>
+      </c>
+      <c r="C105" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D105" t="s">
+        <v>209</v>
+      </c>
+      <c r="E105" s="2">
+        <v>45449</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B106" t="s">
         <v>478</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="C106" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" t="s">
         <v>212</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E106" s="2">
         <v>45446</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
-      <c r="B106" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B107" t="s">
         <v>479</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C107" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D107" t="s">
         <v>213</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E107" s="2">
         <v>45441</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <f t="shared" si="1"/>
-        <v>103</v>
-      </c>
-      <c r="B107" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B108" t="s">
         <v>480</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D107" t="s">
-        <v>214</v>
-      </c>
-      <c r="E107" s="2">
-        <v>45440</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <f t="shared" si="1"/>
-        <v>104</v>
-      </c>
-      <c r="B108" t="s">
-        <v>481</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D108" t="s">
+        <v>214</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45440</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B109" t="s">
+        <v>481</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D109" t="s">
         <v>215</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E109" s="2">
         <v>45439</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-      <c r="B109" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B110" t="s">
         <v>482</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C110" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D110" t="s">
         <v>217</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E110" s="2">
         <v>45422</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <f t="shared" si="1"/>
-        <v>106</v>
-      </c>
-      <c r="B110" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B111" t="s">
         <v>483</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C111" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111" t="s">
         <v>221</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E111" s="2">
         <v>45415</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <f t="shared" si="1"/>
-        <v>107</v>
-      </c>
-      <c r="B111" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B112" t="s">
         <v>285</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="C112" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D112" t="s">
         <v>223</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E112" s="2">
         <v>45411</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <f t="shared" si="1"/>
-        <v>108</v>
-      </c>
-      <c r="B112" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B113" t="s">
         <v>484</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="C113" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" t="s">
         <v>228</v>
-      </c>
-      <c r="E112" s="2">
-        <v>45391</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <f t="shared" si="1"/>
-        <v>109</v>
-      </c>
-      <c r="B113" t="s">
-        <v>485</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D113" t="s">
-        <v>229</v>
       </c>
       <c r="E113" s="2">
         <v>45391</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114">
+      <c r="A114" s="1">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B114" t="s">
+        <v>485</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D114" t="s">
+        <v>229</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45391</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B115" t="s">
         <v>486</v>
       </c>
-      <c r="C114" s="10" t="s">
+      <c r="C115" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D115" t="s">
         <v>105</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E115" s="2">
         <v>45379</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <f t="shared" si="1"/>
-        <v>111</v>
-      </c>
-      <c r="B115" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="B116" t="s">
         <v>487</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D115" t="s">
-        <v>238</v>
-      </c>
-      <c r="E115" s="2">
-        <v>45378</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <f t="shared" si="1"/>
-        <v>112</v>
-      </c>
-      <c r="B116" t="s">
-        <v>488</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D116" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E116" s="2">
         <v>45378</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117">
+      <c r="A117" s="1">
         <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B117" t="s">
+        <v>488</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D117" t="s">
+        <v>239</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45378</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="B118" t="s">
         <v>489</v>
       </c>
-      <c r="C117" s="10" t="s">
+      <c r="C118" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D118" t="s">
         <v>246</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E118" s="2">
         <v>45365</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <f t="shared" si="1"/>
-        <v>114</v>
-      </c>
-      <c r="B118" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="B119" t="s">
         <v>490</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D118" t="s">
-        <v>251</v>
-      </c>
-      <c r="E118" s="2">
-        <v>45362</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <f t="shared" si="1"/>
-        <v>115</v>
-      </c>
-      <c r="B119" t="s">
-        <v>504</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D119" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E119" s="2">
         <v>45362</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120">
+      <c r="A120" s="1">
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D120" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E120" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121">
+      <c r="A121" s="1">
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D121" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E121" s="2">
         <v>45358</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122">
+      <c r="A122" s="1">
         <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D122" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E122" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123">
+      <c r="A123" s="1">
         <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D123" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E123" s="2">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124">
+      <c r="A124" s="1">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D124" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E124" s="2">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125">
+      <c r="A125" s="1">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D125" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E125" s="2">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126">
+      <c r="A126" s="1">
         <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D126" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E126" s="2">
         <v>45336</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127">
+      <c r="A127" s="1">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D127" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E127" s="2">
         <v>45336</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128">
+      <c r="A128" s="1">
         <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E128" s="2">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129">
+      <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D129" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E129" s="2">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130">
+      <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D130" t="s">
+        <v>273</v>
+      </c>
+      <c r="E130" s="2">
+        <v>45331</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="B131" t="s">
+        <v>494</v>
+      </c>
+      <c r="C131" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D131" t="s">
         <v>274</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E131" s="2">
         <v>45324</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <f t="shared" si="1"/>
-        <v>127</v>
-      </c>
-      <c r="B131" t="s">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="B132" t="s">
         <v>493</v>
-      </c>
-      <c r="C131" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D131" t="s">
-        <v>275</v>
-      </c>
-      <c r="E131" s="2">
-        <v>45322</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <f t="shared" si="1"/>
-        <v>128</v>
-      </c>
-      <c r="B132" t="s">
-        <v>492</v>
       </c>
       <c r="C132" s="10">
         <v>2024</v>
       </c>
       <c r="D132" t="s">
+        <v>275</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="B133" t="s">
+        <v>492</v>
+      </c>
+      <c r="C133" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D133" t="s">
         <v>278</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E133" s="2">
         <v>45303</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <f t="shared" si="1"/>
-        <v>129</v>
-      </c>
-      <c r="B133" t="s">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <f t="shared" ref="A134" si="2">ROW()-4</f>
+        <v>130</v>
+      </c>
+      <c r="B134" t="s">
         <v>491</v>
       </c>
-      <c r="C133" s="10" t="s">
+      <c r="C134" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D133" t="s">
+      <c r="D134" t="s">
         <v>280</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E134" s="2">
         <v>45294</v>
       </c>
-    </row>
-    <row r="288" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B288" s="3"/>
     </row>
     <row r="289" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B289" s="3"/>
@@ -5167,17 +5230,17 @@
     <row r="292" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B292" s="3"/>
     </row>
-    <row r="295" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B295" s="3"/>
-    </row>
-    <row r="300" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B300" s="3"/>
-    </row>
-    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B303" s="3"/>
-    </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B305" s="3"/>
+    <row r="293" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B293" s="3"/>
+    </row>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B296" s="3"/>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B301" s="3"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B304" s="3"/>
     </row>
     <row r="306" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B306" s="3"/>
@@ -5185,8 +5248,8 @@
     <row r="307" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B307" s="3"/>
     </row>
-    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B309" s="3"/>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B308" s="3"/>
     </row>
     <row r="310" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B310" s="3"/>
@@ -5200,15 +5263,18 @@
     <row r="313" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B313" s="3"/>
     </row>
-    <row r="315" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B315" s="3"/>
-    </row>
-    <row r="366" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B366" s="3"/>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B314" s="3"/>
+    </row>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B316" s="3"/>
+    </row>
+    <row r="367" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B367" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:E131">
-    <sortCondition descending="1" sortBy="icon" ref="E8:E131"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:E132">
+    <sortCondition descending="1" sortBy="icon" ref="E9:E132"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9639,7 +9705,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="26"/>
@@ -9649,18 +9715,18 @@
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>312</v>
       </c>
       <c r="B1" s="13"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="13"/>
       <c r="D2" s="4"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
@@ -9677,1251 +9743,1300 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="25"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <f>ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>774</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" t="s">
-        <v>773</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46084</v>
-      </c>
-      <c r="F5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28">
+      <c r="B5" s="36" t="s">
+        <v>775</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>776</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>777</v>
+      </c>
+      <c r="F5" s="39">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="25">
         <f>ROW()-4</f>
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>744</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>745</v>
-      </c>
-      <c r="E6" s="32">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28">
+      <c r="B6" s="36" t="s">
+        <v>778</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>779</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>777</v>
+      </c>
+      <c r="F6" s="39">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="25">
         <f t="shared" ref="A7:A70" si="0">ROW()-4</f>
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>746</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>747</v>
-      </c>
-      <c r="E7" s="32">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+      <c r="B7" t="s">
+        <v>774</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>773</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46084</v>
+      </c>
+      <c r="F7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E8" s="32">
         <v>46073</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+    <row r="9" spans="1:6" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="E9" s="32">
         <v>46073</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28">
+    <row r="10" spans="1:6" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="E10" s="32">
         <v>46073</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="26">
+    <row r="11" spans="1:6" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="25">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="27" t="s">
+        <v>750</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>751</v>
+      </c>
+      <c r="E11" s="32">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>752</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>753</v>
+      </c>
+      <c r="E12" s="32">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="25">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
         <v>681</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>385</v>
-      </c>
-      <c r="E11" s="2">
-        <v>46267</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="26">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>682</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>380</v>
-      </c>
-      <c r="E12" s="2">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>683</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" t="s">
+        <v>385</v>
+      </c>
+      <c r="E13" s="2">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="25">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>682</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>380</v>
+      </c>
+      <c r="E14" s="2">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="25">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E15" s="23">
         <v>46045</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B14" s="21" t="s">
+    <row r="16" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="25">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>684</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C16" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D16" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E16" s="20">
         <v>46024</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B15" s="21" t="s">
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="25">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>685</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C17" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D17" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E17" s="20">
         <v>46024</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H17" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B16" s="21" t="s">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="25">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>686</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="19" t="s">
+      <c r="C18" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="E16" s="20">
+      <c r="E18" s="20">
         <v>46022</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B17" s="21" t="s">
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="25">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>687</v>
       </c>
-      <c r="C17" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="19" t="s">
+      <c r="C19" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E19" s="20">
         <v>45986</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B18" s="21" t="s">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="25">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>688</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="21" t="s">
+      <c r="C20" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="E18" s="20">
+      <c r="E20" s="20">
         <v>45961</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B19" s="21" t="s">
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="25">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>689</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="21" t="s">
+      <c r="C21" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="E19" s="20">
+      <c r="E21" s="20">
         <v>45959</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B20" s="21" t="s">
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="25">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>690</v>
       </c>
-      <c r="C20" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="19" t="s">
+      <c r="C22" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E22" s="20">
         <v>45959</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B21" s="21" t="s">
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="25">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>691</v>
       </c>
-      <c r="C21" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="19" t="s">
+      <c r="C23" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E23" s="20">
         <v>45957</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="26">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B22" s="21" t="s">
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="25">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" s="21" t="s">
         <v>692</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="21" t="s">
+      <c r="C24" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E24" s="20">
         <v>45930</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B23" s="21" t="s">
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="25">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" s="21" t="s">
         <v>693</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="19" t="s">
+      <c r="C25" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E25" s="20">
         <v>45924</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B24" s="21" t="s">
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="25">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" s="21" t="s">
         <v>743</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C26" s="19">
         <v>2025</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D26" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="E24" s="20">
+      <c r="E26" s="20">
         <v>45896</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="26">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B25" s="21" t="s">
+    <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="25">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" s="21" t="s">
         <v>742</v>
       </c>
-      <c r="C25" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="19" t="s">
+      <c r="C27" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E27" s="20">
         <v>45866</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B26" s="21" t="s">
+    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" s="21" t="s">
         <v>741</v>
       </c>
-      <c r="C26" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="19" t="s">
+      <c r="C28" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E28" s="20">
         <v>45860</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B27" s="21" t="s">
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="25">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" s="21" t="s">
         <v>740</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C29" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D29" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="E27" s="20">
+      <c r="E29" s="20">
         <v>45852</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B28" s="21" t="s">
+    <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="25">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" s="21" t="s">
         <v>739</v>
       </c>
-      <c r="C28" s="19">
+      <c r="C30" s="19">
         <v>2025</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D30" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E30" s="20">
         <v>45840</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" s="21" t="s">
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="25">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" s="21" t="s">
         <v>738</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="19" t="s">
+      <c r="C31" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E31" s="20">
         <v>45826</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" s="21" t="s">
+    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="25">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" s="21" t="s">
         <v>737</v>
       </c>
-      <c r="C30" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="19" t="s">
+      <c r="C32" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="19" t="s">
         <v>331</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E32" s="20">
         <v>45821</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" s="21" t="s">
+    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="25">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" s="21" t="s">
         <v>736</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="19" t="s">
+      <c r="C33" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E33" s="20">
         <v>45776</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" s="21" t="s">
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="25">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" s="21" t="s">
         <v>735</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C34" s="19">
         <v>2025</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D34" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="E32" s="20">
+      <c r="E34" s="20">
         <v>45770</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="26">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B33" s="21" t="s">
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="25">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" s="21" t="s">
         <v>734</v>
       </c>
-      <c r="C33" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" s="19" t="s">
+      <c r="C35" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="E33" s="20">
+      <c r="E35" s="20">
         <v>45768</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="26">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B34" s="21" t="s">
+    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="25">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" s="21" t="s">
         <v>733</v>
       </c>
-      <c r="C34" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="19" t="s">
+      <c r="C36" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="E34" s="20">
+      <c r="E36" s="20">
         <v>45758</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="26">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B35" s="21" t="s">
+    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="25">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B37" s="21" t="s">
         <v>732</v>
       </c>
-      <c r="C35" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D35" s="21" t="s">
+      <c r="C37" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="E35" s="20">
+      <c r="E37" s="20">
         <v>45741</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="26">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B36" s="21" t="s">
+    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="25">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="21" t="s">
         <v>731</v>
       </c>
-      <c r="C36" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D36" s="19" t="s">
+      <c r="C38" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="E36" s="20">
+      <c r="E38" s="20">
         <v>45736</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="26">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B37" s="21" t="s">
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="25">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" s="21" t="s">
         <v>730</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C39" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D39" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="E37" s="20">
+      <c r="E39" s="20">
         <v>45728</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="26">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B38" s="21" t="s">
+    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="25">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B40" s="21" t="s">
         <v>729</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C40" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D40" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="E38" s="20">
+      <c r="E40" s="20">
         <v>45716</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="26">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B39" s="21" t="s">
+    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="25">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B41" s="21" t="s">
         <v>728</v>
       </c>
-      <c r="C39" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D39" s="19" t="s">
+      <c r="C41" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="E39" s="20">
+      <c r="E41" s="20">
         <v>45701</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="26">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B40" s="21" t="s">
+    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="25">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B42" s="21" t="s">
         <v>727</v>
       </c>
-      <c r="C40" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="19" t="s">
+      <c r="C42" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="E40" s="20">
+      <c r="E42" s="20">
         <v>45700</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="26">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B41" s="21" t="s">
+    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="25">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B43" s="21" t="s">
         <v>726</v>
       </c>
-      <c r="C41" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="19" t="s">
+      <c r="C43" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="19" t="s">
         <v>342</v>
       </c>
-      <c r="E41" s="20">
+      <c r="E43" s="20">
         <v>45699</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="26">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B42" s="21" t="s">
+    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="25">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="21" t="s">
         <v>725</v>
       </c>
-      <c r="C42" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="19" t="s">
+      <c r="C44" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="E42" s="20">
+      <c r="E44" s="20">
         <v>45699</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="26">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B43" s="21" t="s">
+    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="25">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="21" t="s">
         <v>724</v>
       </c>
-      <c r="C43" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D43" s="19" t="s">
+      <c r="C45" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="E43" s="20">
+      <c r="E45" s="20">
         <v>45686</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="26">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B44" s="21" t="s">
+    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="25">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B46" s="21" t="s">
         <v>723</v>
       </c>
-      <c r="C44" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="19" t="s">
+      <c r="C46" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="19" t="s">
         <v>345</v>
       </c>
-      <c r="E44" s="20">
+      <c r="E46" s="20">
         <v>45656</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="26">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B45" s="21" t="s">
+    <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="25">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B47" s="21" t="s">
         <v>722</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C47" s="19">
         <v>2024</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D47" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="E45" s="20">
+      <c r="E47" s="20">
         <v>45656</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="26">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B46" s="21" t="s">
+    <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="25">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B48" s="21" t="s">
         <v>721</v>
       </c>
-      <c r="C46" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D46" s="19" t="s">
+      <c r="C48" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="E46" s="20">
+      <c r="E48" s="20">
         <v>45646</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="26">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B47" s="21" t="s">
+    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="25">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B49" s="21" t="s">
         <v>720</v>
       </c>
-      <c r="C47" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" s="19" t="s">
+      <c r="C49" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D49" s="19" t="s">
         <v>348</v>
       </c>
-      <c r="E47" s="20">
+      <c r="E49" s="20">
         <v>45632</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="26">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B48" s="21" t="s">
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="25">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B50" s="21" t="s">
         <v>719</v>
       </c>
-      <c r="C48" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" s="19" t="s">
+      <c r="C50" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" s="19" t="s">
         <v>349</v>
       </c>
-      <c r="E48" s="20">
+      <c r="E50" s="20">
         <v>45610</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="26">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B49" s="21" t="s">
+    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="25">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B51" s="21" t="s">
         <v>718</v>
       </c>
-      <c r="C49" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" s="19" t="s">
+      <c r="C51" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="19" t="s">
         <v>350</v>
       </c>
-      <c r="E49" s="20">
+      <c r="E51" s="20">
         <v>45582</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="26">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B50" s="21" t="s">
+    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="25">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B52" s="21" t="s">
         <v>717</v>
       </c>
-      <c r="C50" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="19" t="s">
+      <c r="C52" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="19" t="s">
         <v>351</v>
       </c>
-      <c r="E50" s="20">
+      <c r="E52" s="20">
         <v>45572</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="26">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B51" s="21" t="s">
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="25">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B53" s="21" t="s">
         <v>716</v>
       </c>
-      <c r="C51" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D51" s="19" t="s">
+      <c r="C53" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="E51" s="20">
+      <c r="E53" s="20">
         <v>45569</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="26">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B52" s="21" t="s">
+    <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="25">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B54" s="21" t="s">
         <v>715</v>
       </c>
-      <c r="C52" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="19" t="s">
+      <c r="C54" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="19" t="s">
         <v>353</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E54" s="20">
         <v>45565</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="26">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B53" s="21" t="s">
+    <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="25">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B55" s="21" t="s">
         <v>714</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D53" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="E53" s="20">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="26">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>713</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="E54" s="20">
-        <v>45535</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="26">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="B55" s="21" t="s">
-        <v>712</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E55" s="20">
-        <v>45533</v>
+        <v>45552</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="26">
+      <c r="A56" s="25">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D56" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="E56" s="20">
+        <v>45535</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="25">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>712</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="E57" s="20">
+        <v>45533</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="25">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>711</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D58" s="19" t="s">
         <v>357</v>
       </c>
-      <c r="E56" s="20">
+      <c r="E58" s="20">
         <v>45526</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="26">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="B57" s="21" t="s">
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="25">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B59" s="21" t="s">
         <v>710</v>
       </c>
-      <c r="C57" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="19" t="s">
+      <c r="C59" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="19" t="s">
         <v>358</v>
       </c>
-      <c r="E57" s="20">
+      <c r="E59" s="20">
         <v>45520</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="26">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="B58" s="21" t="s">
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="25">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B60" s="21" t="s">
         <v>709</v>
       </c>
-      <c r="C58" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" s="19" t="s">
+      <c r="C60" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D60" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="E58" s="20">
+      <c r="E60" s="20">
         <v>45518</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="26">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="B59" s="21" t="s">
+    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="25">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B61" s="21" t="s">
         <v>708</v>
       </c>
-      <c r="C59" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D59" s="19" t="s">
+      <c r="C61" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D61" s="19" t="s">
         <v>360</v>
       </c>
-      <c r="E59" s="20">
+      <c r="E61" s="20">
         <v>45506</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="26">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="B60" s="21" t="s">
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="25">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B62" s="21" t="s">
         <v>707</v>
       </c>
-      <c r="C60" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D60" s="19" t="s">
+      <c r="C62" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="E60" s="20">
+      <c r="E62" s="20">
         <v>45498</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="26">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="B61" s="21" t="s">
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="25">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B63" s="21" t="s">
         <v>706</v>
       </c>
-      <c r="C61" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D61" s="19" t="s">
+      <c r="C63" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" s="19" t="s">
         <v>362</v>
       </c>
-      <c r="E61" s="20">
+      <c r="E63" s="20">
         <v>45496</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="26">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="B62" s="21" t="s">
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="25">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B64" s="21" t="s">
         <v>705</v>
       </c>
-      <c r="C62" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D62" s="19" t="s">
+      <c r="C64" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="19" t="s">
         <v>363</v>
       </c>
-      <c r="E62" s="20">
+      <c r="E64" s="20">
         <v>45483</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="26">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="B63" s="21" t="s">
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="25">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B65" s="21" t="s">
         <v>704</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C65" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D65" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="E63" s="20">
+      <c r="E65" s="20">
         <v>45471</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="26">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="B64" s="21" t="s">
+    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="25">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B66" s="21" t="s">
         <v>703</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="E64" s="20">
-        <v>45461</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="26">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="B65" s="21" t="s">
-        <v>702</v>
-      </c>
-      <c r="C65" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="E65" s="20">
-        <v>45455</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="26">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="B66" s="30" t="s">
-        <v>701</v>
       </c>
       <c r="C66" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D66" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="E66" s="20">
+        <v>45461</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="25">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>702</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="E67" s="20">
+        <v>45455</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="25">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>701</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E66" s="20">
+      <c r="E68" s="20">
         <v>45440</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="26">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="B67" s="30" t="s">
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="25">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B69" s="30" t="s">
         <v>700</v>
-      </c>
-      <c r="C67" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D67" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="E67" s="20">
-        <v>45422</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="26">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B68" s="21" t="s">
-        <v>699</v>
-      </c>
-      <c r="C68" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="E68" s="20">
-        <v>45400</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="26">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="B69" s="21" t="s">
-        <v>698</v>
       </c>
       <c r="C69" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D69" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="E69" s="20">
+        <v>45422</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="25">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>699</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="E70" s="20">
+        <v>45400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="25">
+        <f t="shared" ref="A71:A75" si="1">ROW()-4</f>
+        <v>67</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>698</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="E69" s="20">
+      <c r="E71" s="20">
         <v>45384</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="26">
-        <f t="shared" si="0"/>
-        <v>66</v>
-      </c>
-      <c r="B70" s="21" t="s">
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="25">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B72" s="21" t="s">
         <v>697</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C72" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="D72" s="19" t="s">
         <v>369</v>
       </c>
-      <c r="E70" s="20">
+      <c r="E72" s="20">
         <v>45371</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="26">
-        <f t="shared" ref="A71:A73" si="1">ROW()-4</f>
-        <v>67</v>
-      </c>
-      <c r="B71" s="21" t="s">
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="25">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B73" s="21" t="s">
         <v>696</v>
-      </c>
-      <c r="C71" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="E71" s="20">
-        <v>45369</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="26">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-      <c r="B72" s="21" t="s">
-        <v>695</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>236</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="E72" s="20">
-        <v>45338</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="26">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="B73" s="21" t="s">
-        <v>694</v>
       </c>
       <c r="C73" s="19" t="s">
         <v>236</v>
       </c>
       <c r="D73" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="E73" s="20">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="25">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>695</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="E74" s="20">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="25">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="D75" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="E73" s="20">
+      <c r="E75" s="20">
         <v>45335</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274EFCE5-3913-4AB0-B524-6B3D0EB8A33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7EC5E5-538C-47DC-A515-7784204D6236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="800">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2408,6 +2408,30 @@
   </si>
   <si>
     <t>Clarification on Support for Interest Subvention for pre-shipment and post-shipment credit</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 53/2025-26</t>
+  </si>
+  <si>
+    <t>Extension in the validity of TRQ Authorisation for import of gold under India-UAE CEPA (Tariff Head 7108) issued in FY 2025-26, till 30.06.2026 - reg.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 68/2025-26</t>
+  </si>
+  <si>
+    <t>Amendment in import policy condition of Urea Exim Code 31021010 in the ITC HS 2022 Schedule I Import Policy Regarding</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 67/2025-26</t>
+  </si>
+  <si>
+    <t>Amendment in Para 9.05 of FTP 2023 to remove per-consignment value limit for courier exports</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 66/2025-26</t>
+  </si>
+  <si>
+    <t>Restoration of RoDTEP rates - reg</t>
   </si>
 </sst>
 </file>
@@ -2484,7 +2508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2583,14 +2607,16 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2871,7 +2897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O369"/>
+  <dimension ref="A1:O370"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
@@ -2909,97 +2935,93 @@
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="42">
-        <f t="shared" ref="A5:A6" si="0">ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="44" t="s">
+        <v>792</v>
+      </c>
+      <c r="C5" s="45">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>793</v>
+      </c>
+      <c r="E5" s="46">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" ref="A6:A7" si="0">ROW()-4</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>787</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="33" t="s">
+      <c r="C6" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="33" t="s">
         <v>788</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E6" s="32">
         <v>46101</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B6" s="27" t="s">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="33" t="s">
+      <c r="C7" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="33" t="s">
         <v>779</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E7" s="32">
         <v>46087</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
+    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <f>ROW()-4</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="40" t="s">
         <v>780</v>
       </c>
-      <c r="C7" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="40" t="s">
+      <c r="C8" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="40" t="s">
         <v>779</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E8" s="41">
         <v>46087</v>
       </c>
-      <c r="F7" s="39"/>
-    </row>
-    <row r="8" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <f t="shared" ref="A8:A71" si="1">ROW()-4</f>
-        <v>4</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>754</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>755</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>756</v>
-      </c>
+      <c r="F8" s="39"/>
     </row>
     <row r="9" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A9:A72" si="1">ROW()-4</f>
         <v>5</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C9" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E9" s="34" t="s">
         <v>756</v>
       </c>
-      <c r="O9" s="27" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="10" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -3007,34 +3029,37 @@
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C10" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E10" s="34" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O10" s="27" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B11" t="s">
-        <v>386</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E11" s="2">
-        <v>46328</v>
+      <c r="B11" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>760</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -3043,16 +3068,16 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>4</v>
+        <v>382</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E12" s="2">
-        <v>46144</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -3061,16 +3086,16 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D13" t="s">
-        <v>5</v>
+      <c r="D13" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="E13" s="2">
-        <v>46045</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -3079,16 +3104,16 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E14" s="2">
-        <v>46038</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -3097,16 +3122,16 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>390</v>
-      </c>
-      <c r="C15" s="10">
-        <v>2026</v>
+        <v>389</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2">
-        <v>46031</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -3115,13 +3140,13 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C16" s="10">
         <v>2026</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2">
         <v>46031</v>
@@ -3133,16 +3158,16 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C17" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2">
-        <v>46022</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3151,16 +3176,16 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>393</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>4</v>
+        <v>392</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2025</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2">
-        <v>46010</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -3169,16 +3194,16 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E19" s="2">
-        <v>46008</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -3187,13 +3212,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2">
         <v>46008</v>
@@ -3205,16 +3230,16 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>374</v>
+        <v>19</v>
       </c>
       <c r="E21" s="2">
-        <v>46002</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -3223,16 +3248,16 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>397</v>
-      </c>
-      <c r="C22" s="10">
-        <v>2025</v>
+        <v>396</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="E22" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -3241,13 +3266,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C23" s="10">
         <v>2025</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2">
         <v>46001</v>
@@ -3259,16 +3284,16 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>399</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>4</v>
+        <v>398</v>
+      </c>
+      <c r="C24" s="10">
+        <v>2025</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E24" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3277,13 +3302,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" s="2">
         <v>45992</v>
@@ -3295,16 +3320,16 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>401</v>
-      </c>
-      <c r="C26" s="10">
-        <v>2025</v>
+        <v>400</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -3313,16 +3338,16 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>402</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="C27" s="10">
+        <v>2025</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2">
-        <v>45959</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3331,16 +3356,16 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>403</v>
-      </c>
-      <c r="C28" s="10">
-        <v>2025</v>
+        <v>402</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -3349,13 +3374,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C29" s="10">
         <v>2025</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E29" s="2">
         <v>45958</v>
@@ -3367,16 +3392,16 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>405</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>8</v>
+        <v>404</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2025</v>
       </c>
       <c r="D30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E30" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -3385,16 +3410,16 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E31" s="2">
-        <v>45952</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3403,16 +3428,16 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E32" s="2">
-        <v>45945</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3421,16 +3446,16 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -3439,13 +3464,13 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E34" s="2">
         <v>45940</v>
@@ -3457,16 +3482,16 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E35" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3475,16 +3500,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E36" s="2">
-        <v>45931</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3493,16 +3518,16 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E37" s="2">
-        <v>45909</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -3511,16 +3536,16 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E38" s="2">
-        <v>45903</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3529,16 +3554,16 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>413</v>
-      </c>
-      <c r="C39" s="10">
-        <v>2025</v>
+        <v>412</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E39" s="2">
-        <v>45895</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3547,16 +3572,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>414</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C40" s="10">
+        <v>2025</v>
       </c>
       <c r="D40" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E40" s="2">
-        <v>45891</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3565,16 +3590,16 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2">
-        <v>45870</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3583,16 +3608,16 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>416</v>
-      </c>
-      <c r="C42" s="10">
-        <v>2025</v>
+        <v>415</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E42" s="2">
-        <v>45868</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3601,16 +3626,16 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>417</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C43" s="10">
+        <v>2025</v>
       </c>
       <c r="D43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E43" s="2">
-        <v>45867</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3619,16 +3644,16 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E44" s="2">
-        <v>45860</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3637,16 +3662,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2">
-        <v>45846</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3655,16 +3680,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E46" s="2">
-        <v>45833</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3673,13 +3698,13 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2">
         <v>45833</v>
@@ -3691,16 +3716,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2">
-        <v>45820</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3709,13 +3734,13 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E49" s="2">
         <v>45820</v>
@@ -3727,16 +3752,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2">
-        <v>45818</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3745,16 +3770,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>425</v>
-      </c>
-      <c r="C51" s="10">
-        <v>2025</v>
+        <v>424</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E51" s="2">
-        <v>45807</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3763,16 +3788,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>426</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C52" s="10">
+        <v>2025</v>
       </c>
       <c r="D52" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E52" s="2">
-        <v>45793</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -3781,16 +3806,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E53" s="2">
-        <v>45784</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3799,16 +3824,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E54" s="2">
-        <v>45783</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3817,13 +3842,13 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E55" s="2">
         <v>45783</v>
@@ -3835,16 +3860,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E56" s="2">
-        <v>45771</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3853,16 +3878,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E57" s="2">
-        <v>45762</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3871,16 +3896,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E58" s="2">
-        <v>45750</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3889,16 +3914,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>433</v>
-      </c>
-      <c r="C59" s="10">
-        <v>2025</v>
+        <v>432</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E59" s="2">
-        <v>45744</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -3907,16 +3932,16 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>110</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>4</v>
+        <v>433</v>
+      </c>
+      <c r="C60" s="10">
+        <v>2025</v>
       </c>
       <c r="D60" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E60" s="2">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3925,13 +3950,13 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>434</v>
+        <v>110</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E61" s="2">
         <v>45743</v>
@@ -3943,16 +3968,16 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D62" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2">
-        <v>45735</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -3961,16 +3986,16 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D63" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E63" s="2">
-        <v>45726</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -3979,16 +4004,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E64" s="2">
-        <v>45719</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3997,16 +4022,16 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E65" s="2">
-        <v>45700</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4015,16 +4040,16 @@
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D66" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E66" s="2">
-        <v>45695</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -4033,16 +4058,16 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D67" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E67" s="2">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -4051,16 +4076,16 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E68" s="2">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -4069,16 +4094,16 @@
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E69" s="2">
-        <v>45688</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -4087,16 +4112,16 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D70" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E70" s="2">
-        <v>45684</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -4105,49 +4130,49 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E71" s="2">
-        <v>45678</v>
+        <v>45684</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <f t="shared" ref="A72:A135" si="2">ROW()-4</f>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D72" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E72" s="2">
-        <v>45672</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A73:A136" si="2">ROW()-4</f>
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E73" s="2">
         <v>45672</v>
@@ -4177,16 +4202,16 @@
         <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E75" s="2">
-        <v>45662</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4195,16 +4220,16 @@
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E76" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4213,16 +4238,16 @@
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E77" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -4231,16 +4256,16 @@
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>450</v>
-      </c>
-      <c r="C78" s="10">
-        <v>2024</v>
+        <v>449</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E78" s="2">
-        <v>45653</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4249,16 +4274,16 @@
         <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C79" s="10">
         <v>2024</v>
       </c>
       <c r="D79" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E79" s="2">
-        <v>45650</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4267,16 +4292,16 @@
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>452</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>114</v>
+        <v>451</v>
+      </c>
+      <c r="C80" s="10">
+        <v>2024</v>
       </c>
       <c r="D80" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E80" s="2">
-        <v>45643</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4285,16 +4310,16 @@
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>284</v>
+        <v>452</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E81" s="2">
-        <v>45639</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4303,16 +4328,16 @@
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>453</v>
+        <v>284</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E82" s="2">
-        <v>45610</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4321,16 +4346,16 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E83" s="2">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4339,16 +4364,16 @@
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>455</v>
-      </c>
-      <c r="C84" s="10">
-        <v>2024</v>
+        <v>454</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E84" s="2">
-        <v>45601</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4357,16 +4382,16 @@
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>456</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C85" s="10">
+        <v>2024</v>
       </c>
       <c r="D85" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E85" s="2">
-        <v>45597</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4375,13 +4400,13 @@
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E86" s="2">
         <v>45597</v>
@@ -4393,16 +4418,16 @@
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E87" s="2">
-        <v>45593</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4411,16 +4436,16 @@
         <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E88" s="2">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4429,16 +4454,16 @@
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E89" s="2">
-        <v>45572</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4447,16 +4472,16 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E90" s="2">
-        <v>45562</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4465,16 +4490,16 @@
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E91" s="2">
-        <v>45555</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4483,16 +4508,16 @@
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>463</v>
-      </c>
-      <c r="C92" s="10">
-        <v>2024</v>
+        <v>462</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E92" s="2">
-        <v>45547</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4501,16 +4526,16 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>464</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>114</v>
+        <v>463</v>
+      </c>
+      <c r="C93" s="10">
+        <v>2024</v>
       </c>
       <c r="D93" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E93" s="2">
-        <v>45538</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4519,16 +4544,16 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E94" s="2">
-        <v>45534</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -4537,16 +4562,16 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E95" s="2">
-        <v>45533</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4555,13 +4580,13 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D96" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E96" s="2">
         <v>45533</v>
@@ -4573,16 +4598,16 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>468</v>
-      </c>
-      <c r="C97" s="10">
-        <v>2024</v>
+        <v>467</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="D97" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E97" s="2">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4591,16 +4616,16 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C98" s="10">
         <v>2024</v>
       </c>
       <c r="D98" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E98" s="2">
-        <v>45518</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4609,16 +4634,16 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>470</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C99" s="10">
+        <v>2024</v>
       </c>
       <c r="D99" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E99" s="2">
-        <v>45502</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4627,16 +4652,16 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E100" s="2">
-        <v>45498</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4645,16 +4670,16 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E101" s="2">
-        <v>45489</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4663,16 +4688,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E102" s="2">
-        <v>45469</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4681,13 +4706,13 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E103" s="2">
         <v>45469</v>
@@ -4699,16 +4724,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>202</v>
+        <v>474</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E104" s="2">
-        <v>45455</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4717,13 +4742,13 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>475</v>
+        <v>202</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E105" s="2">
         <v>45455</v>
@@ -4735,16 +4760,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="E106" s="2">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4753,13 +4778,13 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>477</v>
-      </c>
-      <c r="C107" s="10">
-        <v>2024</v>
+        <v>476</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E107" s="2">
         <v>45449</v>
@@ -4771,16 +4796,16 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>478</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>114</v>
+        <v>477</v>
+      </c>
+      <c r="C108" s="10">
+        <v>2024</v>
       </c>
       <c r="D108" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E108" s="2">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4789,16 +4814,16 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E109" s="2">
-        <v>45441</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -4807,16 +4832,16 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E110" s="2">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -4825,16 +4850,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E111" s="2">
-        <v>45439</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -4843,16 +4868,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D112" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E112" s="2">
-        <v>45422</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -4861,16 +4886,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E113" s="2">
-        <v>45415</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -4879,16 +4904,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>285</v>
+        <v>483</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E114" s="2">
-        <v>45411</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -4897,16 +4922,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>484</v>
+        <v>285</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E115" s="2">
-        <v>45391</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -4915,13 +4940,13 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E116" s="2">
         <v>45391</v>
@@ -4933,16 +4958,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="E117" s="2">
-        <v>45379</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -4951,16 +4976,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D118" t="s">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="E118" s="2">
-        <v>45378</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -4969,13 +4994,13 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D119" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E119" s="2">
         <v>45378</v>
@@ -4987,16 +5012,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D120" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E120" s="2">
-        <v>45365</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -5005,16 +5030,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D121" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E121" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -5023,13 +5048,13 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D122" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E122" s="2">
         <v>45362</v>
@@ -5041,16 +5066,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D123" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E123" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -5059,13 +5084,13 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D124" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E124" s="2">
         <v>45358</v>
@@ -5077,16 +5102,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D125" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E125" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -5095,16 +5120,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D126" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E126" s="2">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -5113,16 +5138,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D127" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E127" s="2">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -5131,16 +5156,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E128" s="2">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -5149,13 +5174,13 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D129" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E129" s="2">
         <v>45336</v>
@@ -5167,13 +5192,13 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D130" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E130" s="2">
         <v>45336</v>
@@ -5185,16 +5210,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D131" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E131" s="2">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5203,16 +5228,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E132" s="2">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -5221,16 +5246,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E133" s="2">
-        <v>45324</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -5239,16 +5264,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>493</v>
-      </c>
-      <c r="C134" s="10">
-        <v>2024</v>
+        <v>494</v>
+      </c>
+      <c r="C134" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E134" s="2">
-        <v>45322</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -5257,38 +5282,53 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C135" s="10">
         <v>2024</v>
       </c>
       <c r="D135" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E135" s="2">
-        <v>45303</v>
+        <v>45322</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <f t="shared" ref="A136" si="3">ROW()-4</f>
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B136" t="s">
+        <v>492</v>
+      </c>
+      <c r="C136" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D136" t="s">
+        <v>278</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <f t="shared" ref="A137" si="3">ROW()-4</f>
+        <v>133</v>
+      </c>
+      <c r="B137" t="s">
         <v>491</v>
       </c>
-      <c r="C136" s="10" t="s">
+      <c r="C137" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D136" t="s">
+      <c r="D137" t="s">
         <v>280</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E137" s="2">
         <v>45294</v>
       </c>
-    </row>
-    <row r="291" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B291" s="3"/>
     </row>
     <row r="292" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B292" s="3"/>
@@ -5302,17 +5342,17 @@
     <row r="295" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B295" s="3"/>
     </row>
-    <row r="298" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B298" s="3"/>
-    </row>
-    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B303" s="3"/>
-    </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B306" s="3"/>
-    </row>
-    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B308" s="3"/>
+    <row r="296" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B296" s="3"/>
+    </row>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B299" s="3"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B304" s="3"/>
+    </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B307" s="3"/>
     </row>
     <row r="309" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B309" s="3"/>
@@ -5320,8 +5360,8 @@
     <row r="310" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B310" s="3"/>
     </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B312" s="3"/>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B311" s="3"/>
     </row>
     <row r="313" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B313" s="3"/>
@@ -5335,15 +5375,18 @@
     <row r="316" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B316" s="3"/>
     </row>
-    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B318" s="3"/>
-    </row>
-    <row r="369" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B369" s="3"/>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B317" s="3"/>
+    </row>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B319" s="3"/>
+    </row>
+    <row r="370" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B370" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:E134">
-    <sortCondition descending="1" sortBy="icon" ref="E11:E134"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:E135">
+    <sortCondition descending="1" sortBy="icon" ref="E12:E135"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5352,7 +5395,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E170"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5383,2937 +5426,2988 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="42">
-        <f t="shared" ref="A5:A68" si="0">ROW()-4</f>
+    <row r="5" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="43">
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="44" t="s">
+        <v>794</v>
+      </c>
+      <c r="C5" s="45">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>795</v>
+      </c>
+      <c r="E5" s="46">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="43">
+        <v>2</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>796</v>
+      </c>
+      <c r="C6" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>797</v>
+      </c>
+      <c r="E6" s="46">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="43">
+        <v>3</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>798</v>
+      </c>
+      <c r="C7" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>799</v>
+      </c>
+      <c r="E7" s="46">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <f t="shared" ref="A8:A71" si="0">ROW()-4</f>
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>781</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="27" t="s">
+      <c r="C8" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="27" t="s">
         <v>782</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E8" s="34">
         <v>46100</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="42">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="B6" s="27" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>783</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="27" t="s">
+      <c r="C9" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>784</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E9" s="34">
         <v>46099</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="42">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B7" s="27" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>785</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="27" t="s">
+      <c r="C10" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="27" t="s">
         <v>786</v>
       </c>
-      <c r="E7" s="34">
+      <c r="E10" s="34">
         <v>46097</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="42">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B8" s="27" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>761</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="27" t="s">
+      <c r="C11" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="27" t="s">
         <v>762</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E11" s="34" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="42">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B9" s="27" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B12" s="27" t="s">
         <v>763</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="27" t="s">
+      <c r="C12" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="27" t="s">
         <v>764</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E12" s="34" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="42">
-        <f t="shared" si="0"/>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>766</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>768</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>588</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>384</v>
+      </c>
+      <c r="E15" s="2">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>589</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>376</v>
+      </c>
+      <c r="E16" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>590</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
+        <v>377</v>
+      </c>
+      <c r="E17" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>591</v>
+      </c>
+      <c r="C18" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D18" t="s">
+        <v>375</v>
+      </c>
+      <c r="E18" s="2">
+        <v>46051</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>592</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>765</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>766</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="42">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>767</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>768</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="42">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>588</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>384</v>
-      </c>
-      <c r="E12" s="2">
-        <v>46267</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="42">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>589</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>376</v>
-      </c>
-      <c r="E13" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="42">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
-        <v>590</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>377</v>
-      </c>
-      <c r="E14" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="42">
-        <f t="shared" si="0"/>
+      <c r="E19" s="2">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>593</v>
+      </c>
+      <c r="C20" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D20" t="s">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
-        <v>591</v>
-      </c>
-      <c r="C15" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D15" t="s">
-        <v>375</v>
-      </c>
-      <c r="E15" s="2">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="42">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>592</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="2">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="42">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>593</v>
-      </c>
-      <c r="C17" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2">
+      <c r="E20" s="2">
         <v>46025</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="42">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
         <v>594</v>
-      </c>
-      <c r="C18" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="2">
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="42">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>595</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="2">
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="42">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>596</v>
-      </c>
-      <c r="C20" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="2">
-        <v>46020</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="42">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
-        <v>597</v>
       </c>
       <c r="C21" s="10">
         <v>2025</v>
       </c>
       <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="2">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>595</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>596</v>
+      </c>
+      <c r="C23" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="2">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>597</v>
+      </c>
+      <c r="C24" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D24" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E24" s="2">
         <v>46009</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="42">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
         <v>598</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="C25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
         <v>22</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E25" s="2">
         <v>46000</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="42">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
         <v>599</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
         <v>25</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E26" s="2">
         <v>45978</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="42">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
         <v>600</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E27" s="2">
         <v>45965</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="42">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
         <v>601</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C28" s="10">
         <v>2025</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D28" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E28" s="2">
         <v>45951</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="42">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
         <v>602</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C29" s="10">
         <v>2025</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D29" t="s">
         <v>33</v>
-      </c>
-      <c r="E26" s="2">
-        <v>45945</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="42">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>602</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="2">
-        <v>45945</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="42">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B28" t="s">
-        <v>603</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="2">
-        <v>45945</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="42">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
-        <v>604</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
       </c>
       <c r="E29" s="2">
         <v>45945</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="42">
+      <c r="A30">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B30" t="s">
+        <v>602</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="2">
+        <v>45945</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
+        <v>603</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>34</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45945</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>604</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45945</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
         <v>605</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="C33" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" t="s">
         <v>37</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E33" s="2">
         <v>45944</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="42">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
         <v>606</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="C34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
         <v>40</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E34" s="2">
         <v>45940</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="42">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
         <v>607</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="C35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E35" s="2">
         <v>45940</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="42">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
         <v>608</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
         <v>43</v>
-      </c>
-      <c r="E33" s="2">
-        <v>45933</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="42">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>609</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>44</v>
-      </c>
-      <c r="E34" s="2">
-        <v>45933</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="42">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>610</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="2">
-        <v>45933</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="42">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>611</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
-        <v>46</v>
       </c>
       <c r="E36" s="2">
         <v>45933</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="42">
+      <c r="A37">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" t="s">
+        <v>609</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>44</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45933</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45933</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="2">
+        <v>45933</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B40" s="10" t="s">
         <v>612</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
         <v>49</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E40" s="2">
         <v>45930</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="42">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B38" s="10" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B41" s="10" t="s">
         <v>613</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E41" s="2">
         <v>45924</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="42">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B39" s="10" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>614</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E42" s="2">
         <v>45924</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="42">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B40" s="10" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B43" s="10" t="s">
         <v>615</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
         <v>52</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E43" s="2">
         <v>45924</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="42">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B41" s="10" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C44" s="10">
         <v>2025</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D44" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E44" s="2">
         <v>45923</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="42">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B42" s="10" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>617</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E45" s="2">
         <v>45918</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="42">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B43" s="10" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B46" s="10" t="s">
         <v>618</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
         <v>56</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E46" s="2">
         <v>45908</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="42">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B44" s="10" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B47" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C47" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" t="s">
         <v>58</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E47" s="2">
         <v>45897</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="42">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B45" s="10" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B48" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C48" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E48" s="2">
         <v>45891</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="42">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B46" s="10" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B49" s="10" t="s">
         <v>621</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C49" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
         <v>61</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E49" s="2">
         <v>45891</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="42">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B47" s="10" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B50" s="10" t="s">
         <v>622</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C50" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
         <v>63</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E50" s="2">
         <v>45888</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="42">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B48" s="10" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B51" s="10" t="s">
         <v>623</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C51" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E51" s="2">
         <v>45880</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="42">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B49" s="10" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C52" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
         <v>70</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E52" s="2">
         <v>45855</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="42">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B50" s="10" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B53" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C53" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
         <v>72</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E53" s="2">
         <v>45838</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="42">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B51" s="10" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B54" s="10" t="s">
         <v>625</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C54" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
         <v>73</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E54" s="2">
         <v>45838</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="42">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B52" s="10" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B55" s="10" t="s">
         <v>626</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C55" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
         <v>74</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E55" s="2">
         <v>45835</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="42">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B53" s="10" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B56" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C56" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
         <v>76</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E56" s="2">
         <v>45833</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="42">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B54" s="10" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B57" s="10" t="s">
         <v>627</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C57" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
         <v>58</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E57" s="2">
         <v>45831</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="42">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="B55" s="10" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C58" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E58" s="2">
         <v>45825</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="42">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="B56" s="10" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B59" s="10" t="s">
         <v>629</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C59" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
         <v>80</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E59" s="2">
         <v>45825</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="42">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="B57" s="10" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>630</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C60" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
         <v>81</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E60" s="2">
         <v>45825</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="42">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="B58" s="10" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B61" s="10" t="s">
         <v>631</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C61" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
         <v>85</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E61" s="2">
         <v>45808</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="42">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="B59" s="10" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B62" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C62" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
         <v>87</v>
-      </c>
-      <c r="E59" s="2">
-        <v>45803</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="42">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>633</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" s="2">
-        <v>45803</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="42">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>634</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D61" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="2">
-        <v>45803</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="42">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>635</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" t="s">
-        <v>90</v>
       </c>
       <c r="E62" s="2">
         <v>45803</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="42">
+      <c r="A63">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E63" s="2">
         <v>45803</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="42">
+      <c r="A64">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E64" s="2">
         <v>45803</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="42">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B65" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
+        <v>90</v>
+      </c>
+      <c r="E65" s="2">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D66" t="s">
+        <v>91</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B68" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="C68" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" t="s">
         <v>94</v>
       </c>
-      <c r="E65" s="2">
+      <c r="E68" s="2">
         <v>45796</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="42">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="B66" s="10" t="s">
+    <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B69" s="10" t="s">
         <v>639</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="C69" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" t="s">
         <v>93</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E69" s="2">
         <v>45796</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="42">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="B67" s="10" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="B70" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="C70" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D70" t="s">
         <v>95</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E70" s="2">
         <v>45794</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="42">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B68" s="10" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <f t="shared" si="0"/>
+        <v>67</v>
+      </c>
+      <c r="B71" s="10" t="s">
         <v>641</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="C71" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D71" t="s">
         <v>100</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E71" s="2">
         <v>45779</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="42">
-        <f t="shared" ref="A69:A132" si="1">ROW()-4</f>
-        <v>65</v>
-      </c>
-      <c r="B69" s="10" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <f t="shared" ref="A72:A135" si="1">ROW()-4</f>
+        <v>68</v>
+      </c>
+      <c r="B72" s="10" t="s">
         <v>642</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C72" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D72" t="s">
         <v>102</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E72" s="2">
         <v>45770</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="42">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-      <c r="B70" s="10" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B73" s="10" t="s">
         <v>643</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="C73" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D73" t="s">
         <v>103</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E73" s="2">
         <v>45762</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="42">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
-      <c r="B71" s="10" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B74" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="C71" s="10">
+      <c r="C74" s="10">
         <v>2025</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D74" t="s">
         <v>106</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E74" s="2">
         <v>45749</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="42">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-      <c r="B72" s="10" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B75" s="10" t="s">
         <v>645</v>
       </c>
-      <c r="C72" s="10">
+      <c r="C75" s="10">
         <v>2025</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D75" t="s">
         <v>107</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E75" s="2">
         <v>45749</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="42">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="B73" s="10" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B76" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="C76" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
         <v>108</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E76" s="2">
         <v>45748</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="42">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="B74" s="10" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B77" s="10" t="s">
         <v>647</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C77" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D77" t="s">
         <v>115</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E77" s="2">
         <v>45736</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="42">
-        <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-      <c r="B75" s="10" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B78" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="C78" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" t="s">
         <v>117</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E78" s="2">
         <v>45734</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="42">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-      <c r="B76" s="10" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B79" s="10" t="s">
         <v>649</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" t="s">
+      <c r="C79" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" t="s">
         <v>118</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E79" s="2">
         <v>45726</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="42">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-      <c r="B77" s="10" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B80" s="10" t="s">
         <v>650</v>
       </c>
-      <c r="C77" s="10">
+      <c r="C80" s="10">
         <v>2025</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D80" t="s">
         <v>119</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E80" s="2">
         <v>45726</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="42">
-        <f t="shared" si="1"/>
-        <v>74</v>
-      </c>
-      <c r="B78" s="10" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B81" s="10" t="s">
         <v>651</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="C81" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" t="s">
         <v>120</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E81" s="2">
         <v>45726</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="42">
-        <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="B79" s="10" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B82" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C82" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" t="s">
         <v>122</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E82" s="2">
         <v>45723</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="42">
-        <f t="shared" si="1"/>
-        <v>76</v>
-      </c>
-      <c r="B80" s="10" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B83" s="10" t="s">
         <v>653</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C83" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" t="s">
         <v>123</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E83" s="2">
         <v>45721</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="42">
-        <f t="shared" si="1"/>
-        <v>77</v>
-      </c>
-      <c r="B81" s="10" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B84" s="10" t="s">
         <v>654</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="C84" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D84" t="s">
         <v>126</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E84" s="2">
         <v>45698</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="42">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-      <c r="B82" s="10" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B85" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="C85" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" t="s">
         <v>127</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E85" s="2">
         <v>45695</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="42">
-        <f t="shared" si="1"/>
-        <v>79</v>
-      </c>
-      <c r="B83" s="10" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B86" s="10" t="s">
         <v>656</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="C86" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D86" t="s">
         <v>129</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E86" s="2">
         <v>45694</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="42">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="B84" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B87" t="s">
         <v>587</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="C87" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D87" t="s">
         <v>131</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E87" s="2">
         <v>45692</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="42">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="B85" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B88" t="s">
         <v>586</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C88" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" t="s">
         <v>134</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E88" s="2">
         <v>45686</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="42">
-        <f t="shared" si="1"/>
-        <v>82</v>
-      </c>
-      <c r="B86" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B89" t="s">
         <v>585</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="C89" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" t="s">
         <v>136</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E89" s="2">
         <v>45681</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="42">
-        <f t="shared" si="1"/>
-        <v>83</v>
-      </c>
-      <c r="B87" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B90" t="s">
         <v>584</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="C90" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" t="s">
         <v>137</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E90" s="2">
         <v>45678</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="42">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-      <c r="B88" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B91" t="s">
         <v>583</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="C91" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" t="s">
         <v>139</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E91" s="2">
         <v>45677</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="42">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="B89" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B92" t="s">
         <v>582</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="C92" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" t="s">
         <v>140</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E92" s="2">
         <v>45677</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="42">
-        <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-      <c r="B90" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B93" t="s">
         <v>581</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C93" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" t="s">
         <v>143</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E93" s="2">
         <v>45670</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="42">
-        <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="B91" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B94" t="s">
         <v>580</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C94" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" t="s">
         <v>145</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E94" s="2">
         <v>45661</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="42">
-        <f t="shared" si="1"/>
-        <v>88</v>
-      </c>
-      <c r="B92" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B95" t="s">
         <v>579</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="C95" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" t="s">
         <v>146</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E95" s="2">
         <v>45661</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="42">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B93" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B96" t="s">
         <v>578</v>
       </c>
-      <c r="C93" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C96" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D96" t="s">
         <v>148</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E96" s="2">
         <v>45659</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="42">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="B94" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B97" t="s">
         <v>577</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C97" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" t="s">
         <v>150</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E97" s="2">
         <v>45656</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="42">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="B95" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B98" t="s">
         <v>576</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="C98" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D98" t="s">
         <v>151</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E98" s="2">
         <v>45656</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="42">
-        <f t="shared" si="1"/>
-        <v>92</v>
-      </c>
-      <c r="B96" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B99" t="s">
         <v>575</v>
       </c>
-      <c r="C96" s="10">
+      <c r="C99" s="10">
         <v>2024</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D99" t="s">
         <v>153</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E99" s="2">
         <v>45652</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="42">
-        <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-      <c r="B97" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B100" t="s">
         <v>574</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C100" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D100" t="s">
         <v>119</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E100" s="2">
         <v>45650</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="42">
-        <f t="shared" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="B98" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B101" t="s">
         <v>573</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="C101" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D101" t="s">
         <v>157</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E101" s="2">
         <v>45631</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="42">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="B99" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B102" t="s">
         <v>572</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C102" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D102" t="s">
         <v>158</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E102" s="2">
         <v>45625</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="42">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="B100" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B103" t="s">
         <v>571</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C103" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D103" t="s">
         <v>159</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E103" s="2">
         <v>45622</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="42">
-        <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-      <c r="B101" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B104" t="s">
         <v>570</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C104" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D104" t="s">
         <v>165</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E104" s="2">
         <v>45593</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="42">
-        <f t="shared" si="1"/>
-        <v>98</v>
-      </c>
-      <c r="B102" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B105" t="s">
         <v>569</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="C105" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D105" t="s">
         <v>167</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E105" s="2">
         <v>45588</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="42">
-        <f t="shared" si="1"/>
-        <v>99</v>
-      </c>
-      <c r="B103" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B106" t="s">
         <v>568</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="C106" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" t="s">
         <v>168</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E106" s="2">
         <v>45588</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="42">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="B104" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B107" t="s">
         <v>567</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="C107" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D107" t="s">
         <v>170</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E107" s="2">
         <v>45578</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="42">
-        <f t="shared" si="1"/>
-        <v>101</v>
-      </c>
-      <c r="B105" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B108" t="s">
         <v>566</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="C108" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" t="s">
         <v>172</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E108" s="2">
         <v>45566</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="42">
-        <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
-      <c r="B106" t="s">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B109" t="s">
         <v>565</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C109" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" t="s">
         <v>173</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E109" s="2">
         <v>45566</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="42">
-        <f t="shared" si="1"/>
-        <v>103</v>
-      </c>
-      <c r="B107" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B110" t="s">
         <v>564</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="C110" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D110" t="s">
         <v>174</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E110" s="2">
         <v>45565</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="42">
-        <f t="shared" si="1"/>
-        <v>104</v>
-      </c>
-      <c r="B108" t="s">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B111" t="s">
         <v>563</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C111" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111" t="s">
         <v>175</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E111" s="2">
         <v>45563</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="42">
-        <f t="shared" si="1"/>
-        <v>105</v>
-      </c>
-      <c r="B109" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B112" t="s">
         <v>562</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D109" t="s">
+      <c r="C112" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D112" t="s">
         <v>178</v>
       </c>
-      <c r="E109" s="2">
+      <c r="E112" s="2">
         <v>45553</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="42">
-        <f t="shared" si="1"/>
-        <v>106</v>
-      </c>
-      <c r="B110" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B113" t="s">
         <v>561</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C113" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" t="s">
         <v>119</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E113" s="2">
         <v>45548</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="42">
-        <f t="shared" si="1"/>
-        <v>107</v>
-      </c>
-      <c r="B111" t="s">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B114" t="s">
         <v>560</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="C114" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D114" t="s">
         <v>179</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E114" s="2">
         <v>45548</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="42">
-        <f t="shared" si="1"/>
-        <v>108</v>
-      </c>
-      <c r="B112" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B115" t="s">
         <v>559</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D112" t="s">
+      <c r="C115" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D115" t="s">
         <v>181</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E115" s="2">
         <v>45539</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="42">
-        <f t="shared" si="1"/>
-        <v>109</v>
-      </c>
-      <c r="B113" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="B116" t="s">
         <v>558</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D113" t="s">
+      <c r="C116" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D116" t="s">
         <v>182</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E116" s="2">
         <v>45538</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="42">
-        <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-      <c r="B114" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="B117" t="s">
         <v>557</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="C117" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D117" t="s">
         <v>184</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E117" s="2">
         <v>45537</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="42">
-        <f t="shared" si="1"/>
-        <v>111</v>
-      </c>
-      <c r="B115" t="s">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="B118" t="s">
         <v>556</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="C118" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D118" t="s">
         <v>189</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E118" s="2">
         <v>45523</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="42">
-        <f t="shared" si="1"/>
-        <v>112</v>
-      </c>
-      <c r="B116" t="s">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <f t="shared" si="1"/>
+        <v>115</v>
+      </c>
+      <c r="B119" t="s">
         <v>555</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="C119" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D119" t="s">
         <v>190</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E119" s="2">
         <v>45520</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="42">
-        <f t="shared" si="1"/>
-        <v>113</v>
-      </c>
-      <c r="B117" t="s">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="B120" t="s">
         <v>554</v>
       </c>
-      <c r="C117" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="C120" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D120" t="s">
         <v>192</v>
       </c>
-      <c r="E117" s="2">
+      <c r="E120" s="2">
         <v>45505</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="42">
-        <f t="shared" si="1"/>
-        <v>114</v>
-      </c>
-      <c r="B118" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="B121" t="s">
         <v>553</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D118" t="s">
+      <c r="C121" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D121" t="s">
         <v>193</v>
       </c>
-      <c r="E118" s="2">
+      <c r="E121" s="2">
         <v>45502</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="42">
-        <f t="shared" si="1"/>
-        <v>115</v>
-      </c>
-      <c r="B119" t="s">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <f t="shared" si="1"/>
+        <v>118</v>
+      </c>
+      <c r="B122" t="s">
         <v>552</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D119" t="s">
+      <c r="C122" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D122" t="s">
         <v>197</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E122" s="2">
         <v>45478</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="42">
-        <f t="shared" si="1"/>
-        <v>116</v>
-      </c>
-      <c r="B120" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="B123" t="s">
         <v>551</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D120" t="s">
+      <c r="C123" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D123" t="s">
         <v>198</v>
       </c>
-      <c r="E120" s="2">
+      <c r="E123" s="2">
         <v>45478</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="42">
-        <f t="shared" si="1"/>
-        <v>117</v>
-      </c>
-      <c r="B121" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="B124" t="s">
         <v>550</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D121" t="s">
+      <c r="C124" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D124" t="s">
         <v>201</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E124" s="2">
         <v>45462</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="42">
-        <f t="shared" si="1"/>
-        <v>118</v>
-      </c>
-      <c r="B122" t="s">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <f t="shared" si="1"/>
+        <v>121</v>
+      </c>
+      <c r="B125" t="s">
         <v>204</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="C125" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D125" t="s">
         <v>205</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E125" s="2">
         <v>45455</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="42">
-        <f t="shared" si="1"/>
-        <v>119</v>
-      </c>
-      <c r="B123" t="s">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
+      <c r="B126" t="s">
         <v>549</v>
       </c>
-      <c r="C123" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="C126" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D126" t="s">
         <v>207</v>
       </c>
-      <c r="E123" s="2">
+      <c r="E126" s="2">
         <v>45454</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="42">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="B124" t="s">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <f t="shared" si="1"/>
+        <v>123</v>
+      </c>
+      <c r="B127" t="s">
         <v>548</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D124" t="s">
+      <c r="C127" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D127" t="s">
         <v>208</v>
       </c>
-      <c r="E124" s="2">
+      <c r="E127" s="2">
         <v>45449</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="42">
-        <f t="shared" si="1"/>
-        <v>121</v>
-      </c>
-      <c r="B125" t="s">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <f t="shared" si="1"/>
+        <v>124</v>
+      </c>
+      <c r="B128" t="s">
         <v>547</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D125" t="s">
+      <c r="C128" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D128" t="s">
         <v>210</v>
       </c>
-      <c r="E125" s="2">
+      <c r="E128" s="2">
         <v>45448</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="42">
-        <f t="shared" si="1"/>
-        <v>122</v>
-      </c>
-      <c r="B126" t="s">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <f t="shared" si="1"/>
+        <v>125</v>
+      </c>
+      <c r="B129" t="s">
         <v>546</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D126" t="s">
+      <c r="C129" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D129" t="s">
         <v>211</v>
       </c>
-      <c r="E126" s="2">
+      <c r="E129" s="2">
         <v>45446</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="42">
-        <f t="shared" si="1"/>
-        <v>123</v>
-      </c>
-      <c r="B127" t="s">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <f t="shared" si="1"/>
+        <v>126</v>
+      </c>
+      <c r="B130" t="s">
         <v>545</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D127" t="s">
+      <c r="C130" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D130" t="s">
         <v>216</v>
       </c>
-      <c r="E127" s="2">
+      <c r="E130" s="2">
         <v>45432</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="42">
-        <f t="shared" si="1"/>
-        <v>124</v>
-      </c>
-      <c r="B128" t="s">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <f t="shared" si="1"/>
+        <v>127</v>
+      </c>
+      <c r="B131" t="s">
         <v>544</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="C131" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D131" t="s">
         <v>218</v>
       </c>
-      <c r="E128" s="2">
+      <c r="E131" s="2">
         <v>45420</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="42">
-        <f t="shared" si="1"/>
-        <v>125</v>
-      </c>
-      <c r="B129" t="s">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <f t="shared" si="1"/>
+        <v>128</v>
+      </c>
+      <c r="B132" t="s">
         <v>543</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="C132" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D132" t="s">
         <v>219</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E132" s="2">
         <v>45418</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="42">
-        <f t="shared" si="1"/>
-        <v>126</v>
-      </c>
-      <c r="B130" t="s">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <f t="shared" si="1"/>
+        <v>129</v>
+      </c>
+      <c r="B133" t="s">
         <v>542</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D130" t="s">
+      <c r="C133" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D133" t="s">
         <v>220</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E133" s="2">
         <v>45416</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="42">
-        <f t="shared" si="1"/>
-        <v>127</v>
-      </c>
-      <c r="B131" t="s">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <f t="shared" si="1"/>
+        <v>130</v>
+      </c>
+      <c r="B134" t="s">
         <v>541</v>
       </c>
-      <c r="C131" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="C134" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D134" t="s">
         <v>224</v>
       </c>
-      <c r="E131" s="2">
+      <c r="E134" s="2">
         <v>45407</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="42">
-        <f t="shared" si="1"/>
-        <v>128</v>
-      </c>
-      <c r="B132" s="6" t="s">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <f t="shared" si="1"/>
+        <v>131</v>
+      </c>
+      <c r="B135" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="C132" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="C135" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D135" t="s">
         <v>225</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E135" s="2">
         <v>45405</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="42">
-        <f t="shared" ref="A133:A167" si="2">ROW()-4</f>
-        <v>129</v>
-      </c>
-      <c r="B133" s="6" t="s">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <f t="shared" ref="A136:A170" si="2">ROW()-4</f>
+        <v>132</v>
+      </c>
+      <c r="B136" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="C133" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D133" t="s">
+      <c r="C136" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D136" t="s">
         <v>226</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E136" s="2">
         <v>45397</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="42">
-        <f t="shared" si="2"/>
-        <v>130</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D134" t="s">
-        <v>227</v>
-      </c>
-      <c r="E134" s="2">
-        <v>45397</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="42">
-        <f t="shared" si="2"/>
-        <v>131</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="C135" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D135" t="s">
-        <v>230</v>
-      </c>
-      <c r="E135" s="2">
-        <v>45387</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="42">
-        <f t="shared" si="2"/>
-        <v>132</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>537</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D136" t="s">
-        <v>231</v>
-      </c>
-      <c r="E136" s="2">
-        <v>45387</v>
-      </c>
-    </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="42">
+      <c r="A137">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E137" s="2">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="42">
+      <c r="A138">
         <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E138" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="42">
+      <c r="A139">
         <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E139" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A140" s="42">
+      <c r="A140">
         <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="C140" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E140" s="2">
-        <v>45378</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141" s="42">
+      <c r="A141">
         <f t="shared" si="2"/>
         <v>137</v>
       </c>
-      <c r="B141" t="s">
-        <v>533</v>
+      <c r="B141" s="6" t="s">
+        <v>505</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E141" s="2">
-        <v>45373</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A142" s="42">
+      <c r="A142">
         <f t="shared" si="2"/>
         <v>138</v>
       </c>
-      <c r="B142" t="s">
-        <v>532</v>
+      <c r="B142" s="6" t="s">
+        <v>534</v>
       </c>
       <c r="C142" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E142" s="2">
-        <v>45373</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143" s="42">
+      <c r="A143">
         <f t="shared" si="2"/>
         <v>139</v>
       </c>
-      <c r="B143" t="s">
-        <v>531</v>
+      <c r="B143" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D143" t="s">
-        <v>117</v>
+        <v>237</v>
       </c>
       <c r="E143" s="2">
-        <v>45369</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A144" s="42">
+      <c r="A144">
         <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D144" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E144" s="2">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145" s="42">
+      <c r="A145">
         <f t="shared" si="2"/>
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D145" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E145" s="2">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A146" s="42">
+      <c r="A146">
         <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D146" t="s">
-        <v>244</v>
+        <v>117</v>
       </c>
       <c r="E146" s="2">
-        <v>45366</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147" s="42">
+      <c r="A147">
         <f t="shared" si="2"/>
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D147" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E147" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A148" s="42">
+      <c r="A148">
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D148" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E148" s="2">
-        <v>45362</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149" s="42">
+      <c r="A149">
         <f t="shared" si="2"/>
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D149" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E149" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A150" s="42">
+      <c r="A150">
         <f t="shared" si="2"/>
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D150" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E150" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151" s="42">
+      <c r="A151">
         <f t="shared" si="2"/>
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D151" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E151" s="2">
         <v>45362</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A152" s="42">
+      <c r="A152">
         <f t="shared" si="2"/>
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D152" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E152" s="2">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153" s="42">
+      <c r="A153">
         <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D153" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E153" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A154" s="42">
+      <c r="A154">
         <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D154" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E154" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155" s="42">
+      <c r="A155">
         <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D155" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E155" s="2">
-        <v>45357</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A156" s="42">
+      <c r="A156">
         <f t="shared" si="2"/>
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D156" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E156" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157" s="42">
+      <c r="A157">
         <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D157" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="E157" s="2">
-        <v>45352</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A158" s="42">
+      <c r="A158">
         <f t="shared" si="2"/>
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D158" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="E158" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159" s="42">
+      <c r="A159">
         <f t="shared" si="2"/>
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E159" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="42">
+      <c r="A160">
         <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D160" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="E160" s="2">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="42">
+      <c r="A161">
         <f t="shared" si="2"/>
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D161" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="E161" s="2">
-        <v>45345</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="42">
+      <c r="A162">
         <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E162" s="2">
-        <v>45335</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="42">
+      <c r="A163">
         <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E163" s="2">
-        <v>45334</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="42">
+      <c r="A164">
         <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="E164" s="2">
-        <v>45314</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="42">
+      <c r="A165">
         <f t="shared" si="2"/>
         <v>161</v>
       </c>
-      <c r="B165" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C165" s="10">
-        <v>2023</v>
+      <c r="B165" t="s">
+        <v>507</v>
+      </c>
+      <c r="C165" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D165" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E165" s="2">
-        <v>45306</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="42">
+      <c r="A166">
         <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E166" s="2">
-        <v>45294</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="42">
+      <c r="A167">
         <f t="shared" si="2"/>
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
+        <v>276</v>
+      </c>
+      <c r="E167" s="2">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <f t="shared" si="2"/>
+        <v>164</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C168" s="10">
+        <v>2023</v>
+      </c>
+      <c r="D168" t="s">
+        <v>277</v>
+      </c>
+      <c r="E168" s="2">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <f t="shared" si="2"/>
+        <v>165</v>
+      </c>
+      <c r="B169" t="s">
+        <v>509</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D169" t="s">
+        <v>279</v>
+      </c>
+      <c r="E169" s="2">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <f t="shared" si="2"/>
+        <v>166</v>
+      </c>
+      <c r="B170" t="s">
+        <v>508</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D170" t="s">
         <v>281</v>
       </c>
-      <c r="E167" s="2">
+      <c r="E170" s="2">
         <v>45292</v>
       </c>
     </row>
@@ -9878,21 +9972,13 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="45"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="45"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="43">
+      <c r="A7" s="26">
         <f>ROW()-6</f>
         <v>1</v>
       </c>
@@ -9910,7 +9996,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="43">
+      <c r="A8" s="26">
         <f t="shared" ref="A8:A71" si="0">ROW()-6</f>
         <v>2</v>
       </c>
@@ -9932,7 +10018,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43">
+      <c r="A9" s="26">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -9951,7 +10037,7 @@
       <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="43">
+      <c r="A10" s="26">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -9972,7 +10058,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="43">
+      <c r="A11" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -9990,7 +10076,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="43">
+      <c r="A12" s="26">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -10008,7 +10094,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43">
+      <c r="A13" s="26">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -10026,7 +10112,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="43">
+      <c r="A14" s="26">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -10044,7 +10130,7 @@
       </c>
     </row>
     <row r="15" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43">
+      <c r="A15" s="26">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -10062,7 +10148,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="43">
+      <c r="A16" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -10080,7 +10166,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="43">
+      <c r="A17" s="26">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -10098,7 +10184,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="43">
+      <c r="A18" s="26">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -10116,7 +10202,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43">
+      <c r="A19" s="26">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -10134,7 +10220,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="43">
+      <c r="A20" s="26">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -10155,7 +10241,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="43">
+      <c r="A21" s="26">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -10173,7 +10259,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="43">
+      <c r="A22" s="26">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -10191,7 +10277,7 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="43">
+      <c r="A23" s="26">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -10209,7 +10295,7 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="43">
+      <c r="A24" s="26">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -10227,7 +10313,7 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="43">
+      <c r="A25" s="26">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -10245,7 +10331,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="43">
+      <c r="A26" s="26">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -10263,7 +10349,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="43">
+      <c r="A27" s="26">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -10281,7 +10367,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="43">
+      <c r="A28" s="26">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -10299,7 +10385,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="43">
+      <c r="A29" s="26">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -10317,7 +10403,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="43">
+      <c r="A30" s="26">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -10335,7 +10421,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="43">
+      <c r="A31" s="26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -10353,7 +10439,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="43">
+      <c r="A32" s="26">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -10371,7 +10457,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="43">
+      <c r="A33" s="26">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -10389,7 +10475,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="43">
+      <c r="A34" s="26">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -10407,7 +10493,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="43">
+      <c r="A35" s="26">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -10425,7 +10511,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="43">
+      <c r="A36" s="26">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -10443,7 +10529,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="43">
+      <c r="A37" s="26">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -10461,7 +10547,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="43">
+      <c r="A38" s="26">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -10479,7 +10565,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="43">
+      <c r="A39" s="26">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -10497,7 +10583,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="43">
+      <c r="A40" s="26">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -10515,7 +10601,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="43">
+      <c r="A41" s="26">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -10533,7 +10619,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="43">
+      <c r="A42" s="26">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -10551,7 +10637,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="43">
+      <c r="A43" s="26">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -10569,7 +10655,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="43">
+      <c r="A44" s="26">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -10587,7 +10673,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="43">
+      <c r="A45" s="26">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -10605,7 +10691,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="43">
+      <c r="A46" s="26">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -10623,7 +10709,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="43">
+      <c r="A47" s="26">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -10641,7 +10727,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="43">
+      <c r="A48" s="26">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -10659,7 +10745,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="43">
+      <c r="A49" s="26">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -10677,7 +10763,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="43">
+      <c r="A50" s="26">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -10695,7 +10781,7 @@
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="43">
+      <c r="A51" s="26">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -10713,7 +10799,7 @@
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="43">
+      <c r="A52" s="26">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -10731,7 +10817,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="43">
+      <c r="A53" s="26">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
@@ -10749,7 +10835,7 @@
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="43">
+      <c r="A54" s="26">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -10767,7 +10853,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="43">
+      <c r="A55" s="26">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -10785,7 +10871,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="43">
+      <c r="A56" s="26">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -10803,7 +10889,7 @@
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="43">
+      <c r="A57" s="26">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
@@ -10821,7 +10907,7 @@
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="43">
+      <c r="A58" s="26">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -10839,7 +10925,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="43">
+      <c r="A59" s="26">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
@@ -10857,7 +10943,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="43">
+      <c r="A60" s="26">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -10875,7 +10961,7 @@
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="43">
+      <c r="A61" s="26">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
@@ -10893,7 +10979,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="43">
+      <c r="A62" s="26">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
@@ -10911,7 +10997,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="43">
+      <c r="A63" s="26">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -10929,7 +11015,7 @@
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="43">
+      <c r="A64" s="26">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
@@ -10947,7 +11033,7 @@
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="43">
+      <c r="A65" s="26">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
@@ -10965,7 +11051,7 @@
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="43">
+      <c r="A66" s="26">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -10983,7 +11069,7 @@
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="43">
+      <c r="A67" s="26">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
@@ -11001,7 +11087,7 @@
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="43">
+      <c r="A68" s="26">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
@@ -11019,7 +11105,7 @@
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="43">
+      <c r="A69" s="26">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
@@ -11037,7 +11123,7 @@
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="43">
+      <c r="A70" s="26">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
@@ -11055,7 +11141,7 @@
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="43">
+      <c r="A71" s="26">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
@@ -11073,7 +11159,7 @@
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="43">
+      <c r="A72" s="26">
         <f t="shared" ref="A72:A78" si="1">ROW()-6</f>
         <v>66</v>
       </c>
@@ -11091,7 +11177,7 @@
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="43">
+      <c r="A73" s="26">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
@@ -11109,7 +11195,7 @@
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="43">
+      <c r="A74" s="26">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -11127,7 +11213,7 @@
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="43">
+      <c r="A75" s="26">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -11145,7 +11231,7 @@
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="43">
+      <c r="A76" s="26">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
@@ -11163,7 +11249,7 @@
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="43">
+      <c r="A77" s="26">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
@@ -11181,7 +11267,7 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="43">
+      <c r="A78" s="26">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7EC5E5-538C-47DC-A515-7784204D6236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A6A7BD-50D7-489B-97DD-B4E6BC8686EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="817">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2432,6 +2432,57 @@
   </si>
   <si>
     <t>Restoration of RoDTEP rates - reg</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 74/2025-26</t>
+  </si>
+  <si>
+    <t>Continuation of RoDTEP Scheme beyond March 31, 2026</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 73/2025-26</t>
+  </si>
+  <si>
+    <t>Amendment to Paragraph 4.43 of the Foreign Trade Policy (FTP) 2023 -One-time relaxation for the Gems and Jewellery Sector.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 72/2025-26</t>
+  </si>
+  <si>
+    <t>Extension in “Free” Import Policy of Tur/Pigeon Peas (Cajanus Cajan) [ITC (HS) 0713 60 00] under ITC (HS) 2022, Schedule – I (Import Policy) till 31.03.2027</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 71/2025-26</t>
+  </si>
+  <si>
+    <t>Extension in “Free” Import Policy of Urad ([Beans of SPP Vigna Mungo (L.) Hepper]) [ITC (HS) Code 07133110] under ITC (HS) 2022, Schedule –I(Import Policy) till 31.03.2027</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 70/2025-26</t>
+  </si>
+  <si>
+    <t>Extension in Import period for Yellow Peas under ITC (HS) code 07131010 of Chapter 07 of ITC (HS) 2022, Schedule-1 (Import Policy)</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 69/2025-26</t>
+  </si>
+  <si>
+    <t>Extension in Minimum Import Price (MIP) Condition of specific items covered under Chapter 48 of ITC HS, 2022, Schedule -I (Import Policy)</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 54/2025-2026</t>
+  </si>
+  <si>
+    <t>Policy Support and Relaxation Measures for the Gem &amp; Jewellery sector under Chapter 4 of FTP-2023</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 34/2025-2026</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
+  </si>
+  <si>
+    <t>Special drive for expeditious issuance of EODCs under Advance Authorisation (AA) and EPCG schemes - extension up to May 31 ,2026</t>
   </si>
 </sst>
 </file>
@@ -2508,7 +2559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2608,15 +2659,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2897,7 +2939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O370"/>
+  <dimension ref="A1:O371"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
@@ -2937,1267 +2979,1266 @@
       <c r="A5" s="42">
         <v>1</v>
       </c>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="27" t="s">
+        <v>812</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>813</v>
+      </c>
+      <c r="E5" s="32">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="42">
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>792</v>
       </c>
-      <c r="C5" s="45">
+      <c r="C6" s="31">
         <v>2025</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D6" s="33" t="s">
         <v>793</v>
       </c>
-      <c r="E5" s="46">
+      <c r="E6" s="32">
         <v>46105</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <f t="shared" ref="A6:A7" si="0">ROW()-4</f>
-        <v>2</v>
-      </c>
-      <c r="B6" s="27" t="s">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="42">
+        <f t="shared" ref="A7:A8" si="0">ROW()-4</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>787</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="33" t="s">
+      <c r="C7" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="33" t="s">
         <v>788</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E7" s="32">
         <v>46101</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B7" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="C8" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>779</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E8" s="32">
         <v>46087</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
+    <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="42">
         <f>ROW()-4</f>
-        <v>4</v>
-      </c>
-      <c r="B8" s="40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>780</v>
       </c>
-      <c r="C8" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="40" t="s">
+      <c r="C9" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="40" t="s">
         <v>779</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E9" s="41">
         <v>46087</v>
       </c>
-      <c r="F8" s="39"/>
-    </row>
-    <row r="9" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <f t="shared" ref="A9:A72" si="1">ROW()-4</f>
-        <v>5</v>
-      </c>
-      <c r="B9" s="27" t="s">
+      <c r="F9" s="39"/>
+    </row>
+    <row r="10" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <f t="shared" ref="A10:A73" si="1">ROW()-4</f>
+        <v>6</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>754</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="C10" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="33" t="s">
         <v>755</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>757</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>758</v>
       </c>
       <c r="E10" s="34" t="s">
         <v>756</v>
       </c>
-      <c r="O10" s="27" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="11" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+      <c r="A11" s="42">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
+      <c r="O11" s="27" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="42">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B12" t="s">
-        <v>386</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E12" s="2">
-        <v>46328</v>
+      <c r="B12" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>760</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
+      <c r="A13" s="42">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>4</v>
+        <v>382</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E13" s="2">
-        <v>46144</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="A14" s="42">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D14" t="s">
-        <v>5</v>
+      <c r="D14" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="E14" s="2">
-        <v>46045</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="A15" s="42">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E15" s="2">
-        <v>46038</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="A16" s="42">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>390</v>
-      </c>
-      <c r="C16" s="10">
-        <v>2026</v>
+        <v>389</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2">
-        <v>46031</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+      <c r="A17" s="42">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C17" s="10">
         <v>2026</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2">
         <v>46031</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
+      <c r="A18" s="42">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C18" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2">
-        <v>46022</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+      <c r="A19" s="42">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>393</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>4</v>
+        <v>392</v>
+      </c>
+      <c r="C19" s="10">
+        <v>2025</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2">
-        <v>46010</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
+      <c r="A20" s="42">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E20" s="2">
-        <v>46008</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
+      <c r="A21" s="42">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2">
         <v>46008</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
+      <c r="A22" s="42">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>374</v>
+        <v>19</v>
       </c>
       <c r="E22" s="2">
-        <v>46002</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
+      <c r="A23" s="42">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>397</v>
-      </c>
-      <c r="C23" s="10">
-        <v>2025</v>
+        <v>396</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="E23" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="A24" s="42">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C24" s="10">
         <v>2025</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2">
         <v>46001</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25" s="42">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>399</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>4</v>
+        <v>398</v>
+      </c>
+      <c r="C25" s="10">
+        <v>2025</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="A26" s="42">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" s="2">
         <v>45992</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27" s="42">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>401</v>
-      </c>
-      <c r="C27" s="10">
-        <v>2025</v>
+        <v>400</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28" s="42">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>402</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2025</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="E28" s="2">
-        <v>45959</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="A29" s="42">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>403</v>
-      </c>
-      <c r="C29" s="10">
-        <v>2025</v>
+        <v>402</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E29" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="A30" s="42">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C30" s="10">
         <v>2025</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E30" s="2">
         <v>45958</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31" s="42">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>405</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>8</v>
+        <v>404</v>
+      </c>
+      <c r="C31" s="10">
+        <v>2025</v>
       </c>
       <c r="D31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E31" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="A32" s="42">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E32" s="2">
-        <v>45952</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="A33" s="42">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E33" s="2">
-        <v>45945</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1">
+      <c r="A34" s="42">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1">
+      <c r="A35" s="42">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2">
         <v>45940</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1">
+      <c r="A36" s="42">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E36" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1">
+      <c r="A37" s="42">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E37" s="2">
-        <v>45931</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1">
+      <c r="A38" s="42">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E38" s="2">
-        <v>45909</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1">
+      <c r="A39" s="42">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E39" s="2">
-        <v>45903</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1">
+      <c r="A40" s="42">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>413</v>
-      </c>
-      <c r="C40" s="10">
-        <v>2025</v>
+        <v>412</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E40" s="2">
-        <v>45895</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1">
+      <c r="A41" s="42">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>414</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C41" s="10">
+        <v>2025</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E41" s="2">
-        <v>45891</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1">
+      <c r="A42" s="42">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E42" s="2">
-        <v>45870</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1">
+      <c r="A43" s="42">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>416</v>
-      </c>
-      <c r="C43" s="10">
-        <v>2025</v>
+        <v>415</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" s="2">
-        <v>45868</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1">
+      <c r="A44" s="42">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>417</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C44" s="10">
+        <v>2025</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2">
-        <v>45867</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1">
+      <c r="A45" s="42">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E45" s="2">
-        <v>45860</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1">
+      <c r="A46" s="42">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2">
-        <v>45846</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
+      <c r="A47" s="42">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E47" s="2">
-        <v>45833</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1">
+      <c r="A48" s="42">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E48" s="2">
         <v>45833</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1">
+      <c r="A49" s="42">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E49" s="2">
-        <v>45820</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1">
+      <c r="A50" s="42">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1">
+      <c r="A51" s="42">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2">
-        <v>45818</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1">
+      <c r="A52" s="42">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>425</v>
-      </c>
-      <c r="C52" s="10">
-        <v>2025</v>
+        <v>424</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2">
-        <v>45807</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1">
+      <c r="A53" s="42">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>426</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C53" s="10">
+        <v>2025</v>
       </c>
       <c r="D53" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E53" s="2">
-        <v>45793</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1">
+      <c r="A54" s="42">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E54" s="2">
-        <v>45784</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1">
+      <c r="A55" s="42">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E55" s="2">
-        <v>45783</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1">
+      <c r="A56" s="42">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E56" s="2">
         <v>45783</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1">
+      <c r="A57" s="42">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E57" s="2">
-        <v>45771</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1">
+      <c r="A58" s="42">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E58" s="2">
-        <v>45762</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1">
+      <c r="A59" s="42">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E59" s="2">
-        <v>45750</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1">
+      <c r="A60" s="42">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>433</v>
-      </c>
-      <c r="C60" s="10">
-        <v>2025</v>
+        <v>432</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E60" s="2">
-        <v>45744</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1">
+      <c r="A61" s="42">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>4</v>
+        <v>433</v>
+      </c>
+      <c r="C61" s="10">
+        <v>2025</v>
       </c>
       <c r="D61" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E61" s="2">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1">
+      <c r="A62" s="42">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>434</v>
+        <v>110</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E62" s="2">
         <v>45743</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1">
+      <c r="A63" s="42">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D63" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E63" s="2">
-        <v>45735</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1">
+      <c r="A64" s="42">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D64" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E64" s="2">
-        <v>45726</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1">
+      <c r="A65" s="42">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D65" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E65" s="2">
-        <v>45719</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1">
+      <c r="A66" s="42">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D66" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E66" s="2">
-        <v>45700</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1">
+      <c r="A67" s="42">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D67" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E67" s="2">
-        <v>45695</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1">
+      <c r="A68" s="42">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E68" s="2">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1">
+      <c r="A69" s="42">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D69" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E69" s="2">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1">
+      <c r="A70" s="42">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E70" s="2">
-        <v>45688</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1">
+      <c r="A71" s="42">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E71" s="2">
-        <v>45684</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1">
+      <c r="A72" s="42">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B72" t="s">
+        <v>443</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" t="s">
+        <v>135</v>
+      </c>
+      <c r="E72" s="2">
+        <v>45684</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="42">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
         <v>444</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C73" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" t="s">
         <v>138</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E73" s="2">
         <v>45678</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1">
-        <f t="shared" ref="A73:A136" si="2">ROW()-4</f>
-        <v>69</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="42">
+        <f t="shared" ref="A74:A137" si="2">ROW()-4</f>
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
         <v>445</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="C74" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" t="s">
         <v>141</v>
-      </c>
-      <c r="E73" s="2">
-        <v>45672</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1">
-        <f t="shared" si="2"/>
-        <v>70</v>
-      </c>
-      <c r="B74" t="s">
-        <v>446</v>
-      </c>
-      <c r="C74" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" t="s">
-        <v>142</v>
       </c>
       <c r="E74" s="2">
         <v>45672</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1">
+      <c r="A75" s="42">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
@@ -4215,1123 +4256,1138 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1">
+      <c r="A76" s="42">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E76" s="2">
-        <v>45662</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1">
+      <c r="A77" s="42">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E77" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1">
+      <c r="A78" s="42">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E78" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1">
+      <c r="A79" s="42">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>450</v>
-      </c>
-      <c r="C79" s="10">
-        <v>2024</v>
+        <v>449</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D79" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E79" s="2">
-        <v>45653</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+      <c r="A80" s="42">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C80" s="10">
         <v>2024</v>
       </c>
       <c r="D80" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E80" s="2">
-        <v>45650</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
+      <c r="A81" s="42">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>452</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>114</v>
+        <v>451</v>
+      </c>
+      <c r="C81" s="10">
+        <v>2024</v>
       </c>
       <c r="D81" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E81" s="2">
-        <v>45643</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
+      <c r="A82" s="42">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>284</v>
+        <v>452</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E82" s="2">
-        <v>45639</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
+      <c r="A83" s="42">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>453</v>
+        <v>284</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E83" s="2">
-        <v>45610</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
+      <c r="A84" s="42">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E84" s="2">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
+      <c r="A85" s="42">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>455</v>
-      </c>
-      <c r="C85" s="10">
-        <v>2024</v>
+        <v>454</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D85" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E85" s="2">
-        <v>45601</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
+      <c r="A86" s="42">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>456</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C86" s="10">
+        <v>2024</v>
       </c>
       <c r="D86" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E86" s="2">
-        <v>45597</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
+      <c r="A87" s="42">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E87" s="2">
         <v>45597</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
+      <c r="A88" s="42">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E88" s="2">
-        <v>45593</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
+      <c r="A89" s="42">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E89" s="2">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
+      <c r="A90" s="42">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E90" s="2">
-        <v>45572</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
+      <c r="A91" s="42">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E91" s="2">
-        <v>45562</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
+      <c r="A92" s="42">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E92" s="2">
-        <v>45555</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
+      <c r="A93" s="42">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>463</v>
-      </c>
-      <c r="C93" s="10">
-        <v>2024</v>
+        <v>462</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E93" s="2">
-        <v>45547</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
+      <c r="A94" s="42">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>464</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>114</v>
+        <v>463</v>
+      </c>
+      <c r="C94" s="10">
+        <v>2024</v>
       </c>
       <c r="D94" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E94" s="2">
-        <v>45538</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
+      <c r="A95" s="42">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E95" s="2">
-        <v>45534</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
+      <c r="A96" s="42">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E96" s="2">
-        <v>45533</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
+      <c r="A97" s="42">
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D97" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E97" s="2">
         <v>45533</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
+      <c r="A98" s="42">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>468</v>
-      </c>
-      <c r="C98" s="10">
-        <v>2024</v>
+        <v>467</v>
+      </c>
+      <c r="C98" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E98" s="2">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
+      <c r="A99" s="42">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C99" s="10">
         <v>2024</v>
       </c>
       <c r="D99" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E99" s="2">
-        <v>45518</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
+      <c r="A100" s="42">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>470</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C100" s="10">
+        <v>2024</v>
       </c>
       <c r="D100" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E100" s="2">
-        <v>45502</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
+      <c r="A101" s="42">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E101" s="2">
-        <v>45498</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
+      <c r="A102" s="42">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E102" s="2">
-        <v>45489</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
+      <c r="A103" s="42">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E103" s="2">
-        <v>45469</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
+      <c r="A104" s="42">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E104" s="2">
         <v>45469</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
+      <c r="A105" s="42">
         <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>202</v>
+        <v>474</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E105" s="2">
-        <v>45455</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
+      <c r="A106" s="42">
         <f t="shared" si="2"/>
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>475</v>
+        <v>202</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E106" s="2">
         <v>45455</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
+      <c r="A107" s="42">
         <f t="shared" si="2"/>
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="E107" s="2">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
+      <c r="A108" s="42">
         <f t="shared" si="2"/>
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>477</v>
-      </c>
-      <c r="C108" s="10">
-        <v>2024</v>
+        <v>476</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E108" s="2">
         <v>45449</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
+      <c r="A109" s="42">
         <f t="shared" si="2"/>
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>478</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>114</v>
+        <v>477</v>
+      </c>
+      <c r="C109" s="10">
+        <v>2024</v>
       </c>
       <c r="D109" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E109" s="2">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
+      <c r="A110" s="42">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E110" s="2">
-        <v>45441</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
+      <c r="A111" s="42">
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E111" s="2">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
+      <c r="A112" s="42">
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D112" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E112" s="2">
-        <v>45439</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
+      <c r="A113" s="42">
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D113" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E113" s="2">
-        <v>45422</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
+      <c r="A114" s="42">
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E114" s="2">
-        <v>45415</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
+      <c r="A115" s="42">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>285</v>
+        <v>483</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E115" s="2">
-        <v>45411</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
+      <c r="A116" s="42">
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>484</v>
+        <v>285</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E116" s="2">
-        <v>45391</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
+      <c r="A117" s="42">
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E117" s="2">
         <v>45391</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
+      <c r="A118" s="42">
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="E118" s="2">
-        <v>45379</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="1">
+      <c r="A119" s="42">
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D119" t="s">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="E119" s="2">
-        <v>45378</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="1">
+      <c r="A120" s="42">
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D120" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E120" s="2">
         <v>45378</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="1">
+      <c r="A121" s="42">
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D121" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E121" s="2">
-        <v>45365</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="1">
+      <c r="A122" s="42">
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D122" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E122" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="1">
+      <c r="A123" s="42">
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D123" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E123" s="2">
         <v>45362</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="1">
+      <c r="A124" s="42">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D124" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E124" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="1">
+      <c r="A125" s="42">
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D125" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E125" s="2">
         <v>45358</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="1">
+      <c r="A126" s="42">
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D126" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E126" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="1">
+      <c r="A127" s="42">
         <f t="shared" si="2"/>
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D127" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E127" s="2">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="1">
+      <c r="A128" s="42">
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E128" s="2">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="1">
+      <c r="A129" s="42">
         <f t="shared" si="2"/>
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D129" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E129" s="2">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="1">
+      <c r="A130" s="42">
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D130" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E130" s="2">
         <v>45336</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="1">
+      <c r="A131" s="42">
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D131" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E131" s="2">
         <v>45336</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="1">
+      <c r="A132" s="42">
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E132" s="2">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="1">
+      <c r="A133" s="42">
         <f t="shared" si="2"/>
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E133" s="2">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="1">
+      <c r="A134" s="42">
         <f t="shared" si="2"/>
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E134" s="2">
-        <v>45324</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="1">
+      <c r="A135" s="42">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>493</v>
-      </c>
-      <c r="C135" s="10">
-        <v>2024</v>
+        <v>494</v>
+      </c>
+      <c r="C135" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D135" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E135" s="2">
-        <v>45322</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="1">
+      <c r="A136" s="42">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C136" s="10">
         <v>2024</v>
       </c>
       <c r="D136" t="s">
+        <v>275</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="42">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+      <c r="B137" t="s">
+        <v>492</v>
+      </c>
+      <c r="C137" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D137" t="s">
         <v>278</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E137" s="2">
         <v>45303</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="1">
-        <f t="shared" ref="A137" si="3">ROW()-4</f>
-        <v>133</v>
-      </c>
-      <c r="B137" t="s">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="42">
+        <f t="shared" ref="A138" si="3">ROW()-4</f>
+        <v>134</v>
+      </c>
+      <c r="B138" t="s">
         <v>491</v>
       </c>
-      <c r="C137" s="10" t="s">
+      <c r="C138" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D138" t="s">
         <v>280</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E138" s="2">
         <v>45294</v>
       </c>
-    </row>
-    <row r="292" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B292" s="3"/>
     </row>
     <row r="293" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B293" s="3"/>
@@ -5345,17 +5401,17 @@
     <row r="296" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B296" s="3"/>
     </row>
-    <row r="299" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B299" s="3"/>
-    </row>
-    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B304" s="3"/>
-    </row>
-    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B307" s="3"/>
-    </row>
-    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B309" s="3"/>
+    <row r="297" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B297" s="3"/>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B300" s="3"/>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B305" s="3"/>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B308" s="3"/>
     </row>
     <row r="310" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B310" s="3"/>
@@ -5363,8 +5419,8 @@
     <row r="311" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B311" s="3"/>
     </row>
-    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B313" s="3"/>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B312" s="3"/>
     </row>
     <row r="314" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B314" s="3"/>
@@ -5378,15 +5434,18 @@
     <row r="317" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B317" s="3"/>
     </row>
-    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B319" s="3"/>
-    </row>
-    <row r="370" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B370" s="3"/>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B318" s="3"/>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B320" s="3"/>
+    </row>
+    <row r="371" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B371" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:E135">
-    <sortCondition descending="1" sortBy="icon" ref="E12:E135"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:E136">
+    <sortCondition descending="1" sortBy="icon" ref="E13:E136"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5395,7 +5454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5426,2988 +5485,2927 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="44" t="s">
-        <v>794</v>
-      </c>
-      <c r="C5" s="45">
+      <c r="B5" s="27" t="s">
+        <v>800</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>801</v>
+      </c>
+      <c r="E5" s="32">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>802</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>803</v>
+      </c>
+      <c r="E6" s="32">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>804</v>
+      </c>
+      <c r="C7" s="31">
         <v>2026</v>
       </c>
-      <c r="D5" s="44" t="s">
-        <v>795</v>
-      </c>
-      <c r="E5" s="46">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43">
-        <v>2</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>796</v>
-      </c>
-      <c r="C6" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>797</v>
-      </c>
-      <c r="E6" s="46">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" s="43" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43">
-        <v>3</v>
-      </c>
-      <c r="B7" s="44" t="s">
-        <v>798</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>799</v>
-      </c>
-      <c r="E7" s="46">
-        <v>46104</v>
+      <c r="D7" s="27" t="s">
+        <v>805</v>
+      </c>
+      <c r="E7" s="32">
+        <v>46112</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" ref="A8:A71" si="0">ROW()-4</f>
         <v>4</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>781</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>4</v>
+        <v>806</v>
+      </c>
+      <c r="C8" s="31">
+        <v>2026</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>782</v>
-      </c>
-      <c r="E8" s="34">
-        <v>46100</v>
+        <v>807</v>
+      </c>
+      <c r="E8" s="32">
+        <v>46112</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>783</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>4</v>
+        <v>808</v>
+      </c>
+      <c r="C9" s="31">
+        <v>2026</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>784</v>
-      </c>
-      <c r="E9" s="34">
-        <v>46099</v>
+        <v>809</v>
+      </c>
+      <c r="E9" s="32">
+        <v>46112</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>785</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>4</v>
+        <v>810</v>
+      </c>
+      <c r="C10" s="31">
+        <v>2026</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>786</v>
-      </c>
-      <c r="E10" s="34">
-        <v>46097</v>
+        <v>811</v>
+      </c>
+      <c r="E10" s="32">
+        <v>46112</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>761</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>4</v>
+        <v>794</v>
+      </c>
+      <c r="C11" s="31">
+        <v>2026</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>762</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>756</v>
+        <v>795</v>
+      </c>
+      <c r="E11" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>764</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>756</v>
+        <v>797</v>
+      </c>
+      <c r="E12" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>765</v>
+        <v>798</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>766</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>756</v>
+        <v>799</v>
+      </c>
+      <c r="E13" s="32">
+        <v>46104</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>767</v>
+        <v>781</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>768</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>769</v>
+        <v>782</v>
+      </c>
+      <c r="E14" s="34">
+        <v>46100</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B15" t="s">
-        <v>588</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>384</v>
-      </c>
-      <c r="E15" s="2">
-        <v>46267</v>
+      <c r="B15" s="27" t="s">
+        <v>783</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>784</v>
+      </c>
+      <c r="E15" s="34">
+        <v>46099</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B16" t="s">
-        <v>589</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>376</v>
-      </c>
-      <c r="E16" s="2">
-        <v>46144</v>
+      <c r="B16" s="27" t="s">
+        <v>785</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>786</v>
+      </c>
+      <c r="E16" s="34">
+        <v>46097</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B17" t="s">
-        <v>590</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
-        <v>377</v>
-      </c>
-      <c r="E17" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="27" t="s">
+        <v>761</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>762</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>591</v>
-      </c>
-      <c r="C18" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D18" t="s">
-        <v>375</v>
-      </c>
-      <c r="E18" s="2">
-        <v>46051</v>
+      <c r="B18" s="27" t="s">
+        <v>763</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>764</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B19" t="s">
-        <v>592</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="2">
-        <v>46038</v>
+      <c r="B19" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>766</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B20" t="s">
-        <v>593</v>
-      </c>
-      <c r="C20" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="2">
-        <v>46025</v>
+      <c r="B20" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>768</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>594</v>
-      </c>
-      <c r="C21" s="10">
-        <v>2025</v>
+        <v>588</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>384</v>
       </c>
       <c r="E21" s="2">
-        <v>46022</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>13</v>
+        <v>376</v>
       </c>
       <c r="E22" s="2">
-        <v>46022</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>596</v>
-      </c>
-      <c r="C23" s="10">
-        <v>2025</v>
+        <v>590</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>377</v>
       </c>
       <c r="E23" s="2">
-        <v>46020</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="C24" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>375</v>
       </c>
       <c r="E24" s="2">
-        <v>46009</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E25" s="2">
-        <v>46000</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>599</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>4</v>
+        <v>593</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2026</v>
       </c>
       <c r="D26" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2">
-        <v>45978</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>600</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>4</v>
+        <v>594</v>
+      </c>
+      <c r="C27" s="10">
+        <v>2025</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2">
-        <v>45965</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>601</v>
-      </c>
-      <c r="C28" s="10">
-        <v>2025</v>
+        <v>595</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E28" s="2">
-        <v>45951</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
       <c r="C29" s="10">
         <v>2025</v>
       </c>
       <c r="D29" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2">
-        <v>45945</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>602</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2025</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E30" s="2">
-        <v>45945</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E31" s="2">
-        <v>45945</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
-        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E32" s="2">
-        <v>45945</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
-        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E33" s="2">
-        <v>45944</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
-        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>606</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>4</v>
+        <v>601</v>
+      </c>
+      <c r="C34" s="10">
+        <v>2025</v>
       </c>
       <c r="D34" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E34" s="2">
-        <v>45940</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
-        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>607</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>4</v>
+        <v>602</v>
+      </c>
+      <c r="C35" s="10">
+        <v>2025</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E35" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
-        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E36" s="2">
-        <v>45933</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
-        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E37" s="2">
-        <v>45933</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
-        <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>610</v>
+      <c r="B38" t="s">
+        <v>604</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E38" s="2">
-        <v>45933</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
-        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>611</v>
+      <c r="B39" t="s">
+        <v>605</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E39" s="2">
-        <v>45933</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
-        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>612</v>
+      <c r="B40" t="s">
+        <v>606</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E40" s="2">
-        <v>45930</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
-        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>613</v>
+      <c r="B41" t="s">
+        <v>607</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E41" s="2">
-        <v>45924</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
-        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>614</v>
+      <c r="B42" t="s">
+        <v>608</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E42" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
-        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>615</v>
+      <c r="B43" t="s">
+        <v>609</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E43" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
-        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="C44" s="10">
-        <v>2025</v>
+        <v>610</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E44" s="2">
-        <v>45923</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
-        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E45" s="2">
-        <v>45918</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
-        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E46" s="2">
-        <v>45908</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
-        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E47" s="2">
-        <v>45897</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
-        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E48" s="2">
-        <v>45891</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
-        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E49" s="2">
-        <v>45891</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
-        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C50" s="10">
+        <v>2025</v>
       </c>
       <c r="D50" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E50" s="2">
-        <v>45888</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
-        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E51" s="2">
-        <v>45880</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
-        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>69</v>
+        <v>618</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E52" s="2">
-        <v>45855</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
-        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E53" s="2">
-        <v>45838</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
-        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E54" s="2">
-        <v>45838</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
-        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E55" s="2">
-        <v>45835</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
-        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>75</v>
+        <v>622</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E56" s="2">
-        <v>45833</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
-        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E57" s="2">
-        <v>45831</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
-        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>628</v>
+        <v>69</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="E58" s="2">
-        <v>45825</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
-        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E59" s="2">
-        <v>45825</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
-        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E60" s="2">
-        <v>45825</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
-        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E61" s="2">
-        <v>45808</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
-        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>632</v>
+        <v>75</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E62" s="2">
-        <v>45803</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
-        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E63" s="2">
-        <v>45803</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
-        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E64" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
-        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E65" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
-        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E66" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
-        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2">
+        <v>45808</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D68" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" s="2">
         <v>45803</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>638</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D68" t="s">
-        <v>94</v>
-      </c>
-      <c r="E68" s="2">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
-        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E69" s="2">
-        <v>45796</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
-        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E70" s="2">
-        <v>45794</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
-        <f t="shared" si="0"/>
         <v>67</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E71" s="2">
-        <v>45779</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
-        <f t="shared" ref="A72:A135" si="1">ROW()-4</f>
         <v>68</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E72" s="2">
-        <v>45770</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
-        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E73" s="2">
-        <v>45762</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74">
-        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="C74" s="10">
-        <v>2025</v>
+        <v>638</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E74" s="2">
-        <v>45749</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75">
-        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="C75" s="10">
-        <v>2025</v>
+        <v>639</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E75" s="2">
-        <v>45749</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
-        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="E76" s="2">
-        <v>45748</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
-        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E77" s="2">
-        <v>45736</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
-        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E78" s="2">
-        <v>45734</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
-        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E79" s="2">
-        <v>45726</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="C80" s="10">
         <v>2025</v>
       </c>
       <c r="D80" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="E80" s="2">
-        <v>45726</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
-        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>651</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>114</v>
+        <v>645</v>
+      </c>
+      <c r="C81" s="10">
+        <v>2025</v>
       </c>
       <c r="D81" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E81" s="2">
-        <v>45726</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
-        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="E82" s="2">
-        <v>45723</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
-        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="E83" s="2">
-        <v>45721</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
-        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E84" s="2">
-        <v>45698</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
-        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D85" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E85" s="2">
-        <v>45695</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
-        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>656</v>
-      </c>
-      <c r="C86" s="10" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C86" s="10">
+        <v>2025</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E86" s="2">
-        <v>45694</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
-        <f t="shared" si="1"/>
         <v>83</v>
       </c>
-      <c r="B87" t="s">
-        <v>587</v>
+      <c r="B87" s="10" t="s">
+        <v>651</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="E87" s="2">
-        <v>45692</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
-        <f t="shared" si="1"/>
         <v>84</v>
       </c>
-      <c r="B88" t="s">
-        <v>586</v>
+      <c r="B88" s="10" t="s">
+        <v>652</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E88" s="2">
-        <v>45686</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
-        <f t="shared" si="1"/>
         <v>85</v>
       </c>
-      <c r="B89" t="s">
-        <v>585</v>
+      <c r="B89" s="10" t="s">
+        <v>653</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E89" s="2">
-        <v>45681</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
-        <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B90" t="s">
-        <v>584</v>
+      <c r="B90" s="10" t="s">
+        <v>654</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="E90" s="2">
-        <v>45678</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
-        <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B91" t="s">
-        <v>583</v>
+      <c r="B91" s="10" t="s">
+        <v>655</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E91" s="2">
-        <v>45677</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
-        <f t="shared" si="1"/>
         <v>88</v>
       </c>
-      <c r="B92" t="s">
-        <v>582</v>
+      <c r="B92" s="10" t="s">
+        <v>656</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="E92" s="2">
-        <v>45677</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
-        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E93" s="2">
-        <v>45670</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
-        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E94" s="2">
-        <v>45661</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
-        <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="E95" s="2">
-        <v>45661</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
-        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E96" s="2">
-        <v>45659</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
-        <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E97" s="2">
-        <v>45656</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
-        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E98" s="2">
-        <v>45656</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
-        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>575</v>
-      </c>
-      <c r="C99" s="10">
-        <v>2024</v>
+        <v>581</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E99" s="2">
-        <v>45652</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
-        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="E100" s="2">
-        <v>45650</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
-        <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="E101" s="2">
-        <v>45631</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
-        <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E102" s="2">
-        <v>45625</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
-        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E103" s="2">
-        <v>45622</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
-        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E104" s="2">
-        <v>45593</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
-        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>569</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>114</v>
+        <v>575</v>
+      </c>
+      <c r="C105" s="10">
+        <v>2024</v>
       </c>
       <c r="D105" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="E105" s="2">
-        <v>45588</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
-        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="E106" s="2">
-        <v>45588</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
-        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E107" s="2">
-        <v>45578</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
-        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D108" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E108" s="2">
-        <v>45566</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
-        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D109" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E109" s="2">
-        <v>45566</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
-        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E110" s="2">
-        <v>45565</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
-        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E111" s="2">
-        <v>45563</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
-        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E112" s="2">
-        <v>45553</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
-        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
       <c r="E113" s="2">
-        <v>45548</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
-        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E114" s="2">
-        <v>45548</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
-        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E115" s="2">
-        <v>45539</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
-        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="E116" s="2">
-        <v>45538</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
-        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E117" s="2">
-        <v>45537</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
-        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="E118" s="2">
-        <v>45523</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
-        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="E119" s="2">
-        <v>45520</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
-        <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="E120" s="2">
-        <v>45505</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
-        <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E121" s="2">
-        <v>45502</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
-        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="E122" s="2">
-        <v>45478</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
-        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E123" s="2">
-        <v>45478</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
-        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="E124" s="2">
-        <v>45462</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
-        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>204</v>
+        <v>555</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="E125" s="2">
-        <v>45455</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
-        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="E126" s="2">
-        <v>45454</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
-        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="E127" s="2">
-        <v>45449</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
-        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="E128" s="2">
-        <v>45448</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
-        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="E129" s="2">
-        <v>45446</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
-        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E130" s="2">
-        <v>45432</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
-        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>544</v>
+        <v>204</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E131" s="2">
-        <v>45420</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
-        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="E132" s="2">
-        <v>45418</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
-        <f t="shared" si="1"/>
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="E133" s="2">
-        <v>45416</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
-        <f t="shared" si="1"/>
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="E134" s="2">
-        <v>45407</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
-        <f t="shared" si="1"/>
         <v>131</v>
       </c>
-      <c r="B135" s="6" t="s">
-        <v>540</v>
+      <c r="B135" t="s">
+        <v>546</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="E135" s="2">
-        <v>45405</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
-        <f t="shared" ref="A136:A170" si="2">ROW()-4</f>
         <v>132</v>
       </c>
-      <c r="B136" s="6" t="s">
-        <v>535</v>
+      <c r="B136" t="s">
+        <v>545</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="E136" s="2">
-        <v>45397</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
-        <f t="shared" si="2"/>
         <v>133</v>
       </c>
-      <c r="B137" s="6" t="s">
-        <v>539</v>
+      <c r="B137" t="s">
+        <v>544</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E137" s="2">
-        <v>45397</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
-        <f t="shared" si="2"/>
         <v>134</v>
       </c>
-      <c r="B138" s="6" t="s">
-        <v>538</v>
+      <c r="B138" t="s">
+        <v>543</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="E138" s="2">
-        <v>45387</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
-        <f t="shared" si="2"/>
         <v>135</v>
       </c>
-      <c r="B139" s="6" t="s">
-        <v>537</v>
+      <c r="B139" t="s">
+        <v>542</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="E139" s="2">
-        <v>45387</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
-        <f t="shared" si="2"/>
         <v>136</v>
       </c>
-      <c r="B140" s="6" t="s">
-        <v>536</v>
+      <c r="B140" t="s">
+        <v>541</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E140" s="2">
-        <v>45387</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
-        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>505</v>
+        <v>540</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="E141" s="2">
-        <v>45385</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
-        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E142" s="2">
-        <v>45384</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
-        <f t="shared" si="2"/>
         <v>139</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>506</v>
+        <v>539</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="E143" s="2">
-        <v>45378</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
-        <f t="shared" si="2"/>
         <v>140</v>
       </c>
-      <c r="B144" t="s">
-        <v>533</v>
+      <c r="B144" s="6" t="s">
+        <v>538</v>
       </c>
       <c r="C144" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E144" s="2">
-        <v>45373</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
-        <f t="shared" si="2"/>
         <v>141</v>
       </c>
-      <c r="B145" t="s">
-        <v>532</v>
+      <c r="B145" s="6" t="s">
+        <v>537</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E145" s="2">
-        <v>45373</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
-        <f t="shared" si="2"/>
         <v>142</v>
       </c>
-      <c r="B146" t="s">
-        <v>531</v>
+      <c r="B146" s="6" t="s">
+        <v>536</v>
       </c>
       <c r="C146" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="E146" s="2">
-        <v>45369</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
-        <f t="shared" si="2"/>
         <v>143</v>
       </c>
-      <c r="B147" t="s">
-        <v>530</v>
+      <c r="B147" s="6" t="s">
+        <v>505</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="E147" s="2">
-        <v>45367</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
-        <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="B148" t="s">
-        <v>529</v>
+      <c r="B148" s="6" t="s">
+        <v>534</v>
       </c>
       <c r="C148" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E148" s="2">
-        <v>45367</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
-        <f t="shared" si="2"/>
         <v>145</v>
       </c>
-      <c r="B149" t="s">
-        <v>528</v>
+      <c r="B149" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D149" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E149" s="2">
-        <v>45366</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
-        <f t="shared" si="2"/>
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D150" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="E150" s="2">
-        <v>45365</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
-        <f t="shared" si="2"/>
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D151" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E151" s="2">
-        <v>45362</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
-        <f t="shared" si="2"/>
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D152" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
       <c r="E152" s="2">
-        <v>45362</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
-        <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D153" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E153" s="2">
-        <v>45362</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
-        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D154" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E154" s="2">
-        <v>45362</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
-        <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D155" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E155" s="2">
-        <v>45359</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
-        <f t="shared" si="2"/>
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D156" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E156" s="2">
-        <v>45358</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
-        <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D157" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="E157" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
-        <f t="shared" si="2"/>
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D158" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="E158" s="2">
-        <v>45357</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
-        <f t="shared" si="2"/>
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E159" s="2">
-        <v>45357</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
-        <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D160" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="E160" s="2">
-        <v>45352</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
-        <f t="shared" si="2"/>
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D161" t="s">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="E161" s="2">
-        <v>45352</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
-        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E162" s="2">
-        <v>45352</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
-        <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E163" s="2">
-        <v>45351</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
-        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E164" s="2">
-        <v>45345</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
-        <f t="shared" si="2"/>
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D165" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="E165" s="2">
-        <v>45335</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
-        <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="E166" s="2">
-        <v>45334</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
-        <f t="shared" si="2"/>
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="E167" s="2">
-        <v>45314</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
-        <f t="shared" si="2"/>
         <v>164</v>
       </c>
-      <c r="B168" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C168" s="10">
-        <v>2023</v>
+      <c r="B168" t="s">
+        <v>515</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>261</v>
       </c>
       <c r="D168" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="E168" s="2">
-        <v>45306</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
-        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="E169" s="2">
-        <v>45294</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
-        <f t="shared" si="2"/>
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C170" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D170" t="s">
+        <v>265</v>
+      </c>
+      <c r="E170" s="2">
+        <v>45345</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>167</v>
+      </c>
+      <c r="B171" t="s">
+        <v>507</v>
+      </c>
+      <c r="C171" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D171" t="s">
+        <v>270</v>
+      </c>
+      <c r="E171" s="2">
+        <v>45335</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>168</v>
+      </c>
+      <c r="B172" t="s">
+        <v>512</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D172" t="s">
+        <v>271</v>
+      </c>
+      <c r="E172" s="2">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>169</v>
+      </c>
+      <c r="B173" t="s">
+        <v>511</v>
+      </c>
+      <c r="C173" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D173" t="s">
+        <v>276</v>
+      </c>
+      <c r="E173" s="2">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>170</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C174" s="10">
+        <v>2023</v>
+      </c>
+      <c r="D174" t="s">
+        <v>277</v>
+      </c>
+      <c r="E174" s="2">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>171</v>
+      </c>
+      <c r="B175" t="s">
+        <v>509</v>
+      </c>
+      <c r="C175" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D175" t="s">
+        <v>279</v>
+      </c>
+      <c r="E175" s="2">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>172</v>
+      </c>
+      <c r="B176" t="s">
+        <v>508</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D176" t="s">
         <v>281</v>
       </c>
-      <c r="E170" s="2">
+      <c r="E176" s="2">
         <v>45292</v>
       </c>
     </row>
@@ -9926,7 +9924,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="26"/>
@@ -9979,100 +9977,99 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
-        <f>ROW()-6</f>
         <v>1</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>790</v>
+        <v>814</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>8</v>
+        <v>815</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>791</v>
+        <v>816</v>
       </c>
       <c r="E7" s="32">
-        <v>46101</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
-        <f t="shared" ref="A8:A71" si="0">ROW()-6</f>
+        <f>ROW()-6</f>
         <v>2</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="B8" s="27" t="s">
+        <v>790</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>791</v>
+      </c>
+      <c r="E8" s="32">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="26">
+        <f t="shared" ref="A9:A72" si="0">ROW()-6</f>
+        <v>3</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>775</v>
       </c>
-      <c r="C8" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="38" t="s">
+      <c r="C9" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>776</v>
-      </c>
-      <c r="E8" s="41">
-        <v>46087</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="26">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>777</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="38" t="s">
-        <v>778</v>
       </c>
       <c r="E9" s="41">
         <v>46087</v>
       </c>
       <c r="F9" s="39"/>
+      <c r="G9" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B10" t="s">
-        <v>774</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>773</v>
-      </c>
-      <c r="E10" s="2">
-        <v>46084</v>
-      </c>
-      <c r="F10" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="36" t="s">
+        <v>777</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>778</v>
+      </c>
+      <c r="E10" s="41">
+        <v>46087</v>
+      </c>
+      <c r="F10" s="39"/>
+    </row>
+    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>744</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>745</v>
-      </c>
-      <c r="E11" s="32">
-        <v>46073</v>
+      <c r="B11" t="s">
+        <v>774</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" t="s">
+        <v>773</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46084</v>
+      </c>
+      <c r="F11" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10081,13 +10078,13 @@
         <v>6</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E12" s="32">
         <v>46073</v>
@@ -10099,13 +10096,13 @@
         <v>7</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E13" s="32">
         <v>46073</v>
@@ -10117,13 +10114,13 @@
         <v>8</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E14" s="32">
         <v>46073</v>
@@ -10135,34 +10132,34 @@
         <v>9</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E15" s="32">
         <v>46073</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B16" t="s">
-        <v>681</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="27" t="s">
+        <v>752</v>
+      </c>
+      <c r="C16" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D16" t="s">
-        <v>385</v>
-      </c>
-      <c r="E16" s="2">
-        <v>46267</v>
+      <c r="D16" s="27" t="s">
+        <v>753</v>
+      </c>
+      <c r="E16" s="32">
+        <v>46073</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -10171,52 +10168,52 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E17" s="2">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>683</v>
+      <c r="B18" t="s">
+        <v>682</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="10" t="s">
-        <v>314</v>
-      </c>
-      <c r="E18" s="23">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>380</v>
+      </c>
+      <c r="E18" s="2">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>684</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="B19" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="E19" s="20">
-        <v>46024</v>
+      <c r="D19" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="E19" s="23">
+        <v>46045</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10225,19 +10222,16 @@
         <v>14</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E20" s="20">
         <v>46024</v>
-      </c>
-      <c r="H20" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10246,16 +10240,19 @@
         <v>15</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E21" s="20">
-        <v>46022</v>
+        <v>46024</v>
+      </c>
+      <c r="H21" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10264,16 +10261,16 @@
         <v>16</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E22" s="20">
-        <v>45986</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10282,16 +10279,16 @@
         <v>17</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="21" t="s">
-        <v>319</v>
+      <c r="D23" s="19" t="s">
+        <v>318</v>
       </c>
       <c r="E23" s="20">
-        <v>45961</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10300,16 +10297,16 @@
         <v>18</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E24" s="20">
-        <v>45959</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10318,13 +10315,13 @@
         <v>19</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="19" t="s">
-        <v>321</v>
+      <c r="D25" s="21" t="s">
+        <v>320</v>
       </c>
       <c r="E25" s="20">
         <v>45959</v>
@@ -10336,16 +10333,16 @@
         <v>20</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E26" s="20">
-        <v>45957</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10354,16 +10351,16 @@
         <v>21</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="21" t="s">
-        <v>323</v>
+      <c r="D27" s="19" t="s">
+        <v>322</v>
       </c>
       <c r="E27" s="20">
-        <v>45930</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10372,16 +10369,16 @@
         <v>22</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="19" t="s">
-        <v>324</v>
+      <c r="D28" s="21" t="s">
+        <v>323</v>
       </c>
       <c r="E28" s="20">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10390,16 +10387,16 @@
         <v>23</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>743</v>
-      </c>
-      <c r="C29" s="19">
-        <v>2025</v>
+        <v>693</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E29" s="20">
-        <v>45896</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10408,16 +10405,16 @@
         <v>24</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>742</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>4</v>
+        <v>743</v>
+      </c>
+      <c r="C30" s="19">
+        <v>2025</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E30" s="20">
-        <v>45866</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10426,16 +10423,16 @@
         <v>25</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E31" s="20">
-        <v>45860</v>
+        <v>45866</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10444,16 +10441,16 @@
         <v>26</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E32" s="20">
-        <v>45852</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10462,16 +10459,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>739</v>
-      </c>
-      <c r="C33" s="19">
-        <v>2025</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>329</v>
+        <v>740</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>328</v>
       </c>
       <c r="E33" s="20">
-        <v>45840</v>
+        <v>45852</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10480,16 +10477,16 @@
         <v>28</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>738</v>
-      </c>
-      <c r="C34" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" s="19" t="s">
-        <v>330</v>
+        <v>739</v>
+      </c>
+      <c r="C34" s="19">
+        <v>2025</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>329</v>
       </c>
       <c r="E34" s="20">
-        <v>45826</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10498,16 +10495,16 @@
         <v>29</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E35" s="20">
-        <v>45821</v>
+        <v>45826</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10516,16 +10513,16 @@
         <v>30</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E36" s="20">
-        <v>45776</v>
+        <v>45821</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10534,16 +10531,16 @@
         <v>31</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>735</v>
-      </c>
-      <c r="C37" s="19">
-        <v>2025</v>
+        <v>736</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E37" s="20">
-        <v>45770</v>
+        <v>45776</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10552,16 +10549,16 @@
         <v>32</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>734</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>4</v>
+        <v>735</v>
+      </c>
+      <c r="C38" s="19">
+        <v>2025</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E38" s="20">
-        <v>45768</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10570,16 +10567,16 @@
         <v>33</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E39" s="20">
-        <v>45758</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10588,16 +10585,16 @@
         <v>34</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>336</v>
+        <v>4</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>335</v>
       </c>
       <c r="E40" s="20">
-        <v>45741</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10606,16 +10603,16 @@
         <v>35</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C41" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="19" t="s">
-        <v>337</v>
+      <c r="D41" s="21" t="s">
+        <v>336</v>
       </c>
       <c r="E41" s="20">
-        <v>45736</v>
+        <v>45741</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10624,16 +10621,16 @@
         <v>36</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E42" s="20">
-        <v>45728</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10642,16 +10639,16 @@
         <v>37</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C43" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E43" s="20">
-        <v>45716</v>
+        <v>45728</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10660,16 +10657,16 @@
         <v>38</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E44" s="20">
-        <v>45701</v>
+        <v>45716</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10678,16 +10675,16 @@
         <v>39</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E45" s="20">
-        <v>45700</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10696,16 +10693,16 @@
         <v>40</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C46" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E46" s="20">
-        <v>45699</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10714,13 +10711,13 @@
         <v>41</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C47" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E47" s="20">
         <v>45699</v>
@@ -10732,16 +10729,16 @@
         <v>42</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C48" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E48" s="20">
-        <v>45686</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10750,16 +10747,16 @@
         <v>43</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C49" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E49" s="20">
-        <v>45656</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10768,13 +10765,13 @@
         <v>44</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>722</v>
-      </c>
-      <c r="C50" s="19">
-        <v>2024</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>346</v>
+        <v>723</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>345</v>
       </c>
       <c r="E50" s="20">
         <v>45656</v>
@@ -10786,16 +10783,16 @@
         <v>45</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>721</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D51" s="19" t="s">
-        <v>347</v>
+        <v>722</v>
+      </c>
+      <c r="C51" s="19">
+        <v>2024</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>346</v>
       </c>
       <c r="E51" s="20">
-        <v>45646</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10804,16 +10801,16 @@
         <v>46</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C52" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E52" s="20">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10822,16 +10819,16 @@
         <v>47</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E53" s="20">
-        <v>45610</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10840,16 +10837,16 @@
         <v>48</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C54" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E54" s="20">
-        <v>45582</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10858,16 +10855,16 @@
         <v>49</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E55" s="20">
-        <v>45572</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10876,16 +10873,16 @@
         <v>50</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C56" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E56" s="20">
-        <v>45569</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10894,16 +10891,16 @@
         <v>51</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E57" s="20">
-        <v>45565</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10912,16 +10909,16 @@
         <v>52</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E58" s="20">
-        <v>45552</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10930,16 +10927,16 @@
         <v>53</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C59" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E59" s="20">
-        <v>45535</v>
+        <v>45552</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10948,16 +10945,16 @@
         <v>54</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C60" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E60" s="20">
-        <v>45533</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10966,16 +10963,16 @@
         <v>55</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C61" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E61" s="20">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10984,16 +10981,16 @@
         <v>56</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E62" s="20">
-        <v>45520</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11002,16 +10999,16 @@
         <v>57</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C63" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E63" s="20">
-        <v>45518</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11020,16 +11017,16 @@
         <v>58</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C64" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E64" s="20">
-        <v>45506</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11038,16 +11035,16 @@
         <v>59</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C65" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E65" s="20">
-        <v>45498</v>
+        <v>45506</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11056,16 +11053,16 @@
         <v>60</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C66" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E66" s="20">
-        <v>45496</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11074,16 +11071,16 @@
         <v>61</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C67" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E67" s="20">
-        <v>45483</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11092,16 +11089,16 @@
         <v>62</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E68" s="20">
-        <v>45471</v>
+        <v>45483</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11110,16 +11107,16 @@
         <v>63</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C69" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>187</v>
+        <v>364</v>
       </c>
       <c r="E69" s="20">
-        <v>45461</v>
+        <v>45471</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11128,16 +11125,16 @@
         <v>64</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>365</v>
+        <v>187</v>
       </c>
       <c r="E70" s="20">
-        <v>45455</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11145,53 +11142,53 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B71" s="30" t="s">
-        <v>701</v>
+      <c r="B71" s="21" t="s">
+        <v>702</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>214</v>
+        <v>365</v>
       </c>
       <c r="E71" s="20">
-        <v>45440</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="26">
-        <f t="shared" ref="A72:A78" si="1">ROW()-6</f>
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C72" s="19" t="s">
         <v>112</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>366</v>
+        <v>214</v>
       </c>
       <c r="E72" s="20">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A73:A79" si="1">ROW()-6</f>
         <v>67</v>
       </c>
-      <c r="B73" s="21" t="s">
-        <v>699</v>
+      <c r="B73" s="30" t="s">
+        <v>700</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E73" s="20">
-        <v>45400</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11200,16 +11197,16 @@
         <v>68</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E74" s="20">
-        <v>45384</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11218,16 +11215,16 @@
         <v>69</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>235</v>
+        <v>112</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E75" s="20">
-        <v>45371</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11236,16 +11233,16 @@
         <v>70</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E76" s="20">
-        <v>45369</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11254,33 +11251,51 @@
         <v>71</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C77" s="19" t="s">
         <v>236</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E77" s="20">
-        <v>45338</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="26">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>236</v>
       </c>
       <c r="D78" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="E78" s="20">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="26">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>694</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="D79" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="E78" s="20">
+      <c r="E79" s="20">
         <v>45335</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A6A7BD-50D7-489B-97DD-B4E6BC8686EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -2559,7 +2559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2658,7 +2658,6 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2976,7 +2975,7 @@
       <c r="E4" s="24"/>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42">
+      <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
@@ -2993,7 +2992,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42">
+      <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
@@ -3010,7 +3009,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42">
+      <c r="A7">
         <f t="shared" ref="A7:A8" si="0">ROW()-4</f>
         <v>3</v>
       </c>
@@ -3028,7 +3027,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -3046,7 +3045,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42">
+      <c r="A9">
         <f>ROW()-4</f>
         <v>5</v>
       </c>
@@ -3065,7 +3064,7 @@
       <c r="F9" s="39"/>
     </row>
     <row r="10" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42">
+      <c r="A10">
         <f t="shared" ref="A10:A73" si="1">ROW()-4</f>
         <v>6</v>
       </c>
@@ -3083,7 +3082,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="42">
+      <c r="A11">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
@@ -3104,7 +3103,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42">
+      <c r="A12">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -3122,7 +3121,7 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="42">
+      <c r="A13">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -3140,7 +3139,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="42">
+      <c r="A14">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -3158,7 +3157,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="42">
+      <c r="A15">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -3176,7 +3175,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="42">
+      <c r="A16">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -3194,7 +3193,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="42">
+      <c r="A17">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
@@ -3212,7 +3211,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="42">
+      <c r="A18">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
@@ -3230,7 +3229,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="42">
+      <c r="A19">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -3248,7 +3247,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="42">
+      <c r="A20">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
@@ -3266,7 +3265,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="42">
+      <c r="A21">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
@@ -3284,7 +3283,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="42">
+      <c r="A22">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
@@ -3302,7 +3301,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="42">
+      <c r="A23">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
@@ -3320,7 +3319,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="42">
+      <c r="A24">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
@@ -3338,7 +3337,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="42">
+      <c r="A25">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -3356,7 +3355,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="42">
+      <c r="A26">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
@@ -3374,7 +3373,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="42">
+      <c r="A27">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
@@ -3392,7 +3391,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="42">
+      <c r="A28">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
@@ -3410,7 +3409,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="42">
+      <c r="A29">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
@@ -3428,7 +3427,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="42">
+      <c r="A30">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
@@ -3446,7 +3445,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="42">
+      <c r="A31">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
@@ -3464,7 +3463,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="42">
+      <c r="A32">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
@@ -3482,7 +3481,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="42">
+      <c r="A33">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
@@ -3500,7 +3499,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="42">
+      <c r="A34">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -3518,7 +3517,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="42">
+      <c r="A35">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
@@ -3536,7 +3535,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="42">
+      <c r="A36">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
@@ -3554,7 +3553,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="42">
+      <c r="A37">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
@@ -3572,7 +3571,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="42">
+      <c r="A38">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
@@ -3590,7 +3589,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="42">
+      <c r="A39">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
@@ -3608,7 +3607,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="42">
+      <c r="A40">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
@@ -3626,7 +3625,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="42">
+      <c r="A41">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
@@ -3644,7 +3643,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="42">
+      <c r="A42">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
@@ -3662,7 +3661,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="42">
+      <c r="A43">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
@@ -3680,7 +3679,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="42">
+      <c r="A44">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
@@ -3698,7 +3697,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="42">
+      <c r="A45">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
@@ -3716,7 +3715,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="42">
+      <c r="A46">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
@@ -3734,7 +3733,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="42">
+      <c r="A47">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
@@ -3752,7 +3751,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="42">
+      <c r="A48">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
@@ -3770,7 +3769,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="42">
+      <c r="A49">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
@@ -3788,7 +3787,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="42">
+      <c r="A50">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
@@ -3806,7 +3805,7 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="42">
+      <c r="A51">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
@@ -3824,7 +3823,7 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="42">
+      <c r="A52">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
@@ -3842,7 +3841,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="42">
+      <c r="A53">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
@@ -3860,7 +3859,7 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="42">
+      <c r="A54">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
@@ -3878,7 +3877,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="42">
+      <c r="A55">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
@@ -3896,7 +3895,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="42">
+      <c r="A56">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
@@ -3914,7 +3913,7 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="42">
+      <c r="A57">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
@@ -3932,7 +3931,7 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="42">
+      <c r="A58">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
@@ -3950,7 +3949,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="42">
+      <c r="A59">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
@@ -3968,7 +3967,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="42">
+      <c r="A60">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
@@ -3986,7 +3985,7 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="42">
+      <c r="A61">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
@@ -4004,7 +4003,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="42">
+      <c r="A62">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
@@ -4022,7 +4021,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="42">
+      <c r="A63">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
@@ -4040,7 +4039,7 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="42">
+      <c r="A64">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
@@ -4058,7 +4057,7 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="42">
+      <c r="A65">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
@@ -4076,7 +4075,7 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="42">
+      <c r="A66">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -4094,7 +4093,7 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="42">
+      <c r="A67">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -4112,7 +4111,7 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="42">
+      <c r="A68">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -4130,7 +4129,7 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="42">
+      <c r="A69">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
@@ -4148,7 +4147,7 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="42">
+      <c r="A70">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
@@ -4166,7 +4165,7 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="42">
+      <c r="A71">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
@@ -4184,7 +4183,7 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="42">
+      <c r="A72">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -4202,7 +4201,7 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="42">
+      <c r="A73">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -4220,7 +4219,7 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="42">
+      <c r="A74">
         <f t="shared" ref="A74:A137" si="2">ROW()-4</f>
         <v>70</v>
       </c>
@@ -4238,7 +4237,7 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="42">
+      <c r="A75">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
@@ -4256,7 +4255,7 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="42">
+      <c r="A76">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
@@ -4274,7 +4273,7 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="42">
+      <c r="A77">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
@@ -4292,7 +4291,7 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="42">
+      <c r="A78">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
@@ -4310,7 +4309,7 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="42">
+      <c r="A79">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
@@ -4328,7 +4327,7 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="42">
+      <c r="A80">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
@@ -4346,7 +4345,7 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="42">
+      <c r="A81">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
@@ -4364,7 +4363,7 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="42">
+      <c r="A82">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
@@ -4382,7 +4381,7 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="42">
+      <c r="A83">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
@@ -4400,7 +4399,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="42">
+      <c r="A84">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
@@ -4418,7 +4417,7 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="42">
+      <c r="A85">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
@@ -4436,7 +4435,7 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="42">
+      <c r="A86">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
@@ -4454,7 +4453,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="42">
+      <c r="A87">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
@@ -4472,7 +4471,7 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="42">
+      <c r="A88">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
@@ -4490,7 +4489,7 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="42">
+      <c r="A89">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
@@ -4508,7 +4507,7 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="42">
+      <c r="A90">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
@@ -4526,7 +4525,7 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="42">
+      <c r="A91">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
@@ -4544,7 +4543,7 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="42">
+      <c r="A92">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
@@ -4562,7 +4561,7 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="42">
+      <c r="A93">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
@@ -4580,7 +4579,7 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="42">
+      <c r="A94">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
@@ -4598,7 +4597,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="42">
+      <c r="A95">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -4616,7 +4615,7 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="42">
+      <c r="A96">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
@@ -4634,7 +4633,7 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="42">
+      <c r="A97">
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
@@ -4652,7 +4651,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="42">
+      <c r="A98">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
@@ -4670,7 +4669,7 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="42">
+      <c r="A99">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
@@ -4688,7 +4687,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="42">
+      <c r="A100">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
@@ -4706,7 +4705,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="42">
+      <c r="A101">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
@@ -4724,7 +4723,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="42">
+      <c r="A102">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
@@ -4742,7 +4741,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="42">
+      <c r="A103">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
@@ -4760,7 +4759,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="42">
+      <c r="A104">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -4778,7 +4777,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="42">
+      <c r="A105">
         <f t="shared" si="2"/>
         <v>101</v>
       </c>
@@ -4796,7 +4795,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="42">
+      <c r="A106">
         <f t="shared" si="2"/>
         <v>102</v>
       </c>
@@ -4814,7 +4813,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="42">
+      <c r="A107">
         <f t="shared" si="2"/>
         <v>103</v>
       </c>
@@ -4832,7 +4831,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="42">
+      <c r="A108">
         <f t="shared" si="2"/>
         <v>104</v>
       </c>
@@ -4850,7 +4849,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="42">
+      <c r="A109">
         <f t="shared" si="2"/>
         <v>105</v>
       </c>
@@ -4868,7 +4867,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="42">
+      <c r="A110">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
@@ -4886,7 +4885,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="42">
+      <c r="A111">
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
@@ -4904,7 +4903,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="42">
+      <c r="A112">
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
@@ -4922,7 +4921,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="42">
+      <c r="A113">
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
@@ -4940,7 +4939,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="42">
+      <c r="A114">
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
@@ -4958,7 +4957,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="42">
+      <c r="A115">
         <f t="shared" si="2"/>
         <v>111</v>
       </c>
@@ -4976,7 +4975,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="42">
+      <c r="A116">
         <f t="shared" si="2"/>
         <v>112</v>
       </c>
@@ -4994,7 +4993,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="42">
+      <c r="A117">
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
@@ -5012,7 +5011,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="42">
+      <c r="A118">
         <f t="shared" si="2"/>
         <v>114</v>
       </c>
@@ -5030,7 +5029,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="42">
+      <c r="A119">
         <f t="shared" si="2"/>
         <v>115</v>
       </c>
@@ -5048,7 +5047,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="42">
+      <c r="A120">
         <f t="shared" si="2"/>
         <v>116</v>
       </c>
@@ -5066,7 +5065,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="42">
+      <c r="A121">
         <f t="shared" si="2"/>
         <v>117</v>
       </c>
@@ -5084,7 +5083,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="42">
+      <c r="A122">
         <f t="shared" si="2"/>
         <v>118</v>
       </c>
@@ -5102,7 +5101,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="42">
+      <c r="A123">
         <f t="shared" si="2"/>
         <v>119</v>
       </c>
@@ -5120,7 +5119,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="42">
+      <c r="A124">
         <f t="shared" si="2"/>
         <v>120</v>
       </c>
@@ -5138,7 +5137,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="42">
+      <c r="A125">
         <f t="shared" si="2"/>
         <v>121</v>
       </c>
@@ -5156,7 +5155,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="42">
+      <c r="A126">
         <f t="shared" si="2"/>
         <v>122</v>
       </c>
@@ -5174,7 +5173,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="42">
+      <c r="A127">
         <f t="shared" si="2"/>
         <v>123</v>
       </c>
@@ -5192,7 +5191,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="42">
+      <c r="A128">
         <f t="shared" si="2"/>
         <v>124</v>
       </c>
@@ -5210,7 +5209,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="42">
+      <c r="A129">
         <f t="shared" si="2"/>
         <v>125</v>
       </c>
@@ -5228,7 +5227,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="42">
+      <c r="A130">
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
@@ -5246,7 +5245,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="42">
+      <c r="A131">
         <f t="shared" si="2"/>
         <v>127</v>
       </c>
@@ -5264,7 +5263,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="42">
+      <c r="A132">
         <f t="shared" si="2"/>
         <v>128</v>
       </c>
@@ -5282,7 +5281,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="42">
+      <c r="A133">
         <f t="shared" si="2"/>
         <v>129</v>
       </c>
@@ -5300,7 +5299,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="42">
+      <c r="A134">
         <f t="shared" si="2"/>
         <v>130</v>
       </c>
@@ -5318,7 +5317,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="42">
+      <c r="A135">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
@@ -5336,7 +5335,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="42">
+      <c r="A136">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
@@ -5354,7 +5353,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="42">
+      <c r="A137">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
@@ -5372,7 +5371,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="42">
+      <c r="A138">
         <f t="shared" ref="A138" si="3">ROW()-4</f>
         <v>134</v>
       </c>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9A6A7BD-50D7-489B-97DD-B4E6BC8686EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360CD6B3-22CA-45C9-BD8B-A6855FB5B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="822">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2483,6 +2483,21 @@
   </si>
   <si>
     <t>Special drive for expeditious issuance of EODCs under Advance Authorisation (AA) and EPCG schemes - extension up to May 31 ,2026</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 02/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in Import Policy of Items covered under CTH 7113 under Chapter 71 of ITC (HS) 2022, Schedule-I (Import Policy).</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 01/2026-27</t>
+  </si>
+  <si>
+    <t>2026-27</t>
+  </si>
+  <si>
+    <t>Supply of essential commodities to the Republic of Maldives during FY 2026-27 - regarding.</t>
   </si>
 </sst>
 </file>
@@ -5453,7 +5468,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5489,16 +5504,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>800</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>4</v>
+        <v>817</v>
+      </c>
+      <c r="C5" s="31">
+        <v>2026</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="E5" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5506,16 +5521,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>4</v>
+        <v>820</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>803</v>
+        <v>821</v>
       </c>
       <c r="E6" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5523,13 +5538,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>804</v>
-      </c>
-      <c r="C7" s="31">
-        <v>2026</v>
+        <v>800</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E7" s="32">
         <v>46112</v>
@@ -5540,13 +5555,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>806</v>
-      </c>
-      <c r="C8" s="31">
-        <v>2026</v>
+        <v>802</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E8" s="32">
         <v>46112</v>
@@ -5557,13 +5572,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C9" s="31">
         <v>2026</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E9" s="32">
         <v>46112</v>
@@ -5574,13 +5589,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C10" s="31">
         <v>2026</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E10" s="32">
         <v>46112</v>
@@ -5591,16 +5606,16 @@
         <v>7</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="C11" s="31">
         <v>2026</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="E11" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5608,16 +5623,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>796</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>4</v>
+        <v>810</v>
+      </c>
+      <c r="C12" s="31">
+        <v>2026</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="E12" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5625,16 +5640,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>798</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>4</v>
+        <v>794</v>
+      </c>
+      <c r="C13" s="31">
+        <v>2026</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E13" s="32">
-        <v>46104</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -5642,16 +5657,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>782</v>
-      </c>
-      <c r="E14" s="34">
-        <v>46100</v>
+        <v>797</v>
+      </c>
+      <c r="E14" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5659,16 +5674,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>784</v>
-      </c>
-      <c r="E15" s="34">
-        <v>46099</v>
+        <v>799</v>
+      </c>
+      <c r="E15" s="32">
+        <v>46104</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5676,16 +5691,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C16" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E16" s="34">
-        <v>46097</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5693,16 +5708,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>761</v>
+        <v>783</v>
       </c>
       <c r="C17" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>762</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>756</v>
+        <v>784</v>
+      </c>
+      <c r="E17" s="34">
+        <v>46099</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5710,16 +5725,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="C18" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>764</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>756</v>
+        <v>786</v>
+      </c>
+      <c r="E18" s="34">
+        <v>46097</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5727,13 +5742,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E19" s="34" t="s">
         <v>756</v>
@@ -5744,50 +5759,50 @@
         <v>16</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>17</v>
       </c>
-      <c r="B21" t="s">
-        <v>588</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>384</v>
-      </c>
-      <c r="E21" s="2">
-        <v>46267</v>
+      <c r="B21" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>766</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>18</v>
       </c>
-      <c r="B22" t="s">
-        <v>589</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>376</v>
-      </c>
-      <c r="E22" s="2">
-        <v>46144</v>
+      <c r="B22" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>768</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5795,33 +5810,33 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E23" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>591</v>
-      </c>
-      <c r="C24" s="10">
-        <v>2026</v>
+        <v>589</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E24" s="2">
-        <v>46051</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5829,33 +5844,33 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>6</v>
+        <v>377</v>
       </c>
       <c r="E25" s="2">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C26" s="10">
         <v>2026</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>375</v>
       </c>
       <c r="E26" s="2">
-        <v>46025</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5863,16 +5878,16 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>594</v>
-      </c>
-      <c r="C27" s="10">
-        <v>2025</v>
+        <v>592</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E27" s="2">
-        <v>46022</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5880,16 +5895,16 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>595</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>4</v>
+        <v>593</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2026</v>
       </c>
       <c r="D28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2">
-        <v>46022</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5897,16 +5912,16 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C29" s="10">
         <v>2025</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2">
-        <v>46020</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5914,16 +5929,16 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>597</v>
-      </c>
-      <c r="C30" s="10">
-        <v>2025</v>
+        <v>595</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E30" s="2">
-        <v>46009</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -5931,16 +5946,16 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>598</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>4</v>
+        <v>596</v>
+      </c>
+      <c r="C31" s="10">
+        <v>2025</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E31" s="2">
-        <v>46000</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5948,16 +5963,16 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>599</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2025</v>
       </c>
       <c r="D32" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E32" s="2">
-        <v>45978</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5965,16 +5980,16 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E33" s="2">
-        <v>45965</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5982,16 +5997,16 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>601</v>
-      </c>
-      <c r="C34" s="10">
-        <v>2025</v>
+        <v>599</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E34" s="2">
-        <v>45951</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5999,16 +6014,16 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>602</v>
-      </c>
-      <c r="C35" s="10">
-        <v>2025</v>
+        <v>600</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E35" s="2">
-        <v>45945</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -6016,16 +6031,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>602</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>4</v>
+        <v>601</v>
+      </c>
+      <c r="C36" s="10">
+        <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E36" s="2">
-        <v>45945</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6033,13 +6048,13 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>603</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>4</v>
+        <v>602</v>
+      </c>
+      <c r="C37" s="10">
+        <v>2025</v>
       </c>
       <c r="D37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E37" s="2">
         <v>45945</v>
@@ -6050,13 +6065,13 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E38" s="2">
         <v>45945</v>
@@ -6067,16 +6082,16 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E39" s="2">
-        <v>45944</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -6084,16 +6099,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E40" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -6101,16 +6116,16 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E41" s="2">
-        <v>45940</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -6118,16 +6133,16 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E42" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6135,30 +6150,30 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>40</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>610</v>
+      <c r="B44" t="s">
+        <v>608</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E44" s="2">
         <v>45933</v>
@@ -6168,14 +6183,14 @@
       <c r="A45">
         <v>41</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>611</v>
+      <c r="B45" t="s">
+        <v>609</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E45" s="2">
         <v>45933</v>
@@ -6186,16 +6201,16 @@
         <v>42</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E46" s="2">
-        <v>45930</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6203,16 +6218,16 @@
         <v>43</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E47" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6220,16 +6235,16 @@
         <v>44</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E48" s="2">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -6237,13 +6252,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E49" s="2">
         <v>45924</v>
@@ -6254,16 +6269,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="C50" s="10">
-        <v>2025</v>
+        <v>614</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E50" s="2">
-        <v>45923</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -6271,16 +6286,16 @@
         <v>47</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E51" s="2">
-        <v>45918</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -6288,16 +6303,16 @@
         <v>48</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C52" s="10">
+        <v>2025</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E52" s="2">
-        <v>45908</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -6305,16 +6320,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E53" s="2">
-        <v>45897</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -6322,16 +6337,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E54" s="2">
-        <v>45891</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -6339,16 +6354,16 @@
         <v>51</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E55" s="2">
-        <v>45891</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -6356,16 +6371,16 @@
         <v>52</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E56" s="2">
-        <v>45888</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -6373,16 +6388,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E57" s="2">
-        <v>45880</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -6390,16 +6405,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>69</v>
+        <v>622</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E58" s="2">
-        <v>45855</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -6407,16 +6422,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E59" s="2">
-        <v>45838</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -6424,16 +6439,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>625</v>
+        <v>69</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E60" s="2">
-        <v>45838</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -6441,16 +6456,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E61" s="2">
-        <v>45835</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -6458,16 +6473,16 @@
         <v>58</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>75</v>
+        <v>625</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E62" s="2">
-        <v>45833</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -6475,16 +6490,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E63" s="2">
-        <v>45831</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -6492,16 +6507,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>628</v>
+        <v>75</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E64" s="2">
-        <v>45825</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -6509,16 +6524,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E65" s="2">
-        <v>45825</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -6526,13 +6541,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E66" s="2">
         <v>45825</v>
@@ -6543,16 +6558,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E67" s="2">
-        <v>45808</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -6560,16 +6575,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E68" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -6577,16 +6592,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E69" s="2">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -6594,13 +6609,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E70" s="2">
         <v>45803</v>
@@ -6611,13 +6626,13 @@
         <v>67</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E71" s="2">
         <v>45803</v>
@@ -6628,13 +6643,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E72" s="2">
         <v>45803</v>
@@ -6645,84 +6660,84 @@
         <v>69</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E73" s="2">
         <v>45803</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>70</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E74" s="2">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>71</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E75" s="2">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>72</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E76" s="2">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>73</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E77" s="2">
-        <v>45779</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -6730,16 +6745,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E78" s="2">
-        <v>45770</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -6747,16 +6762,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E79" s="2">
-        <v>45762</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -6764,16 +6779,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="C80" s="10">
-        <v>2025</v>
+        <v>642</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E80" s="2">
-        <v>45749</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -6781,16 +6796,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="C81" s="10">
-        <v>2025</v>
+        <v>643</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E81" s="2">
-        <v>45749</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -6798,16 +6813,16 @@
         <v>78</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>4</v>
+        <v>644</v>
+      </c>
+      <c r="C82" s="10">
+        <v>2025</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E82" s="2">
-        <v>45748</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -6815,16 +6830,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>647</v>
-      </c>
-      <c r="C83" s="10" t="s">
-        <v>114</v>
+        <v>645</v>
+      </c>
+      <c r="C83" s="10">
+        <v>2025</v>
       </c>
       <c r="D83" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E83" s="2">
-        <v>45736</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -6832,16 +6847,16 @@
         <v>80</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E84" s="2">
-        <v>45734</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -6849,16 +6864,16 @@
         <v>81</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D85" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E85" s="2">
-        <v>45726</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -6866,16 +6881,16 @@
         <v>82</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="C86" s="10">
-        <v>2025</v>
+        <v>648</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E86" s="2">
-        <v>45726</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -6883,13 +6898,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E87" s="2">
         <v>45726</v>
@@ -6900,16 +6915,16 @@
         <v>84</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C88" s="10">
+        <v>2025</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E88" s="2">
-        <v>45723</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -6917,16 +6932,16 @@
         <v>85</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E89" s="2">
-        <v>45721</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -6934,16 +6949,16 @@
         <v>86</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E90" s="2">
-        <v>45698</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -6951,16 +6966,16 @@
         <v>87</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E91" s="2">
-        <v>45695</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -6968,50 +6983,50 @@
         <v>88</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E92" s="2">
-        <v>45694</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>89</v>
       </c>
-      <c r="B93" t="s">
-        <v>587</v>
+      <c r="B93" s="10" t="s">
+        <v>655</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E93" s="2">
-        <v>45692</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>90</v>
       </c>
-      <c r="B94" t="s">
-        <v>586</v>
+      <c r="B94" s="10" t="s">
+        <v>656</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E94" s="2">
-        <v>45686</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -7019,16 +7034,16 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E95" s="2">
-        <v>45681</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -7036,16 +7051,16 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E96" s="2">
-        <v>45678</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -7053,16 +7068,16 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E97" s="2">
-        <v>45677</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7070,16 +7085,16 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E98" s="2">
-        <v>45677</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -7087,16 +7102,16 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E99" s="2">
-        <v>45670</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7104,16 +7119,16 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E100" s="2">
-        <v>45661</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7121,16 +7136,16 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E101" s="2">
-        <v>45661</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7138,16 +7153,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E102" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -7155,16 +7170,16 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E103" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7172,16 +7187,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E104" s="2">
-        <v>45656</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7189,16 +7204,16 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>575</v>
-      </c>
-      <c r="C105" s="10">
-        <v>2024</v>
+        <v>577</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E105" s="2">
-        <v>45652</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7206,16 +7221,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="E106" s="2">
-        <v>45650</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7223,16 +7238,16 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>573</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>114</v>
+        <v>575</v>
+      </c>
+      <c r="C107" s="10">
+        <v>2024</v>
       </c>
       <c r="D107" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E107" s="2">
-        <v>45631</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7240,16 +7255,16 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="E108" s="2">
-        <v>45625</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -7257,16 +7272,16 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E109" s="2">
-        <v>45622</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7274,16 +7289,16 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D110" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E110" s="2">
-        <v>45593</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7291,16 +7306,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E111" s="2">
-        <v>45588</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7308,16 +7323,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E112" s="2">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -7325,16 +7340,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E113" s="2">
-        <v>45578</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7342,16 +7357,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E114" s="2">
-        <v>45566</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7359,16 +7374,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E115" s="2">
-        <v>45566</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7376,16 +7391,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E116" s="2">
-        <v>45565</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7393,16 +7408,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E117" s="2">
-        <v>45563</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7410,16 +7425,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E118" s="2">
-        <v>45553</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7427,16 +7442,16 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="E119" s="2">
-        <v>45548</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -7444,16 +7459,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E120" s="2">
-        <v>45548</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7461,16 +7476,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>181</v>
+        <v>119</v>
       </c>
       <c r="E121" s="2">
-        <v>45539</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7478,16 +7493,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E122" s="2">
-        <v>45538</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -7495,16 +7510,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E123" s="2">
-        <v>45537</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7512,16 +7527,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E124" s="2">
-        <v>45523</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7529,16 +7544,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E125" s="2">
-        <v>45520</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7546,16 +7561,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E126" s="2">
-        <v>45505</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -7563,16 +7578,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E127" s="2">
-        <v>45502</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -7580,16 +7595,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E128" s="2">
-        <v>45478</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -7597,16 +7612,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E129" s="2">
-        <v>45478</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7614,16 +7629,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E130" s="2">
-        <v>45462</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -7631,16 +7646,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>204</v>
+        <v>551</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E131" s="2">
-        <v>45455</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -7648,16 +7663,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E132" s="2">
-        <v>45454</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -7665,16 +7680,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>548</v>
+        <v>204</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E133" s="2">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -7682,16 +7697,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E134" s="2">
-        <v>45448</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -7699,16 +7714,16 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E135" s="2">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -7716,16 +7731,16 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E136" s="2">
-        <v>45432</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -7733,16 +7748,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E137" s="2">
-        <v>45420</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -7750,16 +7765,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E138" s="2">
-        <v>45418</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -7767,16 +7782,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E139" s="2">
-        <v>45416</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -7784,50 +7799,50 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E140" s="2">
-        <v>45407</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>137</v>
       </c>
-      <c r="B141" s="6" t="s">
-        <v>540</v>
+      <c r="B141" t="s">
+        <v>542</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E141" s="2">
-        <v>45405</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>138</v>
       </c>
-      <c r="B142" s="6" t="s">
-        <v>535</v>
+      <c r="B142" t="s">
+        <v>541</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E142" s="2">
-        <v>45397</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -7835,16 +7850,16 @@
         <v>139</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E143" s="2">
-        <v>45397</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -7852,16 +7867,16 @@
         <v>140</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E144" s="2">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -7869,16 +7884,16 @@
         <v>141</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E145" s="2">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -7886,13 +7901,13 @@
         <v>142</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E146" s="2">
         <v>45387</v>
@@ -7903,16 +7918,16 @@
         <v>143</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E147" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -7920,16 +7935,16 @@
         <v>144</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E148" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -7937,50 +7952,50 @@
         <v>145</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E149" s="2">
-        <v>45378</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>146</v>
       </c>
-      <c r="B150" t="s">
-        <v>533</v>
+      <c r="B150" s="6" t="s">
+        <v>534</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E150" s="2">
-        <v>45373</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>147</v>
       </c>
-      <c r="B151" t="s">
-        <v>532</v>
+      <c r="B151" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D151" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E151" s="2">
-        <v>45373</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -7988,16 +8003,16 @@
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D152" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="E152" s="2">
-        <v>45369</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -8005,16 +8020,16 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D153" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E153" s="2">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -8022,16 +8037,16 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D154" t="s">
-        <v>243</v>
+        <v>117</v>
       </c>
       <c r="E154" s="2">
-        <v>45367</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -8039,16 +8054,16 @@
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D155" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E155" s="2">
-        <v>45366</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8056,16 +8071,16 @@
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D156" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E156" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -8073,16 +8088,16 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D157" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E157" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -8090,16 +8105,16 @@
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D158" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E158" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -8107,13 +8122,13 @@
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D159" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E159" s="2">
         <v>45362</v>
@@ -8124,13 +8139,13 @@
         <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D160" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E160" s="2">
         <v>45362</v>
@@ -8141,16 +8156,16 @@
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D161" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E161" s="2">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -8158,16 +8173,16 @@
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E162" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -8175,16 +8190,16 @@
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E163" s="2">
-        <v>45358</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8192,16 +8207,16 @@
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E164" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -8209,16 +8224,16 @@
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D165" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E165" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -8226,16 +8241,16 @@
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E166" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -8243,16 +8258,16 @@
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="E167" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -8260,13 +8275,13 @@
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="E168" s="2">
         <v>45352</v>
@@ -8277,16 +8292,16 @@
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="E169" s="2">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8294,16 +8309,16 @@
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D170" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E170" s="2">
-        <v>45345</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -8311,16 +8326,16 @@
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E171" s="2">
-        <v>45335</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8328,16 +8343,16 @@
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C172" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E172" s="2">
-        <v>45334</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -8345,33 +8360,33 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C173" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E173" s="2">
-        <v>45314</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>170</v>
       </c>
-      <c r="B174" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C174" s="10">
-        <v>2023</v>
+      <c r="B174" t="s">
+        <v>512</v>
+      </c>
+      <c r="C174" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E174" s="2">
-        <v>45306</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -8379,32 +8394,66 @@
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D175" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E175" s="2">
-        <v>45294</v>
+        <v>45314</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>172</v>
       </c>
-      <c r="B176" t="s">
+      <c r="B176" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C176" s="10">
+        <v>2023</v>
+      </c>
+      <c r="D176" t="s">
+        <v>277</v>
+      </c>
+      <c r="E176" s="2">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177">
+        <v>173</v>
+      </c>
+      <c r="B177" t="s">
+        <v>509</v>
+      </c>
+      <c r="C177" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D177" t="s">
+        <v>279</v>
+      </c>
+      <c r="E177" s="2">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>174</v>
+      </c>
+      <c r="B178" t="s">
         <v>508</v>
       </c>
-      <c r="C176" s="10" t="s">
+      <c r="C178" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D176" t="s">
+      <c r="D178" t="s">
         <v>281</v>
       </c>
-      <c r="E176" s="2">
+      <c r="E178" s="2">
         <v>45292</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360CD6B3-22CA-45C9-BD8B-A6855FB5B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360CD6B3-22CA-45C9-BD8B-A6855FB5B98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698573A4-D150-40DF-8C24-FBE0C35E7B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="830">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2498,6 +2498,30 @@
   </si>
   <si>
     <t>Supply of essential commodities to the Republic of Maldives during FY 2026-27 - regarding.</t>
+  </si>
+  <si>
+    <t>Amendments to Para 2.90 of Handbook of Procedures 2023</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE-01/2026-27</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 05/2026-27</t>
+  </si>
+  <si>
+    <t>Amendments to Para 2.62 of Foreign Trade Policy 2023</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 04/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in Export Policy and Policy Condition of Wood Pellets (HS 44013100) and Wood Briquettes (HS 44013200) under Chapter 44 of ITC (HS) 2022, Schedule-2 (Export Policy) - regarding.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 03/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in Import Policy and Policy conditions of items covered under Chapter 71 of ITC (HS) 2022, Schedule-I (Import Policy)-reg.</t>
   </si>
 </sst>
 </file>
@@ -2574,7 +2598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2673,6 +2697,12 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2953,9 +2983,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O371"/>
+  <dimension ref="A1:O372"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.5703125" style="10" customWidth="1"/>
     <col min="4" max="4" width="137.140625" style="4" customWidth="1"/>
@@ -2990,1288 +3021,1290 @@
       <c r="E4" s="24"/>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="A5" s="42">
+        <f>ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" t="s">
+        <v>823</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="E5" s="2">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="42">
+        <f t="shared" ref="A6:A69" si="0">ROW()-4</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>812</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D6" s="33" t="s">
         <v>813</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E6" s="32">
         <v>46111</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6" s="27" t="s">
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="42">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B7" s="27" t="s">
         <v>792</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C7" s="31">
         <v>2025</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D7" s="33" t="s">
         <v>793</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E7" s="32">
         <v>46105</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <f t="shared" ref="A7:A8" si="0">ROW()-4</f>
-        <v>3</v>
-      </c>
-      <c r="B7" s="27" t="s">
+    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="42">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>787</v>
       </c>
-      <c r="C7" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="C8" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>788</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E8" s="32">
         <v>46101</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B8" s="27" t="s">
+    <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="42">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="33" t="s">
+      <c r="C9" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="33" t="s">
         <v>779</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E9" s="32">
         <v>46087</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <f>ROW()-4</f>
-        <v>5</v>
-      </c>
-      <c r="B9" s="40" t="s">
+    <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="42">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>780</v>
       </c>
-      <c r="C9" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="40" t="s">
+      <c r="C10" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="40" t="s">
         <v>779</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E10" s="41">
         <v>46087</v>
       </c>
-      <c r="F9" s="39"/>
-    </row>
-    <row r="10" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <f t="shared" ref="A10:A73" si="1">ROW()-4</f>
-        <v>6</v>
-      </c>
-      <c r="B10" s="27" t="s">
+      <c r="F10" s="39"/>
+    </row>
+    <row r="11" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="42">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>754</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="33" t="s">
+      <c r="C11" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>755</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="27" t="s">
-        <v>757</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>758</v>
       </c>
       <c r="E11" s="34" t="s">
         <v>756</v>
       </c>
-      <c r="O11" s="27" t="s">
-        <v>381</v>
-      </c>
     </row>
     <row r="12" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <f t="shared" si="1"/>
+      <c r="A12" s="42">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C12" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E12" s="34" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <f t="shared" si="1"/>
+      <c r="O12" s="27" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="42">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>760</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="42">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>386</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C14" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E14" s="2">
         <v>46328</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="42">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
         <v>387</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="C15" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E15" s="2">
         <v>46144</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="42">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>388</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E16" s="2">
         <v>46045</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="42">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
         <v>389</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E17" s="2">
         <v>46038</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="42">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
         <v>390</v>
-      </c>
-      <c r="C17" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="2">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>391</v>
       </c>
       <c r="C18" s="10">
         <v>2026</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2">
         <v>46031</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <f t="shared" si="1"/>
+      <c r="A19" s="42">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C19" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="42">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
         <v>392</v>
       </c>
-      <c r="C19" s="10">
+      <c r="C20" s="10">
         <v>2025</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E20" s="2">
         <v>46022</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <f t="shared" si="1"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="42">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>393</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" t="s">
         <v>16</v>
       </c>
-      <c r="B20" t="s">
-        <v>393</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="2">
+      <c r="E21" s="2">
         <v>46010</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="42">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
         <v>394</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C22" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
         <v>18</v>
-      </c>
-      <c r="E21" s="2">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>395</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>19</v>
       </c>
       <c r="E22" s="2">
         <v>46008</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <f t="shared" si="1"/>
+      <c r="A23" s="42">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" t="s">
+        <v>395</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="2">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="42">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
         <v>396</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="C24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
         <v>374</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E24" s="2">
         <v>46002</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="42">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
         <v>397</v>
-      </c>
-      <c r="C24" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24" s="2">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="B25" t="s">
-        <v>398</v>
       </c>
       <c r="C25" s="10">
         <v>2025</v>
       </c>
       <c r="D25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2">
         <v>46001</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <f t="shared" si="1"/>
+      <c r="A26" s="42">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" t="s">
+        <v>398</v>
+      </c>
+      <c r="C26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="42">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
         <v>399</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="C27" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" t="s">
         <v>23</v>
-      </c>
-      <c r="E26" s="2">
-        <v>45992</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>400</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>24</v>
       </c>
       <c r="E27" s="2">
         <v>45992</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <f t="shared" si="1"/>
+      <c r="A28" s="42">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" t="s">
+        <v>400</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="2">
+        <v>45992</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="42">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
         <v>401</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C29" s="10">
         <v>2025</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>373</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E29" s="2">
         <v>45981</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="42">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
         <v>402</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="C30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E30" s="2">
         <v>45959</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="42">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
         <v>403</v>
-      </c>
-      <c r="C30" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D30" t="s">
-        <v>28</v>
-      </c>
-      <c r="E30" s="2">
-        <v>45958</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <f t="shared" si="1"/>
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>404</v>
       </c>
       <c r="C31" s="10">
         <v>2025</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E31" s="2">
         <v>45958</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <f t="shared" si="1"/>
+      <c r="A32" s="42">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B32" t="s">
+        <v>404</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45958</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="42">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
         <v>405</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C33" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E33" s="2">
         <v>45953</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <f t="shared" si="1"/>
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="42">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
         <v>406</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="C34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
         <v>31</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E34" s="2">
         <v>45952</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="42">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
         <v>407</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
         <v>36</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E35" s="2">
         <v>45945</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <f t="shared" si="1"/>
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="42">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
         <v>39</v>
-      </c>
-      <c r="E35" s="2">
-        <v>45940</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <f t="shared" si="1"/>
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
-        <v>408</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
-        <v>42</v>
       </c>
       <c r="E36" s="2">
         <v>45940</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <f t="shared" si="1"/>
+      <c r="A37" s="42">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B37" t="s">
+        <v>408</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="2">
+        <v>45940</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="42">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
         <v>409</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E38" s="2">
         <v>45933</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="42">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
         <v>410</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
         <v>48</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E39" s="2">
         <v>45931</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <f t="shared" si="1"/>
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="42">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
         <v>411</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E40" s="2">
         <v>45909</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <f t="shared" si="1"/>
-        <v>36</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="42">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
         <v>412</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
         <v>57</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E41" s="2">
         <v>45903</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="42">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
         <v>413</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C42" s="10">
         <v>2025</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>59</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E42" s="2">
         <v>45895</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <f t="shared" si="1"/>
-        <v>38</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="42">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
         <v>414</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="C43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
         <v>62</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E43" s="2">
         <v>45891</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <f t="shared" si="1"/>
-        <v>39</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="42">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B44" t="s">
         <v>415</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C44" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E44" s="2">
         <v>45870</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <f t="shared" si="1"/>
-        <v>40</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="42">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B45" t="s">
         <v>416</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C45" s="10">
         <v>2025</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E45" s="2">
         <v>45868</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="42">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
         <v>417</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="C46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E46" s="2">
         <v>45867</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="42">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B47" t="s">
         <v>418</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C47" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E47" s="2">
         <v>45860</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <f t="shared" si="1"/>
-        <v>43</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="42">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
         <v>419</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C48" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E48" s="2">
         <v>45846</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="B48" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="42">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B49" t="s">
         <v>420</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C49" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
         <v>77</v>
-      </c>
-      <c r="E48" s="2">
-        <v>45833</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="B49" t="s">
-        <v>421</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
-        <v>78</v>
       </c>
       <c r="E49" s="2">
         <v>45833</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <f t="shared" si="1"/>
+      <c r="A50" s="42">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B50" t="s">
+        <v>421</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50" s="2">
+        <v>45833</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="42">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
         <v>422</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C51" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
         <v>82</v>
-      </c>
-      <c r="E50" s="2">
-        <v>45820</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <f t="shared" si="1"/>
-        <v>47</v>
-      </c>
-      <c r="B51" t="s">
-        <v>423</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
-        <v>83</v>
       </c>
       <c r="E51" s="2">
         <v>45820</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <f t="shared" si="1"/>
+      <c r="A52" s="42">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B52" t="s">
+        <v>423</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" s="2">
+        <v>45820</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="42">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B53" t="s">
         <v>424</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C53" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
         <v>84</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E53" s="2">
         <v>45818</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <f t="shared" si="1"/>
-        <v>49</v>
-      </c>
-      <c r="B53" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="42">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B54" t="s">
         <v>425</v>
       </c>
-      <c r="C53" s="10">
+      <c r="C54" s="10">
         <v>2025</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>86</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E54" s="2">
         <v>45807</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="B54" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="42">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
         <v>426</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" t="s">
+      <c r="C55" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
         <v>96</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E55" s="2">
         <v>45793</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="42">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
         <v>427</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C56" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" t="s">
         <v>97</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E56" s="2">
         <v>45784</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="42">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B57" t="s">
         <v>428</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C57" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
         <v>98</v>
-      </c>
-      <c r="E56" s="2">
-        <v>45783</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <f t="shared" si="1"/>
-        <v>53</v>
-      </c>
-      <c r="B57" t="s">
-        <v>429</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" t="s">
-        <v>99</v>
       </c>
       <c r="E57" s="2">
         <v>45783</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <f t="shared" si="1"/>
+      <c r="A58" s="42">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B58" t="s">
+        <v>429</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
+        <v>99</v>
+      </c>
+      <c r="E58" s="2">
+        <v>45783</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="42">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B59" t="s">
         <v>430</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C59" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
         <v>101</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E59" s="2">
         <v>45771</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <f t="shared" si="1"/>
-        <v>55</v>
-      </c>
-      <c r="B59" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="42">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B60" t="s">
         <v>431</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C60" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
         <v>104</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E60" s="2">
         <v>45762</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-      <c r="B60" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="42">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B61" t="s">
         <v>432</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C61" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
         <v>105</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E61" s="2">
         <v>45750</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <f t="shared" si="1"/>
-        <v>57</v>
-      </c>
-      <c r="B61" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="42">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B62" t="s">
         <v>433</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C62" s="10">
         <v>2025</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>109</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E62" s="2">
         <v>45744</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <f t="shared" si="1"/>
-        <v>58</v>
-      </c>
-      <c r="B62" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="42">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B63" t="s">
         <v>110</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="C63" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
         <v>111</v>
-      </c>
-      <c r="E62" s="2">
-        <v>45743</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <f t="shared" si="1"/>
-        <v>59</v>
-      </c>
-      <c r="B63" t="s">
-        <v>434</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D63" t="s">
-        <v>113</v>
       </c>
       <c r="E63" s="2">
         <v>45743</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <f t="shared" si="1"/>
+      <c r="A64" s="42">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B64" t="s">
+        <v>434</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D64" t="s">
+        <v>113</v>
+      </c>
+      <c r="E64" s="2">
+        <v>45743</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="42">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
         <v>435</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" t="s">
+      <c r="C65" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" t="s">
         <v>116</v>
       </c>
-      <c r="E64" s="2">
+      <c r="E65" s="2">
         <v>45735</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <f t="shared" si="1"/>
-        <v>61</v>
-      </c>
-      <c r="B65" t="s">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="42">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B66" t="s">
         <v>436</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D65" t="s">
-        <v>121</v>
-      </c>
-      <c r="E65" s="2">
-        <v>45726</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <f t="shared" si="1"/>
-        <v>62</v>
-      </c>
-      <c r="B66" t="s">
-        <v>437</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D66" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45726</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="42">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B67" t="s">
+        <v>437</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D67" t="s">
         <v>124</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E67" s="2">
         <v>45719</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <f t="shared" si="1"/>
-        <v>63</v>
-      </c>
-      <c r="B67" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="42">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
         <v>438</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" t="s">
+      <c r="C68" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E68" s="2">
         <v>45700</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <f t="shared" si="1"/>
-        <v>64</v>
-      </c>
-      <c r="B68" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="42">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B69" t="s">
         <v>439</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="C69" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D69" t="s">
         <v>128</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E69" s="2">
         <v>45695</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <f t="shared" si="1"/>
-        <v>65</v>
-      </c>
-      <c r="B69" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="42">
+        <f t="shared" ref="A70:A133" si="1">ROW()-4</f>
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
         <v>440</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C70" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" t="s">
         <v>130</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E70" s="2">
         <v>45694</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <f t="shared" si="1"/>
-        <v>66</v>
-      </c>
-      <c r="B70" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="42">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B71" t="s">
         <v>441</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="C71" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" t="s">
         <v>132</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E71" s="2">
         <v>45692</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
-      <c r="B71" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="42">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B72" t="s">
         <v>442</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="C72" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" t="s">
         <v>133</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E72" s="2">
         <v>45688</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-      <c r="B72" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="42">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
         <v>443</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C73" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" t="s">
         <v>135</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E73" s="2">
         <v>45684</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="42">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
         <v>444</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="C74" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" t="s">
         <v>138</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E74" s="2">
         <v>45678</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <f t="shared" ref="A74:A137" si="2">ROW()-4</f>
-        <v>70</v>
-      </c>
-      <c r="B74" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="42">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B75" t="s">
         <v>445</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C75" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" t="s">
         <v>141</v>
-      </c>
-      <c r="E74" s="2">
-        <v>45672</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <f t="shared" si="2"/>
-        <v>71</v>
-      </c>
-      <c r="B75" t="s">
-        <v>446</v>
-      </c>
-      <c r="C75" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" t="s">
-        <v>142</v>
       </c>
       <c r="E75" s="2">
         <v>45672</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <f t="shared" si="2"/>
+      <c r="A76" s="42">
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B76" t="s">
@@ -4288,1123 +4321,1138 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <f t="shared" si="2"/>
+      <c r="A77" s="42">
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B77" t="s">
+        <v>446</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D77" t="s">
+        <v>142</v>
+      </c>
+      <c r="E77" s="2">
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="42">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B78" t="s">
         <v>447</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D77" t="s">
+      <c r="C78" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" t="s">
         <v>144</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E78" s="2">
         <v>45662</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <f t="shared" si="2"/>
-        <v>74</v>
-      </c>
-      <c r="B78" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="42">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B79" t="s">
         <v>448</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="C79" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" t="s">
         <v>147</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E79" s="2">
         <v>45660</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <f t="shared" si="2"/>
-        <v>75</v>
-      </c>
-      <c r="B79" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="42">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B80" t="s">
         <v>449</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C80" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" t="s">
         <v>149</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E80" s="2">
         <v>45659</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <f t="shared" si="2"/>
-        <v>76</v>
-      </c>
-      <c r="B80" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="42">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B81" t="s">
         <v>450</v>
-      </c>
-      <c r="C80" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D80" t="s">
-        <v>152</v>
-      </c>
-      <c r="E80" s="2">
-        <v>45653</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <f t="shared" si="2"/>
-        <v>77</v>
-      </c>
-      <c r="B81" t="s">
-        <v>451</v>
       </c>
       <c r="C81" s="10">
         <v>2024</v>
       </c>
       <c r="D81" t="s">
+        <v>152</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45653</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="42">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B82" t="s">
+        <v>451</v>
+      </c>
+      <c r="C82" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D82" t="s">
         <v>154</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E82" s="2">
         <v>45650</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <f t="shared" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="B82" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="42">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B83" t="s">
         <v>452</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D82" t="s">
+      <c r="C83" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D83" t="s">
         <v>155</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E83" s="2">
         <v>45643</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <f t="shared" si="2"/>
-        <v>79</v>
-      </c>
-      <c r="B83" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="42">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B84" t="s">
         <v>284</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C84" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D84" t="s">
         <v>156</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E84" s="2">
         <v>45639</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <f t="shared" si="2"/>
-        <v>80</v>
-      </c>
-      <c r="B84" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="42">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B85" t="s">
         <v>453</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D84" t="s">
+      <c r="C85" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" t="s">
         <v>160</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E85" s="2">
         <v>45610</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <f t="shared" si="2"/>
-        <v>81</v>
-      </c>
-      <c r="B85" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="42">
+        <f t="shared" si="1"/>
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
         <v>454</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C86" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D86" t="s">
         <v>161</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E86" s="2">
         <v>45609</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <f t="shared" si="2"/>
-        <v>82</v>
-      </c>
-      <c r="B86" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="42">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B87" t="s">
         <v>455</v>
       </c>
-      <c r="C86" s="10">
+      <c r="C87" s="10">
         <v>2024</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D87" t="s">
         <v>162</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E87" s="2">
         <v>45601</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <f t="shared" si="2"/>
-        <v>83</v>
-      </c>
-      <c r="B87" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="42">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B88" t="s">
         <v>456</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D87" t="s">
+      <c r="C88" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" t="s">
         <v>163</v>
-      </c>
-      <c r="E87" s="2">
-        <v>45597</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <f t="shared" si="2"/>
-        <v>84</v>
-      </c>
-      <c r="B88" t="s">
-        <v>457</v>
-      </c>
-      <c r="C88" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" t="s">
-        <v>164</v>
       </c>
       <c r="E88" s="2">
         <v>45597</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <f t="shared" si="2"/>
+      <c r="A89" s="42">
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B89" t="s">
+        <v>457</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D89" t="s">
+        <v>164</v>
+      </c>
+      <c r="E89" s="2">
+        <v>45597</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="42">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B90" t="s">
         <v>458</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="C90" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" t="s">
         <v>166</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E90" s="2">
         <v>45593</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <f t="shared" si="2"/>
-        <v>86</v>
-      </c>
-      <c r="B90" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="42">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B91" t="s">
         <v>459</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C91" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" t="s">
         <v>169</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E91" s="2">
         <v>45588</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <f t="shared" si="2"/>
-        <v>87</v>
-      </c>
-      <c r="B91" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="42">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B92" t="s">
         <v>460</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C92" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" t="s">
         <v>171</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E92" s="2">
         <v>45572</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <f t="shared" si="2"/>
-        <v>88</v>
-      </c>
-      <c r="B92" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="42">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B93" t="s">
         <v>461</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="C93" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" t="s">
         <v>176</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E93" s="2">
         <v>45562</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <f t="shared" si="2"/>
-        <v>89</v>
-      </c>
-      <c r="B93" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="42">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B94" t="s">
         <v>462</v>
       </c>
-      <c r="C93" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C94" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" t="s">
         <v>177</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E94" s="2">
         <v>45555</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <f t="shared" si="2"/>
-        <v>90</v>
-      </c>
-      <c r="B94" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="42">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B95" t="s">
         <v>463</v>
       </c>
-      <c r="C94" s="10">
+      <c r="C95" s="10">
         <v>2024</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D95" t="s">
         <v>180</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E95" s="2">
         <v>45547</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <f t="shared" si="2"/>
-        <v>91</v>
-      </c>
-      <c r="B95" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="42">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B96" t="s">
         <v>464</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D95" t="s">
+      <c r="C96" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D96" t="s">
         <v>183</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E96" s="2">
         <v>45538</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <f t="shared" si="2"/>
-        <v>92</v>
-      </c>
-      <c r="B96" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="42">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B97" t="s">
         <v>465</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="C97" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D97" t="s">
         <v>185</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E97" s="2">
         <v>45534</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <f t="shared" si="2"/>
-        <v>93</v>
-      </c>
-      <c r="B97" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="42">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B98" t="s">
         <v>466</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D97" t="s">
-        <v>186</v>
-      </c>
-      <c r="E97" s="2">
-        <v>45533</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <f t="shared" si="2"/>
-        <v>94</v>
-      </c>
-      <c r="B98" t="s">
-        <v>467</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D98" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E98" s="2">
         <v>45533</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <f t="shared" si="2"/>
+      <c r="A99" s="42">
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B99" t="s">
+        <v>467</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D99" t="s">
+        <v>187</v>
+      </c>
+      <c r="E99" s="2">
+        <v>45533</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="42">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B100" t="s">
         <v>468</v>
-      </c>
-      <c r="C99" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D99" t="s">
-        <v>188</v>
-      </c>
-      <c r="E99" s="2">
-        <v>45526</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <f t="shared" si="2"/>
-        <v>96</v>
-      </c>
-      <c r="B100" t="s">
-        <v>469</v>
       </c>
       <c r="C100" s="10">
         <v>2024</v>
       </c>
       <c r="D100" t="s">
+        <v>188</v>
+      </c>
+      <c r="E100" s="2">
+        <v>45526</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="42">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B101" t="s">
+        <v>469</v>
+      </c>
+      <c r="C101" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D101" t="s">
         <v>191</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E101" s="2">
         <v>45518</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <f t="shared" si="2"/>
-        <v>97</v>
-      </c>
-      <c r="B101" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="42">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B102" t="s">
         <v>470</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D101" t="s">
+      <c r="C102" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D102" t="s">
         <v>194</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E102" s="2">
         <v>45502</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <f t="shared" si="2"/>
-        <v>98</v>
-      </c>
-      <c r="B102" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="42">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B103" t="s">
         <v>471</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="C103" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D103" t="s">
         <v>195</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E103" s="2">
         <v>45498</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <f t="shared" si="2"/>
-        <v>99</v>
-      </c>
-      <c r="B103" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="42">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B104" t="s">
         <v>472</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="C104" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D104" t="s">
         <v>196</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E104" s="2">
         <v>45489</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <f t="shared" si="2"/>
-        <v>100</v>
-      </c>
-      <c r="B104" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="42">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B105" t="s">
         <v>473</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="C105" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D105" t="s">
         <v>199</v>
-      </c>
-      <c r="E104" s="2">
-        <v>45469</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <f t="shared" si="2"/>
-        <v>101</v>
-      </c>
-      <c r="B105" t="s">
-        <v>474</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D105" t="s">
-        <v>200</v>
       </c>
       <c r="E105" s="2">
         <v>45469</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <f t="shared" si="2"/>
+      <c r="A106" s="42">
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B106" t="s">
+        <v>474</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" t="s">
+        <v>200</v>
+      </c>
+      <c r="E106" s="2">
+        <v>45469</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="42">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B107" t="s">
         <v>202</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C107" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D107" t="s">
         <v>203</v>
-      </c>
-      <c r="E106" s="2">
-        <v>45455</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <f t="shared" si="2"/>
-        <v>103</v>
-      </c>
-      <c r="B107" t="s">
-        <v>475</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D107" t="s">
-        <v>206</v>
       </c>
       <c r="E107" s="2">
         <v>45455</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <f t="shared" si="2"/>
+      <c r="A108" s="42">
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B108" t="s">
+        <v>475</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" t="s">
+        <v>206</v>
+      </c>
+      <c r="E108" s="2">
+        <v>45455</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="42">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B109" t="s">
         <v>476</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C109" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" t="s">
         <v>162</v>
-      </c>
-      <c r="E108" s="2">
-        <v>45449</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <f t="shared" si="2"/>
-        <v>105</v>
-      </c>
-      <c r="B109" t="s">
-        <v>477</v>
-      </c>
-      <c r="C109" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D109" t="s">
-        <v>209</v>
       </c>
       <c r="E109" s="2">
         <v>45449</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <f t="shared" si="2"/>
+      <c r="A110" s="42">
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B110" t="s">
+        <v>477</v>
+      </c>
+      <c r="C110" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D110" t="s">
+        <v>209</v>
+      </c>
+      <c r="E110" s="2">
+        <v>45449</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="42">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B111" t="s">
         <v>478</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="C111" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111" t="s">
         <v>212</v>
       </c>
-      <c r="E110" s="2">
+      <c r="E111" s="2">
         <v>45446</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <f t="shared" si="2"/>
-        <v>107</v>
-      </c>
-      <c r="B111" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="42">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B112" t="s">
         <v>479</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D111" t="s">
+      <c r="C112" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D112" t="s">
         <v>213</v>
       </c>
-      <c r="E111" s="2">
+      <c r="E112" s="2">
         <v>45441</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <f t="shared" si="2"/>
-        <v>108</v>
-      </c>
-      <c r="B112" t="s">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="42">
+        <f t="shared" si="1"/>
+        <v>109</v>
+      </c>
+      <c r="B113" t="s">
         <v>480</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D112" t="s">
-        <v>214</v>
-      </c>
-      <c r="E112" s="2">
-        <v>45440</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <f t="shared" si="2"/>
-        <v>109</v>
-      </c>
-      <c r="B113" t="s">
-        <v>481</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D113" t="s">
+        <v>214</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45440</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="42">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="B114" t="s">
+        <v>481</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D114" t="s">
         <v>215</v>
       </c>
-      <c r="E113" s="2">
+      <c r="E114" s="2">
         <v>45439</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <f t="shared" si="2"/>
-        <v>110</v>
-      </c>
-      <c r="B114" t="s">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="42">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="B115" t="s">
         <v>482</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D114" t="s">
+      <c r="C115" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D115" t="s">
         <v>217</v>
       </c>
-      <c r="E114" s="2">
+      <c r="E115" s="2">
         <v>45422</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <f t="shared" si="2"/>
-        <v>111</v>
-      </c>
-      <c r="B115" t="s">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="42">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="B116" t="s">
         <v>483</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="C116" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D116" t="s">
         <v>221</v>
       </c>
-      <c r="E115" s="2">
+      <c r="E116" s="2">
         <v>45415</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <f t="shared" si="2"/>
-        <v>112</v>
-      </c>
-      <c r="B116" t="s">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="42">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="B117" t="s">
         <v>285</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D116" t="s">
+      <c r="C117" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D117" t="s">
         <v>223</v>
       </c>
-      <c r="E116" s="2">
+      <c r="E117" s="2">
         <v>45411</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <f t="shared" si="2"/>
-        <v>113</v>
-      </c>
-      <c r="B117" t="s">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="42">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
+      <c r="B118" t="s">
         <v>484</v>
       </c>
-      <c r="C117" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D117" t="s">
+      <c r="C118" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D118" t="s">
         <v>228</v>
-      </c>
-      <c r="E117" s="2">
-        <v>45391</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <f t="shared" si="2"/>
-        <v>114</v>
-      </c>
-      <c r="B118" t="s">
-        <v>485</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D118" t="s">
-        <v>229</v>
       </c>
       <c r="E118" s="2">
         <v>45391</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <f t="shared" si="2"/>
+      <c r="A119" s="42">
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B119" t="s">
+        <v>485</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D119" t="s">
+        <v>229</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45391</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="42">
+        <f t="shared" si="1"/>
+        <v>116</v>
+      </c>
+      <c r="B120" t="s">
         <v>486</v>
       </c>
-      <c r="C119" s="10" t="s">
+      <c r="C120" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D120" t="s">
         <v>105</v>
       </c>
-      <c r="E119" s="2">
+      <c r="E120" s="2">
         <v>45379</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <f t="shared" si="2"/>
-        <v>116</v>
-      </c>
-      <c r="B120" t="s">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="42">
+        <f t="shared" si="1"/>
+        <v>117</v>
+      </c>
+      <c r="B121" t="s">
         <v>487</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D120" t="s">
-        <v>238</v>
-      </c>
-      <c r="E120" s="2">
-        <v>45378</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <f t="shared" si="2"/>
-        <v>117</v>
-      </c>
-      <c r="B121" t="s">
-        <v>488</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D121" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E121" s="2">
         <v>45378</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <f t="shared" si="2"/>
+      <c r="A122" s="42">
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B122" t="s">
+        <v>488</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D122" t="s">
+        <v>239</v>
+      </c>
+      <c r="E122" s="2">
+        <v>45378</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="42">
+        <f t="shared" si="1"/>
+        <v>119</v>
+      </c>
+      <c r="B123" t="s">
         <v>489</v>
       </c>
-      <c r="C122" s="10" t="s">
+      <c r="C123" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D123" t="s">
         <v>246</v>
       </c>
-      <c r="E122" s="2">
+      <c r="E123" s="2">
         <v>45365</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <f t="shared" si="2"/>
-        <v>119</v>
-      </c>
-      <c r="B123" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="42">
+        <f t="shared" si="1"/>
+        <v>120</v>
+      </c>
+      <c r="B124" t="s">
         <v>490</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D123" t="s">
-        <v>251</v>
-      </c>
-      <c r="E123" s="2">
-        <v>45362</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <f t="shared" si="2"/>
-        <v>120</v>
-      </c>
-      <c r="B124" t="s">
-        <v>504</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D124" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E124" s="2">
         <v>45362</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <f t="shared" si="2"/>
+      <c r="A125" s="42">
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D125" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E125" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <f t="shared" si="2"/>
+      <c r="A126" s="42">
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D126" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E126" s="2">
         <v>45358</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <f t="shared" si="2"/>
+      <c r="A127" s="42">
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D127" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E127" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <f t="shared" si="2"/>
+      <c r="A128" s="42">
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E128" s="2">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <f t="shared" si="2"/>
+      <c r="A129" s="42">
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D129" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E129" s="2">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <f t="shared" si="2"/>
+      <c r="A130" s="42">
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D130" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E130" s="2">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <f t="shared" si="2"/>
+      <c r="A131" s="42">
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D131" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E131" s="2">
         <v>45336</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <f t="shared" si="2"/>
+      <c r="A132" s="42">
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E132" s="2">
         <v>45336</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <f t="shared" si="2"/>
+      <c r="A133" s="42">
+        <f t="shared" si="1"/>
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E133" s="2">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <f t="shared" si="2"/>
+      <c r="A134" s="42">
+        <f t="shared" ref="A134:A139" si="2">ROW()-4</f>
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E134" s="2">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135">
+      <c r="A135" s="42">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D135" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E135" s="2">
-        <v>45324</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136">
+      <c r="A136" s="42">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>493</v>
-      </c>
-      <c r="C136" s="10">
-        <v>2024</v>
+        <v>494</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D136" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E136" s="2">
-        <v>45322</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137">
+      <c r="A137" s="42">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C137" s="10">
         <v>2024</v>
       </c>
       <c r="D137" t="s">
+        <v>275</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="42">
+        <f t="shared" si="2"/>
+        <v>134</v>
+      </c>
+      <c r="B138" t="s">
+        <v>492</v>
+      </c>
+      <c r="C138" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D138" t="s">
         <v>278</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E138" s="2">
         <v>45303</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <f t="shared" ref="A138" si="3">ROW()-4</f>
-        <v>134</v>
-      </c>
-      <c r="B138" t="s">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="42">
+        <f t="shared" si="2"/>
+        <v>135</v>
+      </c>
+      <c r="B139" t="s">
         <v>491</v>
       </c>
-      <c r="C138" s="10" t="s">
+      <c r="C139" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D139" t="s">
         <v>280</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E139" s="2">
         <v>45294</v>
       </c>
-    </row>
-    <row r="293" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B293" s="3"/>
     </row>
     <row r="294" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B294" s="3"/>
@@ -5418,17 +5466,17 @@
     <row r="297" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B297" s="3"/>
     </row>
-    <row r="300" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B300" s="3"/>
-    </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B305" s="3"/>
-    </row>
-    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B308" s="3"/>
-    </row>
-    <row r="310" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B310" s="3"/>
+    <row r="298" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B298" s="3"/>
+    </row>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B301" s="3"/>
+    </row>
+    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B306" s="3"/>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B309" s="3"/>
     </row>
     <row r="311" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B311" s="3"/>
@@ -5436,8 +5484,8 @@
     <row r="312" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B312" s="3"/>
     </row>
-    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B314" s="3"/>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B313" s="3"/>
     </row>
     <row r="315" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B315" s="3"/>
@@ -5451,15 +5499,18 @@
     <row r="318" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B318" s="3"/>
     </row>
-    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B320" s="3"/>
-    </row>
-    <row r="371" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B371" s="3"/>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B319" s="3"/>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B321" s="3"/>
+    </row>
+    <row r="372" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B372" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:E136">
-    <sortCondition descending="1" sortBy="icon" ref="E13:E136"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:E137">
+    <sortCondition descending="1" sortBy="icon" ref="E14:E137"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5468,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5501,135 +5552,143 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
+        <f>ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>817</v>
-      </c>
-      <c r="C5" s="31">
-        <v>2026</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>818</v>
-      </c>
-      <c r="E5" s="32">
-        <v>46113</v>
+      <c r="B5" s="43" t="s">
+        <v>824</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>820</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>825</v>
+      </c>
+      <c r="E5" s="45">
+        <v>46119</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
+        <f t="shared" ref="A6:A69" si="0">ROW()-4</f>
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>819</v>
-      </c>
-      <c r="C6" s="31" t="s">
+      <c r="B6" s="43" t="s">
+        <v>826</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>820</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>821</v>
-      </c>
-      <c r="E6" s="32">
-        <v>46113</v>
+      <c r="D6" s="43" t="s">
+        <v>827</v>
+      </c>
+      <c r="E6" s="45">
+        <v>46118</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="s">
-        <v>800</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>801</v>
-      </c>
-      <c r="E7" s="32">
-        <v>46112</v>
+      <c r="B7" s="43" t="s">
+        <v>828</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>820</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>829</v>
+      </c>
+      <c r="E7" s="45">
+        <v>46114</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" s="27" t="s">
-        <v>802</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>803</v>
-      </c>
-      <c r="E8" s="32">
-        <v>46112</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>817</v>
+      </c>
+      <c r="C8" s="44">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="43" t="s">
+        <v>818</v>
+      </c>
+      <c r="E8" s="45">
+        <v>46113</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B9" s="27" t="s">
-        <v>804</v>
-      </c>
-      <c r="C9" s="31">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>805</v>
-      </c>
-      <c r="E9" s="32">
-        <v>46112</v>
+      <c r="B9" s="43" t="s">
+        <v>819</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>820</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>821</v>
+      </c>
+      <c r="E9" s="45">
+        <v>46113</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="C10" s="31">
         <v>2026</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="E10" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>808</v>
-      </c>
-      <c r="C11" s="31">
-        <v>2026</v>
+        <v>819</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>820</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="E11" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>810</v>
-      </c>
-      <c r="C12" s="31">
-        <v>2026</v>
+        <v>800</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="E12" s="32">
         <v>46112</v>
@@ -5637,2823 +5696,3079 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>794</v>
-      </c>
-      <c r="C13" s="31">
-        <v>2026</v>
+        <v>802</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="E13" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>796</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>4</v>
+        <v>804</v>
+      </c>
+      <c r="C14" s="31">
+        <v>2026</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="E14" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>798</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>4</v>
+        <v>806</v>
+      </c>
+      <c r="C15" s="31">
+        <v>2026</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="E15" s="32">
-        <v>46104</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>781</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>4</v>
+        <v>808</v>
+      </c>
+      <c r="C16" s="31">
+        <v>2026</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>782</v>
-      </c>
-      <c r="E16" s="34">
-        <v>46100</v>
+        <v>809</v>
+      </c>
+      <c r="E16" s="32">
+        <v>46112</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>783</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>4</v>
+        <v>810</v>
+      </c>
+      <c r="C17" s="31">
+        <v>2026</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>784</v>
-      </c>
-      <c r="E17" s="34">
-        <v>46099</v>
+        <v>811</v>
+      </c>
+      <c r="E17" s="32">
+        <v>46112</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>785</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>4</v>
+        <v>794</v>
+      </c>
+      <c r="C18" s="31">
+        <v>2026</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>786</v>
-      </c>
-      <c r="E18" s="34">
-        <v>46097</v>
+        <v>795</v>
+      </c>
+      <c r="E18" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>761</v>
+        <v>796</v>
       </c>
       <c r="C19" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>762</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>756</v>
+        <v>797</v>
+      </c>
+      <c r="E19" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>764</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>756</v>
+        <v>799</v>
+      </c>
+      <c r="E20" s="32">
+        <v>46104</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>765</v>
+        <v>781</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>766</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>756</v>
+        <v>782</v>
+      </c>
+      <c r="E21" s="34">
+        <v>46100</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>767</v>
+        <v>783</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>768</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>769</v>
+        <v>784</v>
+      </c>
+      <c r="E22" s="34">
+        <v>46099</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B23" t="s">
-        <v>588</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
-        <v>384</v>
-      </c>
-      <c r="E23" s="2">
-        <v>46267</v>
+      <c r="B23" s="27" t="s">
+        <v>785</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>786</v>
+      </c>
+      <c r="E23" s="34">
+        <v>46097</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B24" t="s">
-        <v>589</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
-        <v>376</v>
-      </c>
-      <c r="E24" s="2">
-        <v>46144</v>
+      <c r="B24" s="27" t="s">
+        <v>761</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>762</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B25" t="s">
-        <v>590</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" t="s">
-        <v>377</v>
-      </c>
-      <c r="E25" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="27" t="s">
+        <v>763</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>764</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B26" t="s">
-        <v>591</v>
-      </c>
-      <c r="C26" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D26" t="s">
-        <v>375</v>
-      </c>
-      <c r="E26" s="2">
-        <v>46051</v>
+      <c r="B26" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>766</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B27" t="s">
-        <v>592</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="2">
-        <v>46038</v>
+      <c r="B27" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>768</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>593</v>
-      </c>
-      <c r="C28" s="10">
-        <v>2026</v>
+        <v>588</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>11</v>
+        <v>384</v>
       </c>
       <c r="E28" s="2">
-        <v>46025</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>594</v>
-      </c>
-      <c r="C29" s="10">
-        <v>2025</v>
+        <v>589</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>376</v>
       </c>
       <c r="E29" s="2">
-        <v>46022</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>13</v>
+        <v>377</v>
       </c>
       <c r="E30" s="2">
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="C31" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>375</v>
       </c>
       <c r="E31" s="2">
-        <v>46020</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>597</v>
-      </c>
-      <c r="C32" s="10">
-        <v>2025</v>
+        <v>592</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E32" s="2">
-        <v>46009</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>598</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>4</v>
+        <v>593</v>
+      </c>
+      <c r="C33" s="10">
+        <v>2026</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2">
-        <v>46000</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>599</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>4</v>
+        <v>594</v>
+      </c>
+      <c r="C34" s="10">
+        <v>2025</v>
       </c>
       <c r="D34" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E34" s="2">
-        <v>45978</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E35" s="2">
-        <v>45965</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C36" s="10">
         <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E36" s="2">
-        <v>45951</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="C37" s="10">
         <v>2025</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E37" s="2">
-        <v>45945</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E38" s="2">
-        <v>45945</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E39" s="2">
-        <v>45945</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E40" s="2">
-        <v>45945</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>605</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>4</v>
+        <v>601</v>
+      </c>
+      <c r="C41" s="10">
+        <v>2025</v>
       </c>
       <c r="D41" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E41" s="2">
-        <v>45944</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>606</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>4</v>
+        <v>602</v>
+      </c>
+      <c r="C42" s="10">
+        <v>2025</v>
       </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E42" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E43" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E44" s="2">
-        <v>45933</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E45" s="2">
-        <v>45933</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>610</v>
+      <c r="B46" t="s">
+        <v>605</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E46" s="2">
-        <v>45933</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>611</v>
+      <c r="B47" t="s">
+        <v>606</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E47" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>612</v>
+      <c r="B48" t="s">
+        <v>607</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E48" s="2">
-        <v>45930</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>613</v>
+      <c r="B49" t="s">
+        <v>608</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E49" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>614</v>
+      <c r="B50" t="s">
+        <v>609</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="E50" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E51" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="C52" s="10">
-        <v>2025</v>
+        <v>611</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E52" s="2">
-        <v>45923</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E53" s="2">
-        <v>45918</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E54" s="2">
-        <v>45908</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
+        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E55" s="2">
-        <v>45897</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
+        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E56" s="2">
-        <v>45891</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
+        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>621</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C57" s="10">
+        <v>2025</v>
       </c>
       <c r="D57" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E57" s="2">
-        <v>45891</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
+        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E58" s="2">
-        <v>45888</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
+        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E59" s="2">
-        <v>45880</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>69</v>
+        <v>619</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E60" s="2">
-        <v>45855</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
+        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E61" s="2">
-        <v>45838</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
+        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E62" s="2">
-        <v>45838</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
+        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E63" s="2">
-        <v>45835</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>75</v>
+        <v>623</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E64" s="2">
-        <v>45833</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
+        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>627</v>
+        <v>69</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E65" s="2">
-        <v>45831</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
+        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E66" s="2">
-        <v>45825</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E67" s="2">
-        <v>45825</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E68" s="2">
-        <v>45825</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>631</v>
+        <v>75</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E69" s="2">
-        <v>45808</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
+        <f t="shared" ref="A70:A133" si="1">ROW()-4</f>
         <v>66</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="E70" s="2">
-        <v>45803</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="E71" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E72" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
+        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="E73" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
+        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E74" s="2">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
+        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E75" s="2">
         <v>45803</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E76" s="2">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
+        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E77" s="2">
-        <v>45796</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
+        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E78" s="2">
-        <v>45794</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="E79" s="2">
-        <v>45779</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E80" s="2">
-        <v>45770</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81">
+        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E81" s="2">
-        <v>45762</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82">
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="C82" s="10">
-        <v>2025</v>
+        <v>639</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E82" s="2">
-        <v>45749</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
+        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="C83" s="10">
-        <v>2025</v>
+        <v>640</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E83" s="2">
-        <v>45749</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
+        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E84" s="2">
-        <v>45748</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
+        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E85" s="2">
-        <v>45736</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
+        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="E86" s="2">
-        <v>45734</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
+        <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>649</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>114</v>
+        <v>644</v>
+      </c>
+      <c r="C87" s="10">
+        <v>2025</v>
       </c>
       <c r="D87" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E87" s="2">
-        <v>45726</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
+        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="C88" s="10">
         <v>2025</v>
       </c>
       <c r="D88" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E88" s="2">
-        <v>45726</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E89" s="2">
-        <v>45726</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
+        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E90" s="2">
-        <v>45723</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
+        <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E91" s="2">
-        <v>45721</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
+        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E92" s="2">
-        <v>45698</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
+        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>655</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C93" s="10">
+        <v>2025</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E93" s="2">
-        <v>45695</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="E94" s="2">
-        <v>45694</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
+        <f t="shared" si="1"/>
         <v>91</v>
       </c>
-      <c r="B95" t="s">
-        <v>587</v>
+      <c r="B95" s="10" t="s">
+        <v>652</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E95" s="2">
-        <v>45692</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
+        <f t="shared" si="1"/>
         <v>92</v>
       </c>
-      <c r="B96" t="s">
-        <v>586</v>
+      <c r="B96" s="10" t="s">
+        <v>653</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E96" s="2">
-        <v>45686</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
+        <f t="shared" si="1"/>
         <v>93</v>
       </c>
-      <c r="B97" t="s">
-        <v>585</v>
+      <c r="B97" s="10" t="s">
+        <v>654</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E97" s="2">
-        <v>45681</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
+        <f t="shared" si="1"/>
         <v>94</v>
       </c>
-      <c r="B98" t="s">
-        <v>584</v>
+      <c r="B98" s="10" t="s">
+        <v>655</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E98" s="2">
-        <v>45678</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
+        <f t="shared" si="1"/>
         <v>95</v>
       </c>
-      <c r="B99" t="s">
-        <v>583</v>
+      <c r="B99" s="10" t="s">
+        <v>656</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E99" s="2">
-        <v>45677</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="E100" s="2">
-        <v>45677</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
+        <f t="shared" si="1"/>
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E101" s="2">
-        <v>45670</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
+        <f t="shared" si="1"/>
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E102" s="2">
-        <v>45661</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
+        <f t="shared" si="1"/>
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E103" s="2">
-        <v>45661</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
+        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E104" s="2">
-        <v>45659</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
+        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E105" s="2">
-        <v>45656</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
+        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E106" s="2">
-        <v>45656</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
+        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>575</v>
-      </c>
-      <c r="C107" s="10">
-        <v>2024</v>
+        <v>580</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E107" s="2">
-        <v>45652</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
+        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="E108" s="2">
-        <v>45650</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
+        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="E109" s="2">
-        <v>45631</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
+        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E110" s="2">
-        <v>45625</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E111" s="2">
-        <v>45622</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>570</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>114</v>
+        <v>575</v>
+      </c>
+      <c r="C112" s="10">
+        <v>2024</v>
       </c>
       <c r="D112" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E112" s="2">
-        <v>45593</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="C113" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>167</v>
+        <v>119</v>
       </c>
       <c r="E113" s="2">
-        <v>45588</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
+        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="E114" s="2">
-        <v>45588</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D115" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E115" s="2">
-        <v>45578</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D116" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E116" s="2">
-        <v>45566</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
+        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E117" s="2">
-        <v>45566</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E118" s="2">
-        <v>45565</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
+        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E119" s="2">
-        <v>45563</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
+        <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E120" s="2">
-        <v>45553</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
+        <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>119</v>
+        <v>172</v>
       </c>
       <c r="E121" s="2">
-        <v>45548</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
+        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E122" s="2">
-        <v>45548</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
+        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E123" s="2">
-        <v>45539</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
+        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E124" s="2">
-        <v>45538</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
+        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E125" s="2">
-        <v>45537</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
+        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>189</v>
+        <v>119</v>
       </c>
       <c r="E126" s="2">
-        <v>45523</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
+        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="E127" s="2">
-        <v>45520</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
+        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="E128" s="2">
-        <v>45505</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
+        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E129" s="2">
-        <v>45502</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
+        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="E130" s="2">
-        <v>45478</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
+        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="E131" s="2">
-        <v>45478</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
+        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="E132" s="2">
-        <v>45462</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
+        <f t="shared" si="1"/>
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>204</v>
+        <v>554</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E133" s="2">
-        <v>45455</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
+        <f t="shared" ref="A134:A183" si="2">ROW()-4</f>
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="E134" s="2">
-        <v>45454</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
+        <f t="shared" si="2"/>
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E135" s="2">
-        <v>45449</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
+        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E136" s="2">
-        <v>45448</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
+        <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E137" s="2">
-        <v>45446</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
+        <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>545</v>
+        <v>204</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="E138" s="2">
-        <v>45432</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
+        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="E139" s="2">
-        <v>45420</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
+        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E140" s="2">
-        <v>45418</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
+        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="E141" s="2">
-        <v>45416</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
+        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="E142" s="2">
-        <v>45407</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
+        <f t="shared" si="2"/>
         <v>139</v>
       </c>
-      <c r="B143" s="6" t="s">
-        <v>540</v>
+      <c r="B143" t="s">
+        <v>545</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E143" s="2">
-        <v>45405</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
+        <f t="shared" si="2"/>
         <v>140</v>
       </c>
-      <c r="B144" s="6" t="s">
-        <v>535</v>
+      <c r="B144" t="s">
+        <v>544</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="E144" s="2">
-        <v>45397</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
+        <f t="shared" si="2"/>
         <v>141</v>
       </c>
-      <c r="B145" s="6" t="s">
-        <v>539</v>
+      <c r="B145" t="s">
+        <v>543</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="E145" s="2">
-        <v>45397</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
+        <f t="shared" si="2"/>
         <v>142</v>
       </c>
-      <c r="B146" s="6" t="s">
-        <v>538</v>
+      <c r="B146" t="s">
+        <v>542</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="E146" s="2">
-        <v>45387</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
+        <f t="shared" si="2"/>
         <v>143</v>
       </c>
-      <c r="B147" s="6" t="s">
-        <v>537</v>
+      <c r="B147" t="s">
+        <v>541</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E147" s="2">
-        <v>45387</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
+        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E148" s="2">
-        <v>45387</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
+        <f t="shared" si="2"/>
         <v>145</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>505</v>
+        <v>535</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E149" s="2">
-        <v>45385</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
+        <f t="shared" si="2"/>
         <v>146</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E150" s="2">
-        <v>45384</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
+        <f t="shared" si="2"/>
         <v>147</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="C151" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E151" s="2">
-        <v>45378</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
+        <f t="shared" si="2"/>
         <v>148</v>
       </c>
-      <c r="B152" t="s">
-        <v>533</v>
+      <c r="B152" s="6" t="s">
+        <v>537</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="E152" s="2">
-        <v>45373</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
+        <f t="shared" si="2"/>
         <v>149</v>
       </c>
-      <c r="B153" t="s">
-        <v>532</v>
+      <c r="B153" s="6" t="s">
+        <v>536</v>
       </c>
       <c r="C153" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D153" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E153" s="2">
-        <v>45373</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
+        <f t="shared" si="2"/>
         <v>150</v>
       </c>
-      <c r="B154" t="s">
-        <v>531</v>
+      <c r="B154" s="6" t="s">
+        <v>505</v>
       </c>
       <c r="C154" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="E154" s="2">
-        <v>45369</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
+        <f t="shared" si="2"/>
         <v>151</v>
       </c>
-      <c r="B155" t="s">
-        <v>530</v>
+      <c r="B155" s="6" t="s">
+        <v>534</v>
       </c>
       <c r="C155" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D155" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E155" s="2">
-        <v>45367</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
+        <f t="shared" si="2"/>
         <v>152</v>
       </c>
-      <c r="B156" t="s">
-        <v>529</v>
+      <c r="B156" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D156" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E156" s="2">
-        <v>45367</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
+        <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D157" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E157" s="2">
-        <v>45366</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
+        <f t="shared" si="2"/>
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D158" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E158" s="2">
-        <v>45365</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
+        <f t="shared" si="2"/>
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>247</v>
+        <v>117</v>
       </c>
       <c r="E159" s="2">
-        <v>45362</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
+        <f t="shared" si="2"/>
         <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D160" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="E160" s="2">
-        <v>45362</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
+        <f t="shared" si="2"/>
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D161" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E161" s="2">
-        <v>45362</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
+        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="E162" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
+        <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E163" s="2">
-        <v>45359</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
+        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D164" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E164" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
+        <f t="shared" si="2"/>
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D165" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E165" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
+        <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E166" s="2">
-        <v>45357</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
+        <f t="shared" si="2"/>
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="E167" s="2">
-        <v>45357</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
+        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="C168" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="E168" s="2">
-        <v>45352</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
+        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>219</v>
+        <v>254</v>
       </c>
       <c r="E169" s="2">
-        <v>45352</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
+        <f t="shared" si="2"/>
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D170" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E170" s="2">
-        <v>45352</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
+        <f t="shared" si="2"/>
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="E171" s="2">
-        <v>45351</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
+        <f t="shared" si="2"/>
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C172" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E172" s="2">
-        <v>45345</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
+        <f t="shared" si="2"/>
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="C173" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>270</v>
+        <v>233</v>
       </c>
       <c r="E173" s="2">
-        <v>45335</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
+        <f t="shared" si="2"/>
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>271</v>
+        <v>219</v>
       </c>
       <c r="E174" s="2">
-        <v>45334</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
+        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D175" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="E175" s="2">
-        <v>45314</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
+        <f t="shared" si="2"/>
         <v>172</v>
       </c>
-      <c r="B176" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C176" s="10">
-        <v>2023</v>
+      <c r="B176" t="s">
+        <v>514</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D176" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="E176" s="2">
-        <v>45306</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
+        <f t="shared" si="2"/>
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D177" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="E177" s="2">
-        <v>45294</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
+        <f t="shared" si="2"/>
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D178" t="s">
+        <v>270</v>
+      </c>
+      <c r="E178" s="2">
+        <v>45335</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179">
+        <f t="shared" si="2"/>
+        <v>175</v>
+      </c>
+      <c r="B179" t="s">
+        <v>512</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D179" t="s">
+        <v>271</v>
+      </c>
+      <c r="E179" s="2">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180">
+        <f t="shared" si="2"/>
+        <v>176</v>
+      </c>
+      <c r="B180" t="s">
+        <v>511</v>
+      </c>
+      <c r="C180" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D180" t="s">
+        <v>276</v>
+      </c>
+      <c r="E180" s="2">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181">
+        <f t="shared" si="2"/>
+        <v>177</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C181" s="10">
+        <v>2023</v>
+      </c>
+      <c r="D181" t="s">
+        <v>277</v>
+      </c>
+      <c r="E181" s="2">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182">
+        <f t="shared" si="2"/>
+        <v>178</v>
+      </c>
+      <c r="B182" t="s">
+        <v>509</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D182" t="s">
+        <v>279</v>
+      </c>
+      <c r="E182" s="2">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183">
+        <f t="shared" si="2"/>
+        <v>179</v>
+      </c>
+      <c r="B183" t="s">
+        <v>508</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D183" t="s">
         <v>281</v>
       </c>
-      <c r="E178" s="2">
+      <c r="E183" s="2">
         <v>45292</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{698573A4-D150-40DF-8C24-FBE0C35E7B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A726916E-D4D4-47BA-965F-831382A47E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -2598,7 +2598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2697,12 +2697,6 @@
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3021,7 +3015,7 @@
       <c r="E4" s="24"/>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="42">
+      <c r="A5">
         <f>ROW()-4</f>
         <v>1</v>
       </c>
@@ -3039,7 +3033,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42">
+      <c r="A6">
         <f t="shared" ref="A6:A69" si="0">ROW()-4</f>
         <v>2</v>
       </c>
@@ -3057,7 +3051,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42">
+      <c r="A7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -3075,7 +3069,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42">
+      <c r="A8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -3093,7 +3087,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="42">
+      <c r="A9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3111,7 +3105,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="42">
+      <c r="A10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -3130,7 +3124,7 @@
       <c r="F10" s="39"/>
     </row>
     <row r="11" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="42">
+      <c r="A11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -3148,7 +3142,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="42">
+      <c r="A12">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -3169,7 +3163,7 @@
       </c>
     </row>
     <row r="13" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="42">
+      <c r="A13">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -3187,7 +3181,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="42">
+      <c r="A14">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -3205,7 +3199,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="42">
+      <c r="A15">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -3223,7 +3217,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="42">
+      <c r="A16">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -3241,7 +3235,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="42">
+      <c r="A17">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -3259,7 +3253,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="42">
+      <c r="A18">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
@@ -3277,7 +3271,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="42">
+      <c r="A19">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -3295,7 +3289,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="42">
+      <c r="A20">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3313,7 +3307,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="42">
+      <c r="A21">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -3331,7 +3325,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="42">
+      <c r="A22">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -3349,7 +3343,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="42">
+      <c r="A23">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -3367,7 +3361,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="42">
+      <c r="A24">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -3385,7 +3379,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="42">
+      <c r="A25">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -3403,7 +3397,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="42">
+      <c r="A26">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -3421,7 +3415,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="42">
+      <c r="A27">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -3439,7 +3433,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="42">
+      <c r="A28">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -3457,7 +3451,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="42">
+      <c r="A29">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -3475,7 +3469,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="42">
+      <c r="A30">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -3493,7 +3487,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="42">
+      <c r="A31">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -3511,7 +3505,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="42">
+      <c r="A32">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -3529,7 +3523,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="42">
+      <c r="A33">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -3547,7 +3541,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="42">
+      <c r="A34">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -3565,7 +3559,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="42">
+      <c r="A35">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -3583,7 +3577,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="42">
+      <c r="A36">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -3601,7 +3595,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="42">
+      <c r="A37">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -3619,7 +3613,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="42">
+      <c r="A38">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -3637,7 +3631,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="42">
+      <c r="A39">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -3655,7 +3649,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="42">
+      <c r="A40">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -3673,7 +3667,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="42">
+      <c r="A41">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -3691,7 +3685,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="42">
+      <c r="A42">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -3709,7 +3703,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="42">
+      <c r="A43">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -3727,7 +3721,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="42">
+      <c r="A44">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -3745,7 +3739,7 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="42">
+      <c r="A45">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -3763,7 +3757,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="42">
+      <c r="A46">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -3781,7 +3775,7 @@
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="42">
+      <c r="A47">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -3799,7 +3793,7 @@
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="42">
+      <c r="A48">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -3817,7 +3811,7 @@
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="42">
+      <c r="A49">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -3835,7 +3829,7 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="42">
+      <c r="A50">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -3853,7 +3847,7 @@
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="42">
+      <c r="A51">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
@@ -3871,7 +3865,7 @@
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="42">
+      <c r="A52">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -3889,7 +3883,7 @@
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="42">
+      <c r="A53">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -3907,7 +3901,7 @@
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="42">
+      <c r="A54">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -3925,7 +3919,7 @@
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="42">
+      <c r="A55">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
@@ -3943,7 +3937,7 @@
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="42">
+      <c r="A56">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -3961,7 +3955,7 @@
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="42">
+      <c r="A57">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
@@ -3979,7 +3973,7 @@
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="42">
+      <c r="A58">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -3997,7 +3991,7 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="42">
+      <c r="A59">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
@@ -4015,7 +4009,7 @@
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="42">
+      <c r="A60">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
@@ -4033,7 +4027,7 @@
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="42">
+      <c r="A61">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -4051,7 +4045,7 @@
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="42">
+      <c r="A62">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
@@ -4069,7 +4063,7 @@
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="42">
+      <c r="A63">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
@@ -4087,7 +4081,7 @@
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="42">
+      <c r="A64">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -4105,7 +4099,7 @@
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="42">
+      <c r="A65">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
@@ -4123,7 +4117,7 @@
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="42">
+      <c r="A66">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
@@ -4141,7 +4135,7 @@
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="42">
+      <c r="A67">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
@@ -4159,7 +4153,7 @@
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="42">
+      <c r="A68">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
@@ -4177,7 +4171,7 @@
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="42">
+      <c r="A69">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
@@ -4195,7 +4189,7 @@
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="42">
+      <c r="A70">
         <f t="shared" ref="A70:A133" si="1">ROW()-4</f>
         <v>66</v>
       </c>
@@ -4213,7 +4207,7 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="42">
+      <c r="A71">
         <f t="shared" si="1"/>
         <v>67</v>
       </c>
@@ -4231,7 +4225,7 @@
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="42">
+      <c r="A72">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -4249,7 +4243,7 @@
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="42">
+      <c r="A73">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -4267,7 +4261,7 @@
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="42">
+      <c r="A74">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
@@ -4285,7 +4279,7 @@
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="42">
+      <c r="A75">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
@@ -4303,7 +4297,7 @@
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="42">
+      <c r="A76">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
@@ -4321,7 +4315,7 @@
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="42">
+      <c r="A77">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
@@ -4339,7 +4333,7 @@
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="42">
+      <c r="A78">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
@@ -4357,7 +4351,7 @@
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="42">
+      <c r="A79">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
@@ -4375,7 +4369,7 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="42">
+      <c r="A80">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
@@ -4393,7 +4387,7 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="42">
+      <c r="A81">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
@@ -4411,7 +4405,7 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="42">
+      <c r="A82">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
@@ -4429,7 +4423,7 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="42">
+      <c r="A83">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
@@ -4447,7 +4441,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="42">
+      <c r="A84">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
@@ -4465,7 +4459,7 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="42">
+      <c r="A85">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
@@ -4483,7 +4477,7 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="42">
+      <c r="A86">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
@@ -4501,7 +4495,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="42">
+      <c r="A87">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
@@ -4519,7 +4513,7 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="42">
+      <c r="A88">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
@@ -4537,7 +4531,7 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="42">
+      <c r="A89">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
@@ -4555,7 +4549,7 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="42">
+      <c r="A90">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
@@ -4573,7 +4567,7 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="42">
+      <c r="A91">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
@@ -4591,7 +4585,7 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="42">
+      <c r="A92">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
@@ -4609,7 +4603,7 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="42">
+      <c r="A93">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
@@ -4627,7 +4621,7 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="42">
+      <c r="A94">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
@@ -4645,7 +4639,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="42">
+      <c r="A95">
         <f t="shared" si="1"/>
         <v>91</v>
       </c>
@@ -4663,7 +4657,7 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="42">
+      <c r="A96">
         <f t="shared" si="1"/>
         <v>92</v>
       </c>
@@ -4681,7 +4675,7 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="42">
+      <c r="A97">
         <f t="shared" si="1"/>
         <v>93</v>
       </c>
@@ -4699,7 +4693,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="42">
+      <c r="A98">
         <f t="shared" si="1"/>
         <v>94</v>
       </c>
@@ -4717,7 +4711,7 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="42">
+      <c r="A99">
         <f t="shared" si="1"/>
         <v>95</v>
       </c>
@@ -4735,7 +4729,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="42">
+      <c r="A100">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
@@ -4753,7 +4747,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="42">
+      <c r="A101">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
@@ -4771,7 +4765,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="42">
+      <c r="A102">
         <f t="shared" si="1"/>
         <v>98</v>
       </c>
@@ -4789,7 +4783,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="42">
+      <c r="A103">
         <f t="shared" si="1"/>
         <v>99</v>
       </c>
@@ -4807,7 +4801,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="42">
+      <c r="A104">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
@@ -4825,7 +4819,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="42">
+      <c r="A105">
         <f t="shared" si="1"/>
         <v>101</v>
       </c>
@@ -4843,7 +4837,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="42">
+      <c r="A106">
         <f t="shared" si="1"/>
         <v>102</v>
       </c>
@@ -4861,7 +4855,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="42">
+      <c r="A107">
         <f t="shared" si="1"/>
         <v>103</v>
       </c>
@@ -4879,7 +4873,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="42">
+      <c r="A108">
         <f t="shared" si="1"/>
         <v>104</v>
       </c>
@@ -4897,7 +4891,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="42">
+      <c r="A109">
         <f t="shared" si="1"/>
         <v>105</v>
       </c>
@@ -4915,7 +4909,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="42">
+      <c r="A110">
         <f t="shared" si="1"/>
         <v>106</v>
       </c>
@@ -4933,7 +4927,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="42">
+      <c r="A111">
         <f t="shared" si="1"/>
         <v>107</v>
       </c>
@@ -4951,7 +4945,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" s="42">
+      <c r="A112">
         <f t="shared" si="1"/>
         <v>108</v>
       </c>
@@ -4969,7 +4963,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" s="42">
+      <c r="A113">
         <f t="shared" si="1"/>
         <v>109</v>
       </c>
@@ -4987,7 +4981,7 @@
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" s="42">
+      <c r="A114">
         <f t="shared" si="1"/>
         <v>110</v>
       </c>
@@ -5005,7 +4999,7 @@
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" s="42">
+      <c r="A115">
         <f t="shared" si="1"/>
         <v>111</v>
       </c>
@@ -5023,7 +5017,7 @@
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" s="42">
+      <c r="A116">
         <f t="shared" si="1"/>
         <v>112</v>
       </c>
@@ -5041,7 +5035,7 @@
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" s="42">
+      <c r="A117">
         <f t="shared" si="1"/>
         <v>113</v>
       </c>
@@ -5059,7 +5053,7 @@
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" s="42">
+      <c r="A118">
         <f t="shared" si="1"/>
         <v>114</v>
       </c>
@@ -5077,7 +5071,7 @@
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" s="42">
+      <c r="A119">
         <f t="shared" si="1"/>
         <v>115</v>
       </c>
@@ -5095,7 +5089,7 @@
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" s="42">
+      <c r="A120">
         <f t="shared" si="1"/>
         <v>116</v>
       </c>
@@ -5113,7 +5107,7 @@
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" s="42">
+      <c r="A121">
         <f t="shared" si="1"/>
         <v>117</v>
       </c>
@@ -5131,7 +5125,7 @@
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122" s="42">
+      <c r="A122">
         <f t="shared" si="1"/>
         <v>118</v>
       </c>
@@ -5149,7 +5143,7 @@
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123" s="42">
+      <c r="A123">
         <f t="shared" si="1"/>
         <v>119</v>
       </c>
@@ -5167,7 +5161,7 @@
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="42">
+      <c r="A124">
         <f t="shared" si="1"/>
         <v>120</v>
       </c>
@@ -5185,7 +5179,7 @@
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125" s="42">
+      <c r="A125">
         <f t="shared" si="1"/>
         <v>121</v>
       </c>
@@ -5203,7 +5197,7 @@
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126" s="42">
+      <c r="A126">
         <f t="shared" si="1"/>
         <v>122</v>
       </c>
@@ -5221,7 +5215,7 @@
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127" s="42">
+      <c r="A127">
         <f t="shared" si="1"/>
         <v>123</v>
       </c>
@@ -5239,7 +5233,7 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128" s="42">
+      <c r="A128">
         <f t="shared" si="1"/>
         <v>124</v>
       </c>
@@ -5257,7 +5251,7 @@
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" s="42">
+      <c r="A129">
         <f t="shared" si="1"/>
         <v>125</v>
       </c>
@@ -5275,7 +5269,7 @@
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" s="42">
+      <c r="A130">
         <f t="shared" si="1"/>
         <v>126</v>
       </c>
@@ -5293,7 +5287,7 @@
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" s="42">
+      <c r="A131">
         <f t="shared" si="1"/>
         <v>127</v>
       </c>
@@ -5311,7 +5305,7 @@
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" s="42">
+      <c r="A132">
         <f t="shared" si="1"/>
         <v>128</v>
       </c>
@@ -5329,7 +5323,7 @@
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133" s="42">
+      <c r="A133">
         <f t="shared" si="1"/>
         <v>129</v>
       </c>
@@ -5347,7 +5341,7 @@
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134" s="42">
+      <c r="A134">
         <f t="shared" ref="A134:A139" si="2">ROW()-4</f>
         <v>130</v>
       </c>
@@ -5365,7 +5359,7 @@
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135" s="42">
+      <c r="A135">
         <f t="shared" si="2"/>
         <v>131</v>
       </c>
@@ -5383,7 +5377,7 @@
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136" s="42">
+      <c r="A136">
         <f t="shared" si="2"/>
         <v>132</v>
       </c>
@@ -5401,7 +5395,7 @@
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137" s="42">
+      <c r="A137">
         <f t="shared" si="2"/>
         <v>133</v>
       </c>
@@ -5419,7 +5413,7 @@
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138" s="42">
+      <c r="A138">
         <f t="shared" si="2"/>
         <v>134</v>
       </c>
@@ -5437,7 +5431,7 @@
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139" s="42">
+      <c r="A139">
         <f t="shared" si="2"/>
         <v>135</v>
       </c>
@@ -5555,16 +5549,16 @@
         <f>ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" t="s">
         <v>824</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" t="s">
         <v>825</v>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="2">
         <v>46119</v>
       </c>
     </row>
@@ -5573,16 +5567,16 @@
         <f t="shared" ref="A6:A69" si="0">ROW()-4</f>
         <v>2</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" t="s">
         <v>826</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" t="s">
         <v>827</v>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="2">
         <v>46118</v>
       </c>
     </row>
@@ -5591,16 +5585,16 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" t="s">
         <v>828</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" t="s">
         <v>829</v>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="2">
         <v>46114</v>
       </c>
     </row>
@@ -5609,16 +5603,16 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B8" s="43" t="s">
+      <c r="B8" t="s">
         <v>817</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="10">
         <v>2026</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" t="s">
         <v>818</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="2">
         <v>46113</v>
       </c>
     </row>
@@ -5627,16 +5621,16 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" t="s">
         <v>819</v>
       </c>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" t="s">
         <v>821</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="2">
         <v>46113</v>
       </c>
     </row>
@@ -8783,7 +8777,7 @@
   <dimension ref="A1:E366"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" style="13" customWidth="1"/>
     <col min="3" max="3" width="11.42578125" style="10" customWidth="1"/>
     <col min="4" max="4" width="136.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A726916E-D4D4-47BA-965F-831382A47E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B12375-AD02-4730-A888-9FFA7D09AC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="832">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2522,6 +2522,12 @@
   </si>
   <si>
     <t>Amendment in Import Policy and Policy conditions of items covered under Chapter 71 of ITC (HS) 2022, Schedule-I (Import Policy)-reg.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 06/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in description against HS Code 73181500 in Appendix-4R and Appendix-4RE of the RoDTEP Schedule - reg.</t>
   </si>
 </sst>
 </file>
@@ -5513,7 +5519,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5549,53 +5555,53 @@
         <f>ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" t="s">
-        <v>824</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>820</v>
       </c>
-      <c r="D5" t="s">
-        <v>825</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46119</v>
+      <c r="D5" s="27" t="s">
+        <v>831</v>
+      </c>
+      <c r="E5" s="32">
+        <v>46121</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f t="shared" ref="A6:A69" si="0">ROW()-4</f>
+        <f>ROW()-4</f>
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>820</v>
       </c>
       <c r="D6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E6" s="2">
-        <v>46118</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A7:A70" si="0">ROW()-4</f>
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>820</v>
       </c>
       <c r="D7" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E7" s="2">
-        <v>46114</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5604,16 +5610,16 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>817</v>
-      </c>
-      <c r="C8" s="10">
-        <v>2026</v>
+        <v>828</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>820</v>
       </c>
       <c r="D8" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="E8" s="2">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5622,13 +5628,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>819</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>820</v>
+        <v>817</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2026</v>
       </c>
       <c r="D9" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E9" s="2">
         <v>46113</v>
@@ -5639,16 +5645,16 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>817</v>
-      </c>
-      <c r="C10" s="31">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>818</v>
-      </c>
-      <c r="E10" s="32">
+      <c r="B10" t="s">
+        <v>819</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="D10" t="s">
+        <v>821</v>
+      </c>
+      <c r="E10" s="2">
         <v>46113</v>
       </c>
     </row>
@@ -5658,13 +5664,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>819</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>820</v>
+        <v>817</v>
+      </c>
+      <c r="C11" s="31">
+        <v>2026</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E11" s="32">
         <v>46113</v>
@@ -5676,16 +5682,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>800</v>
+        <v>819</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>4</v>
+        <v>820</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="E12" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5694,13 +5700,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C13" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="E13" s="32">
         <v>46112</v>
@@ -5712,13 +5718,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>804</v>
-      </c>
-      <c r="C14" s="31">
-        <v>2026</v>
+        <v>802</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="E14" s="32">
         <v>46112</v>
@@ -5730,13 +5736,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C15" s="31">
         <v>2026</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="E15" s="32">
         <v>46112</v>
@@ -5748,13 +5754,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C16" s="31">
         <v>2026</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E16" s="32">
         <v>46112</v>
@@ -5766,13 +5772,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C17" s="31">
         <v>2026</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E17" s="32">
         <v>46112</v>
@@ -5784,16 +5790,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>794</v>
+        <v>810</v>
       </c>
       <c r="C18" s="31">
         <v>2026</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>795</v>
+        <v>811</v>
       </c>
       <c r="E18" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5802,13 +5808,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>796</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>4</v>
+        <v>794</v>
+      </c>
+      <c r="C19" s="31">
+        <v>2026</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E19" s="32">
         <v>46108</v>
@@ -5820,16 +5826,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C20" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="E20" s="32">
-        <v>46104</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5838,16 +5844,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="C21" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>782</v>
-      </c>
-      <c r="E21" s="34">
-        <v>46100</v>
+        <v>799</v>
+      </c>
+      <c r="E21" s="32">
+        <v>46104</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5856,16 +5862,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C22" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="E22" s="34">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5874,16 +5880,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E23" s="34">
-        <v>46097</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5892,16 +5898,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>761</v>
+        <v>785</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>762</v>
-      </c>
-      <c r="E24" s="34" t="s">
-        <v>756</v>
+        <v>786</v>
+      </c>
+      <c r="E24" s="34">
+        <v>46097</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5910,13 +5916,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E25" s="34" t="s">
         <v>756</v>
@@ -5928,13 +5934,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E26" s="34" t="s">
         <v>756</v>
@@ -5946,16 +5952,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5963,17 +5969,17 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B28" t="s">
-        <v>588</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>384</v>
-      </c>
-      <c r="E28" s="2">
-        <v>46267</v>
+      <c r="B28" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>768</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5982,16 +5988,16 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E29" s="2">
-        <v>46144</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6000,52 +6006,52 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E30" s="2">
         <v>46144</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B31" t="s">
+        <v>590</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>377</v>
+      </c>
+      <c r="E31" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
         <v>591</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C32" s="10">
         <v>2026</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>375</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E32" s="2">
         <v>46051</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
-        <v>592</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="2">
-        <v>46038</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6054,16 +6060,16 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>593</v>
-      </c>
-      <c r="C33" s="10">
-        <v>2026</v>
+        <v>592</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E33" s="2">
-        <v>46025</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6072,16 +6078,16 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C34" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2">
-        <v>46022</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -6090,13 +6096,13 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>595</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>4</v>
+        <v>594</v>
+      </c>
+      <c r="C35" s="10">
+        <v>2025</v>
       </c>
       <c r="D35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E35" s="2">
         <v>46022</v>
@@ -6108,16 +6114,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>596</v>
-      </c>
-      <c r="C36" s="10">
-        <v>2025</v>
+        <v>595</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E36" s="2">
-        <v>46020</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6126,16 +6132,16 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C37" s="10">
         <v>2025</v>
       </c>
       <c r="D37" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E37" s="2">
-        <v>46009</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6144,16 +6150,16 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>598</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C38" s="10">
+        <v>2025</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E38" s="2">
-        <v>46000</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6162,16 +6168,16 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E39" s="2">
-        <v>45978</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -6180,16 +6186,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="2">
-        <v>45965</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -6198,16 +6204,16 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>601</v>
-      </c>
-      <c r="C41" s="10">
-        <v>2025</v>
+        <v>600</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E41" s="2">
-        <v>45951</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -6216,16 +6222,16 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C42" s="10">
         <v>2025</v>
       </c>
       <c r="D42" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E42" s="2">
-        <v>45945</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6236,8 +6242,8 @@
       <c r="B43" t="s">
         <v>602</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>4</v>
+      <c r="C43" s="10">
+        <v>2025</v>
       </c>
       <c r="D43" t="s">
         <v>33</v>
@@ -6252,13 +6258,13 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E44" s="2">
         <v>45945</v>
@@ -6270,13 +6276,13 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E45" s="2">
         <v>45945</v>
@@ -6288,16 +6294,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E46" s="2">
-        <v>45944</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6306,16 +6312,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E47" s="2">
-        <v>45940</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6324,13 +6330,13 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E48" s="2">
         <v>45940</v>
@@ -6342,16 +6348,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E49" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -6360,13 +6366,13 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E50" s="2">
         <v>45933</v>
@@ -6377,14 +6383,14 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>610</v>
+      <c r="B51" t="s">
+        <v>609</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E51" s="2">
         <v>45933</v>
@@ -6396,13 +6402,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" s="2">
         <v>45933</v>
@@ -6414,16 +6420,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E53" s="2">
-        <v>45930</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -6432,16 +6438,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E54" s="2">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -6450,13 +6456,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E55" s="2">
         <v>45924</v>
@@ -6468,13 +6474,13 @@
         <v>52</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E56" s="2">
         <v>45924</v>
@@ -6486,16 +6492,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="C57" s="10">
-        <v>2025</v>
+        <v>615</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E57" s="2">
-        <v>45923</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -6504,16 +6510,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>617</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C58" s="10">
+        <v>2025</v>
       </c>
       <c r="D58" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E58" s="2">
-        <v>45918</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -6522,16 +6528,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" s="2">
-        <v>45908</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -6540,16 +6546,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E60" s="2">
-        <v>45897</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -6558,16 +6564,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E61" s="2">
-        <v>45891</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -6576,13 +6582,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E62" s="2">
         <v>45891</v>
@@ -6594,16 +6600,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E63" s="2">
-        <v>45888</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -6612,16 +6618,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E64" s="2">
-        <v>45880</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -6630,16 +6636,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>69</v>
+        <v>623</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E65" s="2">
-        <v>45855</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -6648,16 +6654,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>624</v>
+        <v>69</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E66" s="2">
-        <v>45838</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -6666,13 +6672,13 @@
         <v>63</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E67" s="2">
         <v>45838</v>
@@ -6684,16 +6690,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E68" s="2">
-        <v>45835</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -6702,52 +6708,52 @@
         <v>65</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>75</v>
+        <v>626</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E69" s="2">
-        <v>45833</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
-        <f t="shared" ref="A70:A133" si="1">ROW()-4</f>
+        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>627</v>
+        <v>75</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="E70" s="2">
-        <v>45831</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A71:A134" si="1">ROW()-4</f>
         <v>67</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E71" s="2">
-        <v>45825</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -6756,13 +6762,13 @@
         <v>68</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E72" s="2">
         <v>45825</v>
@@ -6774,13 +6780,13 @@
         <v>69</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E73" s="2">
         <v>45825</v>
@@ -6792,16 +6798,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E74" s="2">
-        <v>45808</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -6810,16 +6816,16 @@
         <v>71</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E75" s="2">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -6828,13 +6834,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E76" s="2">
         <v>45803</v>
@@ -6846,13 +6852,13 @@
         <v>73</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E77" s="2">
         <v>45803</v>
@@ -6864,13 +6870,13 @@
         <v>74</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E78" s="2">
         <v>45803</v>
@@ -6882,13 +6888,13 @@
         <v>75</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E79" s="2">
         <v>45803</v>
@@ -6900,70 +6906,70 @@
         <v>76</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E80" s="2">
         <v>45803</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B81" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D81" t="s">
+        <v>92</v>
+      </c>
+      <c r="E81" s="2">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B82" s="10" t="s">
         <v>638</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="C82" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D82" t="s">
         <v>94</v>
-      </c>
-      <c r="E81" s="2">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>639</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D82" t="s">
-        <v>93</v>
       </c>
       <c r="E82" s="2">
         <v>45796</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E83" s="2">
-        <v>45794</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -6972,16 +6978,16 @@
         <v>80</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E84" s="2">
-        <v>45779</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -6990,16 +6996,16 @@
         <v>81</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E85" s="2">
-        <v>45770</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -7008,16 +7014,16 @@
         <v>82</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E86" s="2">
-        <v>45762</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -7026,16 +7032,16 @@
         <v>83</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="C87" s="10">
-        <v>2025</v>
+        <v>643</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E87" s="2">
-        <v>45749</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -7044,13 +7050,13 @@
         <v>84</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C88" s="10">
         <v>2025</v>
       </c>
       <c r="D88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E88" s="2">
         <v>45749</v>
@@ -7062,16 +7068,16 @@
         <v>85</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="C89" s="10" t="s">
-        <v>4</v>
+        <v>645</v>
+      </c>
+      <c r="C89" s="10">
+        <v>2025</v>
       </c>
       <c r="D89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E89" s="2">
-        <v>45748</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -7080,16 +7086,16 @@
         <v>86</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D90" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E90" s="2">
-        <v>45736</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -7098,16 +7104,16 @@
         <v>87</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E91" s="2">
-        <v>45734</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -7116,16 +7122,16 @@
         <v>88</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E92" s="2">
-        <v>45726</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -7134,13 +7140,13 @@
         <v>89</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="C93" s="10">
-        <v>2025</v>
+        <v>649</v>
+      </c>
+      <c r="C93" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E93" s="2">
         <v>45726</v>
@@ -7152,13 +7158,13 @@
         <v>90</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>651</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C94" s="10">
+        <v>2025</v>
       </c>
       <c r="D94" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E94" s="2">
         <v>45726</v>
@@ -7170,16 +7176,16 @@
         <v>91</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E95" s="2">
-        <v>45723</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -7188,16 +7194,16 @@
         <v>92</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E96" s="2">
-        <v>45721</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -7206,16 +7212,16 @@
         <v>93</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C97" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E97" s="2">
-        <v>45698</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7224,16 +7230,16 @@
         <v>94</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E98" s="2">
-        <v>45695</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -7242,16 +7248,16 @@
         <v>95</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E99" s="2">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7259,17 +7265,17 @@
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="B100" t="s">
-        <v>587</v>
+      <c r="B100" s="10" t="s">
+        <v>656</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E100" s="2">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7278,16 +7284,16 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E101" s="2">
-        <v>45686</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7296,16 +7302,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E102" s="2">
-        <v>45681</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -7314,16 +7320,16 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E103" s="2">
-        <v>45678</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7332,16 +7338,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E104" s="2">
-        <v>45677</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7350,13 +7356,13 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E105" s="2">
         <v>45677</v>
@@ -7368,16 +7374,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E106" s="2">
-        <v>45670</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7386,16 +7392,16 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E107" s="2">
-        <v>45661</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7404,13 +7410,13 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E108" s="2">
         <v>45661</v>
@@ -7422,16 +7428,16 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E109" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7440,16 +7446,16 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E110" s="2">
-        <v>45656</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7458,13 +7464,13 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E111" s="2">
         <v>45656</v>
@@ -7476,16 +7482,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>575</v>
-      </c>
-      <c r="C112" s="10">
-        <v>2024</v>
+        <v>576</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E112" s="2">
-        <v>45652</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -7494,16 +7500,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>574</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>114</v>
+        <v>575</v>
+      </c>
+      <c r="C113" s="10">
+        <v>2024</v>
       </c>
       <c r="D113" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="E113" s="2">
-        <v>45650</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7512,16 +7518,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="E114" s="2">
-        <v>45631</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7530,16 +7536,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E115" s="2">
-        <v>45625</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7548,16 +7554,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D116" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E116" s="2">
-        <v>45622</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7566,16 +7572,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D117" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E117" s="2">
-        <v>45593</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7584,16 +7590,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E118" s="2">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7602,13 +7608,13 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E119" s="2">
         <v>45588</v>
@@ -7620,16 +7626,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E120" s="2">
-        <v>45578</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7638,16 +7644,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E121" s="2">
-        <v>45566</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7656,13 +7662,13 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E122" s="2">
         <v>45566</v>
@@ -7674,16 +7680,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E123" s="2">
-        <v>45565</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7692,16 +7698,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E124" s="2">
-        <v>45563</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7710,16 +7716,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E125" s="2">
-        <v>45553</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7728,16 +7734,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="E126" s="2">
-        <v>45548</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -7746,13 +7752,13 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="E127" s="2">
         <v>45548</v>
@@ -7764,16 +7770,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E128" s="2">
-        <v>45539</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -7782,16 +7788,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E129" s="2">
-        <v>45538</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7800,16 +7806,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E130" s="2">
-        <v>45537</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -7818,16 +7824,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E131" s="2">
-        <v>45523</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -7836,16 +7842,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E132" s="2">
-        <v>45520</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -7854,52 +7860,52 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E133" s="2">
-        <v>45505</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
-        <f t="shared" ref="A134:A183" si="2">ROW()-4</f>
+        <f t="shared" si="1"/>
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E134" s="2">
-        <v>45502</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A135:A184" si="2">ROW()-4</f>
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E135" s="2">
-        <v>45478</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -7908,13 +7914,13 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E136" s="2">
         <v>45478</v>
@@ -7926,16 +7932,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E137" s="2">
-        <v>45462</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -7944,16 +7950,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>204</v>
+        <v>550</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E138" s="2">
-        <v>45455</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -7962,16 +7968,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>549</v>
+        <v>204</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E139" s="2">
-        <v>45454</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -7980,16 +7986,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E140" s="2">
-        <v>45449</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -7998,16 +8004,16 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E141" s="2">
-        <v>45448</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -8016,16 +8022,16 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E142" s="2">
-        <v>45446</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -8034,16 +8040,16 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E143" s="2">
-        <v>45432</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -8052,16 +8058,16 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E144" s="2">
-        <v>45420</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -8070,16 +8076,16 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E145" s="2">
-        <v>45418</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -8088,16 +8094,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E146" s="2">
-        <v>45416</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -8106,16 +8112,16 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E147" s="2">
-        <v>45407</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -8123,17 +8129,17 @@
         <f t="shared" si="2"/>
         <v>144</v>
       </c>
-      <c r="B148" s="6" t="s">
-        <v>540</v>
+      <c r="B148" t="s">
+        <v>541</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E148" s="2">
-        <v>45405</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -8142,16 +8148,16 @@
         <v>145</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E149" s="2">
-        <v>45397</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -8160,13 +8166,13 @@
         <v>146</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E150" s="2">
         <v>45397</v>
@@ -8178,16 +8184,16 @@
         <v>147</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E151" s="2">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -8196,13 +8202,13 @@
         <v>148</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E152" s="2">
         <v>45387</v>
@@ -8214,13 +8220,13 @@
         <v>149</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D153" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E153" s="2">
         <v>45387</v>
@@ -8232,16 +8238,16 @@
         <v>150</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E154" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -8250,16 +8256,16 @@
         <v>151</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D155" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E155" s="2">
-        <v>45384</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8268,16 +8274,16 @@
         <v>152</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D156" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E156" s="2">
-        <v>45378</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -8285,17 +8291,17 @@
         <f t="shared" si="2"/>
         <v>153</v>
       </c>
-      <c r="B157" t="s">
-        <v>533</v>
+      <c r="B157" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D157" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E157" s="2">
-        <v>45373</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -8304,13 +8310,13 @@
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D158" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E158" s="2">
         <v>45373</v>
@@ -8322,16 +8328,16 @@
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>117</v>
+        <v>241</v>
       </c>
       <c r="E159" s="2">
-        <v>45369</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -8340,16 +8346,16 @@
         <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D160" t="s">
-        <v>242</v>
+        <v>117</v>
       </c>
       <c r="E160" s="2">
-        <v>45367</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -8358,13 +8364,13 @@
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D161" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E161" s="2">
         <v>45367</v>
@@ -8376,16 +8382,16 @@
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E162" s="2">
-        <v>45366</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -8394,16 +8400,16 @@
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E163" s="2">
-        <v>45365</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8412,16 +8418,16 @@
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E164" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -8430,13 +8436,13 @@
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D165" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E165" s="2">
         <v>45362</v>
@@ -8448,13 +8454,13 @@
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E166" s="2">
         <v>45362</v>
@@ -8466,13 +8472,13 @@
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E167" s="2">
         <v>45362</v>
@@ -8484,16 +8490,16 @@
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C168" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E168" s="2">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -8502,16 +8508,16 @@
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E169" s="2">
-        <v>45358</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8520,13 +8526,13 @@
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C170" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D170" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E170" s="2">
         <v>45358</v>
@@ -8538,16 +8544,16 @@
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E171" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8556,13 +8562,13 @@
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C172" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E172" s="2">
         <v>45357</v>
@@ -8574,16 +8580,16 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C173" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="E173" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -8592,13 +8598,13 @@
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E174" s="2">
         <v>45352</v>
@@ -8610,13 +8616,13 @@
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D175" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="E175" s="2">
         <v>45352</v>
@@ -8628,16 +8634,16 @@
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E176" s="2">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -8646,16 +8652,16 @@
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D177" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E177" s="2">
-        <v>45345</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8664,16 +8670,16 @@
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D178" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E178" s="2">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -8682,16 +8688,16 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C179" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D179" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E179" s="2">
-        <v>45334</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -8700,16 +8706,16 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D180" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E180" s="2">
-        <v>45314</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -8717,17 +8723,17 @@
         <f t="shared" si="2"/>
         <v>177</v>
       </c>
-      <c r="B181" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C181" s="10">
-        <v>2023</v>
+      <c r="B181" t="s">
+        <v>511</v>
+      </c>
+      <c r="C181" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D181" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E181" s="2">
-        <v>45306</v>
+        <v>45314</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -8735,17 +8741,17 @@
         <f t="shared" si="2"/>
         <v>178</v>
       </c>
-      <c r="B182" t="s">
-        <v>509</v>
-      </c>
-      <c r="C182" s="10" t="s">
-        <v>236</v>
+      <c r="B182" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C182" s="10">
+        <v>2023</v>
       </c>
       <c r="D182" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E182" s="2">
-        <v>45294</v>
+        <v>45306</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -8754,15 +8760,33 @@
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D183" t="s">
+        <v>279</v>
+      </c>
+      <c r="E183" s="2">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184">
+        <f t="shared" si="2"/>
+        <v>180</v>
+      </c>
+      <c r="B184" t="s">
+        <v>508</v>
+      </c>
+      <c r="C184" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D184" t="s">
         <v>281</v>
       </c>
-      <c r="E183" s="2">
+      <c r="E184" s="2">
         <v>45292</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B12375-AD02-4730-A888-9FFA7D09AC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D0325F-C89E-46F2-9ACD-9E8F05ACDB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="841">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2528,6 +2528,33 @@
   </si>
   <si>
     <t>Amendment in description against HS Code 73181500 in Appendix-4R and Appendix-4RE of the RoDTEP Schedule - reg.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 09/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment for extension of validity of Minimum Export Price (MEP) on export of Natural Honey - regarding.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 08/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in Export Policy of Feathers - regarding.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 07/2026-27</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 03/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment to the Last date for submission of TRQ Application for India- Mauritius CECPA and India Nepal Treaty notified under Appendix-2Aof the FTP, 2023 for FY-2026-27 -reg.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 02/2026-27</t>
+  </si>
+  <si>
+    <t>Procedure for Allocation of Quantities for import of Calcined Petroleum Coke for Aluminium Industry and Raw Petroleum Coke for CPC manufacturing industry for the Financial Year 2026 27 reg</t>
   </si>
 </sst>
 </file>
@@ -2604,7 +2631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2702,6 +2729,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2983,7 +3019,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O372"/>
+  <dimension ref="A1:O374"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3020,2445 +3056,2338 @@
       <c r="D4" s="5"/>
       <c r="E4" s="24"/>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <f>ROW()-4</f>
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="42" t="s">
+        <v>837</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>820</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>838</v>
+      </c>
+      <c r="E5" s="44">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>820</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>840</v>
+      </c>
+      <c r="E6" s="44">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>823</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C7" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>822</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E7" s="2">
         <v>46119</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <f t="shared" ref="A6:A69" si="0">ROW()-4</f>
-        <v>2</v>
-      </c>
-      <c r="B6" s="27" t="s">
+    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="s">
         <v>812</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C8" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D8" s="33" t="s">
         <v>813</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E8" s="32">
         <v>46111</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B7" s="27" t="s">
+    <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="27" t="s">
         <v>792</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C9" s="31">
         <v>2025</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D9" s="33" t="s">
         <v>793</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E9" s="32">
         <v>46105</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B8" s="27" t="s">
+    <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>787</v>
       </c>
-      <c r="C8" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="33" t="s">
+      <c r="C10" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="33" t="s">
         <v>788</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E10" s="32">
         <v>46101</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B9" s="27" t="s">
+    <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="C9" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="C11" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>779</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E11" s="32">
         <v>46087</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B10" s="40" t="s">
+    <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>780</v>
       </c>
-      <c r="C10" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="40" t="s">
+      <c r="C12" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="40" t="s">
         <v>779</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E12" s="41">
         <v>46087</v>
       </c>
-      <c r="F10" s="39"/>
-    </row>
-    <row r="11" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B11" s="27" t="s">
+      <c r="F12" s="39"/>
+    </row>
+    <row r="13" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="27" t="s">
         <v>754</v>
       </c>
-      <c r="C11" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="33" t="s">
+      <c r="C13" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="33" t="s">
         <v>755</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>757</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>758</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>756</v>
-      </c>
-      <c r="O12" s="27" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B13" s="27" t="s">
-        <v>759</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>760</v>
       </c>
       <c r="E13" s="34" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <f t="shared" si="0"/>
+    <row r="14" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="27" t="s">
+        <v>757</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>758</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>756</v>
+      </c>
+      <c r="O14" s="27" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>760</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>386</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D16" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E16" s="2">
         <v>46328</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
         <v>387</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="C17" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E17" s="2">
         <v>46144</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
         <v>388</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="s">
         <v>5</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E18" s="2">
         <v>46045</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
         <v>389</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E19" s="2">
         <v>46038</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <f t="shared" si="0"/>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C20" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="2">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C21" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>392</v>
+      </c>
+      <c r="C22" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D22" t="s">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>390</v>
-      </c>
-      <c r="C18" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="2">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>391</v>
-      </c>
-      <c r="C19" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <f t="shared" si="0"/>
+      <c r="E22" s="2">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>393</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
         <v>16</v>
       </c>
-      <c r="B20" t="s">
-        <v>392</v>
-      </c>
-      <c r="C20" s="10">
+      <c r="E23" s="2">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>394</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>395</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="2">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>396</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" t="s">
+        <v>374</v>
+      </c>
+      <c r="E26" s="2">
+        <v>46002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>397</v>
+      </c>
+      <c r="C27" s="10">
         <v>2025</v>
       </c>
-      <c r="D20" t="s">
-        <v>14</v>
-      </c>
-      <c r="E20" s="2">
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B21" t="s">
-        <v>393</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="2">
-        <v>46010</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>394</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>18</v>
-      </c>
-      <c r="E22" s="2">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>395</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="2">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <f t="shared" si="0"/>
+      <c r="D27" t="s">
         <v>20</v>
       </c>
-      <c r="B24" t="s">
-        <v>396</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" t="s">
-        <v>374</v>
-      </c>
-      <c r="E24" s="2">
-        <v>46002</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <f t="shared" si="0"/>
+      <c r="E27" s="2">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>398</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D28" t="s">
         <v>21</v>
       </c>
-      <c r="B25" t="s">
-        <v>397</v>
-      </c>
-      <c r="C25" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="E28" s="2">
         <v>46001</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B26" t="s">
-        <v>398</v>
-      </c>
-      <c r="C26" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D26" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="2">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <f t="shared" si="0"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>399</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" t="s">
         <v>23</v>
       </c>
-      <c r="B27" t="s">
-        <v>399</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" t="s">
-        <v>23</v>
-      </c>
-      <c r="E27" s="2">
+      <c r="E29" s="2">
         <v>45992</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <f t="shared" si="0"/>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>400</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" t="s">
         <v>24</v>
       </c>
-      <c r="B28" t="s">
-        <v>400</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="2">
+      <c r="E30" s="2">
         <v>45992</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B29" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>27</v>
+      </c>
+      <c r="B31" t="s">
         <v>401</v>
-      </c>
-      <c r="C29" s="10">
-        <v>2025</v>
-      </c>
-      <c r="D29" t="s">
-        <v>373</v>
-      </c>
-      <c r="E29" s="2">
-        <v>45981</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B30" t="s">
-        <v>402</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E30" s="2">
-        <v>45959</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B31" t="s">
-        <v>403</v>
       </c>
       <c r="C31" s="10">
         <v>2025</v>
       </c>
       <c r="D31" t="s">
+        <v>373</v>
+      </c>
+      <c r="E31" s="2">
+        <v>45981</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
         <v>28</v>
       </c>
-      <c r="E31" s="2">
+      <c r="B32" t="s">
+        <v>402</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="2">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>29</v>
+      </c>
+      <c r="B33" t="s">
+        <v>403</v>
+      </c>
+      <c r="C33" s="10">
+        <v>2025</v>
+      </c>
+      <c r="D33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="2">
         <v>45958</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>30</v>
+      </c>
+      <c r="B34" t="s">
         <v>404</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C34" s="10">
         <v>2025</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D34" t="s">
         <v>29</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E34" s="2">
         <v>45958</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
         <v>405</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C35" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D35" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E35" s="2">
         <v>45953</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>32</v>
+      </c>
+      <c r="B36" t="s">
         <v>406</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="C36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" t="s">
         <v>31</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E36" s="2">
         <v>45952</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>33</v>
+      </c>
+      <c r="B37" t="s">
         <v>407</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="C37" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" t="s">
         <v>36</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E37" s="2">
         <v>45945</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>34</v>
+      </c>
+      <c r="B38" t="s">
         <v>38</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="C38" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" t="s">
         <v>39</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E38" s="2">
         <v>45940</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
         <v>408</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="C39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" t="s">
         <v>42</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E39" s="2">
         <v>45940</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
         <v>409</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="C40" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E40" s="2">
         <v>45933</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>37</v>
+      </c>
+      <c r="B41" t="s">
         <v>410</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="C41" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" t="s">
         <v>48</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E41" s="2">
         <v>45931</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>38</v>
+      </c>
+      <c r="B42" t="s">
         <v>411</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="C42" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E42" s="2">
         <v>45909</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>39</v>
+      </c>
+      <c r="B43" t="s">
         <v>412</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
+      <c r="C43" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D43" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E43" s="2">
         <v>45903</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>40</v>
+      </c>
+      <c r="B44" t="s">
         <v>413</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C44" s="10">
         <v>2025</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D44" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E44" s="2">
         <v>45895</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>41</v>
+      </c>
+      <c r="B45" t="s">
         <v>414</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C45" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D45" t="s">
         <v>62</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E45" s="2">
         <v>45891</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>42</v>
+      </c>
+      <c r="B46" t="s">
         <v>415</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D44" t="s">
+      <c r="C46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E46" s="2">
         <v>45870</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>43</v>
+      </c>
+      <c r="B47" t="s">
         <v>416</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C47" s="10">
         <v>2025</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D47" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E47" s="2">
         <v>45868</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>44</v>
+      </c>
+      <c r="B48" t="s">
         <v>417</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="C48" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D48" t="s">
         <v>67</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E48" s="2">
         <v>45867</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>45</v>
+      </c>
+      <c r="B49" t="s">
         <v>418</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D47" t="s">
+      <c r="C49" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D49" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E49" s="2">
         <v>45860</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B48" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s">
         <v>419</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="C50" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D50" t="s">
         <v>71</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E50" s="2">
         <v>45846</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B49" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>47</v>
+      </c>
+      <c r="B51" t="s">
         <v>420</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="C51" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
         <v>77</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E51" s="2">
         <v>45833</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B50" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>48</v>
+      </c>
+      <c r="B52" t="s">
         <v>421</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="C52" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" t="s">
         <v>78</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E52" s="2">
         <v>45833</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B51" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>49</v>
+      </c>
+      <c r="B53" t="s">
         <v>422</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="C53" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
         <v>82</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E53" s="2">
         <v>45820</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B52" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>50</v>
+      </c>
+      <c r="B54" t="s">
         <v>423</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="C54" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" t="s">
         <v>83</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E54" s="2">
         <v>45820</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B53" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>51</v>
+      </c>
+      <c r="B55" t="s">
         <v>424</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="C55" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" t="s">
         <v>84</v>
       </c>
-      <c r="E53" s="2">
+      <c r="E55" s="2">
         <v>45818</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B54" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>52</v>
+      </c>
+      <c r="B56" t="s">
         <v>425</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C56" s="10">
         <v>2025</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D56" t="s">
         <v>86</v>
       </c>
-      <c r="E54" s="2">
+      <c r="E56" s="2">
         <v>45807</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>53</v>
+      </c>
+      <c r="B57" t="s">
         <v>426</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" t="s">
+      <c r="C57" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D57" t="s">
         <v>96</v>
       </c>
-      <c r="E55" s="2">
+      <c r="E57" s="2">
         <v>45793</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="B56" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1">
+        <v>54</v>
+      </c>
+      <c r="B58" t="s">
         <v>427</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" t="s">
+      <c r="C58" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" t="s">
         <v>97</v>
       </c>
-      <c r="E56" s="2">
+      <c r="E58" s="2">
         <v>45784</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="B57" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1">
+        <v>55</v>
+      </c>
+      <c r="B59" t="s">
         <v>428</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="C59" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" t="s">
         <v>98</v>
       </c>
-      <c r="E57" s="2">
+      <c r="E59" s="2">
         <v>45783</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="B58" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>56</v>
+      </c>
+      <c r="B60" t="s">
         <v>429</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="C60" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" t="s">
         <v>99</v>
       </c>
-      <c r="E58" s="2">
+      <c r="E60" s="2">
         <v>45783</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="B59" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>57</v>
+      </c>
+      <c r="B61" t="s">
         <v>430</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="C61" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" t="s">
         <v>101</v>
       </c>
-      <c r="E59" s="2">
+      <c r="E61" s="2">
         <v>45771</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="B60" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>58</v>
+      </c>
+      <c r="B62" t="s">
         <v>431</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C62" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D62" t="s">
         <v>104</v>
       </c>
-      <c r="E60" s="2">
+      <c r="E62" s="2">
         <v>45762</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="B61" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>59</v>
+      </c>
+      <c r="B63" t="s">
         <v>432</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="C63" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D63" t="s">
         <v>105</v>
       </c>
-      <c r="E61" s="2">
+      <c r="E63" s="2">
         <v>45750</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="B62" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>60</v>
+      </c>
+      <c r="B64" t="s">
         <v>433</v>
       </c>
-      <c r="C62" s="10">
+      <c r="C64" s="10">
         <v>2025</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D64" t="s">
         <v>109</v>
       </c>
-      <c r="E62" s="2">
+      <c r="E64" s="2">
         <v>45744</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="B63" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>61</v>
+      </c>
+      <c r="B65" t="s">
         <v>110</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63" t="s">
+      <c r="C65" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D65" t="s">
         <v>111</v>
       </c>
-      <c r="E63" s="2">
+      <c r="E65" s="2">
         <v>45743</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="B64" t="s">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>62</v>
+      </c>
+      <c r="B66" t="s">
         <v>434</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D64" t="s">
-        <v>113</v>
-      </c>
-      <c r="E64" s="2">
-        <v>45743</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="B65" t="s">
-        <v>435</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" t="s">
-        <v>116</v>
-      </c>
-      <c r="E65" s="2">
-        <v>45735</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="B66" t="s">
-        <v>436</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D66" t="s">
+        <v>113</v>
+      </c>
+      <c r="E66" s="2">
+        <v>45743</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>63</v>
+      </c>
+      <c r="B67" t="s">
+        <v>435</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" t="s">
+        <v>116</v>
+      </c>
+      <c r="E67" s="2">
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
+        <v>436</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" t="s">
         <v>121</v>
       </c>
-      <c r="E66" s="2">
+      <c r="E68" s="2">
         <v>45726</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="B67" t="s">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>65</v>
+      </c>
+      <c r="B69" t="s">
         <v>437</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C69" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D69" t="s">
         <v>124</v>
       </c>
-      <c r="E67" s="2">
+      <c r="E69" s="2">
         <v>45719</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="B68" t="s">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>66</v>
+      </c>
+      <c r="B70" t="s">
         <v>438</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" t="s">
+      <c r="C70" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D70" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="2">
+      <c r="E70" s="2">
         <v>45700</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="B69" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>67</v>
+      </c>
+      <c r="B71" t="s">
         <v>439</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" t="s">
+      <c r="C71" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" t="s">
         <v>128</v>
       </c>
-      <c r="E69" s="2">
+      <c r="E71" s="2">
         <v>45695</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <f t="shared" ref="A70:A133" si="1">ROW()-4</f>
-        <v>66</v>
-      </c>
-      <c r="B70" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>68</v>
+      </c>
+      <c r="B72" t="s">
         <v>440</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D70" t="s">
+      <c r="C72" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" t="s">
         <v>130</v>
       </c>
-      <c r="E70" s="2">
+      <c r="E72" s="2">
         <v>45694</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <f t="shared" si="1"/>
-        <v>67</v>
-      </c>
-      <c r="B71" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>69</v>
+      </c>
+      <c r="B73" t="s">
         <v>441</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" t="s">
+      <c r="C73" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D73" t="s">
         <v>132</v>
       </c>
-      <c r="E71" s="2">
+      <c r="E73" s="2">
         <v>45692</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <f t="shared" si="1"/>
-        <v>68</v>
-      </c>
-      <c r="B72" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>70</v>
+      </c>
+      <c r="B74" t="s">
         <v>442</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" t="s">
+      <c r="C74" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" t="s">
         <v>133</v>
       </c>
-      <c r="E72" s="2">
+      <c r="E74" s="2">
         <v>45688</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <f t="shared" si="1"/>
-        <v>69</v>
-      </c>
-      <c r="B73" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>71</v>
+      </c>
+      <c r="B75" t="s">
         <v>443</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" t="s">
+      <c r="C75" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" t="s">
         <v>135</v>
       </c>
-      <c r="E73" s="2">
+      <c r="E75" s="2">
         <v>45684</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <f t="shared" si="1"/>
-        <v>70</v>
-      </c>
-      <c r="B74" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>72</v>
+      </c>
+      <c r="B76" t="s">
         <v>444</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="C76" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D76" t="s">
         <v>138</v>
       </c>
-      <c r="E74" s="2">
+      <c r="E76" s="2">
         <v>45678</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <f t="shared" si="1"/>
-        <v>71</v>
-      </c>
-      <c r="B75" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>73</v>
+      </c>
+      <c r="B77" t="s">
         <v>445</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D75" t="s">
+      <c r="C77" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D77" t="s">
         <v>141</v>
-      </c>
-      <c r="E75" s="2">
-        <v>45672</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
-      <c r="B76" t="s">
-        <v>446</v>
-      </c>
-      <c r="C76" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D76" t="s">
-        <v>142</v>
-      </c>
-      <c r="E76" s="2">
-        <v>45672</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <f t="shared" si="1"/>
-        <v>73</v>
-      </c>
-      <c r="B77" t="s">
-        <v>446</v>
-      </c>
-      <c r="C77" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D77" t="s">
-        <v>142</v>
       </c>
       <c r="E77" s="2">
         <v>45672</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <f t="shared" si="1"/>
+      <c r="A78" s="1">
         <v>74</v>
       </c>
       <c r="B78" t="s">
+        <v>446</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D78" t="s">
+        <v>142</v>
+      </c>
+      <c r="E78" s="2">
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>75</v>
+      </c>
+      <c r="B79" t="s">
+        <v>446</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D79" t="s">
+        <v>142</v>
+      </c>
+      <c r="E79" s="2">
+        <v>45672</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>76</v>
+      </c>
+      <c r="B80" t="s">
         <v>447</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="C80" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D80" t="s">
         <v>144</v>
       </c>
-      <c r="E78" s="2">
+      <c r="E80" s="2">
         <v>45662</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-      <c r="B79" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>77</v>
+      </c>
+      <c r="B81" t="s">
         <v>448</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C81" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D81" t="s">
         <v>147</v>
       </c>
-      <c r="E79" s="2">
+      <c r="E81" s="2">
         <v>45660</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <f t="shared" si="1"/>
-        <v>76</v>
-      </c>
-      <c r="B80" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>78</v>
+      </c>
+      <c r="B82" t="s">
         <v>449</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D80" t="s">
+      <c r="C82" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D82" t="s">
         <v>149</v>
       </c>
-      <c r="E80" s="2">
+      <c r="E82" s="2">
         <v>45659</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <f t="shared" si="1"/>
-        <v>77</v>
-      </c>
-      <c r="B81" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>79</v>
+      </c>
+      <c r="B83" t="s">
         <v>450</v>
       </c>
-      <c r="C81" s="10">
+      <c r="C83" s="10">
         <v>2024</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D83" t="s">
         <v>152</v>
       </c>
-      <c r="E81" s="2">
+      <c r="E83" s="2">
         <v>45653</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <f t="shared" si="1"/>
-        <v>78</v>
-      </c>
-      <c r="B82" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>80</v>
+      </c>
+      <c r="B84" t="s">
         <v>451</v>
       </c>
-      <c r="C82" s="10">
+      <c r="C84" s="10">
         <v>2024</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D84" t="s">
         <v>154</v>
       </c>
-      <c r="E82" s="2">
+      <c r="E84" s="2">
         <v>45650</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <f t="shared" si="1"/>
-        <v>79</v>
-      </c>
-      <c r="B83" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>81</v>
+      </c>
+      <c r="B85" t="s">
         <v>452</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D83" t="s">
+      <c r="C85" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D85" t="s">
         <v>155</v>
       </c>
-      <c r="E83" s="2">
+      <c r="E85" s="2">
         <v>45643</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <f t="shared" si="1"/>
-        <v>80</v>
-      </c>
-      <c r="B84" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
         <v>284</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C86" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D86" t="s">
         <v>156</v>
       </c>
-      <c r="E84" s="2">
+      <c r="E86" s="2">
         <v>45639</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <f t="shared" si="1"/>
-        <v>81</v>
-      </c>
-      <c r="B85" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>83</v>
+      </c>
+      <c r="B87" t="s">
         <v>453</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D85" t="s">
+      <c r="C87" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D87" t="s">
         <v>160</v>
       </c>
-      <c r="E85" s="2">
+      <c r="E87" s="2">
         <v>45610</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <f t="shared" si="1"/>
-        <v>82</v>
-      </c>
-      <c r="B86" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>84</v>
+      </c>
+      <c r="B88" t="s">
         <v>454</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D86" t="s">
+      <c r="C88" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D88" t="s">
         <v>161</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E88" s="2">
         <v>45609</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <f t="shared" si="1"/>
-        <v>83</v>
-      </c>
-      <c r="B87" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>85</v>
+      </c>
+      <c r="B89" t="s">
         <v>455</v>
       </c>
-      <c r="C87" s="10">
+      <c r="C89" s="10">
         <v>2024</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D89" t="s">
         <v>162</v>
       </c>
-      <c r="E87" s="2">
+      <c r="E89" s="2">
         <v>45601</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
-      <c r="B88" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>86</v>
+      </c>
+      <c r="B90" t="s">
         <v>456</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D88" t="s">
+      <c r="C90" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" t="s">
         <v>163</v>
       </c>
-      <c r="E88" s="2">
+      <c r="E90" s="2">
         <v>45597</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <f t="shared" si="1"/>
-        <v>85</v>
-      </c>
-      <c r="B89" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>87</v>
+      </c>
+      <c r="B91" t="s">
         <v>457</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D89" t="s">
+      <c r="C91" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D91" t="s">
         <v>164</v>
       </c>
-      <c r="E89" s="2">
+      <c r="E91" s="2">
         <v>45597</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <f t="shared" si="1"/>
-        <v>86</v>
-      </c>
-      <c r="B90" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>88</v>
+      </c>
+      <c r="B92" t="s">
         <v>458</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D90" t="s">
+      <c r="C92" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D92" t="s">
         <v>166</v>
       </c>
-      <c r="E90" s="2">
+      <c r="E92" s="2">
         <v>45593</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <f t="shared" si="1"/>
-        <v>87</v>
-      </c>
-      <c r="B91" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>89</v>
+      </c>
+      <c r="B93" t="s">
         <v>459</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="C93" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D93" t="s">
         <v>169</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E93" s="2">
         <v>45588</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <f t="shared" si="1"/>
-        <v>88</v>
-      </c>
-      <c r="B92" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>90</v>
+      </c>
+      <c r="B94" t="s">
         <v>460</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D92" t="s">
+      <c r="C94" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D94" t="s">
         <v>171</v>
       </c>
-      <c r="E92" s="2">
+      <c r="E94" s="2">
         <v>45572</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <f t="shared" si="1"/>
-        <v>89</v>
-      </c>
-      <c r="B93" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>91</v>
+      </c>
+      <c r="B95" t="s">
         <v>461</v>
       </c>
-      <c r="C93" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D93" t="s">
+      <c r="C95" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D95" t="s">
         <v>176</v>
       </c>
-      <c r="E93" s="2">
+      <c r="E95" s="2">
         <v>45562</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <f t="shared" si="1"/>
-        <v>90</v>
-      </c>
-      <c r="B94" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>92</v>
+      </c>
+      <c r="B96" t="s">
         <v>462</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D94" t="s">
+      <c r="C96" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D96" t="s">
         <v>177</v>
       </c>
-      <c r="E94" s="2">
+      <c r="E96" s="2">
         <v>45555</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <f t="shared" si="1"/>
-        <v>91</v>
-      </c>
-      <c r="B95" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>93</v>
+      </c>
+      <c r="B97" t="s">
         <v>463</v>
       </c>
-      <c r="C95" s="10">
+      <c r="C97" s="10">
         <v>2024</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D97" t="s">
         <v>180</v>
       </c>
-      <c r="E95" s="2">
+      <c r="E97" s="2">
         <v>45547</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <f t="shared" si="1"/>
-        <v>92</v>
-      </c>
-      <c r="B96" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>94</v>
+      </c>
+      <c r="B98" t="s">
         <v>464</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D96" t="s">
+      <c r="C98" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D98" t="s">
         <v>183</v>
       </c>
-      <c r="E96" s="2">
+      <c r="E98" s="2">
         <v>45538</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <f t="shared" si="1"/>
-        <v>93</v>
-      </c>
-      <c r="B97" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>95</v>
+      </c>
+      <c r="B99" t="s">
         <v>465</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D97" t="s">
+      <c r="C99" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D99" t="s">
         <v>185</v>
       </c>
-      <c r="E97" s="2">
+      <c r="E99" s="2">
         <v>45534</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <f t="shared" si="1"/>
-        <v>94</v>
-      </c>
-      <c r="B98" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>96</v>
+      </c>
+      <c r="B100" t="s">
         <v>466</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C100" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D100" t="s">
         <v>186</v>
       </c>
-      <c r="E98" s="2">
+      <c r="E100" s="2">
         <v>45533</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <f t="shared" si="1"/>
-        <v>95</v>
-      </c>
-      <c r="B99" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>97</v>
+      </c>
+      <c r="B101" t="s">
         <v>467</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C101" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D101" t="s">
         <v>187</v>
       </c>
-      <c r="E99" s="2">
+      <c r="E101" s="2">
         <v>45533</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="B100" t="s">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>98</v>
+      </c>
+      <c r="B102" t="s">
         <v>468</v>
       </c>
-      <c r="C100" s="10">
+      <c r="C102" s="10">
         <v>2024</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D102" t="s">
         <v>188</v>
       </c>
-      <c r="E100" s="2">
+      <c r="E102" s="2">
         <v>45526</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <f t="shared" si="1"/>
-        <v>97</v>
-      </c>
-      <c r="B101" t="s">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>99</v>
+      </c>
+      <c r="B103" t="s">
         <v>469</v>
       </c>
-      <c r="C101" s="10">
+      <c r="C103" s="10">
         <v>2024</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D103" t="s">
         <v>191</v>
       </c>
-      <c r="E101" s="2">
+      <c r="E103" s="2">
         <v>45518</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <f t="shared" si="1"/>
-        <v>98</v>
-      </c>
-      <c r="B102" t="s">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>100</v>
+      </c>
+      <c r="B104" t="s">
         <v>470</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D102" t="s">
+      <c r="C104" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D104" t="s">
         <v>194</v>
       </c>
-      <c r="E102" s="2">
+      <c r="E104" s="2">
         <v>45502</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <f t="shared" si="1"/>
-        <v>99</v>
-      </c>
-      <c r="B103" t="s">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>101</v>
+      </c>
+      <c r="B105" t="s">
         <v>471</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D103" t="s">
+      <c r="C105" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D105" t="s">
         <v>195</v>
       </c>
-      <c r="E103" s="2">
+      <c r="E105" s="2">
         <v>45498</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <f t="shared" si="1"/>
-        <v>100</v>
-      </c>
-      <c r="B104" t="s">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>102</v>
+      </c>
+      <c r="B106" t="s">
         <v>472</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D104" t="s">
+      <c r="C106" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D106" t="s">
         <v>196</v>
       </c>
-      <c r="E104" s="2">
+      <c r="E106" s="2">
         <v>45489</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <f t="shared" si="1"/>
-        <v>101</v>
-      </c>
-      <c r="B105" t="s">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>103</v>
+      </c>
+      <c r="B107" t="s">
         <v>473</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D105" t="s">
+      <c r="C107" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D107" t="s">
         <v>199</v>
       </c>
-      <c r="E105" s="2">
+      <c r="E107" s="2">
         <v>45469</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
-      <c r="B106" t="s">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>104</v>
+      </c>
+      <c r="B108" t="s">
         <v>474</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D106" t="s">
+      <c r="C108" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" t="s">
         <v>200</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E108" s="2">
         <v>45469</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <f t="shared" si="1"/>
-        <v>103</v>
-      </c>
-      <c r="B107" t="s">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>105</v>
+      </c>
+      <c r="B109" t="s">
         <v>202</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D107" t="s">
+      <c r="C109" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" t="s">
         <v>203</v>
       </c>
-      <c r="E107" s="2">
+      <c r="E109" s="2">
         <v>45455</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <f t="shared" si="1"/>
-        <v>104</v>
-      </c>
-      <c r="B108" t="s">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>106</v>
+      </c>
+      <c r="B110" t="s">
         <v>475</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D108" t="s">
+      <c r="C110" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D110" t="s">
         <v>206</v>
       </c>
-      <c r="E108" s="2">
+      <c r="E110" s="2">
         <v>45455</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <f t="shared" si="1"/>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>107</v>
+      </c>
+      <c r="B111" t="s">
+        <v>476</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D111" t="s">
+        <v>162</v>
+      </c>
+      <c r="E111" s="2">
+        <v>45449</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>108</v>
+      </c>
+      <c r="B112" t="s">
+        <v>477</v>
+      </c>
+      <c r="C112" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D112" t="s">
+        <v>209</v>
+      </c>
+      <c r="E112" s="2">
+        <v>45449</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>109</v>
+      </c>
+      <c r="B113" t="s">
+        <v>478</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" t="s">
+        <v>212</v>
+      </c>
+      <c r="E113" s="2">
+        <v>45446</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>110</v>
+      </c>
+      <c r="B114" t="s">
+        <v>479</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D114" t="s">
+        <v>213</v>
+      </c>
+      <c r="E114" s="2">
+        <v>45441</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>111</v>
+      </c>
+      <c r="B115" t="s">
+        <v>480</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D115" t="s">
+        <v>214</v>
+      </c>
+      <c r="E115" s="2">
+        <v>45440</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>112</v>
+      </c>
+      <c r="B116" t="s">
+        <v>481</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D116" t="s">
+        <v>215</v>
+      </c>
+      <c r="E116" s="2">
+        <v>45439</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>113</v>
+      </c>
+      <c r="B117" t="s">
+        <v>482</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D117" t="s">
+        <v>217</v>
+      </c>
+      <c r="E117" s="2">
+        <v>45422</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>114</v>
+      </c>
+      <c r="B118" t="s">
+        <v>483</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D118" t="s">
+        <v>221</v>
+      </c>
+      <c r="E118" s="2">
+        <v>45415</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>115</v>
+      </c>
+      <c r="B119" t="s">
+        <v>285</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D119" t="s">
+        <v>223</v>
+      </c>
+      <c r="E119" s="2">
+        <v>45411</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>116</v>
+      </c>
+      <c r="B120" t="s">
+        <v>484</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D120" t="s">
+        <v>228</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45391</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>117</v>
+      </c>
+      <c r="B121" t="s">
+        <v>485</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D121" t="s">
+        <v>229</v>
+      </c>
+      <c r="E121" s="2">
+        <v>45391</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>118</v>
+      </c>
+      <c r="B122" t="s">
+        <v>486</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D122" t="s">
         <v>105</v>
       </c>
-      <c r="B109" t="s">
-        <v>476</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D109" t="s">
-        <v>162</v>
-      </c>
-      <c r="E109" s="2">
-        <v>45449</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <f t="shared" si="1"/>
-        <v>106</v>
-      </c>
-      <c r="B110" t="s">
-        <v>477</v>
-      </c>
-      <c r="C110" s="10">
-        <v>2024</v>
-      </c>
-      <c r="D110" t="s">
-        <v>209</v>
-      </c>
-      <c r="E110" s="2">
-        <v>45449</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <f t="shared" si="1"/>
-        <v>107</v>
-      </c>
-      <c r="B111" t="s">
-        <v>478</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D111" t="s">
-        <v>212</v>
-      </c>
-      <c r="E111" s="2">
-        <v>45446</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112">
-        <f t="shared" si="1"/>
-        <v>108</v>
-      </c>
-      <c r="B112" t="s">
-        <v>479</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D112" t="s">
-        <v>213</v>
-      </c>
-      <c r="E112" s="2">
-        <v>45441</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <f t="shared" si="1"/>
-        <v>109</v>
-      </c>
-      <c r="B113" t="s">
-        <v>480</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D113" t="s">
-        <v>214</v>
-      </c>
-      <c r="E113" s="2">
-        <v>45440</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114">
-        <f t="shared" si="1"/>
-        <v>110</v>
-      </c>
-      <c r="B114" t="s">
-        <v>481</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D114" t="s">
-        <v>215</v>
-      </c>
-      <c r="E114" s="2">
-        <v>45439</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115">
-        <f t="shared" si="1"/>
-        <v>111</v>
-      </c>
-      <c r="B115" t="s">
-        <v>482</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D115" t="s">
-        <v>217</v>
-      </c>
-      <c r="E115" s="2">
-        <v>45422</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116">
-        <f t="shared" si="1"/>
-        <v>112</v>
-      </c>
-      <c r="B116" t="s">
-        <v>483</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D116" t="s">
-        <v>221</v>
-      </c>
-      <c r="E116" s="2">
-        <v>45415</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117">
-        <f t="shared" si="1"/>
-        <v>113</v>
-      </c>
-      <c r="B117" t="s">
-        <v>285</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D117" t="s">
-        <v>223</v>
-      </c>
-      <c r="E117" s="2">
-        <v>45411</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118">
-        <f t="shared" si="1"/>
-        <v>114</v>
-      </c>
-      <c r="B118" t="s">
-        <v>484</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D118" t="s">
-        <v>228</v>
-      </c>
-      <c r="E118" s="2">
-        <v>45391</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119">
-        <f t="shared" si="1"/>
-        <v>115</v>
-      </c>
-      <c r="B119" t="s">
-        <v>485</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D119" t="s">
-        <v>229</v>
-      </c>
-      <c r="E119" s="2">
-        <v>45391</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120">
-        <f t="shared" si="1"/>
-        <v>116</v>
-      </c>
-      <c r="B120" t="s">
-        <v>486</v>
-      </c>
-      <c r="C120" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="D120" t="s">
-        <v>105</v>
-      </c>
-      <c r="E120" s="2">
+      <c r="E122" s="2">
         <v>45379</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <f t="shared" si="1"/>
-        <v>117</v>
-      </c>
-      <c r="B121" t="s">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>119</v>
+      </c>
+      <c r="B123" t="s">
         <v>487</v>
       </c>
-      <c r="C121" s="10" t="s">
+      <c r="C123" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D123" t="s">
         <v>238</v>
       </c>
-      <c r="E121" s="2">
+      <c r="E123" s="2">
         <v>45378</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A122">
-        <f t="shared" si="1"/>
-        <v>118</v>
-      </c>
-      <c r="B122" t="s">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>120</v>
+      </c>
+      <c r="B124" t="s">
         <v>488</v>
-      </c>
-      <c r="C122" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D122" t="s">
-        <v>239</v>
-      </c>
-      <c r="E122" s="2">
-        <v>45378</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123">
-        <f t="shared" si="1"/>
-        <v>119</v>
-      </c>
-      <c r="B123" t="s">
-        <v>489</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="D123" t="s">
-        <v>246</v>
-      </c>
-      <c r="E123" s="2">
-        <v>45365</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124">
-        <f t="shared" si="1"/>
-        <v>120</v>
-      </c>
-      <c r="B124" t="s">
-        <v>490</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D124" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E124" s="2">
-        <v>45362</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125">
-        <f t="shared" si="1"/>
+      <c r="A125" s="1">
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D125" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="E125" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A126">
-        <f t="shared" si="1"/>
+      <c r="A126" s="1">
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D126" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E126" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <f t="shared" si="1"/>
+      <c r="A127" s="1">
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D127" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E127" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A128">
-        <f t="shared" si="1"/>
+      <c r="A128" s="1">
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E128" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129">
-        <f t="shared" si="1"/>
+      <c r="A129" s="1">
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D129" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="E129" s="2">
-        <v>45350</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130">
-        <f t="shared" si="1"/>
+      <c r="A130" s="1">
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D130" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="E130" s="2">
-        <v>45344</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131">
-        <f t="shared" si="1"/>
+      <c r="A131" s="1">
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D131" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E131" s="2">
-        <v>45336</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132">
-        <f t="shared" si="1"/>
+      <c r="A132" s="1">
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E132" s="2">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133">
-        <f t="shared" si="1"/>
+      <c r="A133" s="1">
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E133" s="2">
         <v>45336</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A134">
-        <f t="shared" ref="A134:A139" si="2">ROW()-4</f>
+      <c r="A134" s="1">
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E134" s="2">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135">
-        <f t="shared" si="2"/>
+      <c r="A135" s="1">
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>222</v>
+        <v>496</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D135" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E135" s="2">
-        <v>45331</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A136">
-        <f t="shared" si="2"/>
+      <c r="A136" s="1">
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D136" t="s">
+        <v>272</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>133</v>
+      </c>
+      <c r="B137" t="s">
+        <v>222</v>
+      </c>
+      <c r="C137" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D137" t="s">
+        <v>273</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45331</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>134</v>
+      </c>
+      <c r="B138" t="s">
+        <v>494</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D138" t="s">
         <v>274</v>
       </c>
-      <c r="E136" s="2">
+      <c r="E138" s="2">
         <v>45324</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137">
-        <f t="shared" si="2"/>
-        <v>133</v>
-      </c>
-      <c r="B137" t="s">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>135</v>
+      </c>
+      <c r="B139" t="s">
         <v>493</v>
       </c>
-      <c r="C137" s="10">
+      <c r="C139" s="10">
         <v>2024</v>
       </c>
-      <c r="D137" t="s">
+      <c r="D139" t="s">
         <v>275</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E139" s="2">
         <v>45322</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A138">
-        <f t="shared" si="2"/>
-        <v>134</v>
-      </c>
-      <c r="B138" t="s">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>136</v>
+      </c>
+      <c r="B140" t="s">
         <v>492</v>
       </c>
-      <c r="C138" s="10">
+      <c r="C140" s="10">
         <v>2024</v>
       </c>
-      <c r="D138" t="s">
+      <c r="D140" t="s">
         <v>278</v>
       </c>
-      <c r="E138" s="2">
+      <c r="E140" s="2">
         <v>45303</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139">
-        <f t="shared" si="2"/>
-        <v>135</v>
-      </c>
-      <c r="B139" t="s">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>137</v>
+      </c>
+      <c r="B141" t="s">
         <v>491</v>
       </c>
-      <c r="C139" s="10" t="s">
+      <c r="C141" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D139" t="s">
+      <c r="D141" t="s">
         <v>280</v>
       </c>
-      <c r="E139" s="2">
+      <c r="E141" s="2">
         <v>45294</v>
       </c>
-    </row>
-    <row r="294" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B294" s="3"/>
-    </row>
-    <row r="295" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B295" s="3"/>
     </row>
     <row r="296" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B296" s="3"/>
@@ -5469,30 +5398,30 @@
     <row r="298" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B298" s="3"/>
     </row>
-    <row r="301" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B301" s="3"/>
-    </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B306" s="3"/>
-    </row>
-    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B309" s="3"/>
+    <row r="299" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B299" s="3"/>
+    </row>
+    <row r="300" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B300" s="3"/>
+    </row>
+    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B303" s="3"/>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B308" s="3"/>
     </row>
     <row r="311" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B311" s="3"/>
     </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B312" s="3"/>
-    </row>
     <row r="313" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B313" s="3"/>
     </row>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B314" s="3"/>
+    </row>
     <row r="315" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B315" s="3"/>
     </row>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B316" s="3"/>
-    </row>
     <row r="317" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B317" s="3"/>
     </row>
@@ -5502,15 +5431,21 @@
     <row r="319" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B319" s="3"/>
     </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B320" s="3"/>
+    </row>
     <row r="321" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B321" s="3"/>
     </row>
-    <row r="372" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B372" s="3"/>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B323" s="3"/>
+    </row>
+    <row r="374" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B374" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:E137">
-    <sortCondition descending="1" sortBy="icon" ref="E14:E137"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:E139">
+    <sortCondition descending="1" sortBy="icon" ref="E16:E139"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5519,7 +5454,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E184"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5552,215 +5487,203 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f>ROW()-4</f>
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C5" s="31" t="s">
         <v>820</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E5" s="32">
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f>ROW()-4</f>
         <v>2</v>
       </c>
-      <c r="B6" t="s">
-        <v>824</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="27" t="s">
+        <v>834</v>
+      </c>
+      <c r="C6" s="31" t="s">
         <v>820</v>
       </c>
-      <c r="D6" t="s">
-        <v>825</v>
-      </c>
-      <c r="E6" s="2">
-        <v>46119</v>
+      <c r="D6" s="27" t="s">
+        <v>835</v>
+      </c>
+      <c r="E6" s="32">
+        <v>46122</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f t="shared" ref="A7:A70" si="0">ROW()-4</f>
         <v>3</v>
       </c>
-      <c r="B7" t="s">
-        <v>826</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="27" t="s">
+        <v>836</v>
+      </c>
+      <c r="C7" s="31" t="s">
         <v>820</v>
       </c>
-      <c r="D7" t="s">
-        <v>827</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46118</v>
+      <c r="D7" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="32">
+        <v>46122</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B8" t="s">
-        <v>828</v>
-      </c>
-      <c r="C8" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="C8" s="31" t="s">
         <v>820</v>
       </c>
-      <c r="D8" t="s">
-        <v>829</v>
-      </c>
-      <c r="E8" s="2">
-        <v>46114</v>
+      <c r="D8" s="27" t="s">
+        <v>831</v>
+      </c>
+      <c r="E8" s="32">
+        <v>46121</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>817</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2026</v>
+        <v>824</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>820</v>
       </c>
       <c r="D9" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="E9" s="2">
-        <v>46113</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>820</v>
       </c>
       <c r="D10" t="s">
-        <v>821</v>
+        <v>827</v>
       </c>
       <c r="E10" s="2">
-        <v>46113</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>817</v>
-      </c>
-      <c r="C11" s="31">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>818</v>
-      </c>
-      <c r="E11" s="32">
-        <v>46113</v>
+      <c r="B11" t="s">
+        <v>828</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="D11" t="s">
+        <v>829</v>
+      </c>
+      <c r="E11" s="2">
+        <v>46114</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>819</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>820</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>821</v>
-      </c>
-      <c r="E12" s="32">
+      <c r="B12" t="s">
+        <v>817</v>
+      </c>
+      <c r="C12" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D12" t="s">
+        <v>818</v>
+      </c>
+      <c r="E12" s="2">
         <v>46113</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>800</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>801</v>
-      </c>
-      <c r="E13" s="32">
-        <v>46112</v>
+      <c r="B13" t="s">
+        <v>819</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="D13" t="s">
+        <v>821</v>
+      </c>
+      <c r="E13" s="2">
+        <v>46113</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>802</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>4</v>
+        <v>817</v>
+      </c>
+      <c r="C14" s="31">
+        <v>2026</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="E14" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>804</v>
-      </c>
-      <c r="C15" s="31">
-        <v>2026</v>
+        <v>819</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>820</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>805</v>
+        <v>821</v>
       </c>
       <c r="E15" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>806</v>
-      </c>
-      <c r="C16" s="31">
-        <v>2026</v>
+        <v>800</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="E16" s="32">
         <v>46112</v>
@@ -5768,17 +5691,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>808</v>
-      </c>
-      <c r="C17" s="31">
-        <v>2026</v>
+        <v>802</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E17" s="32">
         <v>46112</v>
@@ -5786,17 +5708,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C18" s="31">
         <v>2026</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="E18" s="32">
         <v>46112</v>
@@ -5804,503 +5725,475 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
-        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="C19" s="31">
         <v>2026</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="E19" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
-        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>796</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>4</v>
+        <v>808</v>
+      </c>
+      <c r="C20" s="31">
+        <v>2026</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="E20" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
-        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>798</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>4</v>
+        <v>810</v>
+      </c>
+      <c r="C21" s="31">
+        <v>2026</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="E21" s="32">
-        <v>46104</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
-        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>781</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>4</v>
+        <v>794</v>
+      </c>
+      <c r="C22" s="31">
+        <v>2026</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>782</v>
-      </c>
-      <c r="E22" s="34">
-        <v>46100</v>
+        <v>795</v>
+      </c>
+      <c r="E22" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
-        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>783</v>
+        <v>796</v>
       </c>
       <c r="C23" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>784</v>
-      </c>
-      <c r="E23" s="34">
-        <v>46099</v>
+        <v>797</v>
+      </c>
+      <c r="E23" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
-        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>785</v>
+        <v>798</v>
       </c>
       <c r="C24" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>786</v>
-      </c>
-      <c r="E24" s="34">
-        <v>46097</v>
+        <v>799</v>
+      </c>
+      <c r="E24" s="32">
+        <v>46104</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
-        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>762</v>
-      </c>
-      <c r="E25" s="34" t="s">
-        <v>756</v>
+        <v>782</v>
+      </c>
+      <c r="E25" s="34">
+        <v>46100</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
-        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>764</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>756</v>
+        <v>784</v>
+      </c>
+      <c r="E26" s="34">
+        <v>46099</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
-        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>766</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>756</v>
+        <v>786</v>
+      </c>
+      <c r="E27" s="34">
+        <v>46097</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
-        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="C28" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
-        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B29" t="s">
-        <v>588</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>384</v>
-      </c>
-      <c r="E29" s="2">
-        <v>46267</v>
+      <c r="B29" s="27" t="s">
+        <v>763</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>764</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
-        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B30" t="s">
-        <v>589</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>376</v>
-      </c>
-      <c r="E30" s="2">
-        <v>46144</v>
+      <c r="B30" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>766</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
-        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B31" t="s">
-        <v>590</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" t="s">
-        <v>377</v>
-      </c>
-      <c r="E31" s="2">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>768</v>
+      </c>
+      <c r="E31" s="34" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
-        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>591</v>
-      </c>
-      <c r="C32" s="10">
-        <v>2026</v>
+        <v>588</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="E32" s="2">
-        <v>46051</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
-        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C33" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>376</v>
       </c>
       <c r="E33" s="2">
-        <v>46038</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
-        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>593</v>
-      </c>
-      <c r="C34" s="10">
+        <v>590</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" t="s">
+        <v>377</v>
+      </c>
+      <c r="E34" s="2">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>591</v>
+      </c>
+      <c r="C35" s="10">
         <v>2026</v>
       </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
-        <v>594</v>
-      </c>
-      <c r="C35" s="10">
-        <v>2025</v>
-      </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>375</v>
       </c>
       <c r="E35" s="2">
-        <v>46022</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
-        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E36" s="2">
-        <v>46022</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
-        <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C37" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2">
-        <v>46020</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
-        <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C38" s="10">
         <v>2025</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E38" s="2">
-        <v>46009</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
-        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E39" s="2">
-        <v>46000</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
-        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>599</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>4</v>
+        <v>596</v>
+      </c>
+      <c r="C40" s="10">
+        <v>2025</v>
       </c>
       <c r="D40" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E40" s="2">
-        <v>45978</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
-        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>600</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C41" s="10">
+        <v>2025</v>
       </c>
       <c r="D41" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E41" s="2">
-        <v>45965</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
-        <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>601</v>
-      </c>
-      <c r="C42" s="10">
-        <v>2025</v>
+        <v>598</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E42" s="2">
-        <v>45951</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
-        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>602</v>
-      </c>
-      <c r="C43" s="10">
-        <v>2025</v>
+        <v>599</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E43" s="2">
-        <v>45945</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
-        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E44" s="2">
-        <v>45945</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
-        <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>603</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>4</v>
+        <v>601</v>
+      </c>
+      <c r="C45" s="10">
+        <v>2025</v>
       </c>
       <c r="D45" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E45" s="2">
-        <v>45945</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
-        <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>604</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>4</v>
+        <v>602</v>
+      </c>
+      <c r="C46" s="10">
+        <v>2025</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E46" s="2">
         <v>45945</v>
@@ -6308,125 +6201,118 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
-        <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E47" s="2">
-        <v>45944</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
-        <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E48" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
-        <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E49" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
-        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E50" s="2">
-        <v>45933</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
-        <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E51" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
-        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>610</v>
+      <c r="B52" t="s">
+        <v>607</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E52" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
-        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>611</v>
+      <c r="B53" t="s">
+        <v>608</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E53" s="2">
         <v>45933</v>
@@ -6434,467 +6320,441 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
-        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>612</v>
+      <c r="B54" t="s">
+        <v>609</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E54" s="2">
-        <v>45930</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
-        <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E55" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
-        <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E56" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
-        <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E57" s="2">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
-        <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="C58" s="10">
-        <v>2025</v>
+        <v>613</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E58" s="2">
-        <v>45923</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
-        <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E59" s="2">
-        <v>45918</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
-        <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E60" s="2">
-        <v>45908</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
-        <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>619</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C61" s="10">
+        <v>2025</v>
       </c>
       <c r="D61" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E61" s="2">
-        <v>45897</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
-        <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E62" s="2">
-        <v>45891</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
-        <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E63" s="2">
-        <v>45891</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
-        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E64" s="2">
-        <v>45888</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
-        <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E65" s="2">
-        <v>45880</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
-        <f t="shared" si="0"/>
         <v>62</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>69</v>
+        <v>621</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E66" s="2">
-        <v>45855</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
-        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C67" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E67" s="2">
-        <v>45838</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
-        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E68" s="2">
-        <v>45838</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
-        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>626</v>
+        <v>69</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E69" s="2">
-        <v>45835</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
-        <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>75</v>
+        <v>624</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E70" s="2">
-        <v>45833</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
-        <f t="shared" ref="A71:A134" si="1">ROW()-4</f>
         <v>67</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E71" s="2">
-        <v>45831</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
-        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E72" s="2">
-        <v>45825</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
-        <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>629</v>
+        <v>75</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E73" s="2">
-        <v>45825</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
-        <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E74" s="2">
-        <v>45825</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
-        <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E75" s="2">
-        <v>45808</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
-        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E76" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
-        <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E77" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
-        <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E78" s="2">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
-        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E79" s="2">
         <v>45803</v>
@@ -6902,17 +6762,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
-        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E80" s="2">
         <v>45803</v>
@@ -6920,1583 +6779,1495 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
-        <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E81" s="2">
         <v>45803</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
-        <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E82" s="2">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
-        <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E83" s="2">
-        <v>45796</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
-        <f t="shared" si="1"/>
         <v>80</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E84" s="2">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85">
-        <f t="shared" si="1"/>
         <v>81</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E85" s="2">
-        <v>45779</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86">
-        <f t="shared" si="1"/>
         <v>82</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E86" s="2">
-        <v>45770</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
-        <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="B87" s="10" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C87" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E87" s="2">
-        <v>45762</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
-        <f t="shared" si="1"/>
         <v>84</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="C88" s="10">
-        <v>2025</v>
+        <v>641</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E88" s="2">
-        <v>45749</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
-        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="C89" s="10">
-        <v>2025</v>
+        <v>642</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E89" s="2">
-        <v>45749</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
-        <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D90" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E90" s="2">
-        <v>45748</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
-        <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>647</v>
-      </c>
-      <c r="C91" s="10" t="s">
-        <v>114</v>
+        <v>644</v>
+      </c>
+      <c r="C91" s="10">
+        <v>2025</v>
       </c>
       <c r="D91" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E91" s="2">
-        <v>45736</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
-        <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="C92" s="10" t="s">
-        <v>114</v>
+        <v>645</v>
+      </c>
+      <c r="C92" s="10">
+        <v>2025</v>
       </c>
       <c r="D92" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E92" s="2">
-        <v>45734</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
-        <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B93" s="10" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D93" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E93" s="2">
-        <v>45726</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
-        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="C94" s="10">
-        <v>2025</v>
+        <v>647</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E94" s="2">
-        <v>45726</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
-        <f t="shared" si="1"/>
         <v>91</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E95" s="2">
-        <v>45726</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
-        <f t="shared" si="1"/>
         <v>92</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E96" s="2">
-        <v>45723</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
-        <f t="shared" si="1"/>
         <v>93</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>653</v>
-      </c>
-      <c r="C97" s="10" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C97" s="10">
+        <v>2025</v>
       </c>
       <c r="D97" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E97" s="2">
-        <v>45721</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
-        <f t="shared" si="1"/>
         <v>94</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E98" s="2">
-        <v>45698</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
-        <f t="shared" si="1"/>
         <v>95</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E99" s="2">
-        <v>45695</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
-        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E100" s="2">
-        <v>45694</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
-        <f t="shared" si="1"/>
         <v>97</v>
       </c>
-      <c r="B101" t="s">
-        <v>587</v>
+      <c r="B101" s="10" t="s">
+        <v>654</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E101" s="2">
-        <v>45692</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
-        <f t="shared" si="1"/>
         <v>98</v>
       </c>
-      <c r="B102" t="s">
-        <v>586</v>
+      <c r="B102" s="10" t="s">
+        <v>655</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E102" s="2">
-        <v>45686</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
-        <f t="shared" si="1"/>
         <v>99</v>
       </c>
-      <c r="B103" t="s">
-        <v>585</v>
+      <c r="B103" s="10" t="s">
+        <v>656</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E103" s="2">
-        <v>45681</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
-        <f t="shared" si="1"/>
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E104" s="2">
-        <v>45678</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
-        <f t="shared" si="1"/>
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E105" s="2">
-        <v>45677</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
-        <f t="shared" si="1"/>
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E106" s="2">
-        <v>45677</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
-        <f t="shared" si="1"/>
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E107" s="2">
-        <v>45670</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
-        <f t="shared" si="1"/>
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E108" s="2">
-        <v>45661</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
-        <f t="shared" si="1"/>
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E109" s="2">
-        <v>45661</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
-        <f t="shared" si="1"/>
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E110" s="2">
-        <v>45659</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
-        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E111" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
-        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E112" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
-        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>575</v>
-      </c>
-      <c r="C113" s="10">
-        <v>2024</v>
+        <v>578</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E113" s="2">
-        <v>45652</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114">
-        <f t="shared" si="1"/>
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="E114" s="2">
-        <v>45650</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115">
-        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E115" s="2">
-        <v>45631</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116">
-        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>572</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>112</v>
+        <v>575</v>
+      </c>
+      <c r="C116" s="10">
+        <v>2024</v>
       </c>
       <c r="D116" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E116" s="2">
-        <v>45625</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117">
-        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="E117" s="2">
-        <v>45622</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118">
-        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E118" s="2">
-        <v>45593</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119">
-        <f t="shared" si="1"/>
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D119" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E119" s="2">
-        <v>45588</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120">
-        <f t="shared" si="1"/>
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D120" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E120" s="2">
-        <v>45588</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121">
-        <f t="shared" si="1"/>
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E121" s="2">
-        <v>45578</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122">
-        <f t="shared" si="1"/>
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C122" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E122" s="2">
-        <v>45566</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123">
-        <f t="shared" si="1"/>
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E123" s="2">
-        <v>45566</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124">
-        <f t="shared" si="1"/>
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E124" s="2">
-        <v>45565</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125">
-        <f t="shared" si="1"/>
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E125" s="2">
-        <v>45563</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126">
-        <f t="shared" si="1"/>
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E126" s="2">
-        <v>45553</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127">
-        <f t="shared" si="1"/>
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="E127" s="2">
-        <v>45548</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128">
-        <f t="shared" si="1"/>
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E128" s="2">
-        <v>45548</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129">
-        <f t="shared" si="1"/>
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E129" s="2">
-        <v>45539</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130">
-        <f t="shared" si="1"/>
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="E130" s="2">
-        <v>45538</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131">
-        <f t="shared" si="1"/>
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E131" s="2">
-        <v>45537</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132">
-        <f t="shared" si="1"/>
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E132" s="2">
-        <v>45523</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133">
-        <f t="shared" si="1"/>
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E133" s="2">
-        <v>45520</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134">
-        <f t="shared" si="1"/>
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E134" s="2">
-        <v>45505</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135">
-        <f t="shared" ref="A135:A184" si="2">ROW()-4</f>
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E135" s="2">
-        <v>45502</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136">
-        <f t="shared" si="2"/>
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E136" s="2">
-        <v>45478</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137">
-        <f t="shared" si="2"/>
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E137" s="2">
-        <v>45478</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138">
-        <f t="shared" si="2"/>
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E138" s="2">
-        <v>45462</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139">
-        <f t="shared" si="2"/>
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>204</v>
+        <v>552</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E139" s="2">
-        <v>45455</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140">
-        <f t="shared" si="2"/>
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E140" s="2">
-        <v>45454</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141">
-        <f t="shared" si="2"/>
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C141" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E141" s="2">
-        <v>45449</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142">
-        <f t="shared" si="2"/>
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>547</v>
+        <v>204</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E142" s="2">
-        <v>45448</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143">
-        <f t="shared" si="2"/>
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E143" s="2">
-        <v>45446</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144">
-        <f t="shared" si="2"/>
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E144" s="2">
-        <v>45432</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145">
-        <f t="shared" si="2"/>
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E145" s="2">
-        <v>45420</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146">
-        <f t="shared" si="2"/>
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E146" s="2">
-        <v>45418</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147">
-        <f t="shared" si="2"/>
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E147" s="2">
-        <v>45416</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148">
-        <f t="shared" si="2"/>
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E148" s="2">
-        <v>45407</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149">
-        <f t="shared" si="2"/>
         <v>145</v>
       </c>
-      <c r="B149" s="6" t="s">
-        <v>540</v>
+      <c r="B149" t="s">
+        <v>543</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E149" s="2">
-        <v>45405</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150">
-        <f t="shared" si="2"/>
         <v>146</v>
       </c>
-      <c r="B150" s="6" t="s">
-        <v>535</v>
+      <c r="B150" t="s">
+        <v>542</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E150" s="2">
-        <v>45397</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151">
-        <f t="shared" si="2"/>
         <v>147</v>
       </c>
-      <c r="B151" s="6" t="s">
-        <v>539</v>
+      <c r="B151" t="s">
+        <v>541</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E151" s="2">
-        <v>45397</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
-        <f t="shared" si="2"/>
         <v>148</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E152" s="2">
-        <v>45387</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153">
-        <f t="shared" si="2"/>
         <v>149</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D153" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E153" s="2">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154">
-        <f t="shared" si="2"/>
         <v>150</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E154" s="2">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155">
-        <f t="shared" si="2"/>
         <v>151</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="C155" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D155" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E155" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156">
-        <f t="shared" si="2"/>
         <v>152</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D156" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E156" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157">
-        <f t="shared" si="2"/>
         <v>153</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="C157" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D157" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E157" s="2">
-        <v>45378</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158">
-        <f t="shared" si="2"/>
         <v>154</v>
       </c>
-      <c r="B158" t="s">
-        <v>533</v>
+      <c r="B158" s="6" t="s">
+        <v>505</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D158" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E158" s="2">
-        <v>45373</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159">
-        <f t="shared" si="2"/>
         <v>155</v>
       </c>
-      <c r="B159" t="s">
-        <v>532</v>
+      <c r="B159" s="6" t="s">
+        <v>534</v>
       </c>
       <c r="C159" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E159" s="2">
-        <v>45373</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160">
-        <f t="shared" si="2"/>
         <v>156</v>
       </c>
-      <c r="B160" t="s">
-        <v>531</v>
+      <c r="B160" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="C160" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D160" t="s">
-        <v>117</v>
+        <v>237</v>
       </c>
       <c r="E160" s="2">
-        <v>45369</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161">
-        <f t="shared" si="2"/>
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C161" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D161" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E161" s="2">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
-        <f t="shared" si="2"/>
         <v>158</v>
       </c>
       <c r="B162" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E162" s="2">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163">
-        <f t="shared" si="2"/>
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>244</v>
+        <v>117</v>
       </c>
       <c r="E163" s="2">
-        <v>45366</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164">
-        <f t="shared" si="2"/>
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E164" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165">
-        <f t="shared" si="2"/>
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C165" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D165" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E165" s="2">
-        <v>45362</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166">
-        <f t="shared" si="2"/>
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E166" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167">
-        <f t="shared" si="2"/>
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E167" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168">
-        <f t="shared" si="2"/>
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D168" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E168" s="2">
         <v>45362</v>
@@ -8504,289 +8275,324 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169">
-        <f t="shared" si="2"/>
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E169" s="2">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170">
-        <f t="shared" si="2"/>
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C170" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D170" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E170" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171">
-        <f t="shared" si="2"/>
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E171" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172">
-        <f t="shared" si="2"/>
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C172" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E172" s="2">
-        <v>45357</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173">
-        <f t="shared" si="2"/>
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C173" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E173" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174">
-        <f t="shared" si="2"/>
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="E174" s="2">
-        <v>45352</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175">
-        <f t="shared" si="2"/>
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D175" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="E175" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176">
-        <f t="shared" si="2"/>
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D176" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E176" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177">
-        <f t="shared" si="2"/>
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D177" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="E177" s="2">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178">
-        <f t="shared" si="2"/>
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D178" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="E178" s="2">
-        <v>45345</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179">
-        <f t="shared" si="2"/>
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D179" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E179" s="2">
-        <v>45335</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180">
-        <f t="shared" si="2"/>
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D180" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E180" s="2">
-        <v>45334</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181">
-        <f t="shared" si="2"/>
         <v>177</v>
       </c>
       <c r="B181" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C181" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D181" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="E181" s="2">
-        <v>45314</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182">
-        <f t="shared" si="2"/>
         <v>178</v>
       </c>
-      <c r="B182" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C182" s="10">
-        <v>2023</v>
+      <c r="B182" t="s">
+        <v>507</v>
+      </c>
+      <c r="C182" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D182" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E182" s="2">
-        <v>45306</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183">
-        <f t="shared" si="2"/>
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D183" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E183" s="2">
-        <v>45294</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184">
-        <f t="shared" si="2"/>
         <v>180</v>
       </c>
       <c r="B184" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D184" t="s">
+        <v>276</v>
+      </c>
+      <c r="E184" s="2">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185">
+        <v>181</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C185" s="10">
+        <v>2023</v>
+      </c>
+      <c r="D185" t="s">
+        <v>277</v>
+      </c>
+      <c r="E185" s="2">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186">
+        <v>182</v>
+      </c>
+      <c r="B186" t="s">
+        <v>509</v>
+      </c>
+      <c r="C186" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D186" t="s">
+        <v>279</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187">
+        <v>183</v>
+      </c>
+      <c r="B187" t="s">
+        <v>508</v>
+      </c>
+      <c r="C187" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D187" t="s">
         <v>281</v>
       </c>
-      <c r="E184" s="2">
+      <c r="E187" s="2">
         <v>45292</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D0325F-C89E-46F2-9ACD-9E8F05ACDB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041574C4-6AB9-4515-80F5-0861BBAB845C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="853">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2555,6 +2555,42 @@
   </si>
   <si>
     <t>Procedure for Allocation of Quantities for import of Calcined Petroleum Coke for Aluminium Industry and Raw Petroleum Coke for CPC manufacturing industry for the Financial Year 2026 27 reg</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 04/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in Appendix 4B of Handbook of Procedures, 2023 - reg</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 11/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment to Notification No. 65/2025-26 for inclusion of Egypt and Jordan under RELIEF – reg</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 12/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in Export Policy of Baryte (Natural Barium Sulphate) - regarding.</t>
+  </si>
+  <si>
+    <t>POLICY CIRCULAR-01/2026-27</t>
+  </si>
+  <si>
+    <t>Clarification on Eligibility of New ECGC Whole Turnover Policy under Component II of the Resilience &amp; Logistics Intervention for Export Facilitation (RELIEF) under Export Promotion Mission (EPM)</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 01/2026-27</t>
+  </si>
+  <si>
+    <t>Inclusion of Chapter 72 tariff lines for Micro and Small Enterprises under Interest Subvention Support – reg.</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 02/2026-2027</t>
+  </si>
+  <si>
+    <t>Instructions regarding Issuance/Re-issuance/Extension of Validity of Post Export EPCG Scrips – Activation of Post Export EPCG Module - regarding.</t>
   </si>
 </sst>
 </file>
@@ -2590,7 +2626,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2606,6 +2642,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2631,7 +2673,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2738,6 +2780,17 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3019,7 +3072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O374"/>
+  <dimension ref="A1:O375"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3056,21 +3109,21 @@
       <c r="D4" s="5"/>
       <c r="E4" s="24"/>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="42" t="s">
-        <v>837</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>820</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>838</v>
-      </c>
-      <c r="E5" s="44">
-        <v>46122</v>
+      <c r="B5" s="45" t="s">
+        <v>841</v>
+      </c>
+      <c r="C5" s="46">
+        <v>2026</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>842</v>
+      </c>
+      <c r="E5" s="48">
+        <v>46129</v>
       </c>
     </row>
     <row r="6" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3078,50 +3131,50 @@
         <v>2</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>820</v>
       </c>
       <c r="D6" s="43" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E6" s="44">
         <v>46122</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
-        <v>823</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="42" t="s">
+        <v>839</v>
+      </c>
+      <c r="C7" s="35" t="s">
         <v>820</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>822</v>
-      </c>
-      <c r="E7" s="2">
-        <v>46119</v>
+      <c r="D7" s="43" t="s">
+        <v>840</v>
+      </c>
+      <c r="E7" s="44">
+        <v>46122</v>
       </c>
     </row>
     <row r="8" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>812</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>813</v>
-      </c>
-      <c r="E8" s="32">
-        <v>46111</v>
+      <c r="B8" t="s">
+        <v>823</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>820</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="E8" s="2">
+        <v>46119</v>
       </c>
     </row>
     <row r="9" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3129,16 +3182,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>792</v>
-      </c>
-      <c r="C9" s="31">
-        <v>2025</v>
+        <v>812</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>8</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="E9" s="32">
-        <v>46105</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="10" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3146,16 +3199,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>787</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>4</v>
+        <v>792</v>
+      </c>
+      <c r="C10" s="31">
+        <v>2025</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="E10" s="32">
-        <v>46101</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="11" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3163,71 +3216,68 @@
         <v>7</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C11" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="E11" s="32">
-        <v>46087</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="12" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="40" t="s">
-        <v>780</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="40" t="s">
+      <c r="B12" s="27" t="s">
+        <v>789</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="33" t="s">
         <v>779</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="32">
         <v>46087</v>
       </c>
-      <c r="F12" s="39"/>
-    </row>
-    <row r="13" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>754</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>755</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>756</v>
-      </c>
+      <c r="B13" s="40" t="s">
+        <v>780</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>779</v>
+      </c>
+      <c r="E13" s="41">
+        <v>46087</v>
+      </c>
+      <c r="F13" s="39"/>
     </row>
     <row r="14" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C14" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E14" s="34" t="s">
         <v>756</v>
-      </c>
-      <c r="O14" s="27" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
@@ -3235,33 +3285,36 @@
         <v>11</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C15" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E15" s="34" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O15" s="27" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" s="27" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
-        <v>386</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="E16" s="2">
-        <v>46328</v>
+      <c r="B16" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>760</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -3269,16 +3322,16 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>4</v>
+        <v>382</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E17" s="2">
-        <v>46144</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -3286,16 +3339,16 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D18" t="s">
-        <v>5</v>
+      <c r="D18" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="E18" s="2">
-        <v>46045</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -3303,16 +3356,16 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2">
-        <v>46038</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -3320,16 +3373,16 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
-      </c>
-      <c r="C20" s="10">
-        <v>2026</v>
+        <v>389</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2">
-        <v>46031</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -3337,13 +3390,13 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C21" s="10">
         <v>2026</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2">
         <v>46031</v>
@@ -3354,16 +3407,16 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C22" s="10">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2">
-        <v>46022</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -3371,16 +3424,16 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>393</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>4</v>
+        <v>392</v>
+      </c>
+      <c r="C23" s="10">
+        <v>2025</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2">
-        <v>46010</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3388,16 +3441,16 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E24" s="2">
-        <v>46008</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -3405,13 +3458,13 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2">
         <v>46008</v>
@@ -3422,16 +3475,16 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>374</v>
+        <v>19</v>
       </c>
       <c r="E26" s="2">
-        <v>46002</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -3439,16 +3492,16 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>397</v>
-      </c>
-      <c r="C27" s="10">
-        <v>2025</v>
+        <v>396</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="E27" s="2">
-        <v>46001</v>
+        <v>46002</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -3456,13 +3509,13 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C28" s="10">
         <v>2025</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2">
         <v>46001</v>
@@ -3473,16 +3526,16 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>399</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>4</v>
+        <v>398</v>
+      </c>
+      <c r="C29" s="10">
+        <v>2025</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2">
-        <v>45992</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3490,13 +3543,13 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E30" s="2">
         <v>45992</v>
@@ -3507,16 +3560,16 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>401</v>
-      </c>
-      <c r="C31" s="10">
-        <v>2025</v>
+        <v>400</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -3524,16 +3577,16 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>402</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="C32" s="10">
+        <v>2025</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="E32" s="2">
-        <v>45959</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3541,16 +3594,16 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>403</v>
-      </c>
-      <c r="C33" s="10">
-        <v>2025</v>
+        <v>402</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E33" s="2">
-        <v>45958</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -3558,13 +3611,13 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C34" s="10">
         <v>2025</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E34" s="2">
         <v>45958</v>
@@ -3575,16 +3628,16 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>405</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>8</v>
+        <v>404</v>
+      </c>
+      <c r="C35" s="10">
+        <v>2025</v>
       </c>
       <c r="D35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" s="2">
-        <v>45953</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3592,16 +3645,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2">
-        <v>45952</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3609,16 +3662,16 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E37" s="2">
-        <v>45945</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -3626,16 +3679,16 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E38" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3643,13 +3696,13 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E39" s="2">
         <v>45940</v>
@@ -3660,16 +3713,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E40" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3677,16 +3730,16 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E41" s="2">
-        <v>45931</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3694,16 +3747,16 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E42" s="2">
-        <v>45909</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3711,16 +3764,16 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E43" s="2">
-        <v>45903</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3728,16 +3781,16 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>413</v>
-      </c>
-      <c r="C44" s="10">
-        <v>2025</v>
+        <v>412</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E44" s="2">
-        <v>45895</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3745,16 +3798,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>414</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C45" s="10">
+        <v>2025</v>
       </c>
       <c r="D45" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E45" s="2">
-        <v>45891</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3762,16 +3815,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2">
-        <v>45870</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3779,16 +3832,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>416</v>
-      </c>
-      <c r="C47" s="10">
-        <v>2025</v>
+        <v>415</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E47" s="2">
-        <v>45868</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3796,16 +3849,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>417</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C48" s="10">
+        <v>2025</v>
       </c>
       <c r="D48" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E48" s="2">
-        <v>45867</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3813,16 +3866,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E49" s="2">
-        <v>45860</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3830,16 +3883,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E50" s="2">
-        <v>45846</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3847,16 +3900,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E51" s="2">
-        <v>45833</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -3864,13 +3917,13 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E52" s="2">
         <v>45833</v>
@@ -3881,16 +3934,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E53" s="2">
-        <v>45820</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -3898,13 +3951,13 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2">
         <v>45820</v>
@@ -3915,16 +3968,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E55" s="2">
-        <v>45818</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -3932,16 +3985,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>425</v>
-      </c>
-      <c r="C56" s="10">
-        <v>2025</v>
+        <v>424</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E56" s="2">
-        <v>45807</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3949,16 +4002,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>426</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C57" s="10">
+        <v>2025</v>
       </c>
       <c r="D57" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E57" s="2">
-        <v>45793</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -3966,16 +4019,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E58" s="2">
-        <v>45784</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -3983,16 +4036,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E59" s="2">
-        <v>45783</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -4000,13 +4053,13 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E60" s="2">
         <v>45783</v>
@@ -4017,16 +4070,16 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E61" s="2">
-        <v>45771</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -4034,16 +4087,16 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E62" s="2">
-        <v>45762</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -4051,16 +4104,16 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E63" s="2">
-        <v>45750</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -4068,16 +4121,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>433</v>
-      </c>
-      <c r="C64" s="10">
-        <v>2025</v>
+        <v>432</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E64" s="2">
-        <v>45744</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -4085,16 +4138,16 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>110</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>4</v>
+        <v>433</v>
+      </c>
+      <c r="C65" s="10">
+        <v>2025</v>
       </c>
       <c r="D65" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E65" s="2">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4102,13 +4155,13 @@
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>434</v>
+        <v>110</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E66" s="2">
         <v>45743</v>
@@ -4119,16 +4172,16 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D67" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E67" s="2">
-        <v>45735</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -4136,16 +4189,16 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D68" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E68" s="2">
-        <v>45726</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -4153,16 +4206,16 @@
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E69" s="2">
-        <v>45719</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -4170,16 +4223,16 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D70" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E70" s="2">
-        <v>45700</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -4187,16 +4240,16 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D71" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E71" s="2">
-        <v>45695</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4204,16 +4257,16 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D72" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E72" s="2">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -4221,16 +4274,16 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D73" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E73" s="2">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4238,16 +4291,16 @@
         <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E74" s="2">
-        <v>45688</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -4255,16 +4308,16 @@
         <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E75" s="2">
-        <v>45684</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4272,16 +4325,16 @@
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E76" s="2">
-        <v>45678</v>
+        <v>45684</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4289,16 +4342,16 @@
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E77" s="2">
-        <v>45672</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -4306,13 +4359,13 @@
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E78" s="2">
         <v>45672</v>
@@ -4340,16 +4393,16 @@
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D80" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E80" s="2">
-        <v>45662</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4357,16 +4410,16 @@
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E81" s="2">
-        <v>45660</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4374,16 +4427,16 @@
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E82" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4391,16 +4444,16 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>450</v>
-      </c>
-      <c r="C83" s="10">
-        <v>2024</v>
+        <v>449</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E83" s="2">
-        <v>45653</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4408,16 +4461,16 @@
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C84" s="10">
         <v>2024</v>
       </c>
       <c r="D84" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E84" s="2">
-        <v>45650</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4425,16 +4478,16 @@
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>452</v>
-      </c>
-      <c r="C85" s="10" t="s">
-        <v>114</v>
+        <v>451</v>
+      </c>
+      <c r="C85" s="10">
+        <v>2024</v>
       </c>
       <c r="D85" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E85" s="2">
-        <v>45643</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4442,16 +4495,16 @@
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>284</v>
+        <v>452</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E86" s="2">
-        <v>45639</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4459,16 +4512,16 @@
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>453</v>
+        <v>284</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E87" s="2">
-        <v>45610</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4476,16 +4529,16 @@
         <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E88" s="2">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4493,16 +4546,16 @@
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>455</v>
-      </c>
-      <c r="C89" s="10">
-        <v>2024</v>
+        <v>454</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E89" s="2">
-        <v>45601</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4510,16 +4563,16 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>456</v>
-      </c>
-      <c r="C90" s="10" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C90" s="10">
+        <v>2024</v>
       </c>
       <c r="D90" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E90" s="2">
-        <v>45597</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4527,13 +4580,13 @@
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E91" s="2">
         <v>45597</v>
@@ -4544,16 +4597,16 @@
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E92" s="2">
-        <v>45593</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4561,16 +4614,16 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E93" s="2">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4578,16 +4631,16 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E94" s="2">
-        <v>45572</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -4595,16 +4648,16 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C95" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E95" s="2">
-        <v>45562</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4612,16 +4665,16 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E96" s="2">
-        <v>45555</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4629,16 +4682,16 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>463</v>
-      </c>
-      <c r="C97" s="10">
-        <v>2024</v>
+        <v>462</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E97" s="2">
-        <v>45547</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4646,16 +4699,16 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>464</v>
-      </c>
-      <c r="C98" s="10" t="s">
-        <v>114</v>
+        <v>463</v>
+      </c>
+      <c r="C98" s="10">
+        <v>2024</v>
       </c>
       <c r="D98" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E98" s="2">
-        <v>45538</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4663,16 +4716,16 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C99" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E99" s="2">
-        <v>45534</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4680,16 +4733,16 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E100" s="2">
-        <v>45533</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4697,13 +4750,13 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D101" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E101" s="2">
         <v>45533</v>
@@ -4714,16 +4767,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>468</v>
-      </c>
-      <c r="C102" s="10">
-        <v>2024</v>
+        <v>467</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="D102" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E102" s="2">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4731,16 +4784,16 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C103" s="10">
         <v>2024</v>
       </c>
       <c r="D103" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E103" s="2">
-        <v>45518</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4748,16 +4801,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>470</v>
-      </c>
-      <c r="C104" s="10" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C104" s="10">
+        <v>2024</v>
       </c>
       <c r="D104" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E104" s="2">
-        <v>45502</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4765,16 +4818,16 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E105" s="2">
-        <v>45498</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4782,16 +4835,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E106" s="2">
-        <v>45489</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4799,16 +4852,16 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E107" s="2">
-        <v>45469</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4816,13 +4869,13 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E108" s="2">
         <v>45469</v>
@@ -4833,16 +4886,16 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>202</v>
+        <v>474</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E109" s="2">
-        <v>45455</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -4850,13 +4903,13 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>475</v>
+        <v>202</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E110" s="2">
         <v>45455</v>
@@ -4867,16 +4920,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="E111" s="2">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -4884,13 +4937,13 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>477</v>
-      </c>
-      <c r="C112" s="10">
-        <v>2024</v>
+        <v>476</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E112" s="2">
         <v>45449</v>
@@ -4901,16 +4954,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>478</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>114</v>
+        <v>477</v>
+      </c>
+      <c r="C113" s="10">
+        <v>2024</v>
       </c>
       <c r="D113" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E113" s="2">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -4918,16 +4971,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E114" s="2">
-        <v>45441</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -4935,16 +4988,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E115" s="2">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -4952,16 +5005,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C116" s="10" t="s">
         <v>112</v>
       </c>
       <c r="D116" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E116" s="2">
-        <v>45439</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -4969,16 +5022,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D117" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E117" s="2">
-        <v>45422</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -4986,16 +5039,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C118" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E118" s="2">
-        <v>45415</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -5003,16 +5056,16 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>285</v>
+        <v>483</v>
       </c>
       <c r="C119" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E119" s="2">
-        <v>45411</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -5020,16 +5073,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>484</v>
+        <v>285</v>
       </c>
       <c r="C120" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E120" s="2">
-        <v>45391</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -5037,13 +5090,13 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C121" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E121" s="2">
         <v>45391</v>
@@ -5054,16 +5107,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="E122" s="2">
-        <v>45379</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -5071,16 +5124,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D123" t="s">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="E123" s="2">
-        <v>45378</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -5088,13 +5141,13 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D124" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E124" s="2">
         <v>45378</v>
@@ -5105,16 +5158,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D125" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E125" s="2">
-        <v>45365</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -5122,16 +5175,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D126" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E126" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -5139,13 +5192,13 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="C127" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D127" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E127" s="2">
         <v>45362</v>
@@ -5156,16 +5209,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D128" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E128" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -5173,13 +5226,13 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D129" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E129" s="2">
         <v>45358</v>
@@ -5190,16 +5243,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D130" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E130" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -5207,16 +5260,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D131" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E131" s="2">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5224,16 +5277,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E132" s="2">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -5241,16 +5294,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E133" s="2">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -5258,13 +5311,13 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E134" s="2">
         <v>45336</v>
@@ -5275,13 +5328,13 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D135" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E135" s="2">
         <v>45336</v>
@@ -5292,16 +5345,16 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D136" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E136" s="2">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -5309,16 +5362,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D137" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E137" s="2">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -5326,16 +5379,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D138" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E138" s="2">
-        <v>45324</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5343,16 +5396,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>493</v>
-      </c>
-      <c r="C139" s="10">
-        <v>2024</v>
+        <v>494</v>
+      </c>
+      <c r="C139" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D139" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E139" s="2">
-        <v>45322</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -5360,16 +5413,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C140" s="10">
         <v>2024</v>
       </c>
       <c r="D140" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E140" s="2">
-        <v>45303</v>
+        <v>45322</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -5377,20 +5430,34 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
+        <v>492</v>
+      </c>
+      <c r="C141" s="10">
+        <v>2024</v>
+      </c>
+      <c r="D141" t="s">
+        <v>278</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>138</v>
+      </c>
+      <c r="B142" t="s">
         <v>491</v>
       </c>
-      <c r="C141" s="10" t="s">
+      <c r="C142" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D141" t="s">
+      <c r="D142" t="s">
         <v>280</v>
       </c>
-      <c r="E141" s="2">
+      <c r="E142" s="2">
         <v>45294</v>
       </c>
-    </row>
-    <row r="296" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B296" s="3"/>
     </row>
     <row r="297" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B297" s="3"/>
@@ -5404,17 +5471,17 @@
     <row r="300" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B300" s="3"/>
     </row>
-    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B303" s="3"/>
-    </row>
-    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B308" s="3"/>
-    </row>
-    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B311" s="3"/>
-    </row>
-    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B313" s="3"/>
+    <row r="301" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B301" s="3"/>
+    </row>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B304" s="3"/>
+    </row>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B309" s="3"/>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B312" s="3"/>
     </row>
     <row r="314" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B314" s="3"/>
@@ -5422,8 +5489,8 @@
     <row r="315" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B315" s="3"/>
     </row>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B317" s="3"/>
+    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B316" s="3"/>
     </row>
     <row r="318" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B318" s="3"/>
@@ -5437,15 +5504,18 @@
     <row r="321" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B321" s="3"/>
     </row>
-    <row r="323" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B323" s="3"/>
-    </row>
-    <row r="374" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B374" s="3"/>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B322" s="3"/>
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B324" s="3"/>
+    </row>
+    <row r="375" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B375" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:E139">
-    <sortCondition descending="1" sortBy="icon" ref="E16:E139"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A17:E140">
+    <sortCondition descending="1" sortBy="icon" ref="E17:E140"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5454,7 +5524,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E189"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5485,52 +5555,55 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="11"/>
+    </row>
+    <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>832</v>
-      </c>
-      <c r="C5" s="31" t="s">
+      <c r="B5" s="45" t="s">
+        <v>845</v>
+      </c>
+      <c r="C5" s="46" t="s">
         <v>820</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>833</v>
-      </c>
-      <c r="E5" s="32">
-        <v>46122</v>
+      <c r="D5" s="45" t="s">
+        <v>846</v>
+      </c>
+      <c r="E5" s="48">
+        <v>46129</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="27" t="s">
-        <v>834</v>
-      </c>
-      <c r="C6" s="31" t="s">
+      <c r="B6" s="45" t="s">
+        <v>843</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>820</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>835</v>
-      </c>
-      <c r="E6" s="32">
-        <v>46122</v>
+      <c r="D6" s="45" t="s">
+        <v>844</v>
+      </c>
+      <c r="E6" s="48">
+        <v>46129</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="A7" s="1">
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C7" s="31" t="s">
         <v>820</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>43</v>
+        <v>833</v>
       </c>
       <c r="E7" s="32">
         <v>46122</v>
@@ -5541,67 +5614,67 @@
         <v>4</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="C8" s="31" t="s">
         <v>820</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="E8" s="32">
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
+      <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" t="s">
-        <v>824</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="27" t="s">
+        <v>836</v>
+      </c>
+      <c r="C9" s="31" t="s">
         <v>820</v>
       </c>
-      <c r="D9" t="s">
-        <v>825</v>
-      </c>
-      <c r="E9" s="2">
-        <v>46119</v>
+      <c r="D9" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="32">
+        <v>46122</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" t="s">
-        <v>826</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="27" t="s">
+        <v>830</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>820</v>
       </c>
-      <c r="D10" t="s">
-        <v>827</v>
-      </c>
-      <c r="E10" s="2">
-        <v>46118</v>
+      <c r="D10" s="27" t="s">
+        <v>831</v>
+      </c>
+      <c r="E10" s="32">
+        <v>46121</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
+      <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>820</v>
       </c>
       <c r="D11" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="E11" s="2">
-        <v>46114</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5609,66 +5682,66 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>817</v>
-      </c>
-      <c r="C12" s="10">
-        <v>2026</v>
+        <v>826</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>820</v>
       </c>
       <c r="D12" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="E12" s="2">
-        <v>46113</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
+      <c r="A13" s="1">
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>819</v>
+        <v>828</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>820</v>
       </c>
       <c r="D13" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="E13" s="2">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" t="s">
         <v>817</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="10">
         <v>2026</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" t="s">
         <v>818</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="2">
         <v>46113</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
+      <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" t="s">
         <v>819</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="10" t="s">
         <v>820</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" t="s">
         <v>821</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="2">
         <v>46113</v>
       </c>
     </row>
@@ -5677,33 +5750,33 @@
         <v>12</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>800</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>4</v>
+        <v>817</v>
+      </c>
+      <c r="C16" s="31">
+        <v>2026</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="E16" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
+      <c r="A17" s="1">
         <v>13</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>4</v>
+        <v>820</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>803</v>
+        <v>821</v>
       </c>
       <c r="E17" s="32">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5711,30 +5784,30 @@
         <v>14</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>804</v>
-      </c>
-      <c r="C18" s="31">
-        <v>2026</v>
+        <v>800</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="E18" s="32">
         <v>46112</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="A19" s="1">
         <v>15</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>806</v>
-      </c>
-      <c r="C19" s="31">
-        <v>2026</v>
+        <v>802</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>4</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="E19" s="32">
         <v>46112</v>
@@ -5745,30 +5818,30 @@
         <v>16</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C20" s="31">
         <v>2026</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="E20" s="32">
         <v>46112</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
+      <c r="A21" s="1">
         <v>17</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C21" s="31">
         <v>2026</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E21" s="32">
         <v>46112</v>
@@ -5779,33 +5852,33 @@
         <v>18</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="C22" s="31">
         <v>2026</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="E22" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="A23" s="1">
         <v>19</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>796</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>4</v>
+        <v>810</v>
+      </c>
+      <c r="C23" s="31">
+        <v>2026</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="E23" s="32">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -5813,33 +5886,33 @@
         <v>20</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>798</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>4</v>
+        <v>794</v>
+      </c>
+      <c r="C24" s="31">
+        <v>2026</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="E24" s="32">
-        <v>46104</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
+      <c r="A25" s="1">
         <v>21</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="C25" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>782</v>
-      </c>
-      <c r="E25" s="34">
-        <v>46100</v>
+        <v>797</v>
+      </c>
+      <c r="E25" s="32">
+        <v>46108</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5847,33 +5920,33 @@
         <v>22</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>784</v>
-      </c>
-      <c r="E26" s="34">
-        <v>46099</v>
+        <v>799</v>
+      </c>
+      <c r="E26" s="32">
+        <v>46104</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27">
+      <c r="A27" s="1">
         <v>23</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C27" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E27" s="34">
-        <v>46097</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5881,33 +5954,33 @@
         <v>24</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>761</v>
+        <v>783</v>
       </c>
       <c r="C28" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>762</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>756</v>
+        <v>784</v>
+      </c>
+      <c r="E28" s="34">
+        <v>46099</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29">
+      <c r="A29" s="1">
         <v>25</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="C29" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>764</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>756</v>
+        <v>786</v>
+      </c>
+      <c r="E29" s="34">
+        <v>46097</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -5915,67 +5988,67 @@
         <v>26</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C30" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E30" s="34" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
+      <c r="A31" s="1">
         <v>27</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C31" s="31" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E31" s="34" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>28</v>
       </c>
-      <c r="B32" t="s">
-        <v>588</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" t="s">
-        <v>384</v>
-      </c>
-      <c r="E32" s="2">
-        <v>46267</v>
+      <c r="B32" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>766</v>
+      </c>
+      <c r="E32" s="34" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
+      <c r="A33" s="1">
         <v>29</v>
       </c>
-      <c r="B33" t="s">
-        <v>589</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D33" t="s">
-        <v>376</v>
-      </c>
-      <c r="E33" s="2">
-        <v>46144</v>
+      <c r="B33" s="27" t="s">
+        <v>767</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>768</v>
+      </c>
+      <c r="E33" s="34" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5983,33 +6056,33 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E34" s="2">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>589</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" t="s">
+        <v>376</v>
+      </c>
+      <c r="E35" s="2">
         <v>46144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>31</v>
-      </c>
-      <c r="B35" t="s">
-        <v>591</v>
-      </c>
-      <c r="C35" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D35" t="s">
-        <v>375</v>
-      </c>
-      <c r="E35" s="2">
-        <v>46051</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -6017,33 +6090,33 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>6</v>
+        <v>377</v>
       </c>
       <c r="E36" s="2">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C37" s="10">
         <v>2026</v>
       </c>
       <c r="D37" t="s">
-        <v>11</v>
+        <v>375</v>
       </c>
       <c r="E37" s="2">
-        <v>46025</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6051,33 +6124,33 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>594</v>
-      </c>
-      <c r="C38" s="10">
-        <v>2025</v>
+        <v>592</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2">
-        <v>46022</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39">
+      <c r="A39" s="1">
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>595</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>4</v>
+        <v>593</v>
+      </c>
+      <c r="C39" s="10">
+        <v>2026</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E39" s="2">
-        <v>46022</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -6085,33 +6158,33 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C40" s="10">
         <v>2025</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E40" s="2">
-        <v>46020</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41">
+      <c r="A41" s="1">
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>597</v>
-      </c>
-      <c r="C41" s="10">
-        <v>2025</v>
+        <v>595</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E41" s="2">
-        <v>46009</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -6119,33 +6192,33 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>598</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>4</v>
+        <v>596</v>
+      </c>
+      <c r="C42" s="10">
+        <v>2025</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E42" s="2">
-        <v>46000</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43">
+      <c r="A43" s="1">
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>599</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C43" s="10">
+        <v>2025</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E43" s="2">
-        <v>45978</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -6153,33 +6226,33 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E44" s="2">
-        <v>45965</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45">
+      <c r="A45" s="1">
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>601</v>
-      </c>
-      <c r="C45" s="10">
-        <v>2025</v>
+        <v>599</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E45" s="2">
-        <v>45951</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -6187,33 +6260,33 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>602</v>
-      </c>
-      <c r="C46" s="10">
+        <v>600</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E46" s="2">
+        <v>45965</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>43</v>
+      </c>
+      <c r="B47" t="s">
+        <v>601</v>
+      </c>
+      <c r="C47" s="10">
         <v>2025</v>
       </c>
-      <c r="D46" t="s">
-        <v>33</v>
-      </c>
-      <c r="E46" s="2">
-        <v>45945</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>43</v>
-      </c>
-      <c r="B47" t="s">
-        <v>602</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>4</v>
-      </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E47" s="2">
-        <v>45945</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6221,30 +6294,30 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>603</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>4</v>
+        <v>602</v>
+      </c>
+      <c r="C48" s="10">
+        <v>2025</v>
       </c>
       <c r="D48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E48" s="2">
         <v>45945</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="A49" s="1">
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E49" s="2">
         <v>45945</v>
@@ -6255,33 +6328,33 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E50" s="2">
-        <v>45944</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="A51" s="1">
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E51" s="2">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -6289,33 +6362,33 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E52" s="2">
+        <v>45944</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>49</v>
+      </c>
+      <c r="B53" t="s">
+        <v>606</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="2">
         <v>45940</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>49</v>
-      </c>
-      <c r="B53" t="s">
-        <v>608</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53" t="s">
-        <v>43</v>
-      </c>
-      <c r="E53" s="2">
-        <v>45933</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -6323,30 +6396,30 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E54" s="2">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="A55" s="1">
         <v>51</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>610</v>
+      <c r="B55" t="s">
+        <v>608</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E55" s="2">
         <v>45933</v>
@@ -6356,34 +6429,34 @@
       <c r="A56">
         <v>52</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>611</v>
+      <c r="B56" t="s">
+        <v>609</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E56" s="2">
         <v>45933</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="A57" s="1">
         <v>53</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E57" s="2">
-        <v>45930</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -6391,33 +6464,33 @@
         <v>54</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E58" s="2">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="A59" s="1">
         <v>55</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E59" s="2">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -6425,33 +6498,33 @@
         <v>56</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E60" s="2">
         <v>45924</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61">
+      <c r="A61" s="1">
         <v>57</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>616</v>
-      </c>
-      <c r="C61" s="10">
-        <v>2025</v>
+        <v>614</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E61" s="2">
-        <v>45923</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -6459,33 +6532,33 @@
         <v>58</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E62" s="2">
-        <v>45918</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63">
+      <c r="A63" s="1">
         <v>59</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>618</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C63" s="10">
+        <v>2025</v>
       </c>
       <c r="D63" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E63" s="2">
-        <v>45908</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -6493,33 +6566,33 @@
         <v>60</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E64" s="2">
-        <v>45897</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65">
+      <c r="A65" s="1">
         <v>61</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C65" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E65" s="2">
-        <v>45891</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -6527,33 +6600,33 @@
         <v>62</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E66" s="2">
+        <v>45897</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>63</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D67" t="s">
+        <v>60</v>
+      </c>
+      <c r="E67" s="2">
         <v>45891</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>63</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>622</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D67" t="s">
-        <v>63</v>
-      </c>
-      <c r="E67" s="2">
-        <v>45888</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -6561,33 +6634,33 @@
         <v>64</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E68" s="2">
-        <v>45880</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69">
+      <c r="A69" s="1">
         <v>65</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>69</v>
+        <v>622</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E69" s="2">
-        <v>45855</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -6595,33 +6668,33 @@
         <v>66</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E70" s="2">
-        <v>45838</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71">
+      <c r="A71" s="1">
         <v>67</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>625</v>
+        <v>69</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E71" s="2">
-        <v>45838</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -6629,33 +6702,33 @@
         <v>68</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E72" s="2">
-        <v>45835</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73">
+      <c r="A73" s="1">
         <v>69</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>75</v>
+        <v>625</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E73" s="2">
-        <v>45833</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -6663,33 +6736,33 @@
         <v>70</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C74" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E74" s="2">
-        <v>45831</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75">
+      <c r="A75" s="1">
         <v>71</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>628</v>
+        <v>75</v>
       </c>
       <c r="C75" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E75" s="2">
-        <v>45825</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -6697,30 +6770,30 @@
         <v>72</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C76" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E76" s="2">
-        <v>45825</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77">
+      <c r="A77" s="1">
         <v>73</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E77" s="2">
         <v>45825</v>
@@ -6731,33 +6804,33 @@
         <v>74</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C78" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2">
-        <v>45808</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79">
+      <c r="A79" s="1">
         <v>75</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C79" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E79" s="2">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -6765,30 +6838,30 @@
         <v>76</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C80" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E80" s="2">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81">
+      <c r="A81" s="1">
         <v>77</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C81" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E81" s="2">
         <v>45803</v>
@@ -6799,30 +6872,30 @@
         <v>78</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E82" s="2">
         <v>45803</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83">
+      <c r="A83" s="1">
         <v>79</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C83" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E83" s="2">
         <v>45803</v>
@@ -6833,101 +6906,101 @@
         <v>80</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C84" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E84" s="2">
         <v>45803</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
         <v>81</v>
       </c>
       <c r="B85" s="10" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C85" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E85" s="2">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>82</v>
       </c>
       <c r="B86" s="10" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C86" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E86" s="2">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>83</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" t="s">
+        <v>94</v>
+      </c>
+      <c r="E87" s="2">
         <v>45796</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>83</v>
-      </c>
-      <c r="B87" s="10" t="s">
-        <v>640</v>
-      </c>
-      <c r="C87" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D87" t="s">
-        <v>95</v>
-      </c>
-      <c r="E87" s="2">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>84</v>
       </c>
       <c r="B88" s="10" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C88" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D88" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E88" s="2">
-        <v>45779</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89">
+      <c r="A89" s="1">
         <v>85</v>
       </c>
       <c r="B89" s="10" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E89" s="2">
-        <v>45770</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -6935,33 +7008,33 @@
         <v>86</v>
       </c>
       <c r="B90" s="10" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>4</v>
       </c>
       <c r="D90" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E90" s="2">
-        <v>45762</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91">
+      <c r="A91" s="1">
         <v>87</v>
       </c>
       <c r="B91" s="10" t="s">
-        <v>644</v>
-      </c>
-      <c r="C91" s="10">
-        <v>2025</v>
+        <v>642</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>4</v>
       </c>
       <c r="D91" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E91" s="2">
-        <v>45749</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -6969,33 +7042,33 @@
         <v>88</v>
       </c>
       <c r="B92" s="10" t="s">
-        <v>645</v>
-      </c>
-      <c r="C92" s="10">
+        <v>643</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92" s="2">
+        <v>45762</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>89</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="C93" s="10">
         <v>2025</v>
       </c>
-      <c r="D92" t="s">
-        <v>107</v>
-      </c>
-      <c r="E92" s="2">
+      <c r="D93" t="s">
+        <v>106</v>
+      </c>
+      <c r="E93" s="2">
         <v>45749</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>89</v>
-      </c>
-      <c r="B93" s="10" t="s">
-        <v>646</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D93" t="s">
-        <v>108</v>
-      </c>
-      <c r="E93" s="2">
-        <v>45748</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -7003,33 +7076,33 @@
         <v>90</v>
       </c>
       <c r="B94" s="10" t="s">
-        <v>647</v>
-      </c>
-      <c r="C94" s="10" t="s">
-        <v>114</v>
+        <v>645</v>
+      </c>
+      <c r="C94" s="10">
+        <v>2025</v>
       </c>
       <c r="D94" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E94" s="2">
-        <v>45736</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95">
+      <c r="A95" s="1">
         <v>91</v>
       </c>
       <c r="B95" s="10" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E95" s="2">
-        <v>45734</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -7037,33 +7110,33 @@
         <v>92</v>
       </c>
       <c r="B96" s="10" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C96" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E96" s="2">
-        <v>45726</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97">
+      <c r="A97" s="1">
         <v>93</v>
       </c>
       <c r="B97" s="10" t="s">
-        <v>650</v>
-      </c>
-      <c r="C97" s="10">
-        <v>2025</v>
+        <v>648</v>
+      </c>
+      <c r="C97" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E97" s="2">
-        <v>45726</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7071,33 +7144,33 @@
         <v>94</v>
       </c>
       <c r="B98" s="10" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C98" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E98" s="2">
         <v>45726</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99">
+      <c r="A99" s="1">
         <v>95</v>
       </c>
       <c r="B99" s="10" t="s">
-        <v>652</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C99" s="10">
+        <v>2025</v>
       </c>
       <c r="D99" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E99" s="2">
-        <v>45723</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7105,33 +7178,33 @@
         <v>96</v>
       </c>
       <c r="B100" s="10" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C100" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E100" s="2">
-        <v>45721</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101">
+      <c r="A101" s="1">
         <v>97</v>
       </c>
       <c r="B101" s="10" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C101" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E101" s="2">
-        <v>45698</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7139,67 +7212,67 @@
         <v>98</v>
       </c>
       <c r="B102" s="10" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C102" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E102" s="2">
-        <v>45695</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103">
+      <c r="A103" s="1">
         <v>99</v>
       </c>
       <c r="B103" s="10" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C103" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E103" s="2">
-        <v>45694</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>100</v>
       </c>
-      <c r="B104" t="s">
-        <v>587</v>
+      <c r="B104" s="10" t="s">
+        <v>655</v>
       </c>
       <c r="C104" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E104" s="2">
-        <v>45692</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105">
+      <c r="A105" s="1">
         <v>101</v>
       </c>
-      <c r="B105" t="s">
-        <v>586</v>
+      <c r="B105" s="10" t="s">
+        <v>656</v>
       </c>
       <c r="C105" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E105" s="2">
-        <v>45686</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7207,33 +7280,33 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C106" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E106" s="2">
-        <v>45681</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107">
+      <c r="A107" s="1">
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C107" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E107" s="2">
-        <v>45678</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7241,33 +7314,33 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C108" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E108" s="2">
-        <v>45677</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109">
+      <c r="A109" s="1">
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C109" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E109" s="2">
-        <v>45677</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7275,33 +7348,33 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C110" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E110" s="2">
-        <v>45670</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111">
+      <c r="A111" s="1">
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C111" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E111" s="2">
-        <v>45661</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7309,33 +7382,33 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C112" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E112" s="2">
+        <v>45670</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>109</v>
+      </c>
+      <c r="B113" t="s">
+        <v>580</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D113" t="s">
+        <v>145</v>
+      </c>
+      <c r="E113" s="2">
         <v>45661</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113">
-        <v>109</v>
-      </c>
-      <c r="B113" t="s">
-        <v>578</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D113" t="s">
-        <v>148</v>
-      </c>
-      <c r="E113" s="2">
-        <v>45659</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7343,33 +7416,33 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C114" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E114" s="2">
-        <v>45656</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115">
+      <c r="A115" s="1">
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C115" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E115" s="2">
-        <v>45656</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7377,33 +7450,33 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>575</v>
-      </c>
-      <c r="C116" s="10">
-        <v>2024</v>
+        <v>577</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E116" s="2">
-        <v>45652</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117">
+      <c r="A117" s="1">
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C117" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="E117" s="2">
-        <v>45650</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7411,33 +7484,33 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>573</v>
-      </c>
-      <c r="C118" s="10" t="s">
-        <v>114</v>
+        <v>575</v>
+      </c>
+      <c r="C118" s="10">
+        <v>2024</v>
       </c>
       <c r="D118" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E118" s="2">
-        <v>45631</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119">
+      <c r="A119" s="1">
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="E119" s="2">
-        <v>45625</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -7445,33 +7518,33 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C120" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D120" t="s">
+        <v>157</v>
+      </c>
+      <c r="E120" s="2">
+        <v>45631</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>117</v>
+      </c>
+      <c r="B121" t="s">
+        <v>572</v>
+      </c>
+      <c r="C121" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D120" t="s">
-        <v>159</v>
-      </c>
-      <c r="E120" s="2">
-        <v>45622</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121">
-        <v>117</v>
-      </c>
-      <c r="B121" t="s">
-        <v>570</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>114</v>
-      </c>
       <c r="D121" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E121" s="2">
-        <v>45593</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7479,33 +7552,33 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D122" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E122" s="2">
-        <v>45588</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A123">
+      <c r="A123" s="1">
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C123" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E123" s="2">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7513,33 +7586,33 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C124" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E124" s="2">
-        <v>45578</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A125">
+      <c r="A125" s="1">
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C125" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E125" s="2">
-        <v>45566</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7547,33 +7620,33 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C126" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E126" s="2">
+        <v>45578</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>123</v>
+      </c>
+      <c r="B127" t="s">
+        <v>566</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D127" t="s">
+        <v>172</v>
+      </c>
+      <c r="E127" s="2">
         <v>45566</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A127">
-        <v>123</v>
-      </c>
-      <c r="B127" t="s">
-        <v>564</v>
-      </c>
-      <c r="C127" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D127" t="s">
-        <v>174</v>
-      </c>
-      <c r="E127" s="2">
-        <v>45565</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -7581,33 +7654,33 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C128" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E128" s="2">
-        <v>45563</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129">
+      <c r="A129" s="1">
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C129" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E129" s="2">
-        <v>45553</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7615,33 +7688,33 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C130" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="E130" s="2">
-        <v>45548</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131">
+      <c r="A131" s="1">
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C131" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E131" s="2">
-        <v>45548</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -7649,33 +7722,33 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C132" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>181</v>
+        <v>119</v>
       </c>
       <c r="E132" s="2">
-        <v>45539</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A133">
+      <c r="A133" s="1">
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C133" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E133" s="2">
-        <v>45538</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -7683,33 +7756,33 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C134" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E134" s="2">
-        <v>45537</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A135">
+      <c r="A135" s="1">
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C135" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E135" s="2">
-        <v>45523</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -7717,33 +7790,33 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C136" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E136" s="2">
-        <v>45520</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A137">
+      <c r="A137" s="1">
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C137" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E137" s="2">
-        <v>45505</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -7751,33 +7824,33 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C138" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E138" s="2">
-        <v>45502</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A139">
+      <c r="A139" s="1">
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C139" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E139" s="2">
-        <v>45478</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -7785,33 +7858,33 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C140" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E140" s="2">
+        <v>45502</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>137</v>
+      </c>
+      <c r="B141" t="s">
+        <v>552</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D141" t="s">
+        <v>197</v>
+      </c>
+      <c r="E141" s="2">
         <v>45478</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A141">
-        <v>137</v>
-      </c>
-      <c r="B141" t="s">
-        <v>550</v>
-      </c>
-      <c r="C141" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D141" t="s">
-        <v>201</v>
-      </c>
-      <c r="E141" s="2">
-        <v>45462</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -7819,33 +7892,33 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>204</v>
+        <v>551</v>
       </c>
       <c r="C142" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E142" s="2">
-        <v>45455</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A143">
+      <c r="A143" s="1">
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C143" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E143" s="2">
-        <v>45454</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -7853,33 +7926,33 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>548</v>
+        <v>204</v>
       </c>
       <c r="C144" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E144" s="2">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A145">
+      <c r="A145" s="1">
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C145" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E145" s="2">
-        <v>45448</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -7887,33 +7960,33 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C146" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E146" s="2">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A147">
+      <c r="A147" s="1">
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C147" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E147" s="2">
-        <v>45432</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -7921,33 +7994,33 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C148" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E148" s="2">
-        <v>45420</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A149">
+      <c r="A149" s="1">
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C149" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E149" s="2">
-        <v>45418</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -7955,67 +8028,67 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C150" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E150" s="2">
-        <v>45416</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A151">
+      <c r="A151" s="1">
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C151" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E151" s="2">
-        <v>45407</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>148</v>
       </c>
-      <c r="B152" s="6" t="s">
-        <v>540</v>
+      <c r="B152" t="s">
+        <v>542</v>
       </c>
       <c r="C152" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E152" s="2">
-        <v>45405</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A153">
+      <c r="A153" s="1">
         <v>149</v>
       </c>
-      <c r="B153" s="6" t="s">
-        <v>535</v>
+      <c r="B153" t="s">
+        <v>541</v>
       </c>
       <c r="C153" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D153" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E153" s="2">
-        <v>45397</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -8023,33 +8096,33 @@
         <v>150</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C154" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E154" s="2">
+        <v>45405</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>151</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D155" t="s">
+        <v>226</v>
+      </c>
+      <c r="E155" s="2">
         <v>45397</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A155">
-        <v>151</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="C155" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D155" t="s">
-        <v>230</v>
-      </c>
-      <c r="E155" s="2">
-        <v>45387</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8057,30 +8130,30 @@
         <v>152</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C156" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D156" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E156" s="2">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A157">
+      <c r="A157" s="1">
         <v>153</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C157" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D157" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E157" s="2">
         <v>45387</v>
@@ -8091,33 +8164,33 @@
         <v>154</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="C158" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D158" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E158" s="2">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A159">
+      <c r="A159" s="1">
         <v>155</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C159" s="10" t="s">
         <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E159" s="2">
-        <v>45384</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -8125,67 +8198,67 @@
         <v>156</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D160" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E160" s="2">
-        <v>45378</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161">
+      <c r="A161" s="1">
         <v>157</v>
       </c>
-      <c r="B161" t="s">
-        <v>533</v>
+      <c r="B161" s="6" t="s">
+        <v>534</v>
       </c>
       <c r="C161" s="10" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D161" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E161" s="2">
-        <v>45373</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>158</v>
       </c>
-      <c r="B162" t="s">
-        <v>532</v>
+      <c r="B162" s="6" t="s">
+        <v>506</v>
       </c>
       <c r="C162" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D162" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E162" s="2">
-        <v>45373</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163">
+      <c r="A163" s="1">
         <v>159</v>
       </c>
       <c r="B163" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C163" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D163" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="E163" s="2">
-        <v>45369</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8193,33 +8266,33 @@
         <v>160</v>
       </c>
       <c r="B164" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C164" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D164" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E164" s="2">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165">
+      <c r="A165" s="1">
         <v>161</v>
       </c>
       <c r="B165" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C165" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D165" t="s">
-        <v>243</v>
+        <v>117</v>
       </c>
       <c r="E165" s="2">
-        <v>45367</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -8227,33 +8300,33 @@
         <v>162</v>
       </c>
       <c r="B166" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C166" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D166" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E166" s="2">
-        <v>45366</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167">
+      <c r="A167" s="1">
         <v>163</v>
       </c>
       <c r="B167" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C167" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E167" s="2">
-        <v>45365</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -8261,33 +8334,33 @@
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E168" s="2">
-        <v>45362</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169">
+      <c r="A169" s="1">
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C169" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E169" s="2">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8295,30 +8368,30 @@
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C170" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D170" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E170" s="2">
         <v>45362</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171">
+      <c r="A171" s="1">
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C171" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E171" s="2">
         <v>45362</v>
@@ -8329,33 +8402,33 @@
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C172" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E172" s="2">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173">
+      <c r="A173" s="1">
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C173" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E173" s="2">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -8363,33 +8436,33 @@
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C174" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E174" s="2">
-        <v>45358</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175">
+      <c r="A175" s="1">
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C175" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D175" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E175" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -8397,33 +8470,33 @@
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C176" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D176" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E176" s="2">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177">
+      <c r="A177" s="1">
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C177" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D177" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E177" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8431,30 +8504,30 @@
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C178" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D178" t="s">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="E178" s="2">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179">
+      <c r="A179" s="1">
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D179" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="E179" s="2">
         <v>45352</v>
@@ -8465,33 +8538,33 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C180" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D180" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="E180" s="2">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A181">
+      <c r="A181" s="1">
         <v>177</v>
       </c>
       <c r="B181" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C181" s="10" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E181" s="2">
-        <v>45345</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -8499,33 +8572,33 @@
         <v>178</v>
       </c>
       <c r="B182" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C182" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D182" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E182" s="2">
-        <v>45335</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A183">
+      <c r="A183" s="1">
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C183" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D183" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E183" s="2">
-        <v>45334</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -8533,33 +8606,33 @@
         <v>180</v>
       </c>
       <c r="B184" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C184" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E184" s="2">
-        <v>45314</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A185">
+      <c r="A185" s="1">
         <v>181</v>
       </c>
-      <c r="B185" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C185" s="10">
-        <v>2023</v>
+      <c r="B185" t="s">
+        <v>512</v>
+      </c>
+      <c r="C185" s="10" t="s">
+        <v>236</v>
       </c>
       <c r="D185" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E185" s="2">
-        <v>45306</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -8567,32 +8640,66 @@
         <v>182</v>
       </c>
       <c r="B186" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C186" s="10" t="s">
         <v>236</v>
       </c>
       <c r="D186" t="s">
+        <v>276</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>183</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="C187" s="10">
+        <v>2023</v>
+      </c>
+      <c r="D187" t="s">
+        <v>277</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188">
+        <v>184</v>
+      </c>
+      <c r="B188" t="s">
+        <v>509</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D188" t="s">
         <v>279</v>
       </c>
-      <c r="E186" s="2">
+      <c r="E188" s="2">
         <v>45294</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A187">
-        <v>183</v>
-      </c>
-      <c r="B187" t="s">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>185</v>
+      </c>
+      <c r="B189" t="s">
         <v>508</v>
       </c>
-      <c r="C187" s="10" t="s">
+      <c r="C189" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D187" t="s">
+      <c r="D189" t="s">
         <v>281</v>
       </c>
-      <c r="E187" s="2">
+      <c r="E189" s="2">
         <v>45292</v>
       </c>
     </row>
@@ -8604,7 +8711,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E366"/>
+  <dimension ref="A1:E367"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.7109375" style="13" customWidth="1"/>
@@ -8635,449 +8742,467 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="14"/>
+      <c r="C4" s="11"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
-        <f t="shared" ref="A5" si="0">ROW()-4</f>
         <v>1</v>
       </c>
-      <c r="B5" s="35" t="s">
+      <c r="B5" s="49" t="s">
+        <v>847</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>820</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>848</v>
+      </c>
+      <c r="E5" s="48">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="27" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <f t="shared" ref="A6" si="0">ROW()-4</f>
+        <v>2</v>
+      </c>
+      <c r="B6" s="35" t="s">
         <v>770</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D6" s="27" t="s">
         <v>771</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E6" s="28" t="s">
         <v>772</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <f>ROW()-4</f>
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>658</v>
-      </c>
-      <c r="C6" s="10">
-        <v>2026</v>
-      </c>
-      <c r="D6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E6" s="2">
-        <v>46175</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7">
+        <f>ROW()-4</f>
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>658</v>
+      </c>
+      <c r="C7" s="10">
+        <v>2026</v>
+      </c>
+      <c r="D7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>2</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B8" s="18" t="s">
         <v>659</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="C8" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E8" s="17">
         <v>46008</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="16">
-        <v>3</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>660</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="E8" s="17">
-        <v>45972</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C9" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E9" s="17">
-        <v>45965</v>
+        <v>45972</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E10" s="17">
-        <v>45957</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="16">
+        <v>5</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>662</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="E11" s="17">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16">
         <v>6</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B12" s="18" t="s">
         <v>663</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="18" t="s">
+      <c r="C12" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E12" s="17">
         <v>45922</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>664</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="E12" s="17">
-        <v>45903</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13">
+        <v>7</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>664</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="17">
+        <v>45903</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>8</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B14" s="18" t="s">
         <v>665</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="18" t="s">
+      <c r="C14" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E14" s="17">
         <v>45869</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16">
-        <v>9</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>666</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="E14" s="17">
-        <v>45860</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>667</v>
-      </c>
-      <c r="C15" s="19">
-        <v>2025</v>
+        <v>666</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>4</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E15" s="17">
-        <v>45853</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="16">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C16" s="19">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E16" s="17">
-        <v>45678</v>
+        <v>45853</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C17" s="19">
         <v>2024</v>
       </c>
       <c r="D17" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="E17" s="17">
+        <v>45678</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="16">
+        <v>12</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="C18" s="19">
+        <v>2024</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E18" s="17">
         <v>45639</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>13</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>670</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="E18" s="17">
-        <v>45637</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>670</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="E19" s="17">
+        <v>45637</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>14</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B20" s="18" t="s">
         <v>671</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C20" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D20" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E20" s="17">
         <v>45576</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="16">
-        <v>15</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>672</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="E20" s="17">
-        <v>45559</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E21" s="17">
-        <v>45462</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>114</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E22" s="17">
-        <v>45456</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16">
+        <v>17</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>674</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="E23" s="17">
+        <v>45456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
         <v>18</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B24" s="29" t="s">
         <v>675</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="18" t="s">
+      <c r="C24" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E24" s="17">
         <v>45446</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>19</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="C24" s="19">
-        <v>2024</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="E24" s="17">
-        <v>45443</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25">
+        <v>19</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="19">
+        <v>2024</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="E25" s="17">
+        <v>45443</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>20</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B26" s="29" t="s">
         <v>676</v>
       </c>
-      <c r="C25" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D25" s="18" t="s">
+      <c r="C26" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="18" t="s">
         <v>305</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E26" s="17">
         <v>45442</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16">
-        <v>21</v>
-      </c>
-      <c r="B26" s="29" t="s">
-        <v>677</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>114</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="E26" s="17">
-        <v>45415</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B27" s="29" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E27" s="17">
-        <v>45394</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16">
-        <v>23</v>
-      </c>
-      <c r="B28" s="18" t="s">
-        <v>679</v>
+        <v>22</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>678</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>235</v>
+        <v>112</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E28" s="17">
-        <v>45344</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="16">
+        <v>23</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>679</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="E29" s="17">
+        <v>45344</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="16">
         <v>24</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B30" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C30" s="19">
         <v>2024</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D30" s="18" t="s">
         <v>309</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E30" s="17">
         <v>45303</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="9"/>
-    </row>
-    <row r="31" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="22"/>
       <c r="E31" s="9"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E32" s="2"/>
+    <row r="32" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A32" s="8"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="9"/>
     </row>
     <row r="33" spans="5:5" x14ac:dyDescent="0.25">
       <c r="E33" s="2"/>
@@ -9290,7 +9415,6 @@
       <c r="E102" s="2"/>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B103" s="15"/>
       <c r="E103" s="2"/>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
@@ -9302,6 +9426,7 @@
       <c r="E105" s="2"/>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B106" s="15"/>
       <c r="E106" s="2"/>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.25">
@@ -9314,10 +9439,10 @@
       <c r="E109" s="2"/>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B110" s="15"/>
       <c r="E110" s="2"/>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B111" s="15"/>
       <c r="E111" s="2"/>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.25">
@@ -9840,7 +9965,6 @@
       <c r="E284" s="2"/>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B285" s="15"/>
       <c r="E285" s="2"/>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.25">
@@ -9860,16 +9984,17 @@
       <c r="E289" s="2"/>
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B290" s="15"/>
       <c r="E290" s="2"/>
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E291" s="2"/>
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B292" s="15"/>
       <c r="E292" s="2"/>
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B293" s="15"/>
       <c r="E293" s="2"/>
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.25">
@@ -9882,24 +10007,23 @@
       <c r="E296" s="2"/>
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B297" s="15"/>
       <c r="E297" s="2"/>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B298" s="15"/>
       <c r="E298" s="2"/>
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E299" s="2"/>
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B300" s="15"/>
       <c r="E300" s="2"/>
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B301" s="15"/>
       <c r="E301" s="2"/>
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B302" s="15"/>
       <c r="E302" s="2"/>
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.25">
@@ -9911,10 +10035,10 @@
       <c r="E304" s="2"/>
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B305" s="15"/>
       <c r="E305" s="2"/>
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B306" s="15"/>
       <c r="E306" s="2"/>
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.25">
@@ -9934,13 +10058,14 @@
       <c r="E310" s="2"/>
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B311" s="15"/>
       <c r="E311" s="2"/>
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B312" s="15"/>
       <c r="E312" s="2"/>
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B313" s="15"/>
       <c r="E313" s="2"/>
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.25">
@@ -10091,10 +10216,10 @@
       <c r="E362" s="2"/>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B363" s="15"/>
       <c r="E363" s="2"/>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B364" s="15"/>
       <c r="E364" s="2"/>
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.25">
@@ -10102,6 +10227,9 @@
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.25">
       <c r="E366" s="2"/>
+    </row>
+    <row r="367" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E367" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10157,14 +10285,42 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E5" s="2"/>
+      <c r="A5" s="26">
+        <v>1</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>851</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>815</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>852</v>
+      </c>
+      <c r="E5" s="48">
+        <v>46133</v>
+      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E6" s="2"/>
+      <c r="A6" s="26">
+        <v>2</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>849</v>
+      </c>
+      <c r="C6" s="46" t="s">
+        <v>820</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>850</v>
+      </c>
+      <c r="E6" s="48">
+        <v>46132</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>814</v>
@@ -10181,8 +10337,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
-        <f>ROW()-6</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" s="27" t="s">
         <v>790</v>
@@ -10199,8 +10354,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
-        <f t="shared" ref="A9:A72" si="0">ROW()-6</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B9" s="36" t="s">
         <v>775</v>
@@ -10221,8 +10375,7 @@
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B10" s="36" t="s">
         <v>777</v>
@@ -10240,8 +10393,7 @@
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
-        <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>774</v>
@@ -10261,8 +10413,7 @@
     </row>
     <row r="12" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B12" s="27" t="s">
         <v>744</v>
@@ -10279,8 +10430,7 @@
     </row>
     <row r="13" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B13" s="27" t="s">
         <v>746</v>
@@ -10297,8 +10447,7 @@
     </row>
     <row r="14" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
-        <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
         <v>748</v>
@@ -10315,8 +10464,7 @@
     </row>
     <row r="15" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B15" s="27" t="s">
         <v>750</v>
@@ -10333,8 +10481,7 @@
     </row>
     <row r="16" spans="1:7" s="27" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B16" s="27" t="s">
         <v>752</v>
@@ -10351,8 +10498,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
-        <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
         <v>681</v>
@@ -10369,8 +10515,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>682</v>
@@ -10387,8 +10532,7 @@
     </row>
     <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26">
-        <f t="shared" si="0"/>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>683</v>
@@ -10405,8 +10549,7 @@
     </row>
     <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="26">
-        <f t="shared" si="0"/>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B20" s="21" t="s">
         <v>684</v>
@@ -10423,8 +10566,7 @@
     </row>
     <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="26">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B21" s="21" t="s">
         <v>685</v>
@@ -10444,8 +10586,7 @@
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="26">
-        <f t="shared" si="0"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>686</v>
@@ -10462,8 +10603,7 @@
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="26">
-        <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B23" s="21" t="s">
         <v>687</v>
@@ -10480,8 +10620,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="26">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
         <v>688</v>
@@ -10498,8 +10637,7 @@
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="26">
-        <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
         <v>689</v>
@@ -10516,8 +10654,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="26">
-        <f t="shared" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B26" s="21" t="s">
         <v>690</v>
@@ -10534,8 +10671,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="26">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B27" s="21" t="s">
         <v>691</v>
@@ -10552,8 +10688,7 @@
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="26">
-        <f t="shared" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B28" s="21" t="s">
         <v>692</v>
@@ -10570,8 +10705,7 @@
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="26">
-        <f t="shared" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B29" s="21" t="s">
         <v>693</v>
@@ -10588,8 +10722,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="26">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B30" s="21" t="s">
         <v>743</v>
@@ -10606,8 +10739,7 @@
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="26">
-        <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31" s="21" t="s">
         <v>742</v>
@@ -10624,8 +10756,7 @@
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="26">
-        <f t="shared" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B32" s="21" t="s">
         <v>741</v>
@@ -10642,8 +10773,7 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="26">
-        <f t="shared" si="0"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B33" s="21" t="s">
         <v>740</v>
@@ -10660,8 +10790,7 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="26">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B34" s="21" t="s">
         <v>739</v>
@@ -10678,8 +10807,7 @@
     </row>
     <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="26">
-        <f t="shared" si="0"/>
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B35" s="21" t="s">
         <v>738</v>
@@ -10696,8 +10824,7 @@
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="26">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B36" s="21" t="s">
         <v>737</v>
@@ -10714,8 +10841,7 @@
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="26">
-        <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B37" s="21" t="s">
         <v>736</v>
@@ -10732,8 +10858,7 @@
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="26">
-        <f t="shared" si="0"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B38" s="21" t="s">
         <v>735</v>
@@ -10750,8 +10875,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="26">
-        <f t="shared" si="0"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B39" s="21" t="s">
         <v>734</v>
@@ -10768,8 +10892,7 @@
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="26">
-        <f t="shared" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B40" s="21" t="s">
         <v>733</v>
@@ -10786,8 +10909,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="26">
-        <f t="shared" si="0"/>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" s="21" t="s">
         <v>732</v>
@@ -10804,8 +10926,7 @@
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="26">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B42" s="21" t="s">
         <v>731</v>
@@ -10822,8 +10943,7 @@
     </row>
     <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="26">
-        <f t="shared" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" s="21" t="s">
         <v>730</v>
@@ -10840,8 +10960,7 @@
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="26">
-        <f t="shared" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B44" s="21" t="s">
         <v>729</v>
@@ -10858,8 +10977,7 @@
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="26">
-        <f t="shared" si="0"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B45" s="21" t="s">
         <v>728</v>
@@ -10876,8 +10994,7 @@
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="26">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B46" s="21" t="s">
         <v>727</v>
@@ -10894,8 +11011,7 @@
     </row>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="26">
-        <f t="shared" si="0"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B47" s="21" t="s">
         <v>726</v>
@@ -10912,8 +11028,7 @@
     </row>
     <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="26">
-        <f t="shared" si="0"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B48" s="21" t="s">
         <v>725</v>
@@ -10930,8 +11045,7 @@
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="26">
-        <f t="shared" si="0"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B49" s="21" t="s">
         <v>724</v>
@@ -10948,8 +11062,7 @@
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="26">
-        <f t="shared" si="0"/>
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B50" s="21" t="s">
         <v>723</v>
@@ -10966,8 +11079,7 @@
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="26">
-        <f t="shared" si="0"/>
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B51" s="21" t="s">
         <v>722</v>
@@ -10984,8 +11096,7 @@
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="26">
-        <f t="shared" si="0"/>
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B52" s="21" t="s">
         <v>721</v>
@@ -11002,8 +11113,7 @@
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="26">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B53" s="21" t="s">
         <v>720</v>
@@ -11020,8 +11130,7 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="26">
-        <f t="shared" si="0"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B54" s="21" t="s">
         <v>719</v>
@@ -11038,8 +11147,7 @@
     </row>
     <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="26">
-        <f t="shared" si="0"/>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B55" s="21" t="s">
         <v>718</v>
@@ -11056,8 +11164,7 @@
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="26">
-        <f t="shared" si="0"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B56" s="21" t="s">
         <v>717</v>
@@ -11074,8 +11181,7 @@
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="26">
-        <f t="shared" si="0"/>
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B57" s="21" t="s">
         <v>716</v>
@@ -11092,8 +11198,7 @@
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="26">
-        <f t="shared" si="0"/>
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B58" s="21" t="s">
         <v>715</v>
@@ -11110,8 +11215,7 @@
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="26">
-        <f t="shared" si="0"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B59" s="21" t="s">
         <v>714</v>
@@ -11128,8 +11232,7 @@
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="26">
-        <f t="shared" si="0"/>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B60" s="21" t="s">
         <v>713</v>
@@ -11146,8 +11249,7 @@
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="26">
-        <f t="shared" si="0"/>
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B61" s="21" t="s">
         <v>712</v>
@@ -11164,8 +11266,7 @@
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="26">
-        <f t="shared" si="0"/>
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B62" s="21" t="s">
         <v>711</v>
@@ -11182,8 +11283,7 @@
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="26">
-        <f t="shared" si="0"/>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B63" s="21" t="s">
         <v>710</v>
@@ -11200,8 +11300,7 @@
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="26">
-        <f t="shared" si="0"/>
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B64" s="21" t="s">
         <v>709</v>
@@ -11218,8 +11317,7 @@
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="26">
-        <f t="shared" si="0"/>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B65" s="21" t="s">
         <v>708</v>
@@ -11236,8 +11334,7 @@
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="26">
-        <f t="shared" si="0"/>
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B66" s="21" t="s">
         <v>707</v>
@@ -11254,8 +11351,7 @@
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="26">
-        <f t="shared" si="0"/>
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B67" s="21" t="s">
         <v>706</v>
@@ -11272,8 +11368,7 @@
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="26">
-        <f t="shared" si="0"/>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B68" s="21" t="s">
         <v>705</v>
@@ -11290,8 +11385,7 @@
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="26">
-        <f t="shared" si="0"/>
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B69" s="21" t="s">
         <v>704</v>
@@ -11308,8 +11402,7 @@
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="26">
-        <f t="shared" si="0"/>
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B70" s="21" t="s">
         <v>703</v>
@@ -11326,8 +11419,7 @@
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="26">
-        <f t="shared" si="0"/>
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B71" s="21" t="s">
         <v>702</v>
@@ -11344,8 +11436,7 @@
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="26">
-        <f t="shared" si="0"/>
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B72" s="30" t="s">
         <v>701</v>
@@ -11362,8 +11453,7 @@
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="26">
-        <f t="shared" ref="A73:A79" si="1">ROW()-6</f>
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B73" s="30" t="s">
         <v>700</v>
@@ -11380,8 +11470,7 @@
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="26">
-        <f t="shared" si="1"/>
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B74" s="21" t="s">
         <v>699</v>
@@ -11398,8 +11487,7 @@
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="26">
-        <f t="shared" si="1"/>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B75" s="21" t="s">
         <v>698</v>
@@ -11416,8 +11504,7 @@
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="26">
-        <f t="shared" si="1"/>
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B76" s="21" t="s">
         <v>697</v>
@@ -11434,8 +11521,7 @@
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="26">
-        <f t="shared" si="1"/>
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B77" s="21" t="s">
         <v>696</v>
@@ -11452,8 +11538,7 @@
     </row>
     <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="26">
-        <f t="shared" si="1"/>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B78" s="21" t="s">
         <v>695</v>
@@ -11470,8 +11555,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="26">
-        <f t="shared" si="1"/>
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B79" s="21" t="s">
         <v>694</v>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{847DB9D1-111C-4201-9DAB-AC1C83F98954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAA92D7-F95D-4CF3-A89A-2F4F92064D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="878">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2621,6 +2621,51 @@
   </si>
   <si>
     <t>Modalities for export of Wheat - regarding.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 11/2026-27</t>
+  </si>
+  <si>
+    <t>Insertion of SION notes below the SIONs M1 to M8– reg.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 10/2026-27</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 09/2026-27</t>
+  </si>
+  <si>
+    <t>Amendments in Para 2.88 and Para 2.91 of Handbook of Procedures-reg.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 08/2026-27</t>
+  </si>
+  <si>
+    <t>Enlistment and updation of Pre-Shipment Inspection Agencies (PSIAs) and Addition of Instruments of existing PSIAs in Appendix-2G under Para 2.52(c) of Handbook of Procedure (HBP), 2023 – Reg.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 07/2026-27</t>
+  </si>
+  <si>
+    <t>Validity of Ad-hoc norms under Para 4.12 (vi) of HBP-2023– reg.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION-  16/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in export policy of sugar</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 17/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in Import Policy of Silver covered under ITC (HS) codes 71069221 and 71069229 of Chapter 71 of ITC (HS), 2022, Schedule-I (Import Policy)</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE-  03/2026-27</t>
+  </si>
+  <si>
+    <t>Clarifications on Interest Subvention Support for Pre- and Post-Shipment Export Credit under Export Promotion Mission – Niryat Protsahan</t>
   </si>
 </sst>
 </file>
@@ -2628,7 +2673,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-14009]dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-14009]dd\-mm\-yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -2659,7 +2704,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2681,6 +2726,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2706,7 +2757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2797,31 +2848,40 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3102,7 +3162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O377"/>
+  <dimension ref="A1:O382"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3112,12 +3172,12 @@
     <col min="5" max="5" width="13.140625" style="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3134,2424 +3194,2503 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C4" s="9"/>
       <c r="D4" s="4"/>
       <c r="E4" s="39"/>
     </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
       <c r="B5" s="34" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>860</v>
-      </c>
-      <c r="E5" s="40">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>864</v>
+      </c>
+      <c r="E5" s="49">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
       <c r="B6" s="34" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D6" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="49">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>866</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>867</v>
+      </c>
+      <c r="E7" s="49">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>868</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>869</v>
+      </c>
+      <c r="E8" s="49">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>5</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>870</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>819</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>871</v>
+      </c>
+      <c r="E9" s="53">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>859</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>860</v>
+      </c>
+      <c r="E10" s="40">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>861</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D11" s="36" t="s">
         <v>862</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E11" s="40">
         <v>46142</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>1</v>
-      </c>
-      <c r="B7" s="34" t="s">
+    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>840</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C12" s="35">
         <v>2026</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="D12" s="36" t="s">
         <v>841</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E12" s="40">
         <v>46129</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>2</v>
-      </c>
-      <c r="B8" s="32" t="s">
+    <row r="13" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="32" t="s">
         <v>836</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C13" s="26" t="s">
         <v>819</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D13" s="33" t="s">
         <v>837</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E13" s="48">
         <v>46122</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>3</v>
-      </c>
-      <c r="B9" s="32" t="s">
+    <row r="14" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="32" t="s">
         <v>838</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C14" s="26" t="s">
         <v>819</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D14" s="33" t="s">
         <v>839</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E14" s="48">
         <v>46122</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
         <v>822</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E15" s="38">
         <v>46119</v>
       </c>
     </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>5</v>
-      </c>
-      <c r="B11" s="21" t="s">
+    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>811</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C16" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D16" s="25" t="s">
         <v>812</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E16" s="41">
         <v>46111</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>6</v>
-      </c>
-      <c r="B12" s="21" t="s">
+    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="21" t="s">
         <v>791</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C17" s="24">
         <v>2025</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D17" s="25" t="s">
         <v>792</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E17" s="41">
         <v>46105</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>7</v>
-      </c>
-      <c r="B13" s="21" t="s">
+    <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="21" t="s">
         <v>786</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="25" t="s">
+      <c r="C18" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="25" t="s">
         <v>787</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E18" s="41">
         <v>46101</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>8</v>
-      </c>
-      <c r="B14" s="21" t="s">
+    <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="21" t="s">
         <v>788</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="25" t="s">
+      <c r="C19" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E19" s="41">
         <v>46087</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>9</v>
-      </c>
-      <c r="B15" s="31" t="s">
+    <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>16</v>
+      </c>
+      <c r="B20" s="31" t="s">
         <v>779</v>
       </c>
-      <c r="C15" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="31" t="s">
+      <c r="C20" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="31" t="s">
         <v>778</v>
       </c>
-      <c r="E15" s="45">
+      <c r="E20" s="45">
         <v>46087</v>
       </c>
-      <c r="F15" s="30"/>
-    </row>
-    <row r="16" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>10</v>
-      </c>
-      <c r="B16" s="21" t="s">
+      <c r="F20" s="30"/>
+    </row>
+    <row r="21" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>17</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>754</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="25" t="s">
+      <c r="C21" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>755</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E21" s="42" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="17" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>11</v>
-      </c>
-      <c r="B17" s="21" t="s">
+    <row r="22" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>18</v>
+      </c>
+      <c r="B22" s="21" t="s">
         <v>757</v>
       </c>
-      <c r="C17" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="25" t="s">
+      <c r="C22" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="25" t="s">
         <v>758</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E22" s="42" t="s">
         <v>853</v>
       </c>
-      <c r="O17" s="21" t="s">
+      <c r="O22" s="21" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>12</v>
-      </c>
-      <c r="B18" s="21" t="s">
+    <row r="23" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>19</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>759</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="25" t="s">
+      <c r="C23" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="25" t="s">
         <v>760</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E23" s="42" t="s">
         <v>853</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>13</v>
-      </c>
-      <c r="B19" t="s">
-        <v>386</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E19" s="38">
-        <v>46328</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>387</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E20" s="38">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>388</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="38">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>389</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="38">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>17</v>
-      </c>
-      <c r="B23" t="s">
-        <v>390</v>
-      </c>
-      <c r="C23" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="38">
-        <v>46031</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>391</v>
-      </c>
-      <c r="C24" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D24" t="s">
-        <v>10</v>
+        <v>386</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="E24" s="38">
-        <v>46031</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>392</v>
-      </c>
-      <c r="C25" s="8">
-        <v>2025</v>
-      </c>
-      <c r="D25" t="s">
-        <v>14</v>
+        <v>387</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="E25" s="38">
-        <v>46022</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E26" s="38">
-        <v>46010</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E27" s="38">
-        <v>46008</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>395</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>4</v>
+        <v>390</v>
+      </c>
+      <c r="C28" s="8">
+        <v>2026</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E28" s="38">
-        <v>46008</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>396</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>4</v>
+        <v>391</v>
+      </c>
+      <c r="C29" s="8">
+        <v>2026</v>
       </c>
       <c r="D29" t="s">
-        <v>374</v>
+        <v>10</v>
       </c>
       <c r="E29" s="38">
-        <v>46002</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C30" s="8">
         <v>2025</v>
       </c>
       <c r="D30" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E30" s="38">
-        <v>46001</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>398</v>
-      </c>
-      <c r="C31" s="8">
-        <v>2025</v>
+        <v>393</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E31" s="38">
-        <v>46001</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E32" s="38">
-        <v>45992</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E33" s="38">
-        <v>45992</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>401</v>
-      </c>
-      <c r="C34" s="8">
-        <v>2025</v>
+        <v>396</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E34" s="38">
-        <v>45981</v>
+        <v>46002</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>402</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>4</v>
+        <v>397</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2025</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E35" s="38">
-        <v>45959</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C36" s="8">
         <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E36" s="38">
-        <v>45958</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>404</v>
-      </c>
-      <c r="C37" s="8">
-        <v>2025</v>
+        <v>399</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E37" s="38">
-        <v>45958</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E38" s="38">
-        <v>45953</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>406</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="C39" s="8">
+        <v>2025</v>
       </c>
       <c r="D39" t="s">
-        <v>31</v>
+        <v>373</v>
       </c>
       <c r="E39" s="38">
-        <v>45952</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E40" s="38">
-        <v>45945</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>4</v>
+        <v>403</v>
+      </c>
+      <c r="C41" s="8">
+        <v>2025</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E41" s="38">
-        <v>45940</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>408</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>4</v>
+        <v>404</v>
+      </c>
+      <c r="C42" s="8">
+        <v>2025</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E42" s="38">
-        <v>45940</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="E43" s="38">
-        <v>45933</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E44" s="38">
-        <v>45931</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="E45" s="38">
-        <v>45909</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>412</v>
+        <v>38</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E46" s="38">
-        <v>45903</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>413</v>
-      </c>
-      <c r="C47" s="8">
-        <v>2025</v>
+        <v>408</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E47" s="38">
-        <v>45895</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E48" s="38">
-        <v>45891</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E49" s="38">
-        <v>45870</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>416</v>
-      </c>
-      <c r="C50" s="8">
-        <v>2025</v>
+        <v>411</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E50" s="38">
-        <v>45868</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E51" s="38">
-        <v>45867</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>418</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C52" s="8">
+        <v>2025</v>
       </c>
       <c r="D52" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E52" s="38">
-        <v>45860</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E53" s="38">
-        <v>45846</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E54" s="38">
-        <v>45833</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>421</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C55" s="8">
+        <v>2025</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E55" s="38">
-        <v>45833</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="E56" s="38">
-        <v>45820</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="E57" s="38">
-        <v>45820</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E58" s="38">
-        <v>45818</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>425</v>
-      </c>
-      <c r="C59" s="8">
-        <v>2025</v>
+        <v>420</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="E59" s="38">
-        <v>45807</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="E60" s="38">
-        <v>45793</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E61" s="38">
-        <v>45784</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E62" s="38">
-        <v>45783</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E63" s="38">
-        <v>45783</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>430</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C64" s="8">
+        <v>2025</v>
       </c>
       <c r="D64" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E64" s="38">
-        <v>45771</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E65" s="38">
-        <v>45762</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E66" s="38">
-        <v>45750</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>433</v>
-      </c>
-      <c r="C67" s="8">
-        <v>2025</v>
+        <v>428</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E67" s="38">
-        <v>45744</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>429</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E68" s="38">
-        <v>45743</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E69" s="38">
-        <v>45743</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E70" s="38">
-        <v>45735</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="E71" s="38">
-        <v>45726</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>437</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>112</v>
+        <v>433</v>
+      </c>
+      <c r="C72" s="8">
+        <v>2025</v>
       </c>
       <c r="D72" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E72" s="38">
-        <v>45719</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>438</v>
+        <v>110</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="E73" s="38">
-        <v>45700</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D74" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E74" s="38">
-        <v>45695</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D75" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="E75" s="38">
-        <v>45694</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="E76" s="38">
-        <v>45692</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="E77" s="38">
-        <v>45688</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="E78" s="38">
-        <v>45684</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D79" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E79" s="38">
-        <v>45678</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D80" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E80" s="38">
-        <v>45672</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E81" s="38">
-        <v>45672</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E82" s="38">
-        <v>45672</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E83" s="38">
-        <v>45662</v>
+        <v>45684</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E84" s="38">
-        <v>45660</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D85" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E85" s="38">
-        <v>45659</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>450</v>
-      </c>
-      <c r="C86" s="8">
-        <v>2024</v>
+        <v>446</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E86" s="38">
-        <v>45653</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>451</v>
-      </c>
-      <c r="C87" s="8">
-        <v>2024</v>
+        <v>446</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E87" s="38">
-        <v>45650</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="E88" s="38">
-        <v>45643</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>284</v>
+        <v>448</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="E89" s="38">
-        <v>45639</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E90" s="38">
-        <v>45610</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>454</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>114</v>
+        <v>450</v>
+      </c>
+      <c r="C91" s="8">
+        <v>2024</v>
       </c>
       <c r="D91" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="E91" s="38">
-        <v>45609</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C92" s="8">
         <v>2024</v>
       </c>
       <c r="D92" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="E92" s="38">
-        <v>45601</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E93" s="38">
-        <v>45597</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>457</v>
+        <v>284</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D94" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E94" s="38">
-        <v>45597</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E95" s="38">
-        <v>45593</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E96" s="38">
-        <v>45588</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>460</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C97" s="8">
+        <v>2024</v>
       </c>
       <c r="D97" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E97" s="38">
-        <v>45572</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E98" s="38">
-        <v>45562</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E99" s="38">
-        <v>45555</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>463</v>
-      </c>
-      <c r="C100" s="8">
-        <v>2024</v>
+        <v>458</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="E100" s="38">
-        <v>45547</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="E101" s="38">
-        <v>45538</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="E102" s="38">
-        <v>45534</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="E103" s="38">
-        <v>45533</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E104" s="38">
-        <v>45533</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C105" s="8">
         <v>2024</v>
       </c>
       <c r="D105" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="E105" s="38">
-        <v>45526</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>469</v>
-      </c>
-      <c r="C106" s="8">
-        <v>2024</v>
+        <v>464</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E106" s="38">
-        <v>45518</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="E107" s="38">
-        <v>45502</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D108" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E108" s="38">
-        <v>45498</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D109" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E109" s="38">
-        <v>45489</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>473</v>
-      </c>
-      <c r="C110" s="8" t="s">
-        <v>114</v>
+        <v>468</v>
+      </c>
+      <c r="C110" s="8">
+        <v>2024</v>
       </c>
       <c r="D110" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="E110" s="38">
-        <v>45469</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>474</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C111" s="8">
+        <v>2024</v>
       </c>
       <c r="D111" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="E111" s="38">
-        <v>45469</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>202</v>
+        <v>470</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E112" s="38">
-        <v>45455</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E113" s="38">
-        <v>45455</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="E114" s="38">
-        <v>45449</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>477</v>
-      </c>
-      <c r="C115" s="8">
-        <v>2024</v>
+        <v>473</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E115" s="38">
-        <v>45449</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E116" s="38">
-        <v>45446</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>479</v>
+        <v>202</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="E117" s="38">
-        <v>45441</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="E118" s="38">
-        <v>45440</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>215</v>
+        <v>162</v>
       </c>
       <c r="E119" s="38">
-        <v>45439</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>482</v>
-      </c>
-      <c r="C120" s="8" t="s">
-        <v>114</v>
+        <v>477</v>
+      </c>
+      <c r="C120" s="8">
+        <v>2024</v>
       </c>
       <c r="D120" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="E120" s="38">
-        <v>45422</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="E121" s="38">
-        <v>45415</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>285</v>
+        <v>479</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="E122" s="38">
-        <v>45411</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D123" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="E123" s="38">
-        <v>45391</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D124" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="E124" s="38">
-        <v>45391</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>105</v>
+        <v>217</v>
       </c>
       <c r="E125" s="38">
-        <v>45379</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="E126" s="38">
-        <v>45378</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>488</v>
+        <v>285</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="E127" s="38">
-        <v>45378</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="E128" s="38">
-        <v>45365</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="E129" s="38">
-        <v>45362</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D130" t="s">
-        <v>252</v>
+        <v>105</v>
       </c>
       <c r="E130" s="38">
-        <v>45362</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D131" t="s">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="E131" s="38">
-        <v>45358</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="E132" s="38">
-        <v>45358</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D133" t="s">
-        <v>260</v>
+        <v>246</v>
       </c>
       <c r="E133" s="38">
-        <v>45357</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="E134" s="38">
-        <v>45350</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D135" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="E135" s="38">
-        <v>45344</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D136" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="E136" s="38">
-        <v>45336</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D137" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="E137" s="38">
-        <v>45336</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D138" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E138" s="38">
-        <v>45336</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D139" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="E139" s="38">
-        <v>45334</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>222</v>
+        <v>499</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D140" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E140" s="38">
-        <v>45331</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D141" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="E141" s="38">
-        <v>45324</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>493</v>
-      </c>
-      <c r="C142" s="8">
-        <v>2024</v>
+        <v>497</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D142" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E142" s="38">
-        <v>45322</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>492</v>
-      </c>
-      <c r="C143" s="8">
-        <v>2024</v>
+        <v>496</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D143" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E143" s="38">
-        <v>45303</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D144" t="s">
+        <v>272</v>
+      </c>
+      <c r="E144" s="38">
+        <v>45334</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>141</v>
+      </c>
+      <c r="B145" t="s">
+        <v>222</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D145" t="s">
+        <v>273</v>
+      </c>
+      <c r="E145" s="38">
+        <v>45331</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>142</v>
+      </c>
+      <c r="B146" t="s">
+        <v>494</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D146" t="s">
+        <v>274</v>
+      </c>
+      <c r="E146" s="38">
+        <v>45324</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>143</v>
+      </c>
+      <c r="B147" t="s">
+        <v>493</v>
+      </c>
+      <c r="C147" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D147" t="s">
+        <v>275</v>
+      </c>
+      <c r="E147" s="38">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>144</v>
+      </c>
+      <c r="B148" t="s">
+        <v>492</v>
+      </c>
+      <c r="C148" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D148" t="s">
+        <v>278</v>
+      </c>
+      <c r="E148" s="38">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>145</v>
+      </c>
+      <c r="B149" t="s">
+        <v>491</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D149" t="s">
         <v>280</v>
       </c>
-      <c r="E144" s="38">
+      <c r="E149" s="38">
         <v>45294</v>
       </c>
     </row>
-    <row r="299" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B299" s="2"/>
-    </row>
-    <row r="300" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B300" s="2"/>
-    </row>
-    <row r="301" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B301" s="2"/>
-    </row>
-    <row r="302" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B302" s="2"/>
-    </row>
-    <row r="303" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B303" s="2"/>
+    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B304" s="2"/>
+    </row>
+    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B305" s="2"/>
     </row>
     <row r="306" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B306" s="2"/>
     </row>
+    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B307" s="2"/>
+    </row>
+    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B308" s="2"/>
+    </row>
     <row r="311" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B311" s="2"/>
     </row>
-    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B314" s="2"/>
-    </row>
     <row r="316" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B316" s="2"/>
     </row>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B317" s="2"/>
-    </row>
-    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B318" s="2"/>
-    </row>
-    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B320" s="2"/>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B319" s="2"/>
     </row>
     <row r="321" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B321" s="2"/>
@@ -5562,18 +5701,30 @@
     <row r="323" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B323" s="2"/>
     </row>
-    <row r="324" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B324" s="2"/>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B325" s="2"/>
     </row>
     <row r="326" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B326" s="2"/>
     </row>
-    <row r="377" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B377" s="2"/>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B327" s="2"/>
+    </row>
+    <row r="328" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B328" s="2"/>
+    </row>
+    <row r="329" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B329" s="2"/>
+    </row>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B331" s="2"/>
+    </row>
+    <row r="382" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B382" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:E142">
-    <sortCondition descending="1" sortBy="icon" ref="E19:E142"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:E147">
+    <sortCondition descending="1" sortBy="icon" ref="E24:E147"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5582,7 +5733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:E194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5622,16 +5773,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>855</v>
-      </c>
-      <c r="E5" s="40">
-        <v>46142</v>
+        <v>875</v>
+      </c>
+      <c r="E5" s="49">
+        <v>46158</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5639,16 +5790,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>856</v>
-      </c>
-      <c r="C6" s="35">
-        <v>2026</v>
+        <v>872</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>819</v>
       </c>
       <c r="D6" s="34" t="s">
-        <v>857</v>
-      </c>
-      <c r="E6" s="40">
-        <v>46142</v>
+        <v>873</v>
+      </c>
+      <c r="E6" s="49">
+        <v>46155</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5656,16 +5807,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>764</v>
+        <v>855</v>
       </c>
       <c r="E7" s="40">
-        <v>46139</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5673,67 +5824,67 @@
         <v>4</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>844</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>819</v>
+        <v>856</v>
+      </c>
+      <c r="C8" s="35">
+        <v>2026</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="E8" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>843</v>
+        <v>764</v>
       </c>
       <c r="E9" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>831</v>
-      </c>
-      <c r="C10" s="24" t="s">
+      <c r="B10" s="34" t="s">
+        <v>844</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>832</v>
-      </c>
-      <c r="E10" s="41">
-        <v>46122</v>
+      <c r="D10" s="34" t="s">
+        <v>845</v>
+      </c>
+      <c r="E10" s="40">
+        <v>46129</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="21" t="s">
-        <v>833</v>
-      </c>
-      <c r="C11" s="24" t="s">
+      <c r="B11" s="34" t="s">
+        <v>842</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>834</v>
-      </c>
-      <c r="E11" s="41">
-        <v>46122</v>
+      <c r="D11" s="34" t="s">
+        <v>843</v>
+      </c>
+      <c r="E11" s="40">
+        <v>46129</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5741,13 +5892,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>819</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>43</v>
+        <v>832</v>
       </c>
       <c r="E12" s="41">
         <v>46122</v>
@@ -5758,50 +5909,50 @@
         <v>9</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>819</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="E13" s="41">
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
-        <v>823</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>819</v>
       </c>
-      <c r="D14" t="s">
-        <v>824</v>
-      </c>
-      <c r="E14" s="38">
-        <v>46119</v>
+      <c r="D14" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="41">
+        <v>46122</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
-        <v>825</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="21" t="s">
+        <v>829</v>
+      </c>
+      <c r="C15" s="24" t="s">
         <v>819</v>
       </c>
-      <c r="D15" t="s">
-        <v>826</v>
-      </c>
-      <c r="E15" s="38">
-        <v>46118</v>
+      <c r="D15" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="E15" s="41">
+        <v>46121</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5809,16 +5960,16 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>819</v>
       </c>
       <c r="D16" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="E16" s="38">
-        <v>46114</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5826,16 +5977,16 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>816</v>
-      </c>
-      <c r="C17" s="8">
-        <v>2026</v>
+        <v>825</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>819</v>
       </c>
       <c r="D17" t="s">
-        <v>817</v>
+        <v>826</v>
       </c>
       <c r="E17" s="38">
-        <v>46113</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5843,32 +5994,32 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>818</v>
+        <v>827</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>819</v>
       </c>
       <c r="D18" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="E18" s="38">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" t="s">
         <v>816</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="8">
         <v>2026</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" t="s">
         <v>817</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="38">
         <v>46113</v>
       </c>
     </row>
@@ -5876,16 +6027,16 @@
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" t="s">
         <v>818</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" t="s">
         <v>820</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="38">
         <v>46113</v>
       </c>
     </row>
@@ -5894,16 +6045,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>799</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>4</v>
+        <v>816</v>
+      </c>
+      <c r="C21" s="24">
+        <v>2026</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
       <c r="E21" s="41">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5911,16 +6062,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>4</v>
+        <v>819</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>802</v>
+        <v>820</v>
       </c>
       <c r="E22" s="41">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5928,13 +6079,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>803</v>
-      </c>
-      <c r="C23" s="24">
-        <v>2026</v>
+        <v>799</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="E23" s="41">
         <v>46112</v>
@@ -5945,13 +6096,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>805</v>
-      </c>
-      <c r="C24" s="24">
-        <v>2026</v>
+        <v>801</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E24" s="41">
         <v>46112</v>
@@ -5962,13 +6113,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C25" s="24">
         <v>2026</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E25" s="41">
         <v>46112</v>
@@ -5979,13 +6130,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="C26" s="24">
         <v>2026</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="E26" s="41">
         <v>46112</v>
@@ -5996,16 +6147,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
       <c r="C27" s="24">
         <v>2026</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
       <c r="E27" s="41">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -6013,16 +6164,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>795</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>4</v>
+        <v>809</v>
+      </c>
+      <c r="C28" s="24">
+        <v>2026</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
       <c r="E28" s="41">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -6030,16 +6181,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>797</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>4</v>
+        <v>793</v>
+      </c>
+      <c r="C29" s="24">
+        <v>2026</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="E29" s="41">
-        <v>46104</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6047,16 +6198,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>781</v>
-      </c>
-      <c r="E30" s="42">
-        <v>46100</v>
+        <v>796</v>
+      </c>
+      <c r="E30" s="41">
+        <v>46108</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -6064,16 +6215,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>783</v>
-      </c>
-      <c r="E31" s="42">
-        <v>46099</v>
+        <v>798</v>
+      </c>
+      <c r="E31" s="41">
+        <v>46104</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -6081,16 +6232,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C32" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="E32" s="42">
-        <v>46097</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6098,16 +6249,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>762</v>
-      </c>
-      <c r="E33" s="42" t="s">
-        <v>756</v>
+        <v>783</v>
+      </c>
+      <c r="E33" s="42">
+        <v>46099</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6115,16 +6266,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>764</v>
-      </c>
-      <c r="E34" s="42" t="s">
-        <v>756</v>
+        <v>785</v>
+      </c>
+      <c r="E34" s="42">
+        <v>46097</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -6132,13 +6283,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E35" s="42" t="s">
         <v>756</v>
@@ -6149,50 +6300,50 @@
         <v>32</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E36" s="42" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>33</v>
       </c>
-      <c r="B37" t="s">
-        <v>588</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" t="s">
-        <v>384</v>
-      </c>
-      <c r="E37" s="38">
-        <v>46267</v>
+      <c r="B37" s="21" t="s">
+        <v>765</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>766</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>34</v>
       </c>
-      <c r="B38" t="s">
-        <v>589</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" t="s">
-        <v>376</v>
-      </c>
-      <c r="E38" s="38">
-        <v>46144</v>
+      <c r="B38" s="21" t="s">
+        <v>767</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>768</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6200,33 +6351,33 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="E39" s="38">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>591</v>
-      </c>
-      <c r="C40" s="8">
-        <v>2026</v>
+        <v>589</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E40" s="38">
-        <v>46051</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -6234,33 +6385,33 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>6</v>
+        <v>377</v>
       </c>
       <c r="E41" s="38">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C42" s="8">
         <v>2026</v>
       </c>
       <c r="D42" t="s">
-        <v>11</v>
+        <v>375</v>
       </c>
       <c r="E42" s="38">
-        <v>46025</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6268,16 +6419,16 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>594</v>
-      </c>
-      <c r="C43" s="8">
-        <v>2025</v>
+        <v>592</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E43" s="38">
-        <v>46022</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -6285,16 +6436,16 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>595</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>4</v>
+        <v>593</v>
+      </c>
+      <c r="C44" s="8">
+        <v>2026</v>
       </c>
       <c r="D44" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E44" s="38">
-        <v>46022</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -6302,16 +6453,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C45" s="8">
         <v>2025</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E45" s="38">
-        <v>46020</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -6319,16 +6470,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>597</v>
-      </c>
-      <c r="C46" s="8">
-        <v>2025</v>
+        <v>595</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E46" s="38">
-        <v>46009</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6336,16 +6487,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>598</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>4</v>
+        <v>596</v>
+      </c>
+      <c r="C47" s="8">
+        <v>2025</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E47" s="38">
-        <v>46000</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6353,16 +6504,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>599</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C48" s="8">
+        <v>2025</v>
       </c>
       <c r="D48" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E48" s="38">
-        <v>45978</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -6370,16 +6521,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E49" s="38">
-        <v>45965</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -6387,16 +6538,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>601</v>
-      </c>
-      <c r="C50" s="8">
-        <v>2025</v>
+        <v>599</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E50" s="38">
-        <v>45951</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -6404,16 +6555,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>602</v>
-      </c>
-      <c r="C51" s="8">
-        <v>2025</v>
+        <v>600</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E51" s="38">
-        <v>45945</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -6421,16 +6572,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>602</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>4</v>
+        <v>601</v>
+      </c>
+      <c r="C52" s="8">
+        <v>2025</v>
       </c>
       <c r="D52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E52" s="38">
-        <v>45945</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -6438,13 +6589,13 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>603</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>4</v>
+        <v>602</v>
+      </c>
+      <c r="C53" s="8">
+        <v>2025</v>
       </c>
       <c r="D53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E53" s="38">
         <v>45945</v>
@@ -6455,13 +6606,13 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E54" s="38">
         <v>45945</v>
@@ -6472,16 +6623,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E55" s="38">
-        <v>45944</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -6489,16 +6640,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E56" s="38">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -6506,16 +6657,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E57" s="38">
-        <v>45940</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -6523,16 +6674,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E58" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -6540,30 +6691,30 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E59" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>56</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>610</v>
+      <c r="B60" t="s">
+        <v>608</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E60" s="38">
         <v>45933</v>
@@ -6573,14 +6724,14 @@
       <c r="A61" s="1">
         <v>57</v>
       </c>
-      <c r="B61" s="8" t="s">
-        <v>611</v>
+      <c r="B61" t="s">
+        <v>609</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E61" s="38">
         <v>45933</v>
@@ -6591,16 +6742,16 @@
         <v>58</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E62" s="38">
-        <v>45930</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -6608,16 +6759,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E63" s="38">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -6625,16 +6776,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E64" s="38">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -6642,13 +6793,13 @@
         <v>61</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E65" s="38">
         <v>45924</v>
@@ -6659,16 +6810,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="C66" s="8">
-        <v>2025</v>
+        <v>614</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E66" s="38">
-        <v>45923</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -6676,16 +6827,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E67" s="38">
-        <v>45918</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -6693,16 +6844,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C68" s="8">
+        <v>2025</v>
       </c>
       <c r="D68" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E68" s="38">
-        <v>45908</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -6710,16 +6861,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E69" s="38">
-        <v>45897</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -6727,16 +6878,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E70" s="38">
-        <v>45891</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -6744,16 +6895,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E71" s="38">
-        <v>45891</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -6761,16 +6912,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E72" s="38">
-        <v>45888</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -6778,16 +6929,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E73" s="38">
-        <v>45880</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -6795,16 +6946,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>69</v>
+        <v>622</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E74" s="38">
-        <v>45855</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -6812,16 +6963,16 @@
         <v>71</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E75" s="38">
-        <v>45838</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -6829,16 +6980,16 @@
         <v>72</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>625</v>
+        <v>69</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E76" s="38">
-        <v>45838</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -6846,16 +6997,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E77" s="38">
-        <v>45835</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -6863,16 +7014,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>75</v>
+        <v>625</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E78" s="38">
-        <v>45833</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -6880,16 +7031,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E79" s="38">
-        <v>45831</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -6897,16 +7048,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>628</v>
+        <v>75</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E80" s="38">
-        <v>45825</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -6914,16 +7065,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="E81" s="38">
-        <v>45825</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -6931,13 +7082,13 @@
         <v>78</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E82" s="38">
         <v>45825</v>
@@ -6948,16 +7099,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E83" s="38">
-        <v>45808</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -6965,16 +7116,16 @@
         <v>80</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E84" s="38">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -6982,16 +7133,16 @@
         <v>81</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E85" s="38">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -6999,13 +7150,13 @@
         <v>82</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E86" s="38">
         <v>45803</v>
@@ -7016,13 +7167,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E87" s="38">
         <v>45803</v>
@@ -7033,13 +7184,13 @@
         <v>84</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D88" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E88" s="38">
         <v>45803</v>
@@ -7050,84 +7201,84 @@
         <v>85</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E89" s="38">
         <v>45803</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>86</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D90" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E90" s="38">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>87</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E91" s="38">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>88</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D92" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E92" s="38">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>89</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D93" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E93" s="38">
-        <v>45779</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -7135,16 +7286,16 @@
         <v>90</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E94" s="38">
-        <v>45770</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -7152,16 +7303,16 @@
         <v>91</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E95" s="38">
-        <v>45762</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -7169,16 +7320,16 @@
         <v>92</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="C96" s="8">
-        <v>2025</v>
+        <v>642</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D96" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E96" s="38">
-        <v>45749</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -7186,16 +7337,16 @@
         <v>93</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="C97" s="8">
-        <v>2025</v>
+        <v>643</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E97" s="38">
-        <v>45749</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7203,16 +7354,16 @@
         <v>94</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>4</v>
+        <v>644</v>
+      </c>
+      <c r="C98" s="8">
+        <v>2025</v>
       </c>
       <c r="D98" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E98" s="38">
-        <v>45748</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -7220,16 +7371,16 @@
         <v>95</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>114</v>
+        <v>645</v>
+      </c>
+      <c r="C99" s="8">
+        <v>2025</v>
       </c>
       <c r="D99" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E99" s="38">
-        <v>45736</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7237,16 +7388,16 @@
         <v>96</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E100" s="38">
-        <v>45734</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7254,16 +7405,16 @@
         <v>97</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E101" s="38">
-        <v>45726</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7271,16 +7422,16 @@
         <v>98</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="C102" s="8">
-        <v>2025</v>
+        <v>648</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E102" s="38">
-        <v>45726</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -7288,13 +7439,13 @@
         <v>99</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E103" s="38">
         <v>45726</v>
@@ -7305,16 +7456,16 @@
         <v>100</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C104" s="8">
+        <v>2025</v>
       </c>
       <c r="D104" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E104" s="38">
-        <v>45723</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7322,16 +7473,16 @@
         <v>101</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E105" s="38">
-        <v>45721</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7339,16 +7490,16 @@
         <v>102</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E106" s="38">
-        <v>45698</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7356,16 +7507,16 @@
         <v>103</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E107" s="38">
-        <v>45695</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7373,50 +7524,50 @@
         <v>104</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E108" s="38">
-        <v>45694</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>105</v>
       </c>
-      <c r="B109" t="s">
-        <v>587</v>
+      <c r="B109" s="8" t="s">
+        <v>655</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E109" s="38">
-        <v>45692</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>106</v>
       </c>
-      <c r="B110" t="s">
-        <v>586</v>
+      <c r="B110" s="8" t="s">
+        <v>656</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E110" s="38">
-        <v>45686</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7424,16 +7575,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E111" s="38">
-        <v>45681</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7441,16 +7592,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E112" s="38">
-        <v>45678</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -7458,16 +7609,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E113" s="38">
-        <v>45677</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7475,16 +7626,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E114" s="38">
-        <v>45677</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7492,16 +7643,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E115" s="38">
-        <v>45670</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7509,16 +7660,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E116" s="38">
-        <v>45661</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7526,16 +7677,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E117" s="38">
-        <v>45661</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7543,16 +7694,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E118" s="38">
-        <v>45659</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7560,16 +7711,16 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E119" s="38">
-        <v>45656</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -7577,16 +7728,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E120" s="38">
-        <v>45656</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7594,16 +7745,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>575</v>
-      </c>
-      <c r="C121" s="8">
-        <v>2024</v>
+        <v>577</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E121" s="38">
-        <v>45652</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7611,16 +7762,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="E122" s="38">
-        <v>45650</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -7628,16 +7779,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>573</v>
-      </c>
-      <c r="C123" s="8" t="s">
-        <v>114</v>
+        <v>575</v>
+      </c>
+      <c r="C123" s="8">
+        <v>2024</v>
       </c>
       <c r="D123" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E123" s="38">
-        <v>45631</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7645,16 +7796,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="E124" s="38">
-        <v>45625</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7662,16 +7813,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E125" s="38">
-        <v>45622</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7679,16 +7830,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D126" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E126" s="38">
-        <v>45593</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -7696,16 +7847,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D127" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E127" s="38">
-        <v>45588</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -7713,16 +7864,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E128" s="38">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -7730,16 +7881,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E129" s="38">
-        <v>45578</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7747,16 +7898,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E130" s="38">
-        <v>45566</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -7764,16 +7915,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E131" s="38">
-        <v>45566</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -7781,16 +7932,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E132" s="38">
-        <v>45565</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -7798,16 +7949,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E133" s="38">
-        <v>45563</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -7815,16 +7966,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E134" s="38">
-        <v>45553</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -7832,16 +7983,16 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="E135" s="38">
-        <v>45548</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -7849,16 +8000,16 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E136" s="38">
-        <v>45548</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -7866,16 +8017,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>181</v>
+        <v>119</v>
       </c>
       <c r="E137" s="38">
-        <v>45539</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -7883,16 +8034,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E138" s="38">
-        <v>45538</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -7900,16 +8051,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E139" s="38">
-        <v>45537</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -7917,16 +8068,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E140" s="38">
-        <v>45523</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -7934,16 +8085,16 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E141" s="38">
-        <v>45520</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -7951,16 +8102,16 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E142" s="38">
-        <v>45505</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -7968,16 +8119,16 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E143" s="38">
-        <v>45502</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -7985,16 +8136,16 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E144" s="38">
-        <v>45478</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -8002,16 +8153,16 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E145" s="38">
-        <v>45478</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -8019,16 +8170,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E146" s="38">
-        <v>45462</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -8036,16 +8187,16 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>204</v>
+        <v>551</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E147" s="38">
-        <v>45455</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -8053,16 +8204,16 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="E148" s="38">
-        <v>45454</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -8070,16 +8221,16 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>548</v>
+        <v>204</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E149" s="38">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -8087,16 +8238,16 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E150" s="38">
-        <v>45448</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -8104,16 +8255,16 @@
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E151" s="38">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -8121,16 +8272,16 @@
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E152" s="38">
-        <v>45432</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -8138,16 +8289,16 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D153" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E153" s="38">
-        <v>45420</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -8155,16 +8306,16 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E154" s="38">
-        <v>45418</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -8172,16 +8323,16 @@
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D155" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E155" s="38">
-        <v>45416</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8189,50 +8340,50 @@
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D156" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E156" s="38">
-        <v>45407</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>153</v>
       </c>
-      <c r="B157" s="5" t="s">
-        <v>540</v>
+      <c r="B157" t="s">
+        <v>542</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D157" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E157" s="38">
-        <v>45405</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>154</v>
       </c>
-      <c r="B158" s="5" t="s">
-        <v>535</v>
+      <c r="B158" t="s">
+        <v>541</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D158" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E158" s="38">
-        <v>45397</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -8240,16 +8391,16 @@
         <v>155</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E159" s="38">
-        <v>45397</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -8257,16 +8408,16 @@
         <v>156</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D160" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E160" s="38">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -8274,16 +8425,16 @@
         <v>157</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D161" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E161" s="38">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -8291,13 +8442,13 @@
         <v>158</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D162" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E162" s="38">
         <v>45387</v>
@@ -8308,16 +8459,16 @@
         <v>159</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D163" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E163" s="38">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8325,16 +8476,16 @@
         <v>160</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D164" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E164" s="38">
-        <v>45384</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -8342,50 +8493,50 @@
         <v>161</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C165" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D165" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E165" s="38">
-        <v>45378</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>162</v>
       </c>
-      <c r="B166" t="s">
-        <v>533</v>
+      <c r="B166" s="5" t="s">
+        <v>534</v>
       </c>
       <c r="C166" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D166" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E166" s="38">
-        <v>45373</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>163</v>
       </c>
-      <c r="B167" t="s">
-        <v>532</v>
+      <c r="B167" s="5" t="s">
+        <v>506</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D167" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E167" s="38">
-        <v>45373</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -8393,16 +8544,16 @@
         <v>164</v>
       </c>
       <c r="B168" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D168" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="E168" s="38">
-        <v>45369</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -8410,16 +8561,16 @@
         <v>165</v>
       </c>
       <c r="B169" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D169" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E169" s="38">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8427,16 +8578,16 @@
         <v>166</v>
       </c>
       <c r="B170" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D170" t="s">
-        <v>243</v>
+        <v>117</v>
       </c>
       <c r="E170" s="38">
-        <v>45367</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -8444,16 +8595,16 @@
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E171" s="38">
-        <v>45366</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8461,16 +8612,16 @@
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E172" s="38">
-        <v>45365</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -8478,16 +8629,16 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E173" s="38">
-        <v>45362</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -8495,16 +8646,16 @@
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E174" s="38">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -8512,13 +8663,13 @@
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D175" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E175" s="38">
         <v>45362</v>
@@ -8529,13 +8680,13 @@
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D176" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E176" s="38">
         <v>45362</v>
@@ -8546,16 +8697,16 @@
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D177" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E177" s="38">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8563,16 +8714,16 @@
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C178" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D178" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E178" s="38">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -8580,16 +8731,16 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D179" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E179" s="38">
-        <v>45358</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -8597,16 +8748,16 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D180" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E180" s="38">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -8614,16 +8765,16 @@
         <v>177</v>
       </c>
       <c r="B181" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D181" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E181" s="38">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -8631,16 +8782,16 @@
         <v>178</v>
       </c>
       <c r="B182" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D182" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="E182" s="38">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -8648,16 +8799,16 @@
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D183" t="s">
-        <v>219</v>
+        <v>259</v>
       </c>
       <c r="E183" s="38">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -8665,13 +8816,13 @@
         <v>180</v>
       </c>
       <c r="B184" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C184" s="8" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="E184" s="38">
         <v>45352</v>
@@ -8682,16 +8833,16 @@
         <v>181</v>
       </c>
       <c r="B185" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D185" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="E185" s="38">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -8699,16 +8850,16 @@
         <v>182</v>
       </c>
       <c r="B186" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E186" s="38">
-        <v>45345</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -8716,16 +8867,16 @@
         <v>183</v>
       </c>
       <c r="B187" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D187" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E187" s="38">
-        <v>45335</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -8733,16 +8884,16 @@
         <v>184</v>
       </c>
       <c r="B188" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D188" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E188" s="38">
-        <v>45334</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -8750,33 +8901,33 @@
         <v>185</v>
       </c>
       <c r="B189" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C189" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D189" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E189" s="38">
-        <v>45314</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>186</v>
       </c>
-      <c r="B190" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C190" s="8">
-        <v>2023</v>
+      <c r="B190" t="s">
+        <v>512</v>
+      </c>
+      <c r="C190" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D190" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="E190" s="38">
-        <v>45306</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -8784,32 +8935,66 @@
         <v>187</v>
       </c>
       <c r="B191" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D191" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E191" s="38">
-        <v>45294</v>
+        <v>45314</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>188</v>
       </c>
-      <c r="B192" t="s">
+      <c r="B192" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C192" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D192" t="s">
+        <v>277</v>
+      </c>
+      <c r="E192" s="38">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>189</v>
+      </c>
+      <c r="B193" t="s">
+        <v>509</v>
+      </c>
+      <c r="C193" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D193" t="s">
+        <v>279</v>
+      </c>
+      <c r="E193" s="38">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>190</v>
+      </c>
+      <c r="B194" t="s">
         <v>508</v>
       </c>
-      <c r="C192" s="8" t="s">
+      <c r="C194" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D192" t="s">
+      <c r="D194" t="s">
         <v>281</v>
       </c>
-      <c r="E192" s="38">
+      <c r="E194" s="38">
         <v>45292</v>
       </c>
     </row>
@@ -9389,7 +9574,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="20"/>
@@ -9435,20 +9620,20 @@
       <c r="E4" s="39"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="A5" s="19">
         <v>1</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>850</v>
+        <v>876</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>851</v>
-      </c>
-      <c r="E5" s="40">
-        <v>46133</v>
+        <v>877</v>
+      </c>
+      <c r="E5" s="49">
+        <v>46155</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9456,33 +9641,33 @@
         <v>2</v>
       </c>
       <c r="B6" s="34" t="s">
+        <v>850</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>814</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>851</v>
+      </c>
+      <c r="E6" s="40">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>3</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>848</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C7" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D6" s="34" t="s">
+      <c r="D7" s="34" t="s">
         <v>849</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E7" s="40">
         <v>46132</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>814</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>815</v>
-      </c>
-      <c r="E7" s="41">
-        <v>46113</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9490,106 +9675,106 @@
         <v>4</v>
       </c>
       <c r="B8" s="21" t="s">
+        <v>813</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>814</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>815</v>
+      </c>
+      <c r="E8" s="41">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>5</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>789</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C9" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D9" s="21" t="s">
         <v>790</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E9" s="41">
         <v>46101</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
-        <v>5</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>774</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="29" t="s">
-        <v>775</v>
-      </c>
-      <c r="E9" s="45">
-        <v>46087</v>
-      </c>
-      <c r="F9" s="30"/>
-      <c r="G9" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="20">
         <v>6</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C10" s="28" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E10" s="45">
         <v>46087</v>
       </c>
       <c r="F10" s="30"/>
+      <c r="G10" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20">
+      <c r="A11" s="19">
         <v>7</v>
       </c>
-      <c r="B11" t="s">
-        <v>773</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>772</v>
-      </c>
-      <c r="E11" s="38">
-        <v>46084</v>
-      </c>
-      <c r="F11" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="27" t="s">
+        <v>776</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>777</v>
+      </c>
+      <c r="E11" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F11" s="30"/>
+    </row>
+    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="20">
         <v>8</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" t="s">
+        <v>773</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" t="s">
+        <v>772</v>
+      </c>
+      <c r="E12" s="38">
+        <v>46084</v>
+      </c>
+      <c r="F12" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>9</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>744</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>745</v>
-      </c>
-      <c r="E12" s="41">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
-        <v>9</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>746</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E13" s="41">
         <v>46073</v>
@@ -9600,30 +9785,30 @@
         <v>10</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E14" s="41">
         <v>46073</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+      <c r="A15" s="19">
         <v>11</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E15" s="41">
         <v>46073</v>
@@ -9634,33 +9819,33 @@
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E16" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+    <row r="17" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="19">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
-        <v>681</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="21" t="s">
+        <v>752</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D17" t="s">
-        <v>385</v>
-      </c>
-      <c r="E17" s="38">
-        <v>46267</v>
+      <c r="D17" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="E17" s="41">
+        <v>46073</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -9668,70 +9853,67 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E18" s="38">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="19">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="s">
-        <v>683</v>
+      <c r="B19" t="s">
+        <v>682</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="E19" s="46">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>380</v>
+      </c>
+      <c r="E19" s="38">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20">
         <v>16</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E20" s="46">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="19">
+        <v>17</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>684</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E20" s="47">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="20">
-        <v>17</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>685</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E21" s="47">
         <v>46024</v>
-      </c>
-      <c r="H21" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9739,33 +9921,36 @@
         <v>18</v>
       </c>
       <c r="B22" s="17" t="s">
+        <v>685</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="E22" s="47">
+        <v>46024</v>
+      </c>
+      <c r="H22" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="19">
+        <v>19</v>
+      </c>
+      <c r="B23" s="17" t="s">
         <v>686</v>
       </c>
-      <c r="C22" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="16" t="s">
+      <c r="C23" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E23" s="47">
         <v>46022</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="20">
-        <v>19</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>687</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="E23" s="47">
-        <v>45986</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9773,33 +9958,33 @@
         <v>20</v>
       </c>
       <c r="B24" s="17" t="s">
+        <v>687</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="E24" s="47">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="19">
+        <v>21</v>
+      </c>
+      <c r="B25" s="17" t="s">
         <v>688</v>
       </c>
-      <c r="C24" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="17" t="s">
+      <c r="C25" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="E24" s="47">
+      <c r="E25" s="47">
         <v>45961</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="20">
-        <v>21</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>689</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="E25" s="47">
-        <v>45959</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9807,33 +9992,33 @@
         <v>22</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>321</v>
+      <c r="D26" s="17" t="s">
+        <v>320</v>
       </c>
       <c r="E26" s="47">
         <v>45959</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="20">
+      <c r="A27" s="19">
         <v>23</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E27" s="47">
-        <v>45957</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9841,33 +10026,33 @@
         <v>24</v>
       </c>
       <c r="B28" s="17" t="s">
+        <v>691</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="E28" s="47">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="19">
+        <v>25</v>
+      </c>
+      <c r="B29" s="17" t="s">
         <v>692</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="17" t="s">
+      <c r="C29" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="E28" s="47">
+      <c r="E29" s="47">
         <v>45930</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="20">
-        <v>25</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>693</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="E29" s="47">
-        <v>45924</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9875,33 +10060,33 @@
         <v>26</v>
       </c>
       <c r="B30" s="17" t="s">
+        <v>693</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="E30" s="47">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="19">
+        <v>27</v>
+      </c>
+      <c r="B31" s="17" t="s">
         <v>743</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C31" s="16">
         <v>2025</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D31" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="E30" s="47">
+      <c r="E31" s="47">
         <v>45896</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="20">
-        <v>27</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>742</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="E31" s="47">
-        <v>45866</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9909,33 +10094,33 @@
         <v>28</v>
       </c>
       <c r="B32" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="E32" s="47">
+        <v>45866</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="19">
+        <v>29</v>
+      </c>
+      <c r="B33" s="17" t="s">
         <v>741</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32" s="16" t="s">
+      <c r="C33" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="E32" s="47">
+      <c r="E33" s="47">
         <v>45860</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="20">
-        <v>29</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>740</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="E33" s="47">
-        <v>45852</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9943,33 +10128,33 @@
         <v>30</v>
       </c>
       <c r="B34" s="17" t="s">
+        <v>740</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E34" s="47">
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="19">
+        <v>31</v>
+      </c>
+      <c r="B35" s="17" t="s">
         <v>739</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C35" s="16">
         <v>2025</v>
       </c>
-      <c r="D34" s="17" t="s">
+      <c r="D35" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="E34" s="47">
+      <c r="E35" s="47">
         <v>45840</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="20">
-        <v>31</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="E35" s="47">
-        <v>45826</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9977,33 +10162,33 @@
         <v>32</v>
       </c>
       <c r="B36" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E36" s="47">
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="19">
+        <v>33</v>
+      </c>
+      <c r="B37" s="17" t="s">
         <v>737</v>
       </c>
-      <c r="C36" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D36" s="16" t="s">
+      <c r="C37" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="E36" s="47">
+      <c r="E37" s="47">
         <v>45821</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="20">
-        <v>33</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>736</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="E37" s="47">
-        <v>45776</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10011,33 +10196,33 @@
         <v>34</v>
       </c>
       <c r="B38" s="17" t="s">
+        <v>736</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="E38" s="47">
+        <v>45776</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="19">
+        <v>35</v>
+      </c>
+      <c r="B39" s="17" t="s">
         <v>735</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C39" s="16">
         <v>2025</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D39" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="E38" s="47">
+      <c r="E39" s="47">
         <v>45770</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="20">
-        <v>35</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>734</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="E39" s="47">
-        <v>45768</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10045,33 +10230,33 @@
         <v>36</v>
       </c>
       <c r="B40" s="17" t="s">
+        <v>734</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="E40" s="47">
+        <v>45768</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="19">
+        <v>37</v>
+      </c>
+      <c r="B41" s="17" t="s">
         <v>733</v>
       </c>
-      <c r="C40" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="16" t="s">
+      <c r="C41" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="E40" s="47">
+      <c r="E41" s="47">
         <v>45758</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="20">
-        <v>37</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>732</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D41" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="E41" s="47">
-        <v>45741</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10079,33 +10264,33 @@
         <v>38</v>
       </c>
       <c r="B42" s="17" t="s">
+        <v>732</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="E42" s="47">
+        <v>45741</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="19">
+        <v>39</v>
+      </c>
+      <c r="B43" s="17" t="s">
         <v>731</v>
       </c>
-      <c r="C42" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="16" t="s">
+      <c r="C43" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D43" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="E42" s="47">
+      <c r="E43" s="47">
         <v>45736</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="20">
-        <v>39</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>730</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="E43" s="47">
-        <v>45728</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10113,33 +10298,33 @@
         <v>40</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D44" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="E44" s="47">
+        <v>45728</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="19">
+        <v>41</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D45" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="E44" s="47">
+      <c r="E45" s="47">
         <v>45716</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="20">
-        <v>41</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>728</v>
-      </c>
-      <c r="C45" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="E45" s="47">
-        <v>45701</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10147,33 +10332,33 @@
         <v>42</v>
       </c>
       <c r="B46" s="17" t="s">
+        <v>728</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>340</v>
+      </c>
+      <c r="E46" s="47">
+        <v>45701</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="19">
+        <v>43</v>
+      </c>
+      <c r="B47" s="17" t="s">
         <v>727</v>
       </c>
-      <c r="C46" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D46" s="16" t="s">
+      <c r="C47" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="E46" s="47">
+      <c r="E47" s="47">
         <v>45700</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="20">
-        <v>43</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>726</v>
-      </c>
-      <c r="C47" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="E47" s="47">
-        <v>45699</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10181,33 +10366,33 @@
         <v>44</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E48" s="47">
         <v>45699</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="20">
+      <c r="A49" s="19">
         <v>45</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E49" s="47">
-        <v>45686</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10215,30 +10400,30 @@
         <v>46</v>
       </c>
       <c r="B50" s="17" t="s">
+        <v>724</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="E50" s="47">
+        <v>45686</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="19">
+        <v>47</v>
+      </c>
+      <c r="B51" s="17" t="s">
         <v>723</v>
       </c>
-      <c r="C50" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="16" t="s">
+      <c r="C51" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="16" t="s">
         <v>345</v>
-      </c>
-      <c r="E50" s="47">
-        <v>45656</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="20">
-        <v>47</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="C51" s="16">
-        <v>2024</v>
-      </c>
-      <c r="D51" s="17" t="s">
-        <v>346</v>
       </c>
       <c r="E51" s="47">
         <v>45656</v>
@@ -10249,33 +10434,33 @@
         <v>48</v>
       </c>
       <c r="B52" s="17" t="s">
+        <v>722</v>
+      </c>
+      <c r="C52" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D52" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="E52" s="47">
+        <v>45656</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="19">
+        <v>49</v>
+      </c>
+      <c r="B53" s="17" t="s">
         <v>721</v>
       </c>
-      <c r="C52" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="16" t="s">
+      <c r="C53" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="E52" s="47">
+      <c r="E53" s="47">
         <v>45646</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="20">
-        <v>49</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>720</v>
-      </c>
-      <c r="C53" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>348</v>
-      </c>
-      <c r="E53" s="47">
-        <v>45632</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10283,33 +10468,33 @@
         <v>50</v>
       </c>
       <c r="B54" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="E54" s="47">
+        <v>45632</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="19">
+        <v>51</v>
+      </c>
+      <c r="B55" s="17" t="s">
         <v>719</v>
       </c>
-      <c r="C54" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="16" t="s">
+      <c r="C55" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="E54" s="47">
+      <c r="E55" s="47">
         <v>45610</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="20">
-        <v>51</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>718</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="E55" s="47">
-        <v>45582</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10317,33 +10502,33 @@
         <v>52</v>
       </c>
       <c r="B56" s="17" t="s">
+        <v>718</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="E56" s="47">
+        <v>45582</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="19">
+        <v>53</v>
+      </c>
+      <c r="B57" s="17" t="s">
         <v>717</v>
       </c>
-      <c r="C56" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="16" t="s">
+      <c r="C57" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D57" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="E56" s="47">
+      <c r="E57" s="47">
         <v>45572</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="20">
-        <v>53</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>716</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="E57" s="47">
-        <v>45569</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10351,33 +10536,33 @@
         <v>54</v>
       </c>
       <c r="B58" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="E58" s="47">
+        <v>45569</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="19">
+        <v>55</v>
+      </c>
+      <c r="B59" s="17" t="s">
         <v>715</v>
       </c>
-      <c r="C58" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D58" s="16" t="s">
+      <c r="C59" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D59" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="E58" s="47">
+      <c r="E59" s="47">
         <v>45565</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="20">
-        <v>55</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>714</v>
-      </c>
-      <c r="C59" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="E59" s="47">
-        <v>45552</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10385,33 +10570,33 @@
         <v>56</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E60" s="47">
-        <v>45535</v>
+        <v>45552</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="20">
+      <c r="A61" s="19">
         <v>57</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E61" s="47">
-        <v>45533</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10419,33 +10604,33 @@
         <v>58</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C62" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D62" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="E62" s="47">
+        <v>45533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="19">
+        <v>59</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>711</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D63" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="E62" s="47">
+      <c r="E63" s="47">
         <v>45526</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="20">
-        <v>59</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>710</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="E63" s="47">
-        <v>45520</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10453,33 +10638,33 @@
         <v>60</v>
       </c>
       <c r="B64" s="17" t="s">
+        <v>710</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="E64" s="47">
+        <v>45520</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="19">
+        <v>61</v>
+      </c>
+      <c r="B65" s="17" t="s">
         <v>709</v>
       </c>
-      <c r="C64" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" s="16" t="s">
+      <c r="C65" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D65" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="E64" s="47">
+      <c r="E65" s="47">
         <v>45518</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="20">
-        <v>61</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>708</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="E65" s="47">
-        <v>45506</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10487,33 +10672,33 @@
         <v>62</v>
       </c>
       <c r="B66" s="17" t="s">
+        <v>708</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="E66" s="47">
+        <v>45506</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="19">
+        <v>63</v>
+      </c>
+      <c r="B67" s="17" t="s">
         <v>707</v>
       </c>
-      <c r="C66" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D66" s="16" t="s">
+      <c r="C67" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D67" s="16" t="s">
         <v>361</v>
       </c>
-      <c r="E66" s="47">
+      <c r="E67" s="47">
         <v>45498</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="20">
-        <v>63</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>706</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="E67" s="47">
-        <v>45496</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10521,33 +10706,33 @@
         <v>64</v>
       </c>
       <c r="B68" s="17" t="s">
+        <v>706</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="E68" s="47">
+        <v>45496</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="19">
+        <v>65</v>
+      </c>
+      <c r="B69" s="17" t="s">
         <v>705</v>
       </c>
-      <c r="C68" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D68" s="16" t="s">
+      <c r="C69" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D69" s="16" t="s">
         <v>363</v>
       </c>
-      <c r="E68" s="47">
+      <c r="E69" s="47">
         <v>45483</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20">
-        <v>65</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>704</v>
-      </c>
-      <c r="C69" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="E69" s="47">
-        <v>45471</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10555,101 +10740,101 @@
         <v>66</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D70" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="E70" s="47">
+        <v>45471</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="19">
+        <v>67</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>703</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D71" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="E70" s="47">
+      <c r="E71" s="47">
         <v>45461</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="20">
-        <v>67</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>702</v>
-      </c>
-      <c r="C71" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="E71" s="47">
-        <v>45455</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="20">
         <v>68</v>
       </c>
-      <c r="B72" s="23" t="s">
+      <c r="B72" s="17" t="s">
+        <v>702</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="E72" s="47">
+        <v>45455</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="19">
+        <v>69</v>
+      </c>
+      <c r="B73" s="23" t="s">
         <v>701</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="E72" s="47">
-        <v>45440</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="20">
-        <v>69</v>
-      </c>
-      <c r="B73" s="23" t="s">
-        <v>700</v>
       </c>
       <c r="C73" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>366</v>
+        <v>214</v>
       </c>
       <c r="E73" s="47">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="20">
         <v>70</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="23" t="s">
+        <v>700</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E74" s="47">
+        <v>45422</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="19">
+        <v>71</v>
+      </c>
+      <c r="B75" s="17" t="s">
         <v>699</v>
       </c>
-      <c r="C74" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D74" s="16" t="s">
+      <c r="C75" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D75" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="E74" s="47">
+      <c r="E75" s="47">
         <v>45400</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20">
-        <v>71</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>698</v>
-      </c>
-      <c r="C75" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="E75" s="47">
-        <v>45384</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10657,33 +10842,33 @@
         <v>72</v>
       </c>
       <c r="B76" s="17" t="s">
+        <v>698</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="E76" s="47">
+        <v>45384</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="19">
+        <v>73</v>
+      </c>
+      <c r="B77" s="17" t="s">
         <v>697</v>
       </c>
-      <c r="C76" s="16" t="s">
+      <c r="C77" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="D76" s="16" t="s">
+      <c r="D77" s="16" t="s">
         <v>369</v>
       </c>
-      <c r="E76" s="47">
+      <c r="E77" s="47">
         <v>45371</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="20">
-        <v>73</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>696</v>
-      </c>
-      <c r="C77" s="16" t="s">
-        <v>236</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>370</v>
-      </c>
-      <c r="E77" s="47">
-        <v>45369</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10691,32 +10876,49 @@
         <v>74</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C78" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E78" s="47">
-        <v>45338</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="20">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="19">
         <v>75</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D79" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E79" s="47">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="20">
+        <v>76</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D80" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="E79" s="47">
+      <c r="E80" s="47">
         <v>45335</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AAA92D7-F95D-4CF3-A89A-2F4F92064D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE36B395-A610-413E-AC97-2C5315136F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="884">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2666,6 +2666,24 @@
   </si>
   <si>
     <t>Clarifications on Interest Subvention Support for Pre- and Post-Shipment Export Credit under Export Promotion Mission – Niryat Protsahan</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 05/2026-27</t>
+  </si>
+  <si>
+    <t>Launch of online module for issuance of Certificate of Origin (CoO) for Agarwood on Trade Connect Platform - regarding.</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 04/2026-27</t>
+  </si>
+  <si>
+    <t>Review and Re-allocation of allocated Export Quota of Pharma Grade Sugar by Special EXIM Facilitation Committee (SEFC) – regarding</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 12/2026-27</t>
+  </si>
+  <si>
+    <t>Allocation of 8606 MTRV of raw cane sugar to USA under TRQ scheme for US fiscal year 2026-regarding.</t>
   </si>
 </sst>
 </file>
@@ -2704,7 +2722,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2735,6 +2753,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2757,7 +2781,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2882,6 +2906,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3162,7 +3194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O382"/>
+  <dimension ref="A1:O383"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3203,17 +3235,17 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>863</v>
-      </c>
-      <c r="C5" s="35" t="s">
+      <c r="B5" s="54" t="s">
+        <v>882</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="36" t="s">
-        <v>864</v>
-      </c>
-      <c r="E5" s="49">
-        <v>46156</v>
+      <c r="D5" s="57" t="s">
+        <v>883</v>
+      </c>
+      <c r="E5" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3221,16 +3253,16 @@
         <v>2</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C6" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>28</v>
+        <v>864</v>
       </c>
       <c r="E6" s="49">
-        <v>46153</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3238,84 +3270,84 @@
         <v>3</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>867</v>
+        <v>28</v>
       </c>
       <c r="E7" s="49">
         <v>46153</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E8" s="49">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="50" t="s">
-        <v>870</v>
-      </c>
-      <c r="C9" s="51" t="s">
+      <c r="B9" s="34" t="s">
+        <v>868</v>
+      </c>
+      <c r="C9" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D9" s="52" t="s">
-        <v>871</v>
-      </c>
-      <c r="E9" s="53">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D9" s="36" t="s">
+        <v>869</v>
+      </c>
+      <c r="E9" s="49">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="34" t="s">
-        <v>859</v>
-      </c>
-      <c r="C10" s="35" t="s">
+      <c r="B10" s="50" t="s">
+        <v>870</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>819</v>
       </c>
-      <c r="D10" s="36" t="s">
-        <v>860</v>
-      </c>
-      <c r="E10" s="40">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D10" s="52" t="s">
+        <v>871</v>
+      </c>
+      <c r="E10" s="53">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E11" s="40">
-        <v>46142</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3323,33 +3355,33 @@
         <v>8</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>840</v>
-      </c>
-      <c r="C12" s="35">
-        <v>2026</v>
+        <v>861</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>819</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="E12" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>836</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>819</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>837</v>
-      </c>
-      <c r="E13" s="48">
-        <v>46122</v>
+      <c r="B13" s="34" t="s">
+        <v>840</v>
+      </c>
+      <c r="C13" s="35">
+        <v>2026</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>841</v>
+      </c>
+      <c r="E13" s="40">
+        <v>46129</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3357,50 +3389,50 @@
         <v>10</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C14" s="26" t="s">
         <v>819</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E14" s="48">
         <v>46122</v>
       </c>
     </row>
-    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
-        <v>822</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="32" t="s">
+        <v>838</v>
+      </c>
+      <c r="C15" s="26" t="s">
         <v>819</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="E15" s="38">
-        <v>46119</v>
+      <c r="D15" s="33" t="s">
+        <v>839</v>
+      </c>
+      <c r="E15" s="48">
+        <v>46122</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>811</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="E16" s="41">
-        <v>46111</v>
+      <c r="B16" t="s">
+        <v>822</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E16" s="38">
+        <v>46119</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3408,16 +3440,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>791</v>
-      </c>
-      <c r="C17" s="24">
-        <v>2025</v>
+        <v>811</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>8</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="E17" s="41">
-        <v>46105</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3425,16 +3457,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>786</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>4</v>
+        <v>791</v>
+      </c>
+      <c r="C18" s="24">
+        <v>2025</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E18" s="41">
-        <v>46101</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3442,71 +3474,68 @@
         <v>15</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="E19" s="41">
-        <v>46087</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="31" t="s">
-        <v>779</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="31" t="s">
+      <c r="B20" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="41">
         <v>46087</v>
       </c>
-      <c r="F20" s="30"/>
-    </row>
-    <row r="21" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>754</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>755</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>853</v>
-      </c>
+      <c r="B21" s="31" t="s">
+        <v>779</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>778</v>
+      </c>
+      <c r="E21" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F21" s="30"/>
     </row>
     <row r="22" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C22" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E22" s="42" t="s">
         <v>853</v>
-      </c>
-      <c r="O22" s="21" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
@@ -3514,33 +3543,36 @@
         <v>19</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E23" s="42" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O23" s="21" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" t="s">
-        <v>386</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E24" s="38">
-        <v>46328</v>
+      <c r="B24" s="21" t="s">
+        <v>759</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -3548,16 +3580,16 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>4</v>
+        <v>382</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E25" s="38">
-        <v>46144</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3565,16 +3597,16 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D26" t="s">
-        <v>5</v>
+      <c r="D26" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="E26" s="38">
-        <v>46045</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3582,16 +3614,16 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" s="38">
-        <v>46038</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -3599,16 +3631,16 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>390</v>
-      </c>
-      <c r="C28" s="8">
-        <v>2026</v>
+        <v>389</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E28" s="38">
-        <v>46031</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3616,13 +3648,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C29" s="8">
         <v>2026</v>
       </c>
       <c r="D29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="38">
         <v>46031</v>
@@ -3633,16 +3665,16 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C30" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E30" s="38">
-        <v>46022</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -3650,16 +3682,16 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>393</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>4</v>
+        <v>392</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2025</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E31" s="38">
-        <v>46010</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3667,16 +3699,16 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E32" s="38">
-        <v>46008</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3684,13 +3716,13 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E33" s="38">
         <v>46008</v>
@@ -3701,16 +3733,16 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>374</v>
+        <v>19</v>
       </c>
       <c r="E34" s="38">
-        <v>46002</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -3718,16 +3750,16 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>397</v>
-      </c>
-      <c r="C35" s="8">
-        <v>2025</v>
+        <v>396</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="E35" s="38">
-        <v>46001</v>
+        <v>46002</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3735,13 +3767,13 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C36" s="8">
         <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E36" s="38">
         <v>46001</v>
@@ -3752,16 +3784,16 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>399</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>4</v>
+        <v>398</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2025</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E37" s="38">
-        <v>45992</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -3769,13 +3801,13 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="38">
         <v>45992</v>
@@ -3786,16 +3818,16 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>401</v>
-      </c>
-      <c r="C39" s="8">
-        <v>2025</v>
+        <v>400</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="E39" s="38">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3803,16 +3835,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>402</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="C40" s="8">
+        <v>2025</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="E40" s="38">
-        <v>45959</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3820,16 +3852,16 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>403</v>
-      </c>
-      <c r="C41" s="8">
-        <v>2025</v>
+        <v>402</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E41" s="38">
-        <v>45958</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3837,13 +3869,13 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C42" s="8">
         <v>2025</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42" s="38">
         <v>45958</v>
@@ -3854,16 +3886,16 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>405</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>8</v>
+        <v>404</v>
+      </c>
+      <c r="C43" s="8">
+        <v>2025</v>
       </c>
       <c r="D43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E43" s="38">
-        <v>45953</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3871,16 +3903,16 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E44" s="38">
-        <v>45952</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3888,16 +3920,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E45" s="38">
-        <v>45945</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3905,16 +3937,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E46" s="38">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3922,13 +3954,13 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E47" s="38">
         <v>45940</v>
@@ -3939,16 +3971,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E48" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -3956,16 +3988,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E49" s="38">
-        <v>45931</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -3973,16 +4005,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E50" s="38">
-        <v>45909</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3990,16 +4022,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E51" s="38">
-        <v>45903</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -4007,16 +4039,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>413</v>
-      </c>
-      <c r="C52" s="8">
-        <v>2025</v>
+        <v>412</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E52" s="38">
-        <v>45895</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -4024,16 +4056,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>414</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C53" s="8">
+        <v>2025</v>
       </c>
       <c r="D53" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E53" s="38">
-        <v>45891</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -4041,16 +4073,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E54" s="38">
-        <v>45870</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -4058,16 +4090,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>416</v>
-      </c>
-      <c r="C55" s="8">
-        <v>2025</v>
+        <v>415</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55" s="38">
-        <v>45868</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -4075,16 +4107,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>417</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C56" s="8">
+        <v>2025</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E56" s="38">
-        <v>45867</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -4092,16 +4124,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E57" s="38">
-        <v>45860</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -4109,16 +4141,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E58" s="38">
-        <v>45846</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -4126,16 +4158,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E59" s="38">
-        <v>45833</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -4143,13 +4175,13 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E60" s="38">
         <v>45833</v>
@@ -4160,16 +4192,16 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E61" s="38">
-        <v>45820</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -4177,13 +4209,13 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E62" s="38">
         <v>45820</v>
@@ -4194,16 +4226,16 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E63" s="38">
-        <v>45818</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -4211,16 +4243,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>425</v>
-      </c>
-      <c r="C64" s="8">
-        <v>2025</v>
+        <v>424</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E64" s="38">
-        <v>45807</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -4228,16 +4260,16 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>426</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C65" s="8">
+        <v>2025</v>
       </c>
       <c r="D65" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E65" s="38">
-        <v>45793</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4245,16 +4277,16 @@
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E66" s="38">
-        <v>45784</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -4262,16 +4294,16 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E67" s="38">
-        <v>45783</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -4279,13 +4311,13 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E68" s="38">
         <v>45783</v>
@@ -4296,16 +4328,16 @@
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E69" s="38">
-        <v>45771</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -4313,16 +4345,16 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E70" s="38">
-        <v>45762</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -4330,16 +4362,16 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E71" s="38">
-        <v>45750</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4347,16 +4379,16 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>433</v>
-      </c>
-      <c r="C72" s="8">
-        <v>2025</v>
+        <v>432</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E72" s="38">
-        <v>45744</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -4364,16 +4396,16 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>110</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>4</v>
+        <v>433</v>
+      </c>
+      <c r="C73" s="8">
+        <v>2025</v>
       </c>
       <c r="D73" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E73" s="38">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4381,13 +4413,13 @@
         <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>434</v>
+        <v>110</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E74" s="38">
         <v>45743</v>
@@ -4398,16 +4430,16 @@
         <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D75" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E75" s="38">
-        <v>45735</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4415,16 +4447,16 @@
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D76" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E76" s="38">
-        <v>45726</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4432,16 +4464,16 @@
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D77" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E77" s="38">
-        <v>45719</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4481,16 @@
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E78" s="38">
-        <v>45700</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4466,16 +4498,16 @@
         <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D79" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E79" s="38">
-        <v>45695</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4483,16 +4515,16 @@
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D80" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E80" s="38">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4500,16 +4532,16 @@
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E81" s="38">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4517,16 +4549,16 @@
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E82" s="38">
-        <v>45688</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4534,16 +4566,16 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E83" s="38">
-        <v>45684</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4551,16 +4583,16 @@
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E84" s="38">
-        <v>45678</v>
+        <v>45684</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4568,16 +4600,16 @@
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D85" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E85" s="38">
-        <v>45672</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4585,13 +4617,13 @@
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E86" s="38">
         <v>45672</v>
@@ -4619,16 +4651,16 @@
         <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E88" s="38">
-        <v>45662</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4636,16 +4668,16 @@
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E89" s="38">
-        <v>45660</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4653,16 +4685,16 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E90" s="38">
-        <v>45659</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4670,16 +4702,16 @@
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>450</v>
-      </c>
-      <c r="C91" s="8">
-        <v>2024</v>
+        <v>449</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E91" s="38">
-        <v>45653</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4687,16 +4719,16 @@
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C92" s="8">
         <v>2024</v>
       </c>
       <c r="D92" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E92" s="38">
-        <v>45650</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4704,16 +4736,16 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>452</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>114</v>
+        <v>451</v>
+      </c>
+      <c r="C93" s="8">
+        <v>2024</v>
       </c>
       <c r="D93" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E93" s="38">
-        <v>45643</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4721,16 +4753,16 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>284</v>
+        <v>452</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E94" s="38">
-        <v>45639</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -4738,16 +4770,16 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>453</v>
+        <v>284</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D95" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E95" s="38">
-        <v>45610</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4755,16 +4787,16 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E96" s="38">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4772,16 +4804,16 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>455</v>
-      </c>
-      <c r="C97" s="8">
-        <v>2024</v>
+        <v>454</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E97" s="38">
-        <v>45601</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4789,16 +4821,16 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>456</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C98" s="8">
+        <v>2024</v>
       </c>
       <c r="D98" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E98" s="38">
-        <v>45597</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4806,13 +4838,13 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E99" s="38">
         <v>45597</v>
@@ -4823,16 +4855,16 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E100" s="38">
-        <v>45593</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4840,16 +4872,16 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E101" s="38">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4857,16 +4889,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E102" s="38">
-        <v>45572</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4874,16 +4906,16 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E103" s="38">
-        <v>45562</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4891,16 +4923,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E104" s="38">
-        <v>45555</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4908,16 +4940,16 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>463</v>
-      </c>
-      <c r="C105" s="8">
-        <v>2024</v>
+        <v>462</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E105" s="38">
-        <v>45547</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4925,16 +4957,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>464</v>
-      </c>
-      <c r="C106" s="8" t="s">
-        <v>114</v>
+        <v>463</v>
+      </c>
+      <c r="C106" s="8">
+        <v>2024</v>
       </c>
       <c r="D106" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E106" s="38">
-        <v>45538</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4942,16 +4974,16 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C107" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E107" s="38">
-        <v>45534</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4959,16 +4991,16 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E108" s="38">
-        <v>45533</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -4976,13 +5008,13 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D109" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E109" s="38">
         <v>45533</v>
@@ -4993,16 +5025,16 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>468</v>
-      </c>
-      <c r="C110" s="8">
-        <v>2024</v>
+        <v>467</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="D110" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E110" s="38">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -5010,16 +5042,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C111" s="8">
         <v>2024</v>
       </c>
       <c r="D111" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E111" s="38">
-        <v>45518</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -5027,16 +5059,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>470</v>
-      </c>
-      <c r="C112" s="8" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C112" s="8">
+        <v>2024</v>
       </c>
       <c r="D112" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E112" s="38">
-        <v>45502</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -5044,16 +5076,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E113" s="38">
-        <v>45498</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -5061,16 +5093,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E114" s="38">
-        <v>45489</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -5078,16 +5110,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E115" s="38">
-        <v>45469</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -5095,13 +5127,13 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E116" s="38">
         <v>45469</v>
@@ -5112,16 +5144,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>202</v>
+        <v>474</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E117" s="38">
-        <v>45455</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -5129,13 +5161,13 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>475</v>
+        <v>202</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E118" s="38">
         <v>45455</v>
@@ -5146,16 +5178,16 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="E119" s="38">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -5163,13 +5195,13 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>477</v>
-      </c>
-      <c r="C120" s="8">
-        <v>2024</v>
+        <v>476</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E120" s="38">
         <v>45449</v>
@@ -5180,16 +5212,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>478</v>
-      </c>
-      <c r="C121" s="8" t="s">
-        <v>114</v>
+        <v>477</v>
+      </c>
+      <c r="C121" s="8">
+        <v>2024</v>
       </c>
       <c r="D121" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E121" s="38">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -5197,16 +5229,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E122" s="38">
-        <v>45441</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -5214,16 +5246,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C123" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E123" s="38">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -5231,16 +5263,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D124" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E124" s="38">
-        <v>45439</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -5248,16 +5280,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D125" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E125" s="38">
-        <v>45422</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -5265,16 +5297,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E126" s="38">
-        <v>45415</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -5282,16 +5314,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>285</v>
+        <v>483</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E127" s="38">
-        <v>45411</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -5299,16 +5331,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>484</v>
+        <v>285</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E128" s="38">
-        <v>45391</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -5316,13 +5348,13 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E129" s="38">
         <v>45391</v>
@@ -5333,16 +5365,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="E130" s="38">
-        <v>45379</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -5350,16 +5382,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D131" t="s">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="E131" s="38">
-        <v>45378</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5367,13 +5399,13 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D132" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E132" s="38">
         <v>45378</v>
@@ -5384,16 +5416,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E133" s="38">
-        <v>45365</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -5401,16 +5433,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D134" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E134" s="38">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -5418,13 +5450,13 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D135" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E135" s="38">
         <v>45362</v>
@@ -5435,16 +5467,16 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D136" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E136" s="38">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -5452,13 +5484,13 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D137" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E137" s="38">
         <v>45358</v>
@@ -5469,16 +5501,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D138" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E138" s="38">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5486,16 +5518,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D139" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E139" s="38">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -5503,16 +5535,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D140" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E140" s="38">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -5520,16 +5552,16 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D141" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E141" s="38">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5537,13 +5569,13 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D142" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E142" s="38">
         <v>45336</v>
@@ -5554,13 +5586,13 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D143" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E143" s="38">
         <v>45336</v>
@@ -5571,16 +5603,16 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D144" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E144" s="38">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5588,16 +5620,16 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D145" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E145" s="38">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -5605,16 +5637,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D146" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E146" s="38">
-        <v>45324</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -5622,16 +5654,16 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>493</v>
-      </c>
-      <c r="C147" s="8">
-        <v>2024</v>
+        <v>494</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D147" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E147" s="38">
-        <v>45322</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -5639,16 +5671,16 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C148" s="8">
         <v>2024</v>
       </c>
       <c r="D148" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E148" s="38">
-        <v>45303</v>
+        <v>45322</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -5656,20 +5688,34 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
+        <v>492</v>
+      </c>
+      <c r="C149" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D149" t="s">
+        <v>278</v>
+      </c>
+      <c r="E149" s="38">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>146</v>
+      </c>
+      <c r="B150" t="s">
         <v>491</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C150" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D149" t="s">
+      <c r="D150" t="s">
         <v>280</v>
       </c>
-      <c r="E149" s="38">
+      <c r="E150" s="38">
         <v>45294</v>
       </c>
-    </row>
-    <row r="304" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B304" s="2"/>
     </row>
     <row r="305" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B305" s="2"/>
@@ -5683,17 +5729,17 @@
     <row r="308" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B308" s="2"/>
     </row>
-    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B311" s="2"/>
-    </row>
-    <row r="316" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B316" s="2"/>
-    </row>
-    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B319" s="2"/>
-    </row>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B321" s="2"/>
+    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B309" s="2"/>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B312" s="2"/>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B317" s="2"/>
+    </row>
+    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B320" s="2"/>
     </row>
     <row r="322" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B322" s="2"/>
@@ -5701,8 +5747,8 @@
     <row r="323" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B323" s="2"/>
     </row>
-    <row r="325" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B325" s="2"/>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B324" s="2"/>
     </row>
     <row r="326" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B326" s="2"/>
@@ -5716,15 +5762,18 @@
     <row r="329" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B329" s="2"/>
     </row>
-    <row r="331" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B331" s="2"/>
-    </row>
-    <row r="382" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B382" s="2"/>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B330" s="2"/>
+    </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B332" s="2"/>
+    </row>
+    <row r="383" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B383" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A24:E147">
-    <sortCondition descending="1" sortBy="icon" ref="E24:E147"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:E148">
+    <sortCondition descending="1" sortBy="icon" ref="E25:E148"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9574,7 +9623,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="20"/>
@@ -9623,34 +9672,34 @@
       <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>876</v>
-      </c>
-      <c r="C5" s="35" t="s">
+      <c r="B5" s="54" t="s">
+        <v>878</v>
+      </c>
+      <c r="C5" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="34" t="s">
-        <v>877</v>
-      </c>
-      <c r="E5" s="49">
-        <v>46155</v>
+      <c r="D5" s="54" t="s">
+        <v>879</v>
+      </c>
+      <c r="E5" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="A6" s="19">
         <v>2</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>850</v>
-      </c>
-      <c r="C6" s="35" t="s">
-        <v>814</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>851</v>
-      </c>
-      <c r="E6" s="40">
-        <v>46133</v>
+      <c r="B6" s="54" t="s">
+        <v>880</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>819</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>881</v>
+      </c>
+      <c r="E6" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9658,143 +9707,143 @@
         <v>3</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>848</v>
+        <v>876</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>849</v>
-      </c>
-      <c r="E7" s="40">
-        <v>46132</v>
+        <v>877</v>
+      </c>
+      <c r="E7" s="49">
+        <v>46155</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
-        <v>4</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="A8" s="19">
+        <v>4</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>850</v>
+      </c>
+      <c r="C8" s="35" t="s">
         <v>814</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>815</v>
-      </c>
-      <c r="E8" s="41">
-        <v>46113</v>
+      <c r="D8" s="34" t="s">
+        <v>851</v>
+      </c>
+      <c r="E8" s="40">
+        <v>46133</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="19">
         <v>5</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>789</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>790</v>
-      </c>
-      <c r="E9" s="41">
-        <v>46101</v>
+      <c r="B9" s="34" t="s">
+        <v>848</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="E9" s="40">
+        <v>46132</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+      <c r="A10" s="19">
         <v>6</v>
       </c>
-      <c r="B10" s="27" t="s">
-        <v>774</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>775</v>
-      </c>
-      <c r="E10" s="45">
-        <v>46087</v>
-      </c>
-      <c r="F10" s="30"/>
-      <c r="G10" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="21" t="s">
+        <v>813</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>814</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>815</v>
+      </c>
+      <c r="E10" s="41">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>7</v>
       </c>
-      <c r="B11" s="27" t="s">
-        <v>776</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="29" t="s">
-        <v>777</v>
-      </c>
-      <c r="E11" s="45">
+      <c r="B11" s="21" t="s">
+        <v>789</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="E11" s="41">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>8</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>774</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="29" t="s">
+        <v>775</v>
+      </c>
+      <c r="E12" s="45">
         <v>46087</v>
       </c>
-      <c r="F11" s="30"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
-        <v>773</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>772</v>
-      </c>
-      <c r="E12" s="38">
-        <v>46084</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="F12" s="30"/>
+      <c r="G12" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>9</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>744</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>745</v>
-      </c>
-      <c r="E13" s="41">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="B13" s="27" t="s">
+        <v>776</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>777</v>
+      </c>
+      <c r="E13" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F13" s="30"/>
+    </row>
+    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
         <v>10</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>746</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>747</v>
-      </c>
-      <c r="E14" s="41">
-        <v>46073</v>
+      <c r="B14" t="s">
+        <v>773</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s">
+        <v>772</v>
+      </c>
+      <c r="E14" s="38">
+        <v>46084</v>
+      </c>
+      <c r="F14" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9802,30 +9851,30 @@
         <v>11</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E15" s="41">
         <v>46073</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+      <c r="A16" s="19">
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="E16" s="41">
         <v>46073</v>
@@ -9836,104 +9885,101 @@
         <v>13</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="E17" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+    <row r="18" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>681</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="21" t="s">
+        <v>750</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D18" t="s">
-        <v>385</v>
-      </c>
-      <c r="E18" s="38">
-        <v>46267</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D18" s="21" t="s">
+        <v>751</v>
+      </c>
+      <c r="E18" s="41">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>15</v>
       </c>
-      <c r="B19" t="s">
-        <v>682</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="21" t="s">
+        <v>752</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D19" t="s">
-        <v>380</v>
-      </c>
-      <c r="E19" s="38">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="20">
+      <c r="D19" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="E19" s="41">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="19">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>683</v>
+      <c r="B20" t="s">
+        <v>681</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" s="46">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>385</v>
+      </c>
+      <c r="E20" s="38">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>17</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>684</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="B21" t="s">
+        <v>682</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E21" s="47">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="20">
+      <c r="D21" t="s">
+        <v>380</v>
+      </c>
+      <c r="E21" s="38">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="19">
         <v>18</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>685</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="E22" s="47">
-        <v>46024</v>
-      </c>
-      <c r="H22" t="s">
-        <v>381</v>
+      <c r="D22" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E22" s="46">
+        <v>46045</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9941,33 +9987,36 @@
         <v>19</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E23" s="47">
-        <v>46022</v>
+        <v>46024</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="20">
+      <c r="A24" s="19">
         <v>20</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E24" s="47">
-        <v>45986</v>
+        <v>46024</v>
+      </c>
+      <c r="H24" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -9975,33 +10024,33 @@
         <v>21</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>319</v>
+      <c r="D25" s="16" t="s">
+        <v>317</v>
       </c>
       <c r="E25" s="47">
-        <v>45961</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="20">
+      <c r="A26" s="19">
         <v>22</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>320</v>
+      <c r="D26" s="16" t="s">
+        <v>318</v>
       </c>
       <c r="E26" s="47">
-        <v>45959</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10009,33 +10058,33 @@
         <v>23</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>321</v>
+      <c r="D27" s="17" t="s">
+        <v>319</v>
       </c>
       <c r="E27" s="47">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="19">
+        <v>24</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>689</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="E28" s="47">
         <v>45959</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="20">
-        <v>24</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>691</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="E28" s="47">
-        <v>45957</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10043,33 +10092,33 @@
         <v>25</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>323</v>
+      <c r="D29" s="16" t="s">
+        <v>321</v>
       </c>
       <c r="E29" s="47">
-        <v>45930</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="20">
+      <c r="A30" s="19">
         <v>26</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E30" s="47">
-        <v>45924</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10077,33 +10126,33 @@
         <v>27</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>743</v>
-      </c>
-      <c r="C31" s="16">
-        <v>2025</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>325</v>
+        <v>692</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>323</v>
       </c>
       <c r="E31" s="47">
-        <v>45896</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="20">
+      <c r="A32" s="19">
         <v>28</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>742</v>
+        <v>693</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E32" s="47">
-        <v>45866</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10111,33 +10160,33 @@
         <v>29</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>741</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>4</v>
+        <v>743</v>
+      </c>
+      <c r="C33" s="16">
+        <v>2025</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E33" s="47">
-        <v>45860</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="20">
+      <c r="A34" s="19">
         <v>30</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E34" s="47">
-        <v>45852</v>
+        <v>45866</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10145,33 +10194,33 @@
         <v>31</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="C35" s="16">
-        <v>2025</v>
-      </c>
-      <c r="D35" s="17" t="s">
-        <v>329</v>
+        <v>741</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>327</v>
       </c>
       <c r="E35" s="47">
-        <v>45840</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="20">
+      <c r="A36" s="19">
         <v>32</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E36" s="47">
-        <v>45826</v>
+        <v>45852</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10179,33 +10228,33 @@
         <v>33</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>737</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>331</v>
+        <v>739</v>
+      </c>
+      <c r="C37" s="16">
+        <v>2025</v>
+      </c>
+      <c r="D37" s="17" t="s">
+        <v>329</v>
       </c>
       <c r="E37" s="47">
-        <v>45821</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="20">
+      <c r="A38" s="19">
         <v>34</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E38" s="47">
-        <v>45776</v>
+        <v>45826</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10213,33 +10262,33 @@
         <v>35</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>735</v>
-      </c>
-      <c r="C39" s="16">
-        <v>2025</v>
+        <v>737</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E39" s="47">
-        <v>45770</v>
+        <v>45821</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="20">
+      <c r="A40" s="19">
         <v>36</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E40" s="47">
-        <v>45768</v>
+        <v>45776</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10247,33 +10296,33 @@
         <v>37</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>733</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>4</v>
+        <v>735</v>
+      </c>
+      <c r="C41" s="16">
+        <v>2025</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E41" s="47">
-        <v>45758</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="20">
+      <c r="A42" s="19">
         <v>38</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="17" t="s">
-        <v>336</v>
+        <v>4</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>334</v>
       </c>
       <c r="E42" s="47">
-        <v>45741</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10281,33 +10330,33 @@
         <v>39</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E43" s="47">
-        <v>45736</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="20">
+      <c r="A44" s="19">
         <v>40</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>338</v>
+        <v>114</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>336</v>
       </c>
       <c r="E44" s="47">
-        <v>45728</v>
+        <v>45741</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10315,33 +10364,33 @@
         <v>41</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C45" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="E45" s="47">
+        <v>45736</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="19">
+        <v>42</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>730</v>
+      </c>
+      <c r="C46" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="E45" s="47">
-        <v>45716</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="20">
-        <v>42</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>728</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>114</v>
-      </c>
       <c r="D46" s="16" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E46" s="47">
-        <v>45701</v>
+        <v>45728</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10349,33 +10398,33 @@
         <v>43</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E47" s="47">
-        <v>45700</v>
+        <v>45716</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="20">
+      <c r="A48" s="19">
         <v>44</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E48" s="47">
-        <v>45699</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10383,33 +10432,33 @@
         <v>45</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E49" s="47">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="19">
+        <v>46</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>726</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="E50" s="47">
         <v>45699</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="20">
-        <v>46</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>724</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>344</v>
-      </c>
-      <c r="E50" s="47">
-        <v>45686</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10417,33 +10466,33 @@
         <v>47</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E51" s="47">
-        <v>45656</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20">
+      <c r="A52" s="19">
         <v>48</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="C52" s="16">
-        <v>2024</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>346</v>
+        <v>724</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>344</v>
       </c>
       <c r="E52" s="47">
-        <v>45656</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10451,33 +10500,33 @@
         <v>49</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E53" s="47">
-        <v>45646</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="20">
+      <c r="A54" s="19">
         <v>50</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>720</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>348</v>
+        <v>722</v>
+      </c>
+      <c r="C54" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>346</v>
       </c>
       <c r="E54" s="47">
-        <v>45632</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10485,33 +10534,33 @@
         <v>51</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E55" s="47">
-        <v>45610</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="20">
+      <c r="A56" s="19">
         <v>52</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E56" s="47">
-        <v>45582</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10519,33 +10568,33 @@
         <v>53</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E57" s="47">
-        <v>45572</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="20">
+      <c r="A58" s="19">
         <v>54</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E58" s="47">
-        <v>45569</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10553,33 +10602,33 @@
         <v>55</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E59" s="47">
-        <v>45565</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="20">
+      <c r="A60" s="19">
         <v>56</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E60" s="47">
-        <v>45552</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10587,33 +10636,33 @@
         <v>57</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E61" s="47">
-        <v>45535</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="20">
+      <c r="A62" s="19">
         <v>58</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C62" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E62" s="47">
-        <v>45533</v>
+        <v>45552</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10621,33 +10670,33 @@
         <v>59</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E63" s="47">
-        <v>45526</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="20">
+      <c r="A64" s="19">
         <v>60</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E64" s="47">
-        <v>45520</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10655,33 +10704,33 @@
         <v>61</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C65" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E65" s="47">
-        <v>45518</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="20">
+      <c r="A66" s="19">
         <v>62</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E66" s="47">
-        <v>45506</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10689,33 +10738,33 @@
         <v>63</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E67" s="47">
-        <v>45498</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="20">
+      <c r="A68" s="19">
         <v>64</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E68" s="47">
-        <v>45496</v>
+        <v>45506</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10723,33 +10772,33 @@
         <v>65</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E69" s="47">
-        <v>45483</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="20">
+      <c r="A70" s="19">
         <v>66</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E70" s="47">
-        <v>45471</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10757,101 +10806,101 @@
         <v>67</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C71" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="E71" s="47">
+        <v>45483</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="19">
+        <v>68</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="C72" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D71" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="E71" s="47">
-        <v>45461</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="20">
-        <v>68</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>702</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>114</v>
-      </c>
       <c r="D72" s="16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E72" s="47">
-        <v>45455</v>
+        <v>45471</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="19">
         <v>69</v>
       </c>
-      <c r="B73" s="23" t="s">
-        <v>701</v>
+      <c r="B73" s="17" t="s">
+        <v>703</v>
       </c>
       <c r="C73" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="E73" s="47">
-        <v>45440</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="20">
+      <c r="A74" s="19">
         <v>70</v>
       </c>
-      <c r="B74" s="23" t="s">
-        <v>700</v>
+      <c r="B74" s="17" t="s">
+        <v>702</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E74" s="47">
-        <v>45422</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
         <v>71</v>
       </c>
-      <c r="B75" s="17" t="s">
-        <v>699</v>
+      <c r="B75" s="23" t="s">
+        <v>701</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>367</v>
+        <v>214</v>
       </c>
       <c r="E75" s="47">
-        <v>45400</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="20">
+      <c r="A76" s="19">
         <v>72</v>
       </c>
-      <c r="B76" s="17" t="s">
-        <v>698</v>
+      <c r="B76" s="23" t="s">
+        <v>700</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E76" s="47">
-        <v>45384</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10859,33 +10908,33 @@
         <v>73</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E77" s="47">
-        <v>45371</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="20">
+      <c r="A78" s="19">
         <v>74</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>236</v>
+        <v>112</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E78" s="47">
-        <v>45369</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10893,32 +10942,66 @@
         <v>75</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E79" s="47">
-        <v>45338</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="20">
+        <v>45371</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="19">
         <v>76</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C80" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D80" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E80" s="47">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="19">
+        <v>77</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>695</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E81" s="47">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="19">
+        <v>78</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C82" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D82" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="E80" s="47">
+      <c r="E82" s="47">
         <v>45335</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE36B395-A610-413E-AC97-2C5315136F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CBD7E3-2B9B-4FD7-933E-C9557D93F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="887">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2684,6 +2684,15 @@
   </si>
   <si>
     <t>Allocation of 8606 MTRV of raw cane sugar to USA under TRQ scheme for US fiscal year 2026-regarding.</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 06/2026-27</t>
+  </si>
+  <si>
+    <t>Electronic filing and Issuance of Preferential Certificate of Origin (CoO) under India-Oman Comprehensive Economic Partnership Agreement (India-Oman CEPA) with effect from June 01, 2026 - regarding.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 13/2026-27</t>
   </si>
 </sst>
 </file>
@@ -2722,7 +2731,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2759,6 +2768,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2781,7 +2796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2912,6 +2927,14 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3194,7 +3217,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O383"/>
+  <dimension ref="A1:O384"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3235,34 +3258,34 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="54" t="s">
-        <v>882</v>
-      </c>
-      <c r="C5" s="55" t="s">
+      <c r="B5" s="58" t="s">
+        <v>886</v>
+      </c>
+      <c r="C5" s="59" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="57" t="s">
-        <v>883</v>
-      </c>
-      <c r="E5" s="56">
-        <v>46164</v>
+      <c r="D5" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="60">
+        <v>46171</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>863</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="54" t="s">
+        <v>882</v>
+      </c>
+      <c r="C6" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D6" s="36" t="s">
-        <v>864</v>
-      </c>
-      <c r="E6" s="49">
-        <v>46156</v>
+      <c r="D6" s="57" t="s">
+        <v>883</v>
+      </c>
+      <c r="E6" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3270,16 +3293,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>28</v>
+        <v>864</v>
       </c>
       <c r="E7" s="49">
-        <v>46153</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3287,84 +3310,84 @@
         <v>4</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>867</v>
+        <v>28</v>
       </c>
       <c r="E8" s="49">
         <v>46153</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E9" s="49">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="50" t="s">
-        <v>870</v>
-      </c>
-      <c r="C10" s="51" t="s">
+      <c r="B10" s="34" t="s">
+        <v>868</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D10" s="52" t="s">
-        <v>871</v>
-      </c>
-      <c r="E10" s="53">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D10" s="36" t="s">
+        <v>869</v>
+      </c>
+      <c r="E10" s="49">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>859</v>
-      </c>
-      <c r="C11" s="35" t="s">
+      <c r="B11" s="50" t="s">
+        <v>870</v>
+      </c>
+      <c r="C11" s="51" t="s">
         <v>819</v>
       </c>
-      <c r="D11" s="36" t="s">
-        <v>860</v>
-      </c>
-      <c r="E11" s="40">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D11" s="52" t="s">
+        <v>871</v>
+      </c>
+      <c r="E11" s="53">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E12" s="40">
-        <v>46142</v>
+        <v>46146</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3372,33 +3395,33 @@
         <v>9</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>840</v>
-      </c>
-      <c r="C13" s="35">
-        <v>2026</v>
+        <v>861</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>819</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="E13" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="32" t="s">
-        <v>836</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>819</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>837</v>
-      </c>
-      <c r="E14" s="48">
-        <v>46122</v>
+      <c r="B14" s="34" t="s">
+        <v>840</v>
+      </c>
+      <c r="C14" s="35">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>841</v>
+      </c>
+      <c r="E14" s="40">
+        <v>46129</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -3406,50 +3429,50 @@
         <v>11</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C15" s="26" t="s">
         <v>819</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E15" s="48">
         <v>46122</v>
       </c>
     </row>
-    <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
-        <v>822</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="32" t="s">
+        <v>838</v>
+      </c>
+      <c r="C16" s="26" t="s">
         <v>819</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="E16" s="38">
-        <v>46119</v>
+      <c r="D16" s="33" t="s">
+        <v>839</v>
+      </c>
+      <c r="E16" s="48">
+        <v>46122</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>811</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="E17" s="41">
-        <v>46111</v>
+      <c r="B17" t="s">
+        <v>822</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E17" s="38">
+        <v>46119</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3457,16 +3480,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>791</v>
-      </c>
-      <c r="C18" s="24">
-        <v>2025</v>
+        <v>811</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>8</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="E18" s="41">
-        <v>46105</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3474,16 +3497,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>786</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>4</v>
+        <v>791</v>
+      </c>
+      <c r="C19" s="24">
+        <v>2025</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E19" s="41">
-        <v>46101</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3491,71 +3514,68 @@
         <v>16</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="E20" s="41">
-        <v>46087</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>779</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="31" t="s">
+      <c r="B21" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="41">
         <v>46087</v>
       </c>
-      <c r="F21" s="30"/>
-    </row>
-    <row r="22" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>754</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>755</v>
-      </c>
-      <c r="E22" s="42" t="s">
-        <v>853</v>
-      </c>
+      <c r="B22" s="31" t="s">
+        <v>779</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="31" t="s">
+        <v>778</v>
+      </c>
+      <c r="E22" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F22" s="30"/>
     </row>
     <row r="23" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>19</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E23" s="42" t="s">
         <v>853</v>
-      </c>
-      <c r="O23" s="21" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="24" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
@@ -3563,33 +3583,36 @@
         <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E24" s="42" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O24" s="21" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" t="s">
-        <v>386</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E25" s="38">
-        <v>46328</v>
+      <c r="B25" s="21" t="s">
+        <v>759</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -3597,16 +3620,16 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>4</v>
+        <v>382</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E26" s="38">
-        <v>46144</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -3614,16 +3637,16 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D27" t="s">
-        <v>5</v>
+      <c r="D27" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="E27" s="38">
-        <v>46045</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -3631,16 +3654,16 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" s="38">
-        <v>46038</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3648,16 +3671,16 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>390</v>
-      </c>
-      <c r="C29" s="8">
-        <v>2026</v>
+        <v>389</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E29" s="38">
-        <v>46031</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3665,13 +3688,13 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C30" s="8">
         <v>2026</v>
       </c>
       <c r="D30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" s="38">
         <v>46031</v>
@@ -3682,16 +3705,16 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C31" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E31" s="38">
-        <v>46022</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3699,16 +3722,16 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>393</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>4</v>
+        <v>392</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2025</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E32" s="38">
-        <v>46010</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3716,16 +3739,16 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E33" s="38">
-        <v>46008</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -3733,13 +3756,13 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E34" s="38">
         <v>46008</v>
@@ -3750,16 +3773,16 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D35" t="s">
-        <v>374</v>
+        <v>19</v>
       </c>
       <c r="E35" s="38">
-        <v>46002</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3767,16 +3790,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>397</v>
-      </c>
-      <c r="C36" s="8">
-        <v>2025</v>
+        <v>396</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D36" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="E36" s="38">
-        <v>46001</v>
+        <v>46002</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3784,13 +3807,13 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C37" s="8">
         <v>2025</v>
       </c>
       <c r="D37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E37" s="38">
         <v>46001</v>
@@ -3801,16 +3824,16 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>399</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>4</v>
+        <v>398</v>
+      </c>
+      <c r="C38" s="8">
+        <v>2025</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E38" s="38">
-        <v>45992</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3818,13 +3841,13 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="38">
         <v>45992</v>
@@ -3835,16 +3858,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>401</v>
-      </c>
-      <c r="C40" s="8">
-        <v>2025</v>
+        <v>400</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="E40" s="38">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3852,16 +3875,16 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>402</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="C41" s="8">
+        <v>2025</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="E41" s="38">
-        <v>45959</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3869,16 +3892,16 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>403</v>
-      </c>
-      <c r="C42" s="8">
-        <v>2025</v>
+        <v>402</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E42" s="38">
-        <v>45958</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3886,13 +3909,13 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C43" s="8">
         <v>2025</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E43" s="38">
         <v>45958</v>
@@ -3903,16 +3926,16 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>405</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>8</v>
+        <v>404</v>
+      </c>
+      <c r="C44" s="8">
+        <v>2025</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E44" s="38">
-        <v>45953</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3920,16 +3943,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E45" s="38">
-        <v>45952</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3937,16 +3960,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E46" s="38">
-        <v>45945</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3954,16 +3977,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E47" s="38">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3971,13 +3994,13 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E48" s="38">
         <v>45940</v>
@@ -3988,16 +4011,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E49" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -4005,16 +4028,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E50" s="38">
-        <v>45931</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -4022,16 +4045,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E51" s="38">
-        <v>45909</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -4039,16 +4062,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E52" s="38">
-        <v>45903</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -4056,16 +4079,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>413</v>
-      </c>
-      <c r="C53" s="8">
-        <v>2025</v>
+        <v>412</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E53" s="38">
-        <v>45895</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -4073,16 +4096,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>414</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C54" s="8">
+        <v>2025</v>
       </c>
       <c r="D54" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E54" s="38">
-        <v>45891</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -4090,16 +4113,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E55" s="38">
-        <v>45870</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -4107,16 +4130,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>416</v>
-      </c>
-      <c r="C56" s="8">
-        <v>2025</v>
+        <v>415</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E56" s="38">
-        <v>45868</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -4124,16 +4147,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>417</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C57" s="8">
+        <v>2025</v>
       </c>
       <c r="D57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E57" s="38">
-        <v>45867</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -4141,16 +4164,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E58" s="38">
-        <v>45860</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -4158,16 +4181,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E59" s="38">
-        <v>45846</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -4175,16 +4198,16 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E60" s="38">
-        <v>45833</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -4192,13 +4215,13 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E61" s="38">
         <v>45833</v>
@@ -4209,16 +4232,16 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E62" s="38">
-        <v>45820</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -4226,13 +4249,13 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E63" s="38">
         <v>45820</v>
@@ -4243,16 +4266,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E64" s="38">
-        <v>45818</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -4260,16 +4283,16 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>425</v>
-      </c>
-      <c r="C65" s="8">
-        <v>2025</v>
+        <v>424</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E65" s="38">
-        <v>45807</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4277,16 +4300,16 @@
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>426</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C66" s="8">
+        <v>2025</v>
       </c>
       <c r="D66" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E66" s="38">
-        <v>45793</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -4294,16 +4317,16 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E67" s="38">
-        <v>45784</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -4311,16 +4334,16 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E68" s="38">
-        <v>45783</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -4328,13 +4351,13 @@
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E69" s="38">
         <v>45783</v>
@@ -4345,16 +4368,16 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E70" s="38">
-        <v>45771</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -4362,16 +4385,16 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E71" s="38">
-        <v>45762</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4379,16 +4402,16 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E72" s="38">
-        <v>45750</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -4396,16 +4419,16 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>433</v>
-      </c>
-      <c r="C73" s="8">
-        <v>2025</v>
+        <v>432</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E73" s="38">
-        <v>45744</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4413,16 +4436,16 @@
         <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>4</v>
+        <v>433</v>
+      </c>
+      <c r="C74" s="8">
+        <v>2025</v>
       </c>
       <c r="D74" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E74" s="38">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -4430,13 +4453,13 @@
         <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>434</v>
+        <v>110</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E75" s="38">
         <v>45743</v>
@@ -4447,16 +4470,16 @@
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E76" s="38">
-        <v>45735</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4464,16 +4487,16 @@
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D77" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E77" s="38">
-        <v>45726</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -4481,16 +4504,16 @@
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D78" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E78" s="38">
-        <v>45719</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4498,16 +4521,16 @@
         <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E79" s="38">
-        <v>45700</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4515,16 +4538,16 @@
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D80" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E80" s="38">
-        <v>45695</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4532,16 +4555,16 @@
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E81" s="38">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4549,16 +4572,16 @@
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E82" s="38">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4566,16 +4589,16 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D83" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E83" s="38">
-        <v>45688</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4583,16 +4606,16 @@
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E84" s="38">
-        <v>45684</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4600,16 +4623,16 @@
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D85" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E85" s="38">
-        <v>45678</v>
+        <v>45684</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4617,16 +4640,16 @@
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E86" s="38">
-        <v>45672</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4634,13 +4657,13 @@
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E87" s="38">
         <v>45672</v>
@@ -4668,16 +4691,16 @@
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E89" s="38">
-        <v>45662</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4685,16 +4708,16 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E90" s="38">
-        <v>45660</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4702,16 +4725,16 @@
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E91" s="38">
-        <v>45659</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4719,16 +4742,16 @@
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>450</v>
-      </c>
-      <c r="C92" s="8">
-        <v>2024</v>
+        <v>449</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E92" s="38">
-        <v>45653</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4736,16 +4759,16 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C93" s="8">
         <v>2024</v>
       </c>
       <c r="D93" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E93" s="38">
-        <v>45650</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4753,16 +4776,16 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>452</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>114</v>
+        <v>451</v>
+      </c>
+      <c r="C94" s="8">
+        <v>2024</v>
       </c>
       <c r="D94" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E94" s="38">
-        <v>45643</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -4770,16 +4793,16 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>284</v>
+        <v>452</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E95" s="38">
-        <v>45639</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4787,16 +4810,16 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>453</v>
+        <v>284</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D96" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E96" s="38">
-        <v>45610</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4804,16 +4827,16 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D97" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E97" s="38">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4821,16 +4844,16 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>455</v>
-      </c>
-      <c r="C98" s="8">
-        <v>2024</v>
+        <v>454</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E98" s="38">
-        <v>45601</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4838,16 +4861,16 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>456</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C99" s="8">
+        <v>2024</v>
       </c>
       <c r="D99" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E99" s="38">
-        <v>45597</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4855,13 +4878,13 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E100" s="38">
         <v>45597</v>
@@ -4872,16 +4895,16 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E101" s="38">
-        <v>45593</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4889,16 +4912,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E102" s="38">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4906,16 +4929,16 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C103" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D103" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E103" s="38">
-        <v>45572</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4923,16 +4946,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E104" s="38">
-        <v>45562</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4940,16 +4963,16 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E105" s="38">
-        <v>45555</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4957,16 +4980,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>463</v>
-      </c>
-      <c r="C106" s="8">
-        <v>2024</v>
+        <v>462</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E106" s="38">
-        <v>45547</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4974,16 +4997,16 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>464</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>114</v>
+        <v>463</v>
+      </c>
+      <c r="C107" s="8">
+        <v>2024</v>
       </c>
       <c r="D107" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E107" s="38">
-        <v>45538</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4991,16 +5014,16 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E108" s="38">
-        <v>45534</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -5008,16 +5031,16 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E109" s="38">
-        <v>45533</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -5025,13 +5048,13 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D110" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E110" s="38">
         <v>45533</v>
@@ -5042,16 +5065,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>468</v>
-      </c>
-      <c r="C111" s="8">
-        <v>2024</v>
+        <v>467</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="D111" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E111" s="38">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -5059,16 +5082,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C112" s="8">
         <v>2024</v>
       </c>
       <c r="D112" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E112" s="38">
-        <v>45518</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -5076,16 +5099,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>470</v>
-      </c>
-      <c r="C113" s="8" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C113" s="8">
+        <v>2024</v>
       </c>
       <c r="D113" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E113" s="38">
-        <v>45502</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -5093,16 +5116,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E114" s="38">
-        <v>45498</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -5110,16 +5133,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E115" s="38">
-        <v>45489</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -5127,16 +5150,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E116" s="38">
-        <v>45469</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -5144,13 +5167,13 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E117" s="38">
         <v>45469</v>
@@ -5161,16 +5184,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>202</v>
+        <v>474</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E118" s="38">
-        <v>45455</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -5178,13 +5201,13 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>475</v>
+        <v>202</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E119" s="38">
         <v>45455</v>
@@ -5195,16 +5218,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="E120" s="38">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -5212,13 +5235,13 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>477</v>
-      </c>
-      <c r="C121" s="8">
-        <v>2024</v>
+        <v>476</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E121" s="38">
         <v>45449</v>
@@ -5229,16 +5252,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>478</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>114</v>
+        <v>477</v>
+      </c>
+      <c r="C122" s="8">
+        <v>2024</v>
       </c>
       <c r="D122" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E122" s="38">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -5246,16 +5269,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E123" s="38">
-        <v>45441</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -5263,16 +5286,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C124" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E124" s="38">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -5280,16 +5303,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D125" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E125" s="38">
-        <v>45439</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -5297,16 +5320,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D126" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E126" s="38">
-        <v>45422</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -5314,16 +5337,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E127" s="38">
-        <v>45415</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -5331,16 +5354,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>285</v>
+        <v>483</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E128" s="38">
-        <v>45411</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -5348,16 +5371,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>484</v>
+        <v>285</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E129" s="38">
-        <v>45391</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -5365,13 +5388,13 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E130" s="38">
         <v>45391</v>
@@ -5382,16 +5405,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="E131" s="38">
-        <v>45379</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5399,16 +5422,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D132" t="s">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="E132" s="38">
-        <v>45378</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -5416,13 +5439,13 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D133" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E133" s="38">
         <v>45378</v>
@@ -5433,16 +5456,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D134" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E134" s="38">
-        <v>45365</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -5450,16 +5473,16 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D135" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E135" s="38">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -5467,13 +5490,13 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D136" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E136" s="38">
         <v>45362</v>
@@ -5484,16 +5507,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D137" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E137" s="38">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -5501,13 +5524,13 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D138" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E138" s="38">
         <v>45358</v>
@@ -5518,16 +5541,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D139" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E139" s="38">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -5535,16 +5558,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D140" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E140" s="38">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -5552,16 +5575,16 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D141" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E141" s="38">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5569,16 +5592,16 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D142" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E142" s="38">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -5586,13 +5609,13 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D143" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E143" s="38">
         <v>45336</v>
@@ -5603,13 +5626,13 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D144" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E144" s="38">
         <v>45336</v>
@@ -5620,16 +5643,16 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D145" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E145" s="38">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -5637,16 +5660,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D146" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E146" s="38">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -5654,16 +5677,16 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D147" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E147" s="38">
-        <v>45324</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -5671,16 +5694,16 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>493</v>
-      </c>
-      <c r="C148" s="8">
-        <v>2024</v>
+        <v>494</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D148" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E148" s="38">
-        <v>45322</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -5688,16 +5711,16 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C149" s="8">
         <v>2024</v>
       </c>
       <c r="D149" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E149" s="38">
-        <v>45303</v>
+        <v>45322</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -5705,20 +5728,34 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
+        <v>492</v>
+      </c>
+      <c r="C150" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D150" t="s">
+        <v>278</v>
+      </c>
+      <c r="E150" s="38">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>147</v>
+      </c>
+      <c r="B151" t="s">
         <v>491</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C151" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D150" t="s">
+      <c r="D151" t="s">
         <v>280</v>
       </c>
-      <c r="E150" s="38">
+      <c r="E151" s="38">
         <v>45294</v>
       </c>
-    </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B305" s="2"/>
     </row>
     <row r="306" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B306" s="2"/>
@@ -5732,17 +5769,17 @@
     <row r="309" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B309" s="2"/>
     </row>
-    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B312" s="2"/>
-    </row>
-    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B317" s="2"/>
-    </row>
-    <row r="320" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B320" s="2"/>
-    </row>
-    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B322" s="2"/>
+    <row r="310" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B310" s="2"/>
+    </row>
+    <row r="313" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B313" s="2"/>
+    </row>
+    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B318" s="2"/>
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B321" s="2"/>
     </row>
     <row r="323" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B323" s="2"/>
@@ -5750,8 +5787,8 @@
     <row r="324" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B324" s="2"/>
     </row>
-    <row r="326" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B326" s="2"/>
+    <row r="325" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B325" s="2"/>
     </row>
     <row r="327" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B327" s="2"/>
@@ -5765,15 +5802,18 @@
     <row r="330" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B330" s="2"/>
     </row>
-    <row r="332" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B332" s="2"/>
-    </row>
-    <row r="383" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B383" s="2"/>
+    <row r="331" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B331" s="2"/>
+    </row>
+    <row r="333" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B333" s="2"/>
+    </row>
+    <row r="384" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B384" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:E148">
-    <sortCondition descending="1" sortBy="icon" ref="E25:E148"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:E149">
+    <sortCondition descending="1" sortBy="icon" ref="E26:E149"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9623,7 +9663,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="20"/>
@@ -9672,17 +9712,17 @@
       <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B5" s="54" t="s">
-        <v>878</v>
-      </c>
-      <c r="C5" s="55" t="s">
+      <c r="B5" s="58" t="s">
+        <v>884</v>
+      </c>
+      <c r="C5" s="59" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="54" t="s">
-        <v>879</v>
-      </c>
-      <c r="E5" s="56">
-        <v>46164</v>
+      <c r="D5" s="58" t="s">
+        <v>885</v>
+      </c>
+      <c r="E5" s="60">
+        <v>46171</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9690,13 +9730,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C6" s="55" t="s">
         <v>819</v>
       </c>
       <c r="D6" s="54" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E6" s="56">
         <v>46164</v>
@@ -9706,17 +9746,17 @@
       <c r="A7" s="19">
         <v>3</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>876</v>
-      </c>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="54" t="s">
+        <v>880</v>
+      </c>
+      <c r="C7" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D7" s="34" t="s">
-        <v>877</v>
-      </c>
-      <c r="E7" s="49">
-        <v>46155</v>
+      <c r="D7" s="54" t="s">
+        <v>881</v>
+      </c>
+      <c r="E7" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,16 +9764,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>850</v>
+        <v>876</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>851</v>
-      </c>
-      <c r="E8" s="40">
-        <v>46133</v>
+        <v>877</v>
+      </c>
+      <c r="E8" s="49">
+        <v>46155</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9741,33 +9781,33 @@
         <v>5</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E9" s="40">
-        <v>46132</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="19">
         <v>6</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>814</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>815</v>
-      </c>
-      <c r="E10" s="41">
-        <v>46113</v>
+      <c r="B10" s="34" t="s">
+        <v>848</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="E10" s="40">
+        <v>46132</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9775,92 +9815,92 @@
         <v>7</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>789</v>
+        <v>813</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>8</v>
+        <v>814</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="E11" s="41">
-        <v>46101</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>774</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="29" t="s">
-        <v>775</v>
-      </c>
-      <c r="E12" s="45">
-        <v>46087</v>
-      </c>
-      <c r="F12" s="30"/>
-      <c r="G12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="21" t="s">
+        <v>789</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="E12" s="41">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>9</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>4</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E13" s="45">
         <v>46087</v>
       </c>
       <c r="F13" s="30"/>
+      <c r="G13" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>10</v>
       </c>
-      <c r="B14" t="s">
-        <v>773</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>772</v>
-      </c>
-      <c r="E14" s="38">
-        <v>46084</v>
-      </c>
-      <c r="F14" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="27" t="s">
+        <v>776</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>777</v>
+      </c>
+      <c r="E14" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>11</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>744</v>
-      </c>
-      <c r="C15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>745</v>
-      </c>
-      <c r="E15" s="41">
-        <v>46073</v>
+      <c r="B15" t="s">
+        <v>773</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" t="s">
+        <v>772</v>
+      </c>
+      <c r="E15" s="38">
+        <v>46084</v>
+      </c>
+      <c r="F15" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9868,13 +9908,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E16" s="41">
         <v>46073</v>
@@ -9885,13 +9925,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E17" s="41">
         <v>46073</v>
@@ -9902,13 +9942,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E18" s="41">
         <v>46073</v>
@@ -9919,33 +9959,33 @@
         <v>15</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E19" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>16</v>
       </c>
-      <c r="B20" t="s">
-        <v>681</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="B20" s="21" t="s">
+        <v>752</v>
+      </c>
+      <c r="C20" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D20" t="s">
-        <v>385</v>
-      </c>
-      <c r="E20" s="38">
-        <v>46267</v>
+      <c r="D20" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="E20" s="41">
+        <v>46073</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -9953,50 +9993,50 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E21" s="38">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>683</v>
+      <c r="B22" t="s">
+        <v>682</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="E22" s="46">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>380</v>
+      </c>
+      <c r="E22" s="38">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19">
         <v>19</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>684</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="B23" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E23" s="47">
-        <v>46024</v>
+      <c r="D23" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E23" s="46">
+        <v>46045</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10004,19 +10044,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E24" s="47">
         <v>46024</v>
-      </c>
-      <c r="H24" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10024,16 +10061,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E25" s="47">
-        <v>46022</v>
+        <v>46024</v>
+      </c>
+      <c r="H25" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10041,16 +10081,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C26" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E26" s="47">
-        <v>45986</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10058,16 +10098,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>319</v>
+      <c r="D27" s="16" t="s">
+        <v>318</v>
       </c>
       <c r="E27" s="47">
-        <v>45961</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10075,16 +10115,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E28" s="47">
-        <v>45959</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10092,13 +10132,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>321</v>
+      <c r="D29" s="17" t="s">
+        <v>320</v>
       </c>
       <c r="E29" s="47">
         <v>45959</v>
@@ -10109,16 +10149,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E30" s="47">
-        <v>45957</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10126,16 +10166,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>323</v>
+      <c r="D31" s="16" t="s">
+        <v>322</v>
       </c>
       <c r="E31" s="47">
-        <v>45930</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10143,16 +10183,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>324</v>
+      <c r="D32" s="17" t="s">
+        <v>323</v>
       </c>
       <c r="E32" s="47">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10160,16 +10200,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>743</v>
-      </c>
-      <c r="C33" s="16">
-        <v>2025</v>
+        <v>693</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E33" s="47">
-        <v>45896</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10177,16 +10217,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>742</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>4</v>
+        <v>743</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2025</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E34" s="47">
-        <v>45866</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10194,16 +10234,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E35" s="47">
-        <v>45860</v>
+        <v>45866</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10211,16 +10251,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E36" s="47">
-        <v>45852</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10228,16 +10268,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="C37" s="16">
-        <v>2025</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>329</v>
+        <v>740</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>328</v>
       </c>
       <c r="E37" s="47">
-        <v>45840</v>
+        <v>45852</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10245,16 +10285,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>330</v>
+        <v>739</v>
+      </c>
+      <c r="C38" s="16">
+        <v>2025</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>329</v>
       </c>
       <c r="E38" s="47">
-        <v>45826</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10262,16 +10302,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E39" s="47">
-        <v>45821</v>
+        <v>45826</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10279,16 +10319,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E40" s="47">
-        <v>45776</v>
+        <v>45821</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10296,16 +10336,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>735</v>
-      </c>
-      <c r="C41" s="16">
-        <v>2025</v>
+        <v>736</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E41" s="47">
-        <v>45770</v>
+        <v>45776</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10313,16 +10353,16 @@
         <v>38</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>734</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>4</v>
+        <v>735</v>
+      </c>
+      <c r="C42" s="16">
+        <v>2025</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E42" s="47">
-        <v>45768</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10330,16 +10370,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E43" s="47">
-        <v>45758</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10347,16 +10387,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>336</v>
+        <v>4</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>335</v>
       </c>
       <c r="E44" s="47">
-        <v>45741</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10364,16 +10404,16 @@
         <v>41</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C45" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D45" s="16" t="s">
-        <v>337</v>
+      <c r="D45" s="17" t="s">
+        <v>336</v>
       </c>
       <c r="E45" s="47">
-        <v>45736</v>
+        <v>45741</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10381,16 +10421,16 @@
         <v>42</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E46" s="47">
-        <v>45728</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10398,16 +10438,16 @@
         <v>43</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E47" s="47">
-        <v>45716</v>
+        <v>45728</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10415,16 +10455,16 @@
         <v>44</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E48" s="47">
-        <v>45701</v>
+        <v>45716</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10432,16 +10472,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C49" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E49" s="47">
-        <v>45700</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10449,16 +10489,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E50" s="47">
-        <v>45699</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10466,13 +10506,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E51" s="47">
         <v>45699</v>
@@ -10483,16 +10523,16 @@
         <v>48</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E52" s="47">
-        <v>45686</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10500,16 +10540,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E53" s="47">
-        <v>45656</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10517,13 +10557,13 @@
         <v>50</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="C54" s="16">
-        <v>2024</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>346</v>
+        <v>723</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>345</v>
       </c>
       <c r="E54" s="47">
         <v>45656</v>
@@ -10534,16 +10574,16 @@
         <v>51</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>721</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>347</v>
+        <v>722</v>
+      </c>
+      <c r="C55" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>346</v>
       </c>
       <c r="E55" s="47">
-        <v>45646</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10551,16 +10591,16 @@
         <v>52</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C56" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E56" s="47">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10568,16 +10608,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E57" s="47">
-        <v>45610</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10585,16 +10625,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E58" s="47">
-        <v>45582</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10602,16 +10642,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E59" s="47">
-        <v>45572</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10619,16 +10659,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E60" s="47">
-        <v>45569</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10636,16 +10676,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E61" s="47">
-        <v>45565</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10653,16 +10693,16 @@
         <v>58</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E62" s="47">
-        <v>45552</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10670,16 +10710,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C63" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E63" s="47">
-        <v>45535</v>
+        <v>45552</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10687,16 +10727,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E64" s="47">
-        <v>45533</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10704,16 +10744,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E65" s="47">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10721,16 +10761,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E66" s="47">
-        <v>45520</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10738,16 +10778,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E67" s="47">
-        <v>45518</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10755,16 +10795,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E68" s="47">
-        <v>45506</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10772,16 +10812,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E69" s="47">
-        <v>45498</v>
+        <v>45506</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10789,16 +10829,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E70" s="47">
-        <v>45496</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10806,16 +10846,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E71" s="47">
-        <v>45483</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10823,16 +10863,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E72" s="47">
-        <v>45471</v>
+        <v>45483</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10840,16 +10880,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C73" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>187</v>
+        <v>364</v>
       </c>
       <c r="E73" s="47">
-        <v>45461</v>
+        <v>45471</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10857,33 +10897,33 @@
         <v>70</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>365</v>
+        <v>187</v>
       </c>
       <c r="E74" s="47">
-        <v>45455</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
         <v>71</v>
       </c>
-      <c r="B75" s="23" t="s">
-        <v>701</v>
+      <c r="B75" s="17" t="s">
+        <v>702</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>214</v>
+        <v>365</v>
       </c>
       <c r="E75" s="47">
-        <v>45440</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10891,33 +10931,33 @@
         <v>72</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>366</v>
+        <v>214</v>
       </c>
       <c r="E76" s="47">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19">
         <v>73</v>
       </c>
-      <c r="B77" s="17" t="s">
-        <v>699</v>
+      <c r="B77" s="23" t="s">
+        <v>700</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E77" s="47">
-        <v>45400</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10925,16 +10965,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E78" s="47">
-        <v>45384</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10942,16 +10982,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>235</v>
+        <v>112</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E79" s="47">
-        <v>45371</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10959,16 +10999,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E80" s="47">
-        <v>45369</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10976,32 +11016,49 @@
         <v>77</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C81" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E81" s="47">
-        <v>45338</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
         <v>78</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C82" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D82" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E82" s="47">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="19">
+        <v>79</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C83" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D83" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="E82" s="47">
+      <c r="E83" s="47">
         <v>45335</v>
       </c>
     </row>

--- a/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CBD7E3-2B9B-4FD7-933E-C9557D93F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24841309-700C-40EB-AE00-56C837172B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="901">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2693,6 +2693,48 @@
   </si>
   <si>
     <t>PUBLIC NOTICE- 13/2026-27</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 20/2026-27</t>
+  </si>
+  <si>
+    <t>Applicability of Quality Control Orders (QCOs)/BIS requirements on imports by Special Economic Zone (SEZ) Units and Developers- Amendment in Para 2.03(A)(iii) of FTP, 2023-reg.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 19/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment in import policy condition of specific ITC HS Codes covered under Chapter 71 of ITC (HS), 2022, Schedule - I (Import Policy)-reg.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 18/2026-27</t>
+  </si>
+  <si>
+    <t>Nomination of Non-official Members of the Board of Trade- reg.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 17/2026-27</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 16/2026-27</t>
+  </si>
+  <si>
+    <t>Amendments in Para 2.88 of Handbook of Procedures- reg.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 15/2026-27</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 14/2026-27</t>
+  </si>
+  <si>
+    <t>Fixation of Six New Standard Input Output Norms (SIONs) at SION No. A-3702, A-3703, A-3704, A-3705, A-3706 &amp; A-3707 under "Chemical and Allied Product" (Product Code-'A')</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 07/2026-27</t>
+  </si>
+  <si>
+    <t>Request for comments on alignment of Schedule-II (Export Policy) of ITC (HS), 2022 consequent to amendments introduced under the Finance Act, 2026 – regarding.</t>
   </si>
 </sst>
 </file>
@@ -2731,7 +2773,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2774,6 +2816,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC99FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2796,7 +2844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2935,6 +2983,14 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3217,7 +3273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O384"/>
+  <dimension ref="A1:O388"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3258,136 +3314,136 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="58" t="s">
-        <v>886</v>
-      </c>
-      <c r="C5" s="59" t="s">
+      <c r="B5" s="62" t="s">
+        <v>893</v>
+      </c>
+      <c r="C5" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="60">
-        <v>46171</v>
+      <c r="D5" s="65" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="64">
+        <v>46177</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="54" t="s">
-        <v>882</v>
-      </c>
-      <c r="C6" s="55" t="s">
+      <c r="B6" s="62" t="s">
+        <v>894</v>
+      </c>
+      <c r="C6" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D6" s="57" t="s">
-        <v>883</v>
-      </c>
-      <c r="E6" s="56">
-        <v>46164</v>
+      <c r="D6" s="65" t="s">
+        <v>895</v>
+      </c>
+      <c r="E6" s="64">
+        <v>46175</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>863</v>
-      </c>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="62" t="s">
+        <v>896</v>
+      </c>
+      <c r="C7" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D7" s="36" t="s">
-        <v>864</v>
-      </c>
-      <c r="E7" s="49">
-        <v>46156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="65" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="64">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>865</v>
-      </c>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="62" t="s">
+        <v>897</v>
+      </c>
+      <c r="C8" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D8" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="49">
-        <v>46153</v>
+      <c r="D8" s="65" t="s">
+        <v>898</v>
+      </c>
+      <c r="E8" s="64">
+        <v>46174</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>866</v>
-      </c>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="58" t="s">
+        <v>886</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>819</v>
       </c>
-      <c r="D9" s="36" t="s">
-        <v>867</v>
-      </c>
-      <c r="E9" s="49">
-        <v>46153</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D9" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="60">
+        <v>46171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="34" t="s">
-        <v>868</v>
-      </c>
-      <c r="C10" s="35" t="s">
+      <c r="B10" s="54" t="s">
+        <v>882</v>
+      </c>
+      <c r="C10" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D10" s="36" t="s">
-        <v>869</v>
-      </c>
-      <c r="E10" s="49">
-        <v>46150</v>
+      <c r="D10" s="57" t="s">
+        <v>883</v>
+      </c>
+      <c r="E10" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="50" t="s">
-        <v>870</v>
-      </c>
-      <c r="C11" s="51" t="s">
+      <c r="B11" s="34" t="s">
+        <v>863</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D11" s="52" t="s">
-        <v>871</v>
-      </c>
-      <c r="E11" s="53">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D11" s="36" t="s">
+        <v>864</v>
+      </c>
+      <c r="E11" s="49">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="C12" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D12" s="36" t="s">
-        <v>860</v>
-      </c>
-      <c r="E12" s="40">
-        <v>46146</v>
+        <v>28</v>
+      </c>
+      <c r="E12" s="49">
+        <v>46153</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3395,292 +3451,292 @@
         <v>9</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>861</v>
+        <v>866</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D13" s="36" t="s">
-        <v>862</v>
-      </c>
-      <c r="E13" s="40">
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>867</v>
+      </c>
+      <c r="E13" s="49">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>840</v>
-      </c>
-      <c r="C14" s="35">
-        <v>2026</v>
+        <v>868</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>819</v>
       </c>
       <c r="D14" s="36" t="s">
-        <v>841</v>
-      </c>
-      <c r="E14" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>869</v>
+      </c>
+      <c r="E14" s="49">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>836</v>
-      </c>
-      <c r="C15" s="26" t="s">
+      <c r="B15" s="50" t="s">
+        <v>870</v>
+      </c>
+      <c r="C15" s="51" t="s">
         <v>819</v>
       </c>
-      <c r="D15" s="33" t="s">
-        <v>837</v>
-      </c>
-      <c r="E15" s="48">
-        <v>46122</v>
+      <c r="D15" s="52" t="s">
+        <v>871</v>
+      </c>
+      <c r="E15" s="53">
+        <v>46147</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="32" t="s">
-        <v>838</v>
-      </c>
-      <c r="C16" s="26" t="s">
+      <c r="B16" s="34" t="s">
+        <v>859</v>
+      </c>
+      <c r="C16" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D16" s="33" t="s">
-        <v>839</v>
-      </c>
-      <c r="E16" s="48">
-        <v>46122</v>
+      <c r="D16" s="36" t="s">
+        <v>860</v>
+      </c>
+      <c r="E16" s="40">
+        <v>46146</v>
       </c>
     </row>
     <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
-        <v>822</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="34" t="s">
+        <v>861</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="E17" s="38">
-        <v>46119</v>
+      <c r="D17" s="36" t="s">
+        <v>862</v>
+      </c>
+      <c r="E17" s="40">
+        <v>46142</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>811</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="E18" s="41">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="34" t="s">
+        <v>840</v>
+      </c>
+      <c r="C18" s="35">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>841</v>
+      </c>
+      <c r="E18" s="40">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="21" t="s">
-        <v>791</v>
-      </c>
-      <c r="C19" s="24">
-        <v>2025</v>
-      </c>
-      <c r="D19" s="25" t="s">
-        <v>792</v>
-      </c>
-      <c r="E19" s="41">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="32" t="s">
+        <v>836</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>819</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>837</v>
+      </c>
+      <c r="E19" s="48">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="21" t="s">
-        <v>786</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>787</v>
-      </c>
-      <c r="E20" s="41">
-        <v>46101</v>
+      <c r="B20" s="32" t="s">
+        <v>838</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>819</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>839</v>
+      </c>
+      <c r="E20" s="48">
+        <v>46122</v>
       </c>
     </row>
     <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>788</v>
-      </c>
-      <c r="C21" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>778</v>
-      </c>
-      <c r="E21" s="41">
-        <v>46087</v>
+      <c r="B21" t="s">
+        <v>822</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E21" s="38">
+        <v>46119</v>
       </c>
     </row>
     <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="31" t="s">
-        <v>779</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>778</v>
-      </c>
-      <c r="E22" s="45">
-        <v>46087</v>
-      </c>
-      <c r="F22" s="30"/>
-    </row>
-    <row r="23" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="21" t="s">
+        <v>811</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>812</v>
+      </c>
+      <c r="E22" s="41">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>19</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>754</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>4</v>
+        <v>791</v>
+      </c>
+      <c r="C23" s="24">
+        <v>2025</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>755</v>
-      </c>
-      <c r="E23" s="42" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+        <v>792</v>
+      </c>
+      <c r="E23" s="41">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>757</v>
+        <v>786</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>758</v>
-      </c>
-      <c r="E24" s="42" t="s">
-        <v>853</v>
-      </c>
-      <c r="O24" s="21" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+        <v>787</v>
+      </c>
+      <c r="E24" s="41">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>759</v>
+        <v>788</v>
       </c>
       <c r="C25" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>760</v>
-      </c>
-      <c r="E25" s="42" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+      <c r="E25" s="41">
+        <v>46087</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" t="s">
-        <v>386</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E26" s="38">
-        <v>46328</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B26" s="31" t="s">
+        <v>779</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="31" t="s">
+        <v>778</v>
+      </c>
+      <c r="E26" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F26" s="30"/>
+    </row>
+    <row r="27" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" t="s">
-        <v>387</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="E27" s="38">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B27" s="21" t="s">
+        <v>754</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" t="s">
-        <v>388</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>5</v>
-      </c>
-      <c r="E28" s="38">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B28" s="21" t="s">
+        <v>757</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>758</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>853</v>
+      </c>
+      <c r="O28" s="21" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" t="s">
-        <v>389</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="38">
-        <v>46038</v>
+      <c r="B29" s="21" t="s">
+        <v>759</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>853</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -3688,16 +3744,16 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>390</v>
-      </c>
-      <c r="C30" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
+        <v>386</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>383</v>
       </c>
       <c r="E30" s="38">
-        <v>46031</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -3705,16 +3761,16 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>391</v>
-      </c>
-      <c r="C31" s="8">
-        <v>2026</v>
-      </c>
-      <c r="D31" t="s">
-        <v>10</v>
+        <v>387</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="E31" s="38">
-        <v>46031</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -3722,16 +3778,16 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>392</v>
-      </c>
-      <c r="C32" s="8">
-        <v>2025</v>
+        <v>388</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E32" s="38">
-        <v>46022</v>
+        <v>46045</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -3739,16 +3795,16 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E33" s="38">
-        <v>46010</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -3756,16 +3812,16 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>394</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>4</v>
+        <v>390</v>
+      </c>
+      <c r="C34" s="8">
+        <v>2026</v>
       </c>
       <c r="D34" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E34" s="38">
-        <v>46008</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -3773,16 +3829,16 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>395</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>4</v>
+        <v>391</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2026</v>
       </c>
       <c r="D35" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E35" s="38">
-        <v>46008</v>
+        <v>46031</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -3790,16 +3846,16 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>396</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>4</v>
+        <v>392</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2025</v>
       </c>
       <c r="D36" t="s">
-        <v>374</v>
+        <v>14</v>
       </c>
       <c r="E36" s="38">
-        <v>46002</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -3807,16 +3863,16 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>397</v>
-      </c>
-      <c r="C37" s="8">
-        <v>2025</v>
+        <v>393</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E37" s="38">
-        <v>46001</v>
+        <v>46010</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -3824,16 +3880,16 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>398</v>
-      </c>
-      <c r="C38" s="8">
-        <v>2025</v>
+        <v>394</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E38" s="38">
-        <v>46001</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -3841,16 +3897,16 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E39" s="38">
-        <v>45992</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3858,16 +3914,16 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>374</v>
       </c>
       <c r="E40" s="38">
-        <v>45992</v>
+        <v>46002</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -3875,16 +3931,16 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C41" s="8">
         <v>2025</v>
       </c>
       <c r="D41" t="s">
-        <v>373</v>
+        <v>20</v>
       </c>
       <c r="E41" s="38">
-        <v>45981</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -3892,16 +3948,16 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>402</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>4</v>
+        <v>398</v>
+      </c>
+      <c r="C42" s="8">
+        <v>2025</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E42" s="38">
-        <v>45959</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -3909,16 +3965,16 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>403</v>
-      </c>
-      <c r="C43" s="8">
-        <v>2025</v>
+        <v>399</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E43" s="38">
-        <v>45958</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3926,16 +3982,16 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>404</v>
-      </c>
-      <c r="C44" s="8">
-        <v>2025</v>
+        <v>400</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E44" s="38">
-        <v>45958</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -3943,16 +3999,16 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>405</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>8</v>
+        <v>401</v>
+      </c>
+      <c r="C45" s="8">
+        <v>2025</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>373</v>
       </c>
       <c r="E45" s="38">
-        <v>45953</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -3960,16 +4016,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E46" s="38">
-        <v>45952</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -3977,16 +4033,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>407</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>4</v>
+        <v>403</v>
+      </c>
+      <c r="C47" s="8">
+        <v>2025</v>
       </c>
       <c r="D47" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E47" s="38">
-        <v>45945</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3994,16 +4050,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>4</v>
+        <v>404</v>
+      </c>
+      <c r="C48" s="8">
+        <v>2025</v>
       </c>
       <c r="D48" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E48" s="38">
-        <v>45940</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -4011,16 +4067,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E49" s="38">
-        <v>45940</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -4028,16 +4084,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C50" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E50" s="38">
-        <v>45933</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -4045,16 +4101,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E51" s="38">
-        <v>45931</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -4062,16 +4118,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>411</v>
+        <v>38</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E52" s="38">
-        <v>45909</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -4079,16 +4135,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E53" s="38">
-        <v>45903</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -4096,16 +4152,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>413</v>
-      </c>
-      <c r="C54" s="8">
-        <v>2025</v>
+        <v>409</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E54" s="38">
-        <v>45895</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -4113,16 +4169,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E55" s="38">
-        <v>45891</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -4130,16 +4186,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E56" s="38">
-        <v>45870</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -4147,16 +4203,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>416</v>
-      </c>
-      <c r="C57" s="8">
-        <v>2025</v>
+        <v>412</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E57" s="38">
-        <v>45868</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -4164,16 +4220,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>417</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C58" s="8">
+        <v>2025</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E58" s="38">
-        <v>45867</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -4181,16 +4237,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E59" s="38">
-        <v>45860</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -4198,16 +4254,16 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E60" s="38">
-        <v>45846</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -4215,16 +4271,16 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>420</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C61" s="8">
+        <v>2025</v>
       </c>
       <c r="D61" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E61" s="38">
-        <v>45833</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -4232,16 +4288,16 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E62" s="38">
-        <v>45833</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -4249,16 +4305,16 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E63" s="38">
-        <v>45820</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -4266,16 +4322,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E64" s="38">
-        <v>45820</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -4283,16 +4339,16 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E65" s="38">
-        <v>45818</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4300,16 +4356,16 @@
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>425</v>
-      </c>
-      <c r="C66" s="8">
-        <v>2025</v>
+        <v>421</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E66" s="38">
-        <v>45807</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -4317,16 +4373,16 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="E67" s="38">
-        <v>45793</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -4334,16 +4390,16 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E68" s="38">
-        <v>45784</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -4351,16 +4407,16 @@
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="E69" s="38">
-        <v>45783</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -4368,16 +4424,16 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>429</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C70" s="8">
+        <v>2025</v>
       </c>
       <c r="D70" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="E70" s="38">
-        <v>45783</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -4385,16 +4441,16 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="E71" s="38">
-        <v>45771</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4402,16 +4458,16 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E72" s="38">
-        <v>45762</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -4419,16 +4475,16 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E73" s="38">
-        <v>45750</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4436,16 +4492,16 @@
         <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>433</v>
-      </c>
-      <c r="C74" s="8">
-        <v>2025</v>
+        <v>429</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="E74" s="38">
-        <v>45744</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -4453,16 +4509,16 @@
         <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>110</v>
+        <v>430</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E75" s="38">
-        <v>45743</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4470,16 +4526,16 @@
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E76" s="38">
-        <v>45743</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4487,16 +4543,16 @@
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="E77" s="38">
-        <v>45735</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -4504,16 +4560,16 @@
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>436</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>112</v>
+        <v>433</v>
+      </c>
+      <c r="C78" s="8">
+        <v>2025</v>
       </c>
       <c r="D78" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E78" s="38">
-        <v>45726</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4521,16 +4577,16 @@
         <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>437</v>
+        <v>110</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E79" s="38">
-        <v>45719</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4538,16 +4594,16 @@
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D80" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E80" s="38">
-        <v>45700</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4555,16 +4611,16 @@
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D81" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E81" s="38">
-        <v>45695</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4572,16 +4628,16 @@
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D82" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E82" s="38">
-        <v>45694</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4589,16 +4645,16 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D83" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="E83" s="38">
-        <v>45692</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4606,16 +4662,16 @@
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D84" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E84" s="38">
-        <v>45688</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -4623,16 +4679,16 @@
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D85" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E85" s="38">
-        <v>45684</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4640,16 +4696,16 @@
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E86" s="38">
-        <v>45678</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4657,16 +4713,16 @@
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D87" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E87" s="38">
-        <v>45672</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4674,16 +4730,16 @@
         <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D88" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="E88" s="38">
-        <v>45672</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4691,16 +4747,16 @@
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E89" s="38">
-        <v>45672</v>
+        <v>45684</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4708,16 +4764,16 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E90" s="38">
-        <v>45662</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4725,16 +4781,16 @@
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E91" s="38">
-        <v>45660</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4742,16 +4798,16 @@
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E92" s="38">
-        <v>45659</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4759,16 +4815,16 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>450</v>
-      </c>
-      <c r="C93" s="8">
-        <v>2024</v>
+        <v>446</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E93" s="38">
-        <v>45653</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4776,16 +4832,16 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>451</v>
-      </c>
-      <c r="C94" s="8">
-        <v>2024</v>
+        <v>447</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="E94" s="38">
-        <v>45650</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -4793,16 +4849,16 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E95" s="38">
-        <v>45643</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4810,16 +4866,16 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>284</v>
+        <v>449</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E96" s="38">
-        <v>45639</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -4827,16 +4883,16 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>453</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>114</v>
+        <v>450</v>
+      </c>
+      <c r="C97" s="8">
+        <v>2024</v>
       </c>
       <c r="D97" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E97" s="38">
-        <v>45610</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -4844,16 +4900,16 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>454</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>114</v>
+        <v>451</v>
+      </c>
+      <c r="C98" s="8">
+        <v>2024</v>
       </c>
       <c r="D98" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E98" s="38">
-        <v>45609</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -4861,16 +4917,16 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>455</v>
-      </c>
-      <c r="C99" s="8">
-        <v>2024</v>
+        <v>452</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E99" s="38">
-        <v>45601</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4878,16 +4934,16 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>456</v>
+        <v>284</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D100" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E100" s="38">
-        <v>45597</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -4895,16 +4951,16 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E101" s="38">
-        <v>45597</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -4912,16 +4968,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C102" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D102" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E102" s="38">
-        <v>45593</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -4929,16 +4985,16 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>459</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C103" s="8">
+        <v>2024</v>
       </c>
       <c r="D103" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E103" s="38">
-        <v>45588</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4946,16 +5002,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C104" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E104" s="38">
-        <v>45572</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -4963,16 +5019,16 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E105" s="38">
-        <v>45562</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4980,16 +5036,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="E106" s="38">
-        <v>45555</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -4997,16 +5053,16 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>463</v>
-      </c>
-      <c r="C107" s="8">
-        <v>2024</v>
+        <v>459</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="E107" s="38">
-        <v>45547</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -5014,16 +5070,16 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E108" s="38">
-        <v>45538</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -5031,16 +5087,16 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="E109" s="38">
-        <v>45534</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -5048,16 +5104,16 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="E110" s="38">
-        <v>45533</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -5065,16 +5121,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>467</v>
-      </c>
-      <c r="C111" s="8" t="s">
-        <v>112</v>
+        <v>463</v>
+      </c>
+      <c r="C111" s="8">
+        <v>2024</v>
       </c>
       <c r="D111" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E111" s="38">
-        <v>45533</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -5082,16 +5138,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>468</v>
-      </c>
-      <c r="C112" s="8">
-        <v>2024</v>
+        <v>464</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E112" s="38">
-        <v>45526</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -5099,16 +5155,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>469</v>
-      </c>
-      <c r="C113" s="8">
-        <v>2024</v>
+        <v>465</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E113" s="38">
-        <v>45518</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -5116,16 +5172,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D114" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E114" s="38">
-        <v>45502</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -5133,16 +5189,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D115" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E115" s="38">
-        <v>45498</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -5150,16 +5206,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>472</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>114</v>
+        <v>468</v>
+      </c>
+      <c r="C116" s="8">
+        <v>2024</v>
       </c>
       <c r="D116" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E116" s="38">
-        <v>45489</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -5167,16 +5223,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>473</v>
-      </c>
-      <c r="C117" s="8" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C117" s="8">
+        <v>2024</v>
       </c>
       <c r="D117" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E117" s="38">
-        <v>45469</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -5184,16 +5240,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E118" s="38">
-        <v>45469</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -5201,16 +5257,16 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>202</v>
+        <v>471</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="E119" s="38">
-        <v>45455</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -5218,16 +5274,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E120" s="38">
-        <v>45455</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -5235,16 +5291,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="E121" s="38">
-        <v>45449</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -5252,16 +5308,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>477</v>
-      </c>
-      <c r="C122" s="8">
-        <v>2024</v>
+        <v>474</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E122" s="38">
-        <v>45449</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -5269,16 +5325,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>478</v>
+        <v>202</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="E123" s="38">
-        <v>45446</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -5286,16 +5342,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E124" s="38">
-        <v>45441</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -5303,16 +5359,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>214</v>
+        <v>162</v>
       </c>
       <c r="E125" s="38">
-        <v>45440</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -5320,16 +5376,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>481</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>112</v>
+        <v>477</v>
+      </c>
+      <c r="C126" s="8">
+        <v>2024</v>
       </c>
       <c r="D126" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="E126" s="38">
-        <v>45439</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -5337,16 +5393,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E127" s="38">
-        <v>45422</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -5354,16 +5410,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="E128" s="38">
-        <v>45415</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -5371,16 +5427,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>285</v>
+        <v>480</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D129" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E129" s="38">
-        <v>45411</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -5388,16 +5444,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D130" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E130" s="38">
-        <v>45391</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -5405,16 +5461,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E131" s="38">
-        <v>45391</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5422,16 +5478,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="E132" s="38">
-        <v>45379</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -5439,16 +5495,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>487</v>
+        <v>285</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="E133" s="38">
-        <v>45378</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -5456,16 +5512,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C134" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="E134" s="38">
-        <v>45378</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -5473,16 +5529,16 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="E135" s="38">
-        <v>45365</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -5490,16 +5546,16 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C136" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D136" t="s">
-        <v>251</v>
+        <v>105</v>
       </c>
       <c r="E136" s="38">
-        <v>45362</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -5507,16 +5563,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D137" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E137" s="38">
-        <v>45362</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -5524,16 +5580,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D138" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="E138" s="38">
-        <v>45358</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5541,16 +5597,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="C139" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D139" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="E139" s="38">
-        <v>45358</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -5558,16 +5614,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D140" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="E140" s="38">
-        <v>45357</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -5575,16 +5631,16 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D141" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="E141" s="38">
-        <v>45350</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5592,16 +5648,16 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D142" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E142" s="38">
-        <v>45344</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -5609,16 +5665,16 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D143" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="E143" s="38">
-        <v>45336</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5626,16 +5682,16 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D144" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E144" s="38">
-        <v>45336</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5643,16 +5699,16 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D145" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E145" s="38">
-        <v>45336</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -5660,16 +5716,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D146" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E146" s="38">
-        <v>45334</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -5677,16 +5733,16 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>222</v>
+        <v>498</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D147" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="E147" s="38">
-        <v>45331</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -5694,16 +5750,16 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D148" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="E148" s="38">
-        <v>45324</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -5711,16 +5767,16 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>493</v>
-      </c>
-      <c r="C149" s="8">
-        <v>2024</v>
+        <v>496</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D149" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="E149" s="38">
-        <v>45322</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -5728,16 +5784,16 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>492</v>
-      </c>
-      <c r="C150" s="8">
-        <v>2024</v>
+        <v>495</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D150" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="E150" s="38">
-        <v>45303</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -5745,47 +5801,106 @@
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>491</v>
+        <v>222</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D151" t="s">
+        <v>273</v>
+      </c>
+      <c r="E151" s="38">
+        <v>45331</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>148</v>
+      </c>
+      <c r="B152" t="s">
+        <v>494</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D152" t="s">
+        <v>274</v>
+      </c>
+      <c r="E152" s="38">
+        <v>45324</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>149</v>
+      </c>
+      <c r="B153" t="s">
+        <v>493</v>
+      </c>
+      <c r="C153" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D153" t="s">
+        <v>275</v>
+      </c>
+      <c r="E153" s="38">
+        <v>45322</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>150</v>
+      </c>
+      <c r="B154" t="s">
+        <v>492</v>
+      </c>
+      <c r="C154" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D154" t="s">
+        <v>278</v>
+      </c>
+      <c r="E154" s="38">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>151</v>
+      </c>
+      <c r="B155" t="s">
+        <v>491</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D155" t="s">
         <v>280</v>
       </c>
-      <c r="E151" s="38">
+      <c r="E155" s="38">
         <v>45294</v>
       </c>
-    </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B306" s="2"/>
-    </row>
-    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B307" s="2"/>
-    </row>
-    <row r="308" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B308" s="2"/>
-    </row>
-    <row r="309" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B309" s="2"/>
     </row>
     <row r="310" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B310" s="2"/>
     </row>
+    <row r="311" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B311" s="2"/>
+    </row>
+    <row r="312" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B312" s="2"/>
+    </row>
     <row r="313" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B313" s="2"/>
     </row>
-    <row r="318" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B318" s="2"/>
-    </row>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B321" s="2"/>
-    </row>
-    <row r="323" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B323" s="2"/>
-    </row>
-    <row r="324" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B324" s="2"/>
+    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B314" s="2"/>
+    </row>
+    <row r="317" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B317" s="2"/>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B322" s="2"/>
     </row>
     <row r="325" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B325" s="2"/>
@@ -5799,21 +5914,30 @@
     <row r="329" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B329" s="2"/>
     </row>
-    <row r="330" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B330" s="2"/>
-    </row>
     <row r="331" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B331" s="2"/>
     </row>
+    <row r="332" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B332" s="2"/>
+    </row>
     <row r="333" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B333" s="2"/>
     </row>
-    <row r="384" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B384" s="2"/>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B334" s="2"/>
+    </row>
+    <row r="335" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B335" s="2"/>
+    </row>
+    <row r="337" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B337" s="2"/>
+    </row>
+    <row r="388" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B388" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A26:E149">
-    <sortCondition descending="1" sortBy="icon" ref="E26:E149"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:E153">
+    <sortCondition descending="1" sortBy="icon" ref="E30:E153"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5822,7 +5946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5861,51 +5985,51 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>874</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>819</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>875</v>
-      </c>
-      <c r="E5" s="49">
-        <v>46158</v>
+      <c r="B5" s="62" t="s">
+        <v>887</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>814</v>
+      </c>
+      <c r="D5" s="62" t="s">
+        <v>888</v>
+      </c>
+      <c r="E5" s="64">
+        <v>46175</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="34" t="s">
-        <v>872</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="62" t="s">
+        <v>889</v>
+      </c>
+      <c r="C6" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D6" s="34" t="s">
-        <v>873</v>
-      </c>
-      <c r="E6" s="49">
-        <v>46155</v>
+      <c r="D6" s="62" t="s">
+        <v>890</v>
+      </c>
+      <c r="E6" s="64">
+        <v>46175</v>
       </c>
     </row>
     <row r="7" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>854</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>819</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>855</v>
-      </c>
-      <c r="E7" s="40">
-        <v>46142</v>
+      <c r="B7" s="62" t="s">
+        <v>891</v>
+      </c>
+      <c r="C7" s="63">
+        <v>2026</v>
+      </c>
+      <c r="D7" s="62" t="s">
+        <v>892</v>
+      </c>
+      <c r="E7" s="64">
+        <v>46175</v>
       </c>
     </row>
     <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5913,16 +6037,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>856</v>
-      </c>
-      <c r="C8" s="35">
-        <v>2026</v>
+        <v>874</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>819</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>857</v>
-      </c>
-      <c r="E8" s="40">
-        <v>46142</v>
+        <v>875</v>
+      </c>
+      <c r="E8" s="49">
+        <v>46158</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5930,16 +6054,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>764</v>
-      </c>
-      <c r="E9" s="40">
-        <v>46139</v>
+        <v>873</v>
+      </c>
+      <c r="E9" s="49">
+        <v>46155</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -5947,84 +6071,84 @@
         <v>6</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="E10" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>842</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>819</v>
+        <v>856</v>
+      </c>
+      <c r="C11" s="35">
+        <v>2026</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>843</v>
+        <v>857</v>
       </c>
       <c r="E11" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="21" t="s">
-        <v>831</v>
-      </c>
-      <c r="C12" s="24" t="s">
+      <c r="B12" s="34" t="s">
+        <v>858</v>
+      </c>
+      <c r="C12" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D12" s="21" t="s">
-        <v>832</v>
-      </c>
-      <c r="E12" s="41">
-        <v>46122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="E12" s="40">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="21" t="s">
-        <v>833</v>
-      </c>
-      <c r="C13" s="24" t="s">
+      <c r="B13" s="34" t="s">
+        <v>844</v>
+      </c>
+      <c r="C13" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D13" s="21" t="s">
-        <v>834</v>
-      </c>
-      <c r="E13" s="41">
-        <v>46122</v>
+      <c r="D13" s="34" t="s">
+        <v>845</v>
+      </c>
+      <c r="E13" s="40">
+        <v>46129</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="21" t="s">
-        <v>835</v>
-      </c>
-      <c r="C14" s="24" t="s">
+      <c r="B14" s="34" t="s">
+        <v>842</v>
+      </c>
+      <c r="C14" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="41">
-        <v>46122</v>
+      <c r="D14" s="34" t="s">
+        <v>843</v>
+      </c>
+      <c r="E14" s="40">
+        <v>46129</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -6032,67 +6156,67 @@
         <v>11</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>819</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="E15" s="41">
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
-        <v>823</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="21" t="s">
+        <v>833</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>819</v>
       </c>
-      <c r="D16" t="s">
-        <v>824</v>
-      </c>
-      <c r="E16" s="38">
-        <v>46119</v>
+      <c r="D16" s="21" t="s">
+        <v>834</v>
+      </c>
+      <c r="E16" s="41">
+        <v>46122</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
-        <v>825</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B17" s="21" t="s">
+        <v>835</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>819</v>
       </c>
-      <c r="D17" t="s">
-        <v>826</v>
-      </c>
-      <c r="E17" s="38">
-        <v>46118</v>
+      <c r="D17" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="41">
+        <v>46122</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>827</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="21" t="s">
+        <v>829</v>
+      </c>
+      <c r="C18" s="24" t="s">
         <v>819</v>
       </c>
-      <c r="D18" t="s">
-        <v>828</v>
-      </c>
-      <c r="E18" s="38">
-        <v>46114</v>
+      <c r="D18" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="E18" s="41">
+        <v>46121</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -6100,16 +6224,16 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>816</v>
-      </c>
-      <c r="C19" s="8">
-        <v>2026</v>
+        <v>823</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>819</v>
       </c>
       <c r="D19" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="E19" s="38">
-        <v>46113</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6117,49 +6241,49 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>819</v>
       </c>
       <c r="D20" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
       <c r="E20" s="38">
-        <v>46113</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="21" t="s">
-        <v>816</v>
-      </c>
-      <c r="C21" s="24">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>817</v>
-      </c>
-      <c r="E21" s="41">
-        <v>46113</v>
+      <c r="B21" t="s">
+        <v>827</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D21" t="s">
+        <v>828</v>
+      </c>
+      <c r="E21" s="38">
+        <v>46114</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="21" t="s">
-        <v>818</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>820</v>
-      </c>
-      <c r="E22" s="41">
+      <c r="B22" t="s">
+        <v>816</v>
+      </c>
+      <c r="C22" s="8">
+        <v>2026</v>
+      </c>
+      <c r="D22" t="s">
+        <v>817</v>
+      </c>
+      <c r="E22" s="38">
         <v>46113</v>
       </c>
     </row>
@@ -6167,17 +6291,17 @@
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>799</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>800</v>
-      </c>
-      <c r="E23" s="41">
-        <v>46112</v>
+      <c r="B23" t="s">
+        <v>818</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D23" t="s">
+        <v>820</v>
+      </c>
+      <c r="E23" s="38">
+        <v>46113</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -6185,16 +6309,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>801</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>4</v>
+        <v>816</v>
+      </c>
+      <c r="C24" s="24">
+        <v>2026</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="E24" s="41">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -6202,16 +6326,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>803</v>
-      </c>
-      <c r="C25" s="24">
-        <v>2026</v>
+        <v>818</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>819</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>804</v>
+        <v>820</v>
       </c>
       <c r="E25" s="41">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -6219,13 +6343,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>805</v>
-      </c>
-      <c r="C26" s="24">
-        <v>2026</v>
+        <v>799</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="E26" s="41">
         <v>46112</v>
@@ -6236,13 +6360,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>807</v>
-      </c>
-      <c r="C27" s="24">
-        <v>2026</v>
+        <v>801</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="E27" s="41">
         <v>46112</v>
@@ -6253,13 +6377,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="C28" s="24">
         <v>2026</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="E28" s="41">
         <v>46112</v>
@@ -6270,16 +6394,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="C29" s="24">
         <v>2026</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="E29" s="41">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -6287,16 +6411,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>795</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>4</v>
+        <v>807</v>
+      </c>
+      <c r="C30" s="24">
+        <v>2026</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="E30" s="41">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -6304,16 +6428,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>797</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>4</v>
+        <v>809</v>
+      </c>
+      <c r="C31" s="24">
+        <v>2026</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="E31" s="41">
-        <v>46104</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -6321,16 +6445,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>780</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>4</v>
+        <v>793</v>
+      </c>
+      <c r="C32" s="24">
+        <v>2026</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>781</v>
-      </c>
-      <c r="E32" s="42">
-        <v>46100</v>
+        <v>794</v>
+      </c>
+      <c r="E32" s="41">
+        <v>46108</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6338,16 +6462,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>782</v>
+        <v>795</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>783</v>
-      </c>
-      <c r="E33" s="42">
-        <v>46099</v>
+        <v>796</v>
+      </c>
+      <c r="E33" s="41">
+        <v>46108</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -6355,16 +6479,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>784</v>
+        <v>797</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>785</v>
-      </c>
-      <c r="E34" s="42">
-        <v>46097</v>
+        <v>798</v>
+      </c>
+      <c r="E34" s="41">
+        <v>46104</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -6372,16 +6496,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>762</v>
-      </c>
-      <c r="E35" s="42" t="s">
-        <v>756</v>
+        <v>781</v>
+      </c>
+      <c r="E35" s="42">
+        <v>46100</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -6389,16 +6513,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>763</v>
+        <v>782</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>764</v>
-      </c>
-      <c r="E36" s="42" t="s">
-        <v>756</v>
+        <v>783</v>
+      </c>
+      <c r="E36" s="42">
+        <v>46099</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6406,16 +6530,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>765</v>
+        <v>784</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>766</v>
-      </c>
-      <c r="E37" s="42" t="s">
-        <v>756</v>
+        <v>785</v>
+      </c>
+      <c r="E37" s="42">
+        <v>46097</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6423,84 +6547,84 @@
         <v>34</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>35</v>
       </c>
-      <c r="B39" t="s">
-        <v>588</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" t="s">
-        <v>384</v>
-      </c>
-      <c r="E39" s="38">
-        <v>46267</v>
+      <c r="B39" s="21" t="s">
+        <v>763</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>764</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>36</v>
       </c>
-      <c r="B40" t="s">
-        <v>589</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" t="s">
-        <v>376</v>
-      </c>
-      <c r="E40" s="38">
-        <v>46144</v>
+      <c r="B40" s="21" t="s">
+        <v>765</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>766</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>37</v>
       </c>
-      <c r="B41" t="s">
-        <v>590</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D41" t="s">
-        <v>377</v>
-      </c>
-      <c r="E41" s="38">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="21" t="s">
+        <v>767</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>768</v>
+      </c>
+      <c r="E41" s="42" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>591</v>
-      </c>
-      <c r="C42" s="8">
-        <v>2026</v>
+        <v>588</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="E42" s="38">
-        <v>46051</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6508,16 +6632,16 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>6</v>
+        <v>376</v>
       </c>
       <c r="E43" s="38">
-        <v>46038</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -6525,33 +6649,33 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>593</v>
-      </c>
-      <c r="C44" s="8">
-        <v>2026</v>
+        <v>590</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>377</v>
       </c>
       <c r="E44" s="38">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C45" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>375</v>
       </c>
       <c r="E45" s="38">
-        <v>46022</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -6559,16 +6683,16 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E46" s="38">
-        <v>46022</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6576,16 +6700,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C47" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E47" s="38">
-        <v>46020</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6593,16 +6717,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C48" s="8">
         <v>2025</v>
       </c>
       <c r="D48" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E48" s="38">
-        <v>46009</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -6610,16 +6734,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E49" s="38">
-        <v>46000</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -6627,16 +6751,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>599</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>4</v>
+        <v>596</v>
+      </c>
+      <c r="C50" s="8">
+        <v>2025</v>
       </c>
       <c r="D50" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E50" s="38">
-        <v>45978</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -6644,16 +6768,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>600</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C51" s="8">
+        <v>2025</v>
       </c>
       <c r="D51" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E51" s="38">
-        <v>45965</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -6661,16 +6785,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>601</v>
-      </c>
-      <c r="C52" s="8">
-        <v>2025</v>
+        <v>598</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E52" s="38">
-        <v>45951</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -6678,16 +6802,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>602</v>
-      </c>
-      <c r="C53" s="8">
-        <v>2025</v>
+        <v>599</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E53" s="38">
-        <v>45945</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -6695,16 +6819,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E54" s="38">
-        <v>45945</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -6712,16 +6836,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>603</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>4</v>
+        <v>601</v>
+      </c>
+      <c r="C55" s="8">
+        <v>2025</v>
       </c>
       <c r="D55" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E55" s="38">
-        <v>45945</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -6729,13 +6853,13 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>604</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>4</v>
+        <v>602</v>
+      </c>
+      <c r="C56" s="8">
+        <v>2025</v>
       </c>
       <c r="D56" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E56" s="38">
         <v>45945</v>
@@ -6746,16 +6870,16 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E57" s="38">
-        <v>45944</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -6763,16 +6887,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E58" s="38">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -6780,16 +6904,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E59" s="38">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -6797,16 +6921,16 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E60" s="38">
-        <v>45933</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -6814,47 +6938,47 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E61" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>58</v>
       </c>
-      <c r="B62" s="8" t="s">
-        <v>610</v>
+      <c r="B62" t="s">
+        <v>607</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E62" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>59</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>611</v>
+      <c r="B63" t="s">
+        <v>608</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E63" s="38">
         <v>45933</v>
@@ -6864,17 +6988,17 @@
       <c r="A64" s="1">
         <v>60</v>
       </c>
-      <c r="B64" s="8" t="s">
-        <v>612</v>
+      <c r="B64" t="s">
+        <v>609</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E64" s="38">
-        <v>45930</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -6882,16 +7006,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E65" s="38">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -6899,16 +7023,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E66" s="38">
-        <v>45924</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -6916,16 +7040,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E67" s="38">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -6933,16 +7057,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="C68" s="8">
-        <v>2025</v>
+        <v>613</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E68" s="38">
-        <v>45923</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -6950,16 +7074,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E69" s="38">
-        <v>45918</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -6967,16 +7091,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E70" s="38">
-        <v>45908</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -6984,16 +7108,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C71" s="8">
+        <v>2025</v>
       </c>
       <c r="D71" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E71" s="38">
-        <v>45897</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -7001,16 +7125,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E72" s="38">
-        <v>45891</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -7018,16 +7142,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E73" s="38">
-        <v>45891</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -7035,16 +7159,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E74" s="38">
-        <v>45888</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -7052,16 +7176,16 @@
         <v>71</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E75" s="38">
-        <v>45880</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -7069,16 +7193,16 @@
         <v>72</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>69</v>
+        <v>621</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E76" s="38">
-        <v>45855</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -7086,16 +7210,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E77" s="38">
-        <v>45838</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -7103,16 +7227,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="E78" s="38">
-        <v>45838</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -7120,16 +7244,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>626</v>
+        <v>69</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E79" s="38">
-        <v>45835</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -7137,16 +7261,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>75</v>
+        <v>624</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E80" s="38">
-        <v>45833</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -7154,16 +7278,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="E81" s="38">
-        <v>45831</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -7171,16 +7295,16 @@
         <v>78</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E82" s="38">
-        <v>45825</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -7188,16 +7312,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>629</v>
+        <v>75</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E83" s="38">
-        <v>45825</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -7205,16 +7329,16 @@
         <v>80</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="E84" s="38">
-        <v>45825</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -7222,16 +7346,16 @@
         <v>81</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E85" s="38">
-        <v>45808</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -7239,16 +7363,16 @@
         <v>82</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E86" s="38">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -7256,16 +7380,16 @@
         <v>83</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E87" s="38">
-        <v>45803</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -7273,16 +7397,16 @@
         <v>84</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D88" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E88" s="38">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -7290,13 +7414,13 @@
         <v>85</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E89" s="38">
         <v>45803</v>
@@ -7307,13 +7431,13 @@
         <v>86</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D90" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E90" s="38">
         <v>45803</v>
@@ -7324,50 +7448,50 @@
         <v>87</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D91" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E91" s="38">
         <v>45803</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>88</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D92" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E92" s="38">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>89</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D93" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E93" s="38">
-        <v>45796</v>
+        <v>45803</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -7375,50 +7499,50 @@
         <v>90</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E94" s="38">
-        <v>45794</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>91</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="E95" s="38">
-        <v>45779</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>92</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D96" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E96" s="38">
-        <v>45770</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -7426,16 +7550,16 @@
         <v>93</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E97" s="38">
-        <v>45762</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7443,16 +7567,16 @@
         <v>94</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="C98" s="8">
-        <v>2025</v>
+        <v>641</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D98" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E98" s="38">
-        <v>45749</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -7460,16 +7584,16 @@
         <v>95</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="C99" s="8">
-        <v>2025</v>
+        <v>642</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E99" s="38">
-        <v>45749</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7477,16 +7601,16 @@
         <v>96</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E100" s="38">
-        <v>45748</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7494,16 +7618,16 @@
         <v>97</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>114</v>
+        <v>644</v>
+      </c>
+      <c r="C101" s="8">
+        <v>2025</v>
       </c>
       <c r="D101" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E101" s="38">
-        <v>45736</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7511,16 +7635,16 @@
         <v>98</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>114</v>
+        <v>645</v>
+      </c>
+      <c r="C102" s="8">
+        <v>2025</v>
       </c>
       <c r="D102" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="E102" s="38">
-        <v>45734</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -7528,16 +7652,16 @@
         <v>99</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D103" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E103" s="38">
-        <v>45726</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7545,16 +7669,16 @@
         <v>100</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="C104" s="8">
-        <v>2025</v>
+        <v>647</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E104" s="38">
-        <v>45726</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7562,16 +7686,16 @@
         <v>101</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E105" s="38">
-        <v>45726</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7579,16 +7703,16 @@
         <v>102</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E106" s="38">
-        <v>45723</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7596,16 +7720,16 @@
         <v>103</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="C107" s="8" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C107" s="8">
+        <v>2025</v>
       </c>
       <c r="D107" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E107" s="38">
-        <v>45721</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -7613,16 +7737,16 @@
         <v>104</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C108" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E108" s="38">
-        <v>45698</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -7630,16 +7754,16 @@
         <v>105</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E109" s="38">
-        <v>45695</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7647,67 +7771,67 @@
         <v>106</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E110" s="38">
-        <v>45694</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>107</v>
       </c>
-      <c r="B111" t="s">
-        <v>587</v>
+      <c r="B111" s="8" t="s">
+        <v>654</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E111" s="38">
-        <v>45692</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>108</v>
       </c>
-      <c r="B112" t="s">
-        <v>586</v>
+      <c r="B112" s="8" t="s">
+        <v>655</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E112" s="38">
-        <v>45686</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>109</v>
       </c>
-      <c r="B113" t="s">
-        <v>585</v>
+      <c r="B113" s="8" t="s">
+        <v>656</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E113" s="38">
-        <v>45681</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -7715,16 +7839,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E114" s="38">
-        <v>45678</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7732,16 +7856,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E115" s="38">
-        <v>45677</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7749,16 +7873,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E116" s="38">
-        <v>45677</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7766,16 +7890,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E117" s="38">
-        <v>45670</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7783,16 +7907,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E118" s="38">
-        <v>45661</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7800,16 +7924,16 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E119" s="38">
-        <v>45661</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -7817,16 +7941,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E120" s="38">
-        <v>45659</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7834,16 +7958,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E121" s="38">
-        <v>45656</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7851,16 +7975,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E122" s="38">
-        <v>45656</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -7868,16 +7992,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>575</v>
-      </c>
-      <c r="C123" s="8">
-        <v>2024</v>
+        <v>578</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E123" s="38">
-        <v>45652</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -7885,16 +8009,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="E124" s="38">
-        <v>45650</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -7902,16 +8026,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E125" s="38">
-        <v>45631</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -7919,16 +8043,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>572</v>
-      </c>
-      <c r="C126" s="8" t="s">
-        <v>112</v>
+        <v>575</v>
+      </c>
+      <c r="C126" s="8">
+        <v>2024</v>
       </c>
       <c r="D126" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E126" s="38">
-        <v>45625</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -7936,16 +8060,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="E127" s="38">
-        <v>45622</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -7953,16 +8077,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E128" s="38">
-        <v>45593</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -7970,16 +8094,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D129" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E129" s="38">
-        <v>45588</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -7987,16 +8111,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D130" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="E130" s="38">
-        <v>45588</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -8004,16 +8128,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C131" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D131" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E131" s="38">
-        <v>45578</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -8021,16 +8145,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E132" s="38">
-        <v>45566</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -8038,16 +8162,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E133" s="38">
-        <v>45566</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -8055,16 +8179,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E134" s="38">
-        <v>45565</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -8072,16 +8196,16 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E135" s="38">
-        <v>45563</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -8089,16 +8213,16 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E136" s="38">
-        <v>45553</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -8106,16 +8230,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="E137" s="38">
-        <v>45548</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -8123,16 +8247,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E138" s="38">
-        <v>45548</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -8140,16 +8264,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E139" s="38">
-        <v>45539</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -8157,16 +8281,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>182</v>
+        <v>119</v>
       </c>
       <c r="E140" s="38">
-        <v>45538</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -8174,16 +8298,16 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E141" s="38">
-        <v>45537</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -8191,16 +8315,16 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="E142" s="38">
-        <v>45523</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -8208,16 +8332,16 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E143" s="38">
-        <v>45520</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -8225,16 +8349,16 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E144" s="38">
-        <v>45505</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -8242,16 +8366,16 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E145" s="38">
-        <v>45502</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -8259,16 +8383,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E146" s="38">
-        <v>45478</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -8276,16 +8400,16 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E147" s="38">
-        <v>45478</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -8293,16 +8417,16 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E148" s="38">
-        <v>45462</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -8310,16 +8434,16 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>204</v>
+        <v>552</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="E149" s="38">
-        <v>45455</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -8327,16 +8451,16 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E150" s="38">
-        <v>45454</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -8344,16 +8468,16 @@
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E151" s="38">
-        <v>45449</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -8361,16 +8485,16 @@
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>547</v>
+        <v>204</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E152" s="38">
-        <v>45448</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -8378,16 +8502,16 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D153" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E153" s="38">
-        <v>45446</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -8395,16 +8519,16 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E154" s="38">
-        <v>45432</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -8412,16 +8536,16 @@
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D155" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E155" s="38">
-        <v>45420</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8429,16 +8553,16 @@
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D156" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E156" s="38">
-        <v>45418</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -8446,16 +8570,16 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D157" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E157" s="38">
-        <v>45416</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -8463,67 +8587,67 @@
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D158" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E158" s="38">
-        <v>45407</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>155</v>
       </c>
-      <c r="B159" s="5" t="s">
-        <v>540</v>
+      <c r="B159" t="s">
+        <v>543</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="E159" s="38">
-        <v>45405</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>156</v>
       </c>
-      <c r="B160" s="5" t="s">
-        <v>535</v>
+      <c r="B160" t="s">
+        <v>542</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D160" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E160" s="38">
-        <v>45397</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>157</v>
       </c>
-      <c r="B161" s="5" t="s">
-        <v>539</v>
+      <c r="B161" t="s">
+        <v>541</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D161" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E161" s="38">
-        <v>45397</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -8531,16 +8655,16 @@
         <v>158</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D162" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E162" s="38">
-        <v>45387</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -8548,16 +8672,16 @@
         <v>159</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D163" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E163" s="38">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8565,16 +8689,16 @@
         <v>160</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D164" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E164" s="38">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -8582,16 +8706,16 @@
         <v>161</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>505</v>
+        <v>538</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D165" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E165" s="38">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -8599,16 +8723,16 @@
         <v>162</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D166" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E166" s="38">
-        <v>45384</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -8616,67 +8740,67 @@
         <v>163</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>506</v>
+        <v>536</v>
       </c>
       <c r="C167" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D167" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E167" s="38">
-        <v>45378</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>164</v>
       </c>
-      <c r="B168" t="s">
-        <v>533</v>
+      <c r="B168" s="5" t="s">
+        <v>505</v>
       </c>
       <c r="C168" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D168" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="E168" s="38">
-        <v>45373</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>165</v>
       </c>
-      <c r="B169" t="s">
-        <v>532</v>
+      <c r="B169" s="5" t="s">
+        <v>534</v>
       </c>
       <c r="C169" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D169" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="E169" s="38">
-        <v>45373</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>166</v>
       </c>
-      <c r="B170" t="s">
-        <v>531</v>
+      <c r="B170" s="5" t="s">
+        <v>506</v>
       </c>
       <c r="C170" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D170" t="s">
-        <v>117</v>
+        <v>237</v>
       </c>
       <c r="E170" s="38">
-        <v>45369</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -8684,16 +8808,16 @@
         <v>167</v>
       </c>
       <c r="B171" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E171" s="38">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8701,16 +8825,16 @@
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E172" s="38">
-        <v>45367</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -8718,16 +8842,16 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>244</v>
+        <v>117</v>
       </c>
       <c r="E173" s="38">
-        <v>45366</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -8735,16 +8859,16 @@
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E174" s="38">
-        <v>45365</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -8752,16 +8876,16 @@
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C175" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D175" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E175" s="38">
-        <v>45362</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -8769,16 +8893,16 @@
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D176" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E176" s="38">
-        <v>45362</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -8786,16 +8910,16 @@
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D177" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E177" s="38">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8803,13 +8927,13 @@
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D178" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E178" s="38">
         <v>45362</v>
@@ -8820,16 +8944,16 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D179" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E179" s="38">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -8837,16 +8961,16 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D180" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E180" s="38">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -8854,16 +8978,16 @@
         <v>177</v>
       </c>
       <c r="B181" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D181" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E181" s="38">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -8871,16 +8995,16 @@
         <v>178</v>
       </c>
       <c r="B182" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D182" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E182" s="38">
-        <v>45357</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -8888,16 +9012,16 @@
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D183" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E183" s="38">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -8905,16 +9029,16 @@
         <v>180</v>
       </c>
       <c r="B184" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="E184" s="38">
-        <v>45352</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -8922,16 +9046,16 @@
         <v>181</v>
       </c>
       <c r="B185" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D185" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="E185" s="38">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -8939,16 +9063,16 @@
         <v>182</v>
       </c>
       <c r="B186" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C186" s="8" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D186" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E186" s="38">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -8956,16 +9080,16 @@
         <v>183</v>
       </c>
       <c r="B187" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D187" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
       <c r="E187" s="38">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -8973,16 +9097,16 @@
         <v>184</v>
       </c>
       <c r="B188" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D188" t="s">
-        <v>265</v>
+        <v>219</v>
       </c>
       <c r="E188" s="38">
-        <v>45345</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -8990,16 +9114,16 @@
         <v>185</v>
       </c>
       <c r="B189" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="E189" s="38">
-        <v>45335</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -9007,16 +9131,16 @@
         <v>186</v>
       </c>
       <c r="B190" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C190" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D190" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E190" s="38">
-        <v>45334</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -9024,33 +9148,33 @@
         <v>187</v>
       </c>
       <c r="B191" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D191" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="E191" s="38">
-        <v>45314</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>188</v>
       </c>
-      <c r="B192" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C192" s="8">
-        <v>2023</v>
+      <c r="B192" t="s">
+        <v>507</v>
+      </c>
+      <c r="C192" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D192" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="E192" s="38">
-        <v>45306</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -9058,16 +9182,16 @@
         <v>189</v>
       </c>
       <c r="B193" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D193" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E193" s="38">
-        <v>45294</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -9075,15 +9199,66 @@
         <v>190</v>
       </c>
       <c r="B194" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D194" t="s">
+        <v>276</v>
+      </c>
+      <c r="E194" s="38">
+        <v>45314</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>191</v>
+      </c>
+      <c r="B195" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C195" s="8">
+        <v>2023</v>
+      </c>
+      <c r="D195" t="s">
+        <v>277</v>
+      </c>
+      <c r="E195" s="38">
+        <v>45306</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>192</v>
+      </c>
+      <c r="B196" t="s">
+        <v>509</v>
+      </c>
+      <c r="C196" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D196" t="s">
+        <v>279</v>
+      </c>
+      <c r="E196" s="38">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>193</v>
+      </c>
+      <c r="B197" t="s">
+        <v>508</v>
+      </c>
+      <c r="C197" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D197" t="s">
         <v>281</v>
       </c>
-      <c r="E194" s="38">
+      <c r="E197" s="38">
         <v>45292</v>
       </c>
     </row>
@@ -9663,7 +9838,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="20"/>
@@ -9712,34 +9887,34 @@
       <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B5" s="58" t="s">
-        <v>884</v>
-      </c>
-      <c r="C5" s="59" t="s">
+      <c r="B5" s="62" t="s">
+        <v>899</v>
+      </c>
+      <c r="C5" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="58" t="s">
-        <v>885</v>
-      </c>
-      <c r="E5" s="60">
-        <v>46171</v>
+      <c r="D5" s="62" t="s">
+        <v>900</v>
+      </c>
+      <c r="E5" s="64">
+        <v>46176</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="19">
         <v>2</v>
       </c>
-      <c r="B6" s="54" t="s">
-        <v>878</v>
-      </c>
-      <c r="C6" s="55" t="s">
+      <c r="B6" s="58" t="s">
+        <v>884</v>
+      </c>
+      <c r="C6" s="59" t="s">
         <v>819</v>
       </c>
-      <c r="D6" s="54" t="s">
-        <v>879</v>
-      </c>
-      <c r="E6" s="56">
-        <v>46164</v>
+      <c r="D6" s="58" t="s">
+        <v>885</v>
+      </c>
+      <c r="E6" s="60">
+        <v>46171</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9747,13 +9922,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="54" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C7" s="55" t="s">
         <v>819</v>
       </c>
       <c r="D7" s="54" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E7" s="56">
         <v>46164</v>
@@ -9763,17 +9938,17 @@
       <c r="A8" s="19">
         <v>4</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>876</v>
-      </c>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="54" t="s">
+        <v>880</v>
+      </c>
+      <c r="C8" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D8" s="34" t="s">
-        <v>877</v>
-      </c>
-      <c r="E8" s="49">
-        <v>46155</v>
+      <c r="D8" s="54" t="s">
+        <v>881</v>
+      </c>
+      <c r="E8" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9781,16 +9956,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>850</v>
+        <v>876</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>851</v>
-      </c>
-      <c r="E9" s="40">
-        <v>46133</v>
+        <v>877</v>
+      </c>
+      <c r="E9" s="49">
+        <v>46155</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9798,33 +9973,33 @@
         <v>6</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E10" s="40">
-        <v>46132</v>
+        <v>46133</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="19">
         <v>7</v>
       </c>
-      <c r="B11" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>814</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>815</v>
-      </c>
-      <c r="E11" s="41">
-        <v>46113</v>
+      <c r="B11" s="34" t="s">
+        <v>848</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="E11" s="40">
+        <v>46132</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -9832,92 +10007,92 @@
         <v>8</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>789</v>
+        <v>813</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>8</v>
+        <v>814</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="E12" s="41">
-        <v>46101</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>9</v>
       </c>
-      <c r="B13" s="27" t="s">
-        <v>774</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="29" t="s">
-        <v>775</v>
-      </c>
-      <c r="E13" s="45">
-        <v>46087</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>789</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="E13" s="41">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="19">
         <v>10</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C14" s="28" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E14" s="45">
         <v>46087</v>
       </c>
       <c r="F14" s="30"/>
+      <c r="G14" t="s">
+        <v>381</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>11</v>
       </c>
-      <c r="B15" t="s">
-        <v>773</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>772</v>
-      </c>
-      <c r="E15" s="38">
-        <v>46084</v>
-      </c>
-      <c r="F15" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="27" t="s">
+        <v>776</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="29" t="s">
+        <v>777</v>
+      </c>
+      <c r="E15" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F15" s="30"/>
+    </row>
+    <row r="16" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19">
         <v>12</v>
       </c>
-      <c r="B16" s="21" t="s">
-        <v>744</v>
-      </c>
-      <c r="C16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>745</v>
-      </c>
-      <c r="E16" s="41">
-        <v>46073</v>
+      <c r="B16" t="s">
+        <v>773</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" t="s">
+        <v>772</v>
+      </c>
+      <c r="E16" s="38">
+        <v>46084</v>
+      </c>
+      <c r="F16" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9925,13 +10100,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E17" s="41">
         <v>46073</v>
@@ -9942,13 +10117,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E18" s="41">
         <v>46073</v>
@@ -9959,13 +10134,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E19" s="41">
         <v>46073</v>
@@ -9976,33 +10151,33 @@
         <v>16</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E20" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>17</v>
       </c>
-      <c r="B21" t="s">
-        <v>681</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="B21" s="21" t="s">
+        <v>752</v>
+      </c>
+      <c r="C21" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D21" t="s">
-        <v>385</v>
-      </c>
-      <c r="E21" s="38">
-        <v>46267</v>
+      <c r="D21" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="E21" s="41">
+        <v>46073</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -10010,50 +10185,50 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E22" s="38">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>683</v>
+      <c r="B23" t="s">
+        <v>682</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="E23" s="46">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>380</v>
+      </c>
+      <c r="E23" s="38">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
         <v>20</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>684</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E24" s="47">
-        <v>46024</v>
+      <c r="D24" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E24" s="46">
+        <v>46045</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10061,19 +10236,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C25" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E25" s="47">
         <v>46024</v>
-      </c>
-      <c r="H25" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10081,16 +10253,19 @@
         <v>22</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E26" s="47">
-        <v>46022</v>
+        <v>46024</v>
+      </c>
+      <c r="H26" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10098,16 +10273,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C27" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E27" s="47">
-        <v>45986</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10115,16 +10290,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>319</v>
+      <c r="D28" s="16" t="s">
+        <v>318</v>
       </c>
       <c r="E28" s="47">
-        <v>45961</v>
+        <v>45986</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10132,16 +10307,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C29" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E29" s="47">
-        <v>45959</v>
+        <v>45961</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10149,13 +10324,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>321</v>
+      <c r="D30" s="17" t="s">
+        <v>320</v>
       </c>
       <c r="E30" s="47">
         <v>45959</v>
@@ -10166,16 +10341,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C31" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E31" s="47">
-        <v>45957</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10183,16 +10358,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>323</v>
+      <c r="D32" s="16" t="s">
+        <v>322</v>
       </c>
       <c r="E32" s="47">
-        <v>45930</v>
+        <v>45957</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10200,16 +10375,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C33" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>324</v>
+      <c r="D33" s="17" t="s">
+        <v>323</v>
       </c>
       <c r="E33" s="47">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10217,16 +10392,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>743</v>
-      </c>
-      <c r="C34" s="16">
-        <v>2025</v>
+        <v>693</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E34" s="47">
-        <v>45896</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10234,16 +10409,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>742</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>4</v>
+        <v>743</v>
+      </c>
+      <c r="C35" s="16">
+        <v>2025</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E35" s="47">
-        <v>45866</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10251,16 +10426,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E36" s="47">
-        <v>45860</v>
+        <v>45866</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10268,16 +10443,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E37" s="47">
-        <v>45852</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10285,16 +10460,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="C38" s="16">
-        <v>2025</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>329</v>
+        <v>740</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>328</v>
       </c>
       <c r="E38" s="47">
-        <v>45840</v>
+        <v>45852</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10302,16 +10477,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>330</v>
+        <v>739</v>
+      </c>
+      <c r="C39" s="16">
+        <v>2025</v>
+      </c>
+      <c r="D39" s="17" t="s">
+        <v>329</v>
       </c>
       <c r="E39" s="47">
-        <v>45826</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10319,16 +10494,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E40" s="47">
-        <v>45821</v>
+        <v>45826</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10336,16 +10511,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C41" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E41" s="47">
-        <v>45776</v>
+        <v>45821</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10353,16 +10528,16 @@
         <v>38</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>735</v>
-      </c>
-      <c r="C42" s="16">
-        <v>2025</v>
+        <v>736</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E42" s="47">
-        <v>45770</v>
+        <v>45776</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10370,16 +10545,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>734</v>
-      </c>
-      <c r="C43" s="16" t="s">
-        <v>4</v>
+        <v>735</v>
+      </c>
+      <c r="C43" s="16">
+        <v>2025</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E43" s="47">
-        <v>45768</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10387,16 +10562,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C44" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E44" s="47">
-        <v>45758</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10404,16 +10579,16 @@
         <v>41</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>336</v>
+        <v>4</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>335</v>
       </c>
       <c r="E45" s="47">
-        <v>45741</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10421,16 +10596,16 @@
         <v>42</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C46" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="16" t="s">
-        <v>337</v>
+      <c r="D46" s="17" t="s">
+        <v>336</v>
       </c>
       <c r="E46" s="47">
-        <v>45736</v>
+        <v>45741</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10438,16 +10613,16 @@
         <v>43</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E47" s="47">
-        <v>45728</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10455,16 +10630,16 @@
         <v>44</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E48" s="47">
-        <v>45716</v>
+        <v>45728</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10472,16 +10647,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E49" s="47">
-        <v>45701</v>
+        <v>45716</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10489,16 +10664,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C50" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E50" s="47">
-        <v>45700</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10506,16 +10681,16 @@
         <v>47</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E51" s="47">
-        <v>45699</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10523,13 +10698,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C52" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E52" s="47">
         <v>45699</v>
@@ -10540,16 +10715,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E53" s="47">
-        <v>45686</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10557,16 +10732,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C54" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E54" s="47">
-        <v>45656</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10574,13 +10749,13 @@
         <v>51</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="C55" s="16">
-        <v>2024</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>346</v>
+        <v>723</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" s="16" t="s">
+        <v>345</v>
       </c>
       <c r="E55" s="47">
         <v>45656</v>
@@ -10591,16 +10766,16 @@
         <v>52</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>721</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>347</v>
+        <v>722</v>
+      </c>
+      <c r="C56" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>346</v>
       </c>
       <c r="E56" s="47">
-        <v>45646</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10608,16 +10783,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E57" s="47">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10625,16 +10800,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E58" s="47">
-        <v>45610</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10642,16 +10817,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E59" s="47">
-        <v>45582</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10659,16 +10834,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E60" s="47">
-        <v>45572</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10676,16 +10851,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E61" s="47">
-        <v>45569</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10693,16 +10868,16 @@
         <v>58</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C62" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E62" s="47">
-        <v>45565</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10710,16 +10885,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C63" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D63" s="16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E63" s="47">
-        <v>45552</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10727,16 +10902,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E64" s="47">
-        <v>45535</v>
+        <v>45552</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10744,16 +10919,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E65" s="47">
-        <v>45533</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10761,16 +10936,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E66" s="47">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10778,16 +10953,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C67" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E67" s="47">
-        <v>45520</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10795,16 +10970,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E68" s="47">
-        <v>45518</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10812,16 +10987,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E69" s="47">
-        <v>45506</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10829,16 +11004,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C70" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E70" s="47">
-        <v>45498</v>
+        <v>45506</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10846,16 +11021,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E71" s="47">
-        <v>45496</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10863,16 +11038,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C72" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E72" s="47">
-        <v>45483</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10880,16 +11055,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E73" s="47">
-        <v>45471</v>
+        <v>45483</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10897,16 +11072,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C74" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>187</v>
+        <v>364</v>
       </c>
       <c r="E74" s="47">
-        <v>45461</v>
+        <v>45471</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10914,33 +11089,33 @@
         <v>71</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>365</v>
+        <v>187</v>
       </c>
       <c r="E75" s="47">
-        <v>45455</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19">
         <v>72</v>
       </c>
-      <c r="B76" s="23" t="s">
-        <v>701</v>
+      <c r="B76" s="17" t="s">
+        <v>702</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>214</v>
+        <v>365</v>
       </c>
       <c r="E76" s="47">
-        <v>45440</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10948,33 +11123,33 @@
         <v>73</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C77" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>366</v>
+        <v>214</v>
       </c>
       <c r="E77" s="47">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19">
         <v>74</v>
       </c>
-      <c r="B78" s="17" t="s">
-        <v>699</v>
+      <c r="B78" s="23" t="s">
+        <v>700</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E78" s="47">
-        <v>45400</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10982,16 +11157,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E79" s="47">
-        <v>45384</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -10999,16 +11174,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>235</v>
+        <v>112</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E80" s="47">
-        <v>45371</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11016,16 +11191,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E81" s="47">
-        <v>45369</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -11033,32 +11208,49 @@
         <v>78</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C82" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E82" s="47">
-        <v>45338</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19">
         <v>79</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C83" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D83" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E83" s="47">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="19">
+        <v>80</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C84" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D84" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="E83" s="47">
+      <c r="E84" s="47">
         <v>45335</v>
       </c>
     </row>
